--- a/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF26FC5-1C13-4F8F-AE89-E29897DBF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199531C6-C37A-4433-A6FE-B5CC7FC419E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95E6C139-84C6-42BA-8CBB-FF1D79072BFF}"/>
   </bookViews>
@@ -6801,7 +6801,7 @@
         <v>42</v>
       </c>
       <c r="W63" t="s">
-        <v>352</v>
+        <v>68</v>
       </c>
       <c r="X63" t="s">
         <v>380</v>
@@ -9128,7 +9128,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="300" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -12200,7 +12200,7 @@
         <v>42</v>
       </c>
       <c r="W175" t="s">
-        <v>352</v>
+        <v>68</v>
       </c>
       <c r="X175" t="s">
         <v>380</v>
@@ -14524,7 +14524,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="225" spans="1:24" ht="300" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>112</v>
       </c>
@@ -17596,7 +17596,7 @@
         <v>42</v>
       </c>
       <c r="W287" t="s">
-        <v>352</v>
+        <v>68</v>
       </c>
       <c r="X287" t="s">
         <v>380</v>
@@ -19920,7 +19920,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="337" spans="1:24" ht="300" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>112</v>
       </c>

--- a/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199531C6-C37A-4433-A6FE-B5CC7FC419E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA1C5AB-0FD5-4484-A21C-B1A99AE19AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95E6C139-84C6-42BA-8CBB-FF1D79072BFF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4860" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4860" uniqueCount="775">
   <si>
     <t>index</t>
   </si>
@@ -1548,9 +1548,6 @@
 "Presumed no" can be specified only if a general cancer disease option is present in a select all that apply question where at least another option is selected but not this one.</t>
   </si>
   <si>
-    <t>malignanttumor1</t>
-  </si>
-  <si>
     <t>Malignant tumor (cancer)</t>
   </si>
   <si>
@@ -1685,9 +1682,6 @@
   <si>
     <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
 If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
-  </si>
-  <si>
-    <t>highcholesterol1</t>
   </si>
   <si>
     <t>High cholesterol</t>
@@ -2057,25 +2051,16 @@
     <t>Particiant identification code.</t>
   </si>
   <si>
-    <t>bmi1</t>
-  </si>
-  <si>
     <t>Average of 2 measures</t>
   </si>
   <si>
     <t>Average of 2 measures (left and right arms)</t>
   </si>
   <si>
-    <t>round(rowMeans(select(., systolicBP_right1, systolicBP_left1), na.rm=TRUE), 2)</t>
-  </si>
-  <si>
     <t>Wording was, daily time spent at home watching TV or videos</t>
   </si>
   <si>
     <t>Wording specifies "daily time spent at home using a computer"</t>
-  </si>
-  <si>
-    <t>mci1</t>
   </si>
   <si>
     <t>FRA_FU3</t>
@@ -2250,6 +2235,756 @@
 med7atc_w2;
 med8atc_w2;
 med9atc_w2</t>
+  </si>
+  <si>
+    <t>osteoarthrosis_w2;
+osteoporosis_w2;
+sciatica_w2;
+rheumatoidarthritis_w2</t>
+  </si>
+  <si>
+    <t>case_when(
+osteoarthrosis_w2 %in% c(2, 3) | osteoporosis_w2 %in% c(2, 3) | sciatica_w2 %in% c(2, 3) | rheumatoidarthritis_w2 %in% c(2, 3) ~ 1L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>depression_w2</t>
+  </si>
+  <si>
+    <t>alzheimer_w2</t>
+  </si>
+  <si>
+    <t>med1atc_w2;
+med2atc_w2;
+med3atc_w2;
+med4atc_w2;
+med5atc_w2;
+med6atc_w2;
+med7atc_w2;
+med8atc_w2;
+med9atc_w2</t>
+  </si>
+  <si>
+    <t>mci_w2</t>
+  </si>
+  <si>
+    <t>pacommuting_w2</t>
+  </si>
+  <si>
+    <t>pa_running_w2</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w2;
+dis_moderate_w2;
+dis_lift_w2;
+dis_climbseveral_w2;
+dis_climbone_w2;
+dis_bending_w2;
+dis_walk2km__w2;
+dis_walk1km__w2;
+dis_walk100m__w2;
+dis_bath_w2</t>
+  </si>
+  <si>
+    <t>DOM_w3</t>
+  </si>
+  <si>
+    <t>format(as.Date(DOM_w3, format = "%d/%m/%y"), "%Y-%m-%d")</t>
+  </si>
+  <si>
+    <t>age_w3</t>
+  </si>
+  <si>
+    <t>employmentstatus_w3</t>
+  </si>
+  <si>
+    <t>maritalstatus_w3</t>
+  </si>
+  <si>
+    <t>height_w3</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(height_w3), 2, NA)</t>
+  </si>
+  <si>
+    <t>weight_w3</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(weight_w3), 2, NA)</t>
+  </si>
+  <si>
+    <t>fatmass_w3</t>
+  </si>
+  <si>
+    <t>fatmass_w3/weight_w3*100</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(fatmass_w3), "Bioelectrical impedance measurement (InBody 720)", NA)</t>
+  </si>
+  <si>
+    <t>systolicBP_right_w3; systolicBP_left_w3</t>
+  </si>
+  <si>
+    <t>diastolicBP_right_w3; diastolicBP_left_w3</t>
+  </si>
+  <si>
+    <t>round(rowMeans(select(., diastolicBP_right_w3, diastolicBP_left_w3), na.rm=TRUE), 2)</t>
+  </si>
+  <si>
+    <t>Cholesterol_w3</t>
+  </si>
+  <si>
+    <t>HDL_w3</t>
+  </si>
+  <si>
+    <t>LDL_w3</t>
+  </si>
+  <si>
+    <t>Cholesterol_w3;
+HDL_w3;
+Trig_w3</t>
+  </si>
+  <si>
+    <t>round(Cholesterol_w3 - HDL_w3 - (Trig_w3/2.2), 2)</t>
+  </si>
+  <si>
+    <t>Trig_w3</t>
+  </si>
+  <si>
+    <t>CRP_w3</t>
+  </si>
+  <si>
+    <t>freshvegetables_w3; cooked_vegetables_w3</t>
+  </si>
+  <si>
+    <t>alcohol_w3</t>
+  </si>
+  <si>
+    <t>sleepduration_w3</t>
+  </si>
+  <si>
+    <t>sleepquality_categorized_w3</t>
+  </si>
+  <si>
+    <t>sitting_tv_w3</t>
+  </si>
+  <si>
+    <t>sitting_computer_w3</t>
+  </si>
+  <si>
+    <t>ifelse(sitting_computer_w3 %in% 0:10, sitting_computer_w3+1, NA)</t>
+  </si>
+  <si>
+    <t>sitting_tv_w3;sitting_vehicle_w3;sitting_computer_w3;sitting_other_w3; sitting_office_w3</t>
+  </si>
+  <si>
+    <t>rowSums(select(., sitting_tv_w3,sitting_vehicle_w3,sitting_computer_w3,sitting_other_w3, sitting_office_w3), na.rm=TRUE)</t>
+  </si>
+  <si>
+    <t>sitting_other_w3; sitting_office_w3</t>
+  </si>
+  <si>
+    <t>case_when(
+sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 == 0 ~ 0L;
+sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt; 0 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 1 ~ 1L;
+sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 1 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 3 ~ 2L;
+sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 3 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 5 ~ 3L;
+sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 5 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 7 ~ 4L;
+sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 7 ~ 5L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>selfratedhealth_w3</t>
+  </si>
+  <si>
+    <t>hypertension_w3;
+mi_w3;
+stroke_w3;
+anginapectoris_w3</t>
+  </si>
+  <si>
+    <t>case_when(
+hypertension_w3 %in% 2:3 ~ 1L;
+mi_w3 %in% 2:3 ~ 1L;
+stroke_w3 %in% 2:3 ~1L;
+anginapectoris_w3 %in% 2:3 ~ 1L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>mi_w3</t>
+  </si>
+  <si>
+    <t>anginapectoris_w3</t>
+  </si>
+  <si>
+    <t>stroke_w3</t>
+  </si>
+  <si>
+    <t>hypertension_w3</t>
+  </si>
+  <si>
+    <t>hypertension_w3;
+med1atc_w3;
+med2atc_w3;
+med3atc_w3;
+med4atc_w3;
+med5atc_w3;
+med6atc_w3;
+med7atc_w3;
+med8atc_w3;
+med9atc_w3</t>
+  </si>
+  <si>
+    <t>osteoarthrosis_w3;
+osteoporosis_w3;
+sciatica_w3;
+rheumatoidarthritis_w3</t>
+  </si>
+  <si>
+    <t>case_when(
+osteoarthrosis_w3 %in% c(2, 3) | osteoporosis_w3 %in% c(2, 3) | sciatica_w3 %in% c(2, 3) | rheumatoidarthritis_w3 %in% c(2, 3) ~ 1L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>diabetes_w3</t>
+  </si>
+  <si>
+    <t>malignanttumor_w3</t>
+  </si>
+  <si>
+    <t>highcholesterol_w3</t>
+  </si>
+  <si>
+    <t>depression_w3</t>
+  </si>
+  <si>
+    <t>alzheimer_w3</t>
+  </si>
+  <si>
+    <t>med1atc_w3;
+med2atc_w3;
+med3atc_w3;
+med4atc_w3;
+med5atc_w3;
+med6atc_w3;
+med7atc_w3;
+med8atc_w3;
+med9atc_w3</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w3 == "X04" ~ 1L;
+med2atc_w3 == "X04" ~ 1L;
+med3atc_w3 == "X04" ~ 1L;
+med4atc_w3 == "X04" ~ 1L;
+med5atc_w3 == "X04" ~ 1L;
+med6atc_w3 == "X04" ~ 1L;
+med7atc_w3 == "X04" ~ 1L;
+med8atc_w3 == "X04" ~ 1L;
+med9atc_w3 == "X04" ~ 1L;
+grepl("^C10", med1atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med2atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med3atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med4atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med5atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med6atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med7atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med8atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med9atc_w3, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w3 == "X01" ~ 1L;
+med2atc_w3 == "X01" ~ 1L;
+med3atc_w3 == "X01" ~ 1L;
+med4atc_w3 == "X01" ~ 1L;
+med5atc_w3 == "X01" ~ 1L;
+med6atc_w3 == "X01" ~ 1L;
+med7atc_w3 == "X01" ~ 1L;
+med8atc_w3 == "X01" ~ 1L;
+med9atc_w3 == "X01" ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w3, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w3 == "X02" ~ 1L;
+med2atc_w3 == "X02" ~ 1L;
+med3atc_w3 == "X02" ~ 1L;
+med4atc_w3 == "X02" ~ 1L;
+med5atc_w3 == "X02" ~ 1L;
+med6atc_w3 == "X02" ~ 1L;
+med7atc_w3 == "X02" ~ 1L;
+med8atc_w3 == "X02" ~ 1L;
+med9atc_w3 == "X02" ~ 1L;
+grepl("^A10", med1atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med2atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med3atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med4atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med5atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med6atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med7atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med8atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med9atc_w3, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>pacommuting_w3</t>
+  </si>
+  <si>
+    <t>pa_running_w3</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w3;
+dis_moderate_w3;
+dis_lift_w3;
+dis_climbseveral_w3;
+dis_climbone_w3;
+dis_bending_w3;
+dis_walk2km__w3;
+dis_walk1km__w3;
+dis_walk100m__w3;
+dis_bath_w3</t>
+  </si>
+  <si>
+    <t>DOM_w4</t>
+  </si>
+  <si>
+    <t>format(as.Date(DOM_w4, format = "%d/%m/%y"), "%Y-%m-%d")</t>
+  </si>
+  <si>
+    <t>age_w4</t>
+  </si>
+  <si>
+    <t>employmentstatus_w4</t>
+  </si>
+  <si>
+    <t>maritalstatus_w4</t>
+  </si>
+  <si>
+    <t>height_w4</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(height_w4), 2, NA)</t>
+  </si>
+  <si>
+    <t>weight_w4</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(weight_w4), 2, NA)</t>
+  </si>
+  <si>
+    <t>fatmass_w4</t>
+  </si>
+  <si>
+    <t>fatmass_w4/weight_w4*100</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(fatmass_w4), "Bioelectrical impedance measurement (InBody 720)", NA)</t>
+  </si>
+  <si>
+    <t>systolicBP_right_w4; systolicBP_left_w4</t>
+  </si>
+  <si>
+    <t>diastolicBP_right_w4; diastolicBP_left_w4</t>
+  </si>
+  <si>
+    <t>round(rowMeans(select(., diastolicBP_right_w4, diastolicBP_left_w4), na.rm=TRUE), 2)</t>
+  </si>
+  <si>
+    <t>Cholesterol_w4</t>
+  </si>
+  <si>
+    <t>HDL_w4</t>
+  </si>
+  <si>
+    <t>LDL_w4</t>
+  </si>
+  <si>
+    <t>Cholesterol_w4;
+HDL_w4;
+Trig_w4</t>
+  </si>
+  <si>
+    <t>round(Cholesterol_w4 - HDL_w4 - (Trig_w4/2.2), 2)</t>
+  </si>
+  <si>
+    <t>Trig_w4</t>
+  </si>
+  <si>
+    <t>CRP_w4</t>
+  </si>
+  <si>
+    <t>freshvegetables_w4; cooked_vegetables_w4</t>
+  </si>
+  <si>
+    <t>alcohol_w4</t>
+  </si>
+  <si>
+    <t>sleepduration_w4</t>
+  </si>
+  <si>
+    <t>sleepquality_categorized_w4</t>
+  </si>
+  <si>
+    <t>sitting_tv_w4</t>
+  </si>
+  <si>
+    <t>sitting_computer_w4</t>
+  </si>
+  <si>
+    <t>ifelse(sitting_computer_w4 %in% 0:10, sitting_computer_w4+1, NA)</t>
+  </si>
+  <si>
+    <t>sitting_tv_w4;sitting_vehicle_w4;sitting_computer_w4;sitting_other_w4; sitting_office_w4</t>
+  </si>
+  <si>
+    <t>rowSums(select(., sitting_tv_w4,sitting_vehicle_w4,sitting_computer_w4,sitting_other_w4, sitting_office_w4), na.rm=TRUE)</t>
+  </si>
+  <si>
+    <t>sitting_other_w4; sitting_office_w4</t>
+  </si>
+  <si>
+    <t>case_when(
+sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 == 0 ~ 0L;
+sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt; 0 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 1 ~ 1L;
+sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 1 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 3 ~ 2L;
+sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 3 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 5 ~ 3L;
+sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 5 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 7 ~ 4L;
+sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 7 ~ 5L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>selfratedhealth_w4</t>
+  </si>
+  <si>
+    <t>hypertension_w4;
+mi_w4;
+stroke_w4;
+anginapectoris_w4</t>
+  </si>
+  <si>
+    <t>case_when(
+hypertension_w4 %in% 2:3 ~ 1L;
+mi_w4 %in% 2:3 ~ 1L;
+stroke_w4 %in% 2:3 ~1L;
+anginapectoris_w4 %in% 2:3 ~ 1L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>mi_w4</t>
+  </si>
+  <si>
+    <t>anginapectoris_w4</t>
+  </si>
+  <si>
+    <t>stroke_w4</t>
+  </si>
+  <si>
+    <t>hypertension_w4</t>
+  </si>
+  <si>
+    <t>hypertension_w4;
+med1atc_w4;
+med2atc_w4;
+med3atc_w4;
+med4atc_w4;
+med5atc_w4;
+med6atc_w4;
+med7atc_w4;
+med8atc_w4;
+med9atc_w4</t>
+  </si>
+  <si>
+    <t>osteoarthrosis_w4;
+osteoporosis_w4;
+sciatica_w4;
+rheumatoidarthritis_w4</t>
+  </si>
+  <si>
+    <t>case_when(
+osteoarthrosis_w4 %in% c(2, 3) | osteoporosis_w4 %in% c(2, 3) | sciatica_w4 %in% c(2, 3) | rheumatoidarthritis_w4 %in% c(2, 3) ~ 1L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>diabetes_w4</t>
+  </si>
+  <si>
+    <t>malignanttumor_w4</t>
+  </si>
+  <si>
+    <t>highcholesterol_w4</t>
+  </si>
+  <si>
+    <t>depression_w4</t>
+  </si>
+  <si>
+    <t>alzheimer_w4</t>
+  </si>
+  <si>
+    <t>med1atc_w4;
+med2atc_w4;
+med3atc_w4;
+med4atc_w4;
+med5atc_w4;
+med6atc_w4;
+med7atc_w4;
+med8atc_w4;
+med9atc_w4</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w4 == "X04" ~ 1L;
+med2atc_w4 == "X04" ~ 1L;
+med3atc_w4 == "X04" ~ 1L;
+med4atc_w4 == "X04" ~ 1L;
+med5atc_w4 == "X04" ~ 1L;
+med6atc_w4 == "X04" ~ 1L;
+med7atc_w4 == "X04" ~ 1L;
+med8atc_w4 == "X04" ~ 1L;
+med9atc_w4 == "X04" ~ 1L;
+grepl("^C10", med1atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med2atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med3atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med4atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med5atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med6atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med7atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med8atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med9atc_w4, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w4 == "X01" ~ 1L;
+med2atc_w4 == "X01" ~ 1L;
+med3atc_w4 == "X01" ~ 1L;
+med4atc_w4 == "X01" ~ 1L;
+med5atc_w4 == "X01" ~ 1L;
+med6atc_w4 == "X01" ~ 1L;
+med7atc_w4 == "X01" ~ 1L;
+med8atc_w4 == "X01" ~ 1L;
+med9atc_w4 == "X01" ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w4, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w4 == "X02" ~ 1L;
+med2atc_w4 == "X02" ~ 1L;
+med3atc_w4 == "X02" ~ 1L;
+med4atc_w4 == "X02" ~ 1L;
+med5atc_w4 == "X02" ~ 1L;
+med6atc_w4 == "X02" ~ 1L;
+med7atc_w4 == "X02" ~ 1L;
+med8atc_w4 == "X02" ~ 1L;
+med9atc_w4 == "X02" ~ 1L;
+grepl("^A10", med1atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med2atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med3atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med4atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med5atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med6atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med7atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med8atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med9atc_w4, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>pacommuting_w4</t>
+  </si>
+  <si>
+    <t>pa_running_w4</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w4;
+dis_moderate_w4;
+dis_lift_w4;
+dis_climbseveral_w4;
+dis_climbone_w4;
+dis_bending_w4;
+dis_walk2km__w4;
+dis_walk1km__w4;
+dis_walk100m__w4;
+dis_bath_w4</t>
+  </si>
+  <si>
+    <t>waist_mean_w3</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(waist_mean_w3), 2, NA)</t>
+  </si>
+  <si>
+    <t>waist_mean_w4</t>
+  </si>
+  <si>
+    <t>smoking_status_w3</t>
+  </si>
+  <si>
+    <t>smoking_status_w4</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w2 == "X04" ~ 1L;
+med2atc_w2 == "X04" ~ 1L;
+med3atc_w2 == "X04" ~ 1L;
+med4atc_w2 == "X04" ~ 1L;
+med5atc_w2 == "X04" ~ 1L;
+med6atc_w2 == "X04" ~ 1L;
+med7atc_w2 == "X04" ~ 1L;
+med8atc_w2 == "X04" ~ 1L;
+med9atc_w2 == "X04" ~ 1L;
+grepl("^C10", med1atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med2atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med3atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med4atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med5atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med6atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med7atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med8atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med9atc_w2, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w2 == "X01" ~ 1L;
+med2atc_w2 == "X01" ~ 1L;
+med3atc_w2 == "X01" ~ 1L;
+med4atc_w2 == "X01" ~ 1L;
+med5atc_w2 == "X01" ~ 1L;
+med6atc_w2 == "X01" ~ 1L;
+med7atc_w2== "X01" ~ 1L;
+med8atc_w2 == "X01" ~ 1L;
+med9atc_w2 == "X01" ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w2, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc_w2 == "X02" ~ 1L;
+med2atc_w2 == "X02" ~ 1L;
+med3atc_w2 == "X02" ~ 1L;
+med4atc_w2 == "X02" ~ 1L;
+med5atc_w2 == "X02" ~ 1L;
+med6atc_w2 == "X02" ~ 1L;
+med7atc_w2 == "X02" ~ 1L;
+med8atc_w2 == "X02" ~ 1L;
+med9atc_w2 == "X02" ~ 1L;
+grepl("^A10", med1atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med2atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med3atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med4atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med5atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med6atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med7atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med8atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med9atc_w2, ignore.case = TRUE) ~ 1L;
+ELSE ~ 0L)</t>
+  </si>
+  <si>
+    <t>case_when(
+hypertension_w3 %in% c(2,3) ~ 1L;
+med1atc_w3 == "X01" ~ 1L;
+med2atc_w3 == "X01" ~ 1L;
+med3atc_w3 == "X01" ~ 1L;
+med4atc_w3 == "X01" ~ 1L;
+med5atc_w3 == "X01" ~ 1L;
+med6atc_w3 == "X01" ~ 1L;
+med7atc_w3== "X01" ~ 1L;
+med8atc_w3 == "X01" ~ 1L;
+med9atc_w3 == "X01" ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w3, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w3, ignore.case = TRUE) ~ 1L;
+hypertension_w3 == 1 &amp; 
+med1atc_w3 != "X01" &amp;
+med2atc_w3 != "X01" &amp;
+med3atc_w3 != "X01"&amp;
+med4atc_w3 != "X01"&amp;
+med5atc_w3 != "X01"&amp;
+med6atc_w3 != "X01"&amp;
+med7atc_w3 != "X01"&amp;
+med8atc_w3 != "X01"&amp;
+med9atc_w3 != "X01" &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w3, ignore.case = TRUE) ~ 0L;
+is.na(hypertension_w3) &amp;
+med1atc_w3 != "X01" &amp;
+med2atc_w3 != "X01" &amp;
+med3atc_w3 != "X01"&amp;
+med4atc_w3 != "X01"&amp;
+med5atc_w3 != "X01"&amp;
+med6atc_w3 != "X01"&amp;
+med7atc_w3 != "X01"&amp;
+med8atc_w3 != "X01"&amp;
+med9atc_w3 != "X01" &amp;
+(!is.na(med1atc_w3) |
+!is.na(med2atc_w3) |
+!is.na(med3atc_w3) |
+!is.na(med4atc_w3) |
+!is.na(med5atc_w3) |
+!is.na(med6atc_w3) |
+!is.na(med7atc_w3) |
+!is.na(med8atc_w3) |
+!is.na(med9atc_w3)) &amp; 
+!grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w3, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w3, ignore.case = TRUE) ~ 2L;
+hypertension_w3 == 1 &amp;
+is.na(med1atc_w3) &amp;
+is.na(med2atc_w3) &amp;
+is.na(med3atc_w3) &amp;
+is.na(med4atc_w3) &amp;
+is.na(med5atc_w3) &amp;
+is.na(med6atc_w3) &amp;
+is.na(med7atc_w3) &amp;
+is.na(med8atc_w3) &amp;
+is.na(med9atc_w3) ~ 2L;
+ELSE ~ NA)</t>
   </si>
   <si>
     <t>case_when(
@@ -2266,12 +3001,12 @@
 grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w2, ignore.case = TRUE) ~ 1L;
 grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w2, ignore.case = TRUE) ~ 1L;
 grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w2, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w2, ignore.case = TRUE) ~ 1L;
 hypertension_w2 == 1 &amp; 
 med1atc_w2 != "X01" &amp;
 med2atc_w2 != "X01" &amp;
@@ -2332,714 +3067,6 @@
 ELSE ~ NA)</t>
   </si>
   <si>
-    <t>osteoarthrosis_w2;
-osteoporosis_w2;
-sciatica_w2;
-rheumatoidarthritis_w2</t>
-  </si>
-  <si>
-    <t>case_when(
-osteoarthrosis_w2 %in% c(2, 3) | osteoporosis_w2 %in% c(2, 3) | sciatica_w2 %in% c(2, 3) | rheumatoidarthritis_w2 %in% c(2, 3) ~ 1L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>depression_w2</t>
-  </si>
-  <si>
-    <t>alzheimer_w2</t>
-  </si>
-  <si>
-    <t>med1atc_w2;
-med2atc_w2;
-med3atc_w2;
-med4atc_w2;
-med5atc_w2;
-med6atc_w2;
-med7atc_w2;
-med8atc_w2;
-med9atc_w2</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w2 == "X04" ~ 1L;
-med2atc_w2 == "X04" ~ 1L;
-med3atc_w2 == "X04" ~ 1L;
-med4atc_w2 == "X04" ~ 1L;
-med5atc_w2 == "X04" ~ 1L;
-med6atc_w2 == "X04" ~ 1L;
-med7atc_w2 == "X04" ~ 1L;
-med8atc_w2 == "X04" ~ 1L;
-med9atc_w2 == "X04" ~ 1L;
-grepl("^C10", med1atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med2atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med3atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med9atc1, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w2 == "X01" ~ 1L;
-med2atc_w2 == "X01" ~ 1L;
-med3atc_w2 == "X01" ~ 1L;
-med4atc_w2 == "X01" ~ 1L;
-med5atc_w2 == "X01" ~ 1L;
-med6atc_w2 == "X01" ~ 1L;
-med7atc_w2== "X01" ~ 1L;
-med8atc_w2 == "X01" ~ 1L;
-med9atc_w2 == "X01" ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w2 == "X02" ~ 1L;
-med2atc_w2 == "X02" ~ 1L;
-med3atc_w2 == "X02" ~ 1L;
-med4atc_w2 == "X02" ~ 1L;
-med5atc_w2 == "X02" ~ 1L;
-med6atc_w2 == "X02" ~ 1L;
-med7atc_w2 == "X02" ~ 1L;
-med8atc_w2 == "X02" ~ 1L;
-med9atc_w2 == "X02" ~ 1L;
-grepl("^A10", med1atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med2atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med3atc_w2, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med9atc1, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>mci_w2</t>
-  </si>
-  <si>
-    <t>pacommuting_w2</t>
-  </si>
-  <si>
-    <t>pa_running_w2</t>
-  </si>
-  <si>
-    <t>dis_vigorous_w2;
-dis_moderate_w2;
-dis_lift_w2;
-dis_climbseveral_w2;
-dis_climbone_w2;
-dis_bending_w2;
-dis_walk2km__w2;
-dis_walk1km__w2;
-dis_walk100m__w2;
-dis_bath_w2</t>
-  </si>
-  <si>
-    <t>ifelse(rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w2)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w2)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift_w2)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w2)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w2)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending_w2)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km__w2)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km__w2)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m__w2)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath_w2))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE) &lt; 5,NA,
-rowMeans(mutate(.,
-temp_dis_vigorous1 = 50 * dis_vigorous_w2 - 50, 
-temp_dis_moderate1 = 50 * dis_moderate_w2 - 50,
-temp_dis_lift1 = 50 * dis_lift_w2 - 50,
-temp_dis_climbseveral1 = 50 * dis_climbseveral_w2 - 50,
-temp_dis_climbone1 = 50 * dis_climbone_w2 - 50,
-temp_dis_bending1 = 50 * dis_bending_w2 - 50,
-temp_dis_walk2km_1 = 50 * dis_walk2km__w2 - 50,
-temp_dis_walk1km_1 = 50 * dis_walk1km__w2 - 50,
-temp_dis_walk100m_1 = 50 * dis_walk100m__w2 - 50,
-temp_dis_bath1 = 50 * dis_bath_w2 - 50) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE))</t>
-  </si>
-  <si>
-    <t>rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w2)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w2)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift_w2)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w2)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w2)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending_w2)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km__w2)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km__w2)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m__w2)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath_w2))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) %&gt;%
-mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
-  </si>
-  <si>
-    <t>DOM_w3</t>
-  </si>
-  <si>
-    <t>format(as.Date(DOM_w3, format = "%d/%m/%y"), "%Y-%m-%d")</t>
-  </si>
-  <si>
-    <t>age_w3</t>
-  </si>
-  <si>
-    <t>employmentstatus_w3</t>
-  </si>
-  <si>
-    <t>maritalstatus_w3</t>
-  </si>
-  <si>
-    <t>height_w3</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(height_w3), 2, NA)</t>
-  </si>
-  <si>
-    <t>weight_w3</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(weight_w3), 2, NA)</t>
-  </si>
-  <si>
-    <t>fatmass_w3</t>
-  </si>
-  <si>
-    <t>fatmass_w3/weight_w3*100</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(fatmass_w3), "Bioelectrical impedance measurement (InBody 720)", NA)</t>
-  </si>
-  <si>
-    <t>systolicBP_right_w3; systolicBP_left_w3</t>
-  </si>
-  <si>
-    <t>diastolicBP_right_w3; diastolicBP_left_w3</t>
-  </si>
-  <si>
-    <t>round(rowMeans(select(., diastolicBP_right_w3, diastolicBP_left_w3), na.rm=TRUE), 2)</t>
-  </si>
-  <si>
-    <t>Cholesterol_w3</t>
-  </si>
-  <si>
-    <t>HDL_w3</t>
-  </si>
-  <si>
-    <t>LDL_w3</t>
-  </si>
-  <si>
-    <t>Cholesterol_w3;
-HDL_w3;
-Trig_w3</t>
-  </si>
-  <si>
-    <t>round(Cholesterol_w3 - HDL_w3 - (Trig_w3/2.2), 2)</t>
-  </si>
-  <si>
-    <t>Trig_w3</t>
-  </si>
-  <si>
-    <t>CRP_w3</t>
-  </si>
-  <si>
-    <t>freshvegetables_w3; cooked_vegetables_w3</t>
-  </si>
-  <si>
-    <t>alcohol_w3</t>
-  </si>
-  <si>
-    <t>sleepduration_w3</t>
-  </si>
-  <si>
-    <t>sleepquality_categorized_w3</t>
-  </si>
-  <si>
-    <t>sitting_tv_w3</t>
-  </si>
-  <si>
-    <t>sitting_computer_w3</t>
-  </si>
-  <si>
-    <t>ifelse(sitting_computer_w3 %in% 0:10, sitting_computer_w3+1, NA)</t>
-  </si>
-  <si>
-    <t>sitting_tv_w3;sitting_vehicle_w3;sitting_computer_w3;sitting_other_w3; sitting_office_w3</t>
-  </si>
-  <si>
-    <t>rowSums(select(., sitting_tv_w3,sitting_vehicle_w3,sitting_computer_w3,sitting_other_w3, sitting_office_w3), na.rm=TRUE)</t>
-  </si>
-  <si>
-    <t>sitting_other_w3; sitting_office_w3</t>
-  </si>
-  <si>
-    <t>case_when(
-sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 == 0 ~ 0L;
-sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt; 0 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 1 ~ 1L;
-sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 1 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 3 ~ 2L;
-sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 3 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 5 ~ 3L;
-sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 5 &amp; sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &lt; 7 ~ 4L;
-sitting_tv_w3 + sitting_vehicle_w3 + sitting_computer_w3 + sitting_other_w3 + sitting_office_w3 &gt;= 7 ~ 5L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>selfratedhealth_w3</t>
-  </si>
-  <si>
-    <t>hypertension_w3;
-mi_w3;
-stroke_w3;
-anginapectoris_w3</t>
-  </si>
-  <si>
-    <t>case_when(
-hypertension_w3 %in% 2:3 ~ 1L;
-mi_w3 %in% 2:3 ~ 1L;
-stroke_w3 %in% 2:3 ~1L;
-anginapectoris_w3 %in% 2:3 ~ 1L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>mi_w3</t>
-  </si>
-  <si>
-    <t>anginapectoris_w3</t>
-  </si>
-  <si>
-    <t>stroke_w3</t>
-  </si>
-  <si>
-    <t>hypertension_w3</t>
-  </si>
-  <si>
-    <t>hypertension_w3;
-med1atc_w3;
-med2atc_w3;
-med3atc_w3;
-med4atc_w3;
-med5atc_w3;
-med6atc_w3;
-med7atc_w3;
-med8atc_w3;
-med9atc_w3</t>
-  </si>
-  <si>
-    <t>case_when(
-hypertension_w3 %in% c(2,3) ~ 1L;
-med1atc_w3 == "X01" ~ 1L;
-med2atc_w3 == "X01" ~ 1L;
-med3atc_w3 == "X01" ~ 1L;
-med4atc_w3 == "X01" ~ 1L;
-med5atc_w3 == "X01" ~ 1L;
-med6atc_w3 == "X01" ~ 1L;
-med7atc_w3== "X01" ~ 1L;
-med8atc_w3 == "X01" ~ 1L;
-med9atc_w3 == "X01" ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 1L;
-hypertension_w3 == 1 &amp; 
-med1atc_w3 != "X01" &amp;
-med2atc_w3 != "X01" &amp;
-med3atc_w3 != "X01"&amp;
-med4atc_w3 != "X01"&amp;
-med5atc_w3 != "X01"&amp;
-med6atc_w3 != "X01"&amp;
-med7atc_w3 != "X01"&amp;
-med8atc_w3 != "X01"&amp;
-med9atc_w3 != "X01" &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w3, ignore.case = TRUE) ~ 0L;
-is.na(hypertension_w3) &amp;
-med1atc_w3 != "X01" &amp;
-med2atc_w3 != "X01" &amp;
-med3atc_w3 != "X01"&amp;
-med4atc_w3 != "X01"&amp;
-med5atc_w3 != "X01"&amp;
-med6atc_w3 != "X01"&amp;
-med7atc_w3 != "X01"&amp;
-med8atc_w3 != "X01"&amp;
-med9atc_w3 != "X01" &amp;
-(!is.na(med1atc_w3) |
-!is.na(med2atc_w3) |
-!is.na(med3atc_w3) |
-!is.na(med4atc_w3) |
-!is.na(med5atc_w3) |
-!is.na(med6atc_w3) |
-!is.na(med7atc_w3) |
-!is.na(med8atc_w3) |
-!is.na(med9atc_w3)) &amp; 
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w3, ignore.case = TRUE) ~ 2L;
-hypertension_w3 == 1 &amp;
-is.na(med1atc_w3) &amp;
-is.na(med2atc_w3) &amp;
-is.na(med3atc_w3) &amp;
-is.na(med4atc_w3) &amp;
-is.na(med5atc_w3) &amp;
-is.na(med6atc_w3) &amp;
-is.na(med7atc_w3) &amp;
-is.na(med8atc_w3) &amp;
-is.na(med9atc_w3) ~ 2L;
-ELSE ~ NA)</t>
-  </si>
-  <si>
-    <t>osteoarthrosis_w3;
-osteoporosis_w3;
-sciatica_w3;
-rheumatoidarthritis_w3</t>
-  </si>
-  <si>
-    <t>case_when(
-osteoarthrosis_w3 %in% c(2, 3) | osteoporosis_w3 %in% c(2, 3) | sciatica_w3 %in% c(2, 3) | rheumatoidarthritis_w3 %in% c(2, 3) ~ 1L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>diabetes_w3</t>
-  </si>
-  <si>
-    <t>malignanttumor_w3</t>
-  </si>
-  <si>
-    <t>highcholesterol_w3</t>
-  </si>
-  <si>
-    <t>depression_w3</t>
-  </si>
-  <si>
-    <t>alzheimer_w3</t>
-  </si>
-  <si>
-    <t>med1atc_w3;
-med2atc_w3;
-med3atc_w3;
-med4atc_w3;
-med5atc_w3;
-med6atc_w3;
-med7atc_w3;
-med8atc_w3;
-med9atc_w3</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w3 == "X04" ~ 1L;
-med2atc_w3 == "X04" ~ 1L;
-med3atc_w3 == "X04" ~ 1L;
-med4atc_w3 == "X04" ~ 1L;
-med5atc_w3 == "X04" ~ 1L;
-med6atc_w3 == "X04" ~ 1L;
-med7atc_w3 == "X04" ~ 1L;
-med8atc_w3 == "X04" ~ 1L;
-med9atc_w3 == "X04" ~ 1L;
-grepl("^C10", med1atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med2atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med3atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med4atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med5atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med6atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med7atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med8atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med9atc_w3, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w3 == "X01" ~ 1L;
-med2atc_w3 == "X01" ~ 1L;
-med3atc_w3 == "X01" ~ 1L;
-med4atc_w3 == "X01" ~ 1L;
-med5atc_w3 == "X01" ~ 1L;
-med6atc_w3 == "X01" ~ 1L;
-med7atc_w3 == "X01" ~ 1L;
-med8atc_w3 == "X01" ~ 1L;
-med9atc_w3 == "X01" ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w3, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w3 == "X02" ~ 1L;
-med2atc_w3 == "X02" ~ 1L;
-med3atc_w3 == "X02" ~ 1L;
-med4atc_w3 == "X02" ~ 1L;
-med5atc_w3 == "X02" ~ 1L;
-med6atc_w3 == "X02" ~ 1L;
-med7atc_w3 == "X02" ~ 1L;
-med8atc_w3 == "X02" ~ 1L;
-med9atc_w3 == "X02" ~ 1L;
-grepl("^A10", med1atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med2atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med3atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med4atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med5atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med6atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med7atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med8atc_w3, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med9atc_w3, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>pacommuting_w3</t>
-  </si>
-  <si>
-    <t>pa_running_w3</t>
-  </si>
-  <si>
-    <t>dis_vigorous_w3;
-dis_moderate_w3;
-dis_lift_w3;
-dis_climbseveral_w3;
-dis_climbone_w3;
-dis_bending_w3;
-dis_walk2km__w3;
-dis_walk1km__w3;
-dis_walk100m__w3;
-dis_bath_w3</t>
-  </si>
-  <si>
-    <t>ifelse(rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift_w3)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w3)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w3)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending_w3)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km__w3)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km__w3)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m__w3)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath_w3))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE) &lt; 5,NA,
-rowMeans(mutate(.,
-temp_dis_vigorous1 = 50 * dis_vigorous_w3 - 50, 
-temp_dis_moderate1 = 50 * dis_moderate_w3 - 50,
-temp_dis_lift1 = 50 * dis_lift_w3 - 50,
-temp_dis_climbseveral1 = 50 * dis_climbseveral_w3 - 50,
-temp_dis_climbone1 = 50 * dis_climbone_w3 - 50,
-temp_dis_bending1 = 50 * dis_bending_w3 - 50,
-temp_dis_walk2km_1 = 50 * dis_walk2km__w3 - 50,
-temp_dis_walk1km_1 = 50 * dis_walk1km__w3 - 50,
-temp_dis_walk100m_1 = 50 * dis_walk100m__w3 - 50,
-temp_dis_bath1 = 50 * dis_bath_w3 - 50) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE))</t>
-  </si>
-  <si>
-    <t>rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift_w3)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w3)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w3)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending_w3)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km__w3)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km__w3)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m__w3)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath_w3))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) %&gt;%
-mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
-  </si>
-  <si>
-    <t>DOM_w4</t>
-  </si>
-  <si>
-    <t>format(as.Date(DOM_w4, format = "%d/%m/%y"), "%Y-%m-%d")</t>
-  </si>
-  <si>
-    <t>age_w4</t>
-  </si>
-  <si>
-    <t>employmentstatus_w4</t>
-  </si>
-  <si>
-    <t>maritalstatus_w4</t>
-  </si>
-  <si>
-    <t>height_w4</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(height_w4), 2, NA)</t>
-  </si>
-  <si>
-    <t>weight_w4</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(weight_w4), 2, NA)</t>
-  </si>
-  <si>
-    <t>fatmass_w4</t>
-  </si>
-  <si>
-    <t>fatmass_w4/weight_w4*100</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(fatmass_w4), "Bioelectrical impedance measurement (InBody 720)", NA)</t>
-  </si>
-  <si>
-    <t>systolicBP_right_w4; systolicBP_left_w4</t>
-  </si>
-  <si>
-    <t>diastolicBP_right_w4; diastolicBP_left_w4</t>
-  </si>
-  <si>
-    <t>round(rowMeans(select(., diastolicBP_right_w4, diastolicBP_left_w4), na.rm=TRUE), 2)</t>
-  </si>
-  <si>
-    <t>Cholesterol_w4</t>
-  </si>
-  <si>
-    <t>HDL_w4</t>
-  </si>
-  <si>
-    <t>LDL_w4</t>
-  </si>
-  <si>
-    <t>Cholesterol_w4;
-HDL_w4;
-Trig_w4</t>
-  </si>
-  <si>
-    <t>round(Cholesterol_w4 - HDL_w4 - (Trig_w4/2.2), 2)</t>
-  </si>
-  <si>
-    <t>Trig_w4</t>
-  </si>
-  <si>
-    <t>CRP_w4</t>
-  </si>
-  <si>
-    <t>freshvegetables_w4; cooked_vegetables_w4</t>
-  </si>
-  <si>
-    <t>alcohol_w4</t>
-  </si>
-  <si>
-    <t>sleepduration_w4</t>
-  </si>
-  <si>
-    <t>sleepquality_categorized_w4</t>
-  </si>
-  <si>
-    <t>sitting_tv_w4</t>
-  </si>
-  <si>
-    <t>sitting_computer_w4</t>
-  </si>
-  <si>
-    <t>ifelse(sitting_computer_w4 %in% 0:10, sitting_computer_w4+1, NA)</t>
-  </si>
-  <si>
-    <t>sitting_tv_w4;sitting_vehicle_w4;sitting_computer_w4;sitting_other_w4; sitting_office_w4</t>
-  </si>
-  <si>
-    <t>rowSums(select(., sitting_tv_w4,sitting_vehicle_w4,sitting_computer_w4,sitting_other_w4, sitting_office_w4), na.rm=TRUE)</t>
-  </si>
-  <si>
-    <t>sitting_other_w4; sitting_office_w4</t>
-  </si>
-  <si>
-    <t>case_when(
-sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 == 0 ~ 0L;
-sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt; 0 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 1 ~ 1L;
-sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 1 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 3 ~ 2L;
-sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 3 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 5 ~ 3L;
-sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 5 &amp; sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &lt; 7 ~ 4L;
-sitting_tv_w4 + sitting_vehicle_w4 + sitting_computer_w4 + sitting_other_w4 + sitting_office_w4 &gt;= 7 ~ 5L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>selfratedhealth_w4</t>
-  </si>
-  <si>
-    <t>hypertension_w4;
-mi_w4;
-stroke_w4;
-anginapectoris_w4</t>
-  </si>
-  <si>
-    <t>case_when(
-hypertension_w4 %in% 2:3 ~ 1L;
-mi_w4 %in% 2:3 ~ 1L;
-stroke_w4 %in% 2:3 ~1L;
-anginapectoris_w4 %in% 2:3 ~ 1L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>mi_w4</t>
-  </si>
-  <si>
-    <t>anginapectoris_w4</t>
-  </si>
-  <si>
-    <t>stroke_w4</t>
-  </si>
-  <si>
-    <t>hypertension_w4</t>
-  </si>
-  <si>
-    <t>hypertension_w4;
-med1atc_w4;
-med2atc_w4;
-med3atc_w4;
-med4atc_w4;
-med5atc_w4;
-med6atc_w4;
-med7atc_w4;
-med8atc_w4;
-med9atc_w4</t>
-  </si>
-  <si>
     <t>case_when(
 hypertension_w4 %in% c(2,3) ~ 1L;
 med1atc_w4 == "X01" ~ 1L;
@@ -3054,12 +3081,12 @@
 grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w4, ignore.case = TRUE) ~ 1L;
 grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w4, ignore.case = TRUE) ~ 1L;
 grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w4, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w4, ignore.case = TRUE) ~ 1L;
 hypertension_w4 == 1 &amp; 
 med1atc_w4 != "X01" &amp;
 med2atc_w4 != "X01" &amp;
@@ -3120,125 +3147,104 @@
 ELSE ~ NA)</t>
   </si>
   <si>
-    <t>osteoarthrosis_w4;
-osteoporosis_w4;
-sciatica_w4;
-rheumatoidarthritis_w4</t>
-  </si>
-  <si>
-    <t>case_when(
-osteoarthrosis_w4 %in% c(2, 3) | osteoporosis_w4 %in% c(2, 3) | sciatica_w4 %in% c(2, 3) | rheumatoidarthritis_w4 %in% c(2, 3) ~ 1L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>diabetes_w4</t>
-  </si>
-  <si>
-    <t>malignanttumor_w4</t>
-  </si>
-  <si>
-    <t>highcholesterol_w4</t>
-  </si>
-  <si>
-    <t>depression_w4</t>
-  </si>
-  <si>
-    <t>alzheimer_w4</t>
-  </si>
-  <si>
-    <t>med1atc_w4;
-med2atc_w4;
-med3atc_w4;
-med4atc_w4;
-med5atc_w4;
-med6atc_w4;
-med7atc_w4;
-med8atc_w4;
-med9atc_w4</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w4 == "X04" ~ 1L;
-med2atc_w4 == "X04" ~ 1L;
-med3atc_w4 == "X04" ~ 1L;
-med4atc_w4 == "X04" ~ 1L;
-med5atc_w4 == "X04" ~ 1L;
-med6atc_w4 == "X04" ~ 1L;
-med7atc_w4 == "X04" ~ 1L;
-med8atc_w4 == "X04" ~ 1L;
-med9atc_w4 == "X04" ~ 1L;
-grepl("^C10", med1atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med2atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med3atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med4atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med5atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med6atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med7atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med8atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med9atc_w4, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w4 == "X01" ~ 1L;
-med2atc_w4 == "X01" ~ 1L;
-med3atc_w4 == "X01" ~ 1L;
-med4atc_w4 == "X01" ~ 1L;
-med5atc_w4 == "X01" ~ 1L;
-med6atc_w4 == "X01" ~ 1L;
-med7atc_w4 == "X01" ~ 1L;
-med8atc_w4 == "X01" ~ 1L;
-med9atc_w4 == "X01" ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med1atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med2atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med3atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med4atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med5atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med6atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med7atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med8atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med9atc_w4, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc_w4 == "X02" ~ 1L;
-med2atc_w4 == "X02" ~ 1L;
-med3atc_w4 == "X02" ~ 1L;
-med4atc_w4 == "X02" ~ 1L;
-med5atc_w4 == "X02" ~ 1L;
-med6atc_w4 == "X02" ~ 1L;
-med7atc_w4 == "X02" ~ 1L;
-med8atc_w4 == "X02" ~ 1L;
-med9atc_w4 == "X02" ~ 1L;
-grepl("^A10", med1atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med2atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med3atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med4atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med5atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med6atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med7atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med8atc_w4, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med9atc_w4, ignore.case = TRUE) ~ 1L;
-ELSE ~ 0L)</t>
-  </si>
-  <si>
-    <t>pacommuting_w4</t>
-  </si>
-  <si>
-    <t>pa_running_w4</t>
-  </si>
-  <si>
-    <t>dis_vigorous_w4;
-dis_moderate_w4;
-dis_lift_w4;
-dis_climbseveral_w4;
-dis_climbone_w4;
-dis_bending_w4;
-dis_walk2km__w4;
-dis_walk1km__w4;
-dis_walk100m__w4;
-dis_bath_w4</t>
+    <t>malignanttumor_w2</t>
+  </si>
+  <si>
+    <t>highcholesterol_w2</t>
+  </si>
+  <si>
+    <t>ifelse(rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w2)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w2)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w2)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w2)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w2)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w2)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w2)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w2)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w2)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w2))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE) &lt; 5,NA,
+rowMeans(mutate(.,
+temp_dis_vigorous1 = 50 * dis_vigorous_w2 - 50, 
+temp_dis_moderate1 = 50 * dis_moderate_w2 - 50,
+temp_dis_lift1 = 50 * dis_lift_w2 - 50,
+temp_dis_climbseveral1 = 50 * dis_climbseveral_w2 - 50,
+temp_dis_climbone1 = 50 * dis_climbone_w2 - 50,
+temp_dis_bending1 = 50 * dis_bending_w2 - 50,
+temp_dis_walk2km_1 = 50 * dis_walk2km_w2 - 50,
+temp_dis_walk1km_1 = 50 * dis_walk1km_w2 - 50,
+temp_dis_walk100m_1 = 50 * dis_walk100m_w2 - 50,
+temp_dis_bath1 = 50 * dis_bath_w2 - 50) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE))</t>
+  </si>
+  <si>
+    <t>rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w2)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w2)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w2)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w2)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w2)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w2)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w2)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w2)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w2)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w2))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE)) %&gt;%
+mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
+  </si>
+  <si>
+    <t>ifelse(rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w3)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w3)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w3)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w3)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w3)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w3)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w3)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w3))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE) &lt; 5,NA,
+rowMeans(mutate(.,
+temp_dis_vigorous1 = 50 * dis_vigorous_w3 - 50, 
+temp_dis_moderate1 = 50 * dis_moderate_w3 - 50,
+temp_dis_lift1 = 50 * dis_lift_w3 - 50,
+temp_dis_climbseveral1 = 50 * dis_climbseveral_w3 - 50,
+temp_dis_climbone1 = 50 * dis_climbone_w3 - 50,
+temp_dis_bending1 = 50 * dis_bending_w3 - 50,
+temp_dis_walk2km_1 = 50 * dis_walk2km_w3 - 50,
+temp_dis_walk1km_1 = 50 * dis_walk1km_w3 - 50,
+temp_dis_walk100m_1 = 50 * dis_walk100m_w3 - 50,
+temp_dis_bath1 = 50 * dis_bath_w3 - 50) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE))</t>
+  </si>
+  <si>
+    <t>rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w3)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w3)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w3)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w3)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w3)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w3)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w3)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w3))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE)) %&gt;%
+mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
   </si>
   <si>
     <t>ifelse(rowSums(mutate(.,
@@ -3248,9 +3254,9 @@
 temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w4)),
 temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w4)),
 temp_dis_bending1 = as.numeric(!is.na(dis_bending_w4)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km__w4)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km__w4)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m__w4)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w4)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w4)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w4)),
 temp_dis_bath1 = as.numeric(!is.na(dis_bath_w4))) %&gt;%
 select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
 temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
@@ -3262,9 +3268,9 @@
 temp_dis_climbseveral1 = 50 * dis_climbseveral_w4 - 50,
 temp_dis_climbone1 = 50 * dis_climbone_w4 - 50,
 temp_dis_bending1 = 50 * dis_bending_w4 - 50,
-temp_dis_walk2km_1 = 50 * dis_walk2km__w4 - 50,
-temp_dis_walk1km_1 = 50 * dis_walk1km__w4 - 50,
-temp_dis_walk100m_1 = 50 * dis_walk100m__w4 - 50,
+temp_dis_walk2km_1 = 50 * dis_walk2km_w4 - 50,
+temp_dis_walk1km_1 = 50 * dis_walk1km_w4 - 50,
+temp_dis_walk100m_1 = 50 * dis_walk100m_w4 - 50,
 temp_dis_bath1 = 50 * dis_bath_w4 - 50) %&gt;%
 select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
 temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
@@ -3278,9 +3284,9 @@
 temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w4)),
 temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w4)),
 temp_dis_bending1 = as.numeric(!is.na(dis_bending_w4)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km__w4)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km__w4)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m__w4)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w4)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w4)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w4)),
 temp_dis_bath1 = as.numeric(!is.na(dis_bath_w4))) %&gt;%
 select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
 temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
@@ -3288,22 +3294,25 @@
 mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
   </si>
   <si>
-    <t>waist_mean_w3</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(waist_mean_w3), 2, NA)</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(waistmean_w4), 2, NA)</t>
-  </si>
-  <si>
-    <t>waist_mean_w4</t>
-  </si>
-  <si>
-    <t>smoking_status_w3</t>
-  </si>
-  <si>
-    <t>smoking_status_w4</t>
+    <t>bmi_w3</t>
+  </si>
+  <si>
+    <t>round(rowMeans(select(., systolicBP_right_w3, systolicBP_left_w3), na.rm=TRUE), 2)</t>
+  </si>
+  <si>
+    <t>mci_w3</t>
+  </si>
+  <si>
+    <t>mci_w4</t>
+  </si>
+  <si>
+    <t>bmi_w4</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(waist_mean_w4), 2, NA)</t>
+  </si>
+  <si>
+    <t>round(rowMeans(select(., systolicBP_right_w4, systolicBP_left_w4), na.rm=TRUE), 2)</t>
   </si>
 </sst>
 </file>
@@ -3681,6 +3690,7 @@
   <dimension ref="A1:X337"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="11" max="11" width="40.140625" customWidth="1"/>
     <col min="24" max="24" width="71" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3743,10 +3753,10 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="U1" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="V1" t="s">
         <v>19</v>
@@ -3849,7 +3859,7 @@
         <v>43</v>
       </c>
       <c r="X3" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3887,7 +3897,7 @@
         <v>43</v>
       </c>
       <c r="X4" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -3954,7 +3964,7 @@
         <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -3975,7 +3985,7 @@
         <v>59</v>
       </c>
       <c r="X6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.25">
@@ -4051,7 +4061,7 @@
         <v>74</v>
       </c>
       <c r="K8" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="L8" t="s">
         <v>75</v>
@@ -4192,7 +4202,7 @@
         <v>96</v>
       </c>
       <c r="K11" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="L11" t="s">
         <v>97</v>
@@ -4254,7 +4264,7 @@
         <v>107</v>
       </c>
       <c r="K12" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="L12" t="s">
         <v>97</v>
@@ -4389,7 +4399,7 @@
         <v>121</v>
       </c>
       <c r="K15" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="L15" t="s">
         <v>97</v>
@@ -4448,7 +4458,7 @@
         <v>125</v>
       </c>
       <c r="K16" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="L16" t="s">
         <v>126</v>
@@ -4548,7 +4558,7 @@
         <v>139</v>
       </c>
       <c r="K18" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="L18" t="s">
         <v>140</v>
@@ -4607,7 +4617,7 @@
         <v>146</v>
       </c>
       <c r="K19" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="U19" t="s">
         <v>35</v>
@@ -4619,7 +4629,7 @@
         <v>59</v>
       </c>
       <c r="X19" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -4648,7 +4658,7 @@
         <v>139</v>
       </c>
       <c r="K20" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="L20" t="s">
         <v>150</v>
@@ -4707,7 +4717,7 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="U21" t="s">
         <v>35</v>
@@ -4719,7 +4729,7 @@
         <v>59</v>
       </c>
       <c r="X21" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -4748,7 +4758,7 @@
         <v>158</v>
       </c>
       <c r="K22" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="L22" t="s">
         <v>159</v>
@@ -4810,7 +4820,7 @@
         <v>139</v>
       </c>
       <c r="K23" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="L23" t="s">
         <v>164</v>
@@ -4872,7 +4882,7 @@
         <v>146</v>
       </c>
       <c r="K24" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
@@ -4905,7 +4915,7 @@
         <v>59</v>
       </c>
       <c r="X24" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="45" x14ac:dyDescent="0.25">
@@ -4931,7 +4941,7 @@
         <v>173</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="L25" t="s">
         <v>174</v>
@@ -4964,7 +4974,7 @@
         <v>59</v>
       </c>
       <c r="X25" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -4987,7 +4997,7 @@
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="U26" t="s">
         <v>35</v>
@@ -4999,7 +5009,7 @@
         <v>59</v>
       </c>
       <c r="X26" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -5028,7 +5038,7 @@
         <v>184</v>
       </c>
       <c r="K27" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="L27" t="s">
         <v>185</v>
@@ -5058,7 +5068,7 @@
         <v>59</v>
       </c>
       <c r="X27" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -5087,7 +5097,7 @@
         <v>184</v>
       </c>
       <c r="K28" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="L28" t="s">
         <v>191</v>
@@ -5117,7 +5127,7 @@
         <v>59</v>
       </c>
       <c r="X28" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -5339,7 +5349,7 @@
         <v>211</v>
       </c>
       <c r="K34" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="L34" t="s">
         <v>210</v>
@@ -5386,7 +5396,7 @@
         <v>211</v>
       </c>
       <c r="K35" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="L35" t="s">
         <v>215</v>
@@ -5433,7 +5443,7 @@
         <v>211</v>
       </c>
       <c r="K36" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="L36" t="s">
         <v>219</v>
@@ -5483,7 +5493,7 @@
         <v>224</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>225</v>
@@ -5498,7 +5508,7 @@
         <v>59</v>
       </c>
       <c r="X37" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -5524,7 +5534,7 @@
         <v>211</v>
       </c>
       <c r="K38" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="L38" t="s">
         <v>227</v>
@@ -5571,7 +5581,7 @@
         <v>232</v>
       </c>
       <c r="K39" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="L39" t="s">
         <v>231</v>
@@ -5744,7 +5754,7 @@
         <v>244</v>
       </c>
       <c r="K43" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="L43" t="s">
         <v>252</v>
@@ -5838,7 +5848,7 @@
         <v>263</v>
       </c>
       <c r="K45" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="L45" t="s">
         <v>264</v>
@@ -5929,7 +5939,7 @@
         <v>273</v>
       </c>
       <c r="K47" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="L47" t="s">
         <v>274</v>
@@ -6067,7 +6077,7 @@
         <v>113</v>
       </c>
       <c r="K50" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="L50" t="s">
         <v>289</v>
@@ -6129,7 +6139,7 @@
         <v>299</v>
       </c>
       <c r="K51" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="L51" t="s">
         <v>289</v>
@@ -6188,7 +6198,7 @@
         <v>304</v>
       </c>
       <c r="K52" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="L52" t="s">
         <v>305</v>
@@ -6285,7 +6295,7 @@
         <v>313</v>
       </c>
       <c r="K54" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="L54" t="s">
         <v>316</v>
@@ -6382,7 +6392,7 @@
         <v>328</v>
       </c>
       <c r="K56" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="L56" t="s">
         <v>329</v>
@@ -6415,7 +6425,7 @@
         <v>59</v>
       </c>
       <c r="X56" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -6526,7 +6536,7 @@
         <v>312</v>
       </c>
       <c r="K59" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>343</v>
@@ -6559,7 +6569,7 @@
         <v>59</v>
       </c>
       <c r="X59" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6585,7 +6595,7 @@
         <v>350</v>
       </c>
       <c r="K60" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>343</v>
@@ -6618,7 +6628,7 @@
         <v>352</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -6709,7 +6719,7 @@
         <v>367</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="L62" t="s">
         <v>368</v>
@@ -6742,7 +6752,7 @@
         <v>352</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="63" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6771,7 +6781,7 @@
         <v>367</v>
       </c>
       <c r="K63" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="L63" t="s">
         <v>377</v>
@@ -6833,7 +6843,7 @@
         <v>367</v>
       </c>
       <c r="K64" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="L64" t="s">
         <v>377</v>
@@ -6892,7 +6902,7 @@
         <v>367</v>
       </c>
       <c r="K65" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="L65" t="s">
         <v>389</v>
@@ -6951,7 +6961,7 @@
         <v>367</v>
       </c>
       <c r="K66" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="L66" t="s">
         <v>394</v>
@@ -7010,7 +7020,7 @@
         <v>367</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="L67" t="s">
         <v>368</v>
@@ -7110,7 +7120,7 @@
         <v>367</v>
       </c>
       <c r="K69" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="L69" t="s">
         <v>406</v>
@@ -7169,7 +7179,7 @@
         <v>367</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="U70" t="s">
         <v>35</v>
@@ -7181,7 +7191,7 @@
         <v>352</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>635</v>
+        <v>758</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7210,7 +7220,7 @@
         <v>367</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>415</v>
@@ -7243,7 +7253,7 @@
         <v>352</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7396,16 +7406,16 @@
         <v>367</v>
       </c>
       <c r="K74" t="s">
+        <v>760</v>
+      </c>
+      <c r="L74" t="s">
         <v>436</v>
-      </c>
-      <c r="L74" t="s">
-        <v>437</v>
       </c>
       <c r="M74" t="s">
         <v>384</v>
       </c>
       <c r="N74" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>78</v>
@@ -7437,19 +7447,19 @@
         <v>22</v>
       </c>
       <c r="C75" t="s">
+        <v>438</v>
+      </c>
+      <c r="D75" t="s">
         <v>439</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>439</v>
+      </c>
+      <c r="F75" t="s">
+        <v>49</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="E75" t="s">
-        <v>440</v>
-      </c>
-      <c r="F75" t="s">
-        <v>49</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>367</v>
@@ -7478,19 +7488,19 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
+        <v>441</v>
+      </c>
+      <c r="D76" t="s">
         <v>442</v>
       </c>
-      <c r="D76" t="s">
-        <v>443</v>
-      </c>
       <c r="E76" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F76" t="s">
         <v>49</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>367</v>
@@ -7519,19 +7529,19 @@
         <v>22</v>
       </c>
       <c r="C77" t="s">
+        <v>443</v>
+      </c>
+      <c r="D77" t="s">
         <v>444</v>
       </c>
-      <c r="D77" t="s">
-        <v>445</v>
-      </c>
       <c r="E77" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F77" t="s">
         <v>49</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>367</v>
@@ -7560,19 +7570,19 @@
         <v>22</v>
       </c>
       <c r="C78" t="s">
+        <v>445</v>
+      </c>
+      <c r="D78" t="s">
         <v>446</v>
       </c>
-      <c r="D78" t="s">
-        <v>447</v>
-      </c>
       <c r="E78" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F78" t="s">
         <v>49</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>367</v>
@@ -7601,19 +7611,19 @@
         <v>22</v>
       </c>
       <c r="C79" t="s">
+        <v>447</v>
+      </c>
+      <c r="D79" t="s">
         <v>448</v>
       </c>
-      <c r="D79" t="s">
-        <v>449</v>
-      </c>
       <c r="E79" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F79" t="s">
         <v>49</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>367</v>
@@ -7642,19 +7652,19 @@
         <v>22</v>
       </c>
       <c r="C80" t="s">
+        <v>449</v>
+      </c>
+      <c r="D80" t="s">
         <v>450</v>
       </c>
-      <c r="D80" t="s">
-        <v>451</v>
-      </c>
       <c r="E80" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F80" t="s">
         <v>49</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>367</v>
@@ -7683,19 +7693,19 @@
         <v>22</v>
       </c>
       <c r="C81" t="s">
+        <v>451</v>
+      </c>
+      <c r="D81" t="s">
         <v>452</v>
       </c>
-      <c r="D81" t="s">
-        <v>453</v>
-      </c>
       <c r="E81" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F81" t="s">
         <v>49</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>367</v>
@@ -7724,19 +7734,19 @@
         <v>22</v>
       </c>
       <c r="C82" t="s">
+        <v>453</v>
+      </c>
+      <c r="D82" t="s">
         <v>454</v>
       </c>
-      <c r="D82" t="s">
-        <v>455</v>
-      </c>
       <c r="E82" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F82" t="s">
         <v>49</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>367</v>
@@ -7765,19 +7775,19 @@
         <v>22</v>
       </c>
       <c r="C83" t="s">
+        <v>455</v>
+      </c>
+      <c r="D83" t="s">
         <v>456</v>
       </c>
-      <c r="D83" t="s">
-        <v>457</v>
-      </c>
       <c r="E83" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F83" t="s">
         <v>49</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>367</v>
@@ -7806,19 +7816,19 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
+        <v>457</v>
+      </c>
+      <c r="D84" t="s">
         <v>458</v>
       </c>
-      <c r="D84" t="s">
-        <v>459</v>
-      </c>
       <c r="E84" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F84" t="s">
         <v>49</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>367</v>
@@ -7847,19 +7857,19 @@
         <v>22</v>
       </c>
       <c r="C85" t="s">
+        <v>459</v>
+      </c>
+      <c r="D85" t="s">
         <v>460</v>
       </c>
-      <c r="D85" t="s">
-        <v>461</v>
-      </c>
       <c r="E85" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F85" t="s">
         <v>49</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>367</v>
@@ -7888,19 +7898,19 @@
         <v>22</v>
       </c>
       <c r="C86" t="s">
+        <v>461</v>
+      </c>
+      <c r="D86" t="s">
         <v>462</v>
       </c>
-      <c r="D86" t="s">
-        <v>463</v>
-      </c>
       <c r="E86" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F86" t="s">
         <v>49</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>367</v>
@@ -7929,19 +7939,19 @@
         <v>22</v>
       </c>
       <c r="C87" t="s">
+        <v>463</v>
+      </c>
+      <c r="D87" t="s">
         <v>464</v>
       </c>
-      <c r="D87" t="s">
-        <v>465</v>
-      </c>
       <c r="E87" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F87" t="s">
         <v>49</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>367</v>
@@ -7970,19 +7980,19 @@
         <v>22</v>
       </c>
       <c r="C88" t="s">
+        <v>465</v>
+      </c>
+      <c r="D88" t="s">
         <v>466</v>
       </c>
-      <c r="D88" t="s">
-        <v>467</v>
-      </c>
       <c r="E88" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F88" t="s">
         <v>49</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>367</v>
@@ -8011,19 +8021,19 @@
         <v>22</v>
       </c>
       <c r="C89" t="s">
+        <v>467</v>
+      </c>
+      <c r="D89" t="s">
         <v>468</v>
       </c>
-      <c r="D89" t="s">
-        <v>469</v>
-      </c>
       <c r="E89" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F89" t="s">
         <v>49</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>367</v>
@@ -8052,19 +8062,19 @@
         <v>22</v>
       </c>
       <c r="C90" t="s">
+        <v>469</v>
+      </c>
+      <c r="D90" t="s">
         <v>470</v>
       </c>
-      <c r="D90" t="s">
-        <v>471</v>
-      </c>
       <c r="E90" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F90" t="s">
         <v>49</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>367</v>
@@ -8093,19 +8103,19 @@
         <v>22</v>
       </c>
       <c r="C91" t="s">
+        <v>471</v>
+      </c>
+      <c r="D91" t="s">
         <v>472</v>
       </c>
-      <c r="D91" t="s">
-        <v>473</v>
-      </c>
       <c r="E91" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F91" t="s">
         <v>49</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>367</v>
@@ -8134,19 +8144,19 @@
         <v>22</v>
       </c>
       <c r="C92" t="s">
+        <v>473</v>
+      </c>
+      <c r="D92" t="s">
         <v>474</v>
       </c>
-      <c r="D92" t="s">
-        <v>475</v>
-      </c>
       <c r="E92" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F92" t="s">
         <v>49</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>367</v>
@@ -8175,19 +8185,19 @@
         <v>22</v>
       </c>
       <c r="C93" t="s">
+        <v>475</v>
+      </c>
+      <c r="D93" t="s">
         <v>476</v>
       </c>
-      <c r="D93" t="s">
-        <v>477</v>
-      </c>
       <c r="E93" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F93" t="s">
         <v>49</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>367</v>
@@ -8216,34 +8226,34 @@
         <v>22</v>
       </c>
       <c r="C94" t="s">
+        <v>477</v>
+      </c>
+      <c r="D94" t="s">
         <v>478</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>478</v>
+      </c>
+      <c r="F94" t="s">
+        <v>49</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="E94" t="s">
-        <v>479</v>
-      </c>
-      <c r="F94" t="s">
-        <v>49</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K94" t="s">
-        <v>481</v>
+        <v>761</v>
       </c>
       <c r="L94" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M94" t="s">
         <v>384</v>
       </c>
       <c r="N94" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="P94" s="1" t="s">
         <v>78</v>
@@ -8275,34 +8285,34 @@
         <v>22</v>
       </c>
       <c r="C95" t="s">
+        <v>482</v>
+      </c>
+      <c r="D95" t="s">
+        <v>483</v>
+      </c>
+      <c r="E95" t="s">
         <v>484</v>
       </c>
-      <c r="D95" t="s">
+      <c r="F95" t="s">
+        <v>49</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="E95" t="s">
-        <v>486</v>
-      </c>
-      <c r="F95" t="s">
-        <v>49</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K95" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="L95" t="s">
+        <v>486</v>
+      </c>
+      <c r="M95" t="s">
+        <v>487</v>
+      </c>
+      <c r="N95" t="s">
         <v>488</v>
-      </c>
-      <c r="M95" t="s">
-        <v>489</v>
-      </c>
-      <c r="N95" t="s">
-        <v>490</v>
       </c>
       <c r="P95" s="1" t="s">
         <v>78</v>
@@ -8334,34 +8344,34 @@
         <v>22</v>
       </c>
       <c r="C96" t="s">
+        <v>489</v>
+      </c>
+      <c r="D96" t="s">
+        <v>490</v>
+      </c>
+      <c r="E96" t="s">
         <v>491</v>
       </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
+        <v>49</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E96" t="s">
+      <c r="J96" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F96" t="s">
-        <v>49</v>
-      </c>
-      <c r="I96" s="1" t="s">
+      <c r="K96" t="s">
+        <v>633</v>
+      </c>
+      <c r="L96" t="s">
         <v>494</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="M96" t="s">
         <v>495</v>
       </c>
-      <c r="K96" t="s">
-        <v>639</v>
-      </c>
-      <c r="L96" t="s">
+      <c r="N96" t="s">
         <v>496</v>
-      </c>
-      <c r="M96" t="s">
-        <v>497</v>
-      </c>
-      <c r="N96" t="s">
-        <v>498</v>
       </c>
       <c r="P96" s="1" t="s">
         <v>78</v>
@@ -8393,34 +8403,34 @@
         <v>22</v>
       </c>
       <c r="C97" t="s">
+        <v>497</v>
+      </c>
+      <c r="D97" t="s">
+        <v>498</v>
+      </c>
+      <c r="E97" t="s">
+        <v>498</v>
+      </c>
+      <c r="F97" t="s">
+        <v>49</v>
+      </c>
+      <c r="I97" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="D97" t="s">
-        <v>500</v>
-      </c>
-      <c r="E97" t="s">
-        <v>500</v>
-      </c>
-      <c r="F97" t="s">
-        <v>49</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="L97" t="s">
+        <v>500</v>
+      </c>
+      <c r="M97" t="s">
+        <v>501</v>
+      </c>
+      <c r="N97" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M97" t="s">
-        <v>503</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P97" s="1" t="s">
         <v>78</v>
@@ -8429,7 +8439,7 @@
         <v>33</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U97" t="s">
         <v>35</v>
@@ -8441,7 +8451,7 @@
         <v>352</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>641</v>
+        <v>754</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8452,34 +8462,34 @@
         <v>22</v>
       </c>
       <c r="C98" t="s">
+        <v>504</v>
+      </c>
+      <c r="D98" t="s">
+        <v>505</v>
+      </c>
+      <c r="E98" t="s">
+        <v>505</v>
+      </c>
+      <c r="F98" t="s">
+        <v>49</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="D98" t="s">
-        <v>507</v>
-      </c>
-      <c r="E98" t="s">
-        <v>507</v>
-      </c>
-      <c r="F98" t="s">
-        <v>49</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="L98" t="s">
+        <v>500</v>
+      </c>
+      <c r="M98" t="s">
+        <v>501</v>
+      </c>
+      <c r="N98" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M98" t="s">
-        <v>503</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P98" s="1" t="s">
         <v>78</v>
@@ -8488,7 +8498,7 @@
         <v>33</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U98" t="s">
         <v>35</v>
@@ -8500,7 +8510,7 @@
         <v>352</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>642</v>
+        <v>755</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8511,34 +8521,34 @@
         <v>22</v>
       </c>
       <c r="C99" t="s">
+        <v>507</v>
+      </c>
+      <c r="D99" t="s">
+        <v>508</v>
+      </c>
+      <c r="E99" t="s">
+        <v>508</v>
+      </c>
+      <c r="F99" t="s">
+        <v>49</v>
+      </c>
+      <c r="I99" t="s">
         <v>509</v>
-      </c>
-      <c r="D99" t="s">
-        <v>510</v>
-      </c>
-      <c r="E99" t="s">
-        <v>510</v>
-      </c>
-      <c r="F99" t="s">
-        <v>49</v>
-      </c>
-      <c r="I99" t="s">
-        <v>511</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="L99" t="s">
+        <v>500</v>
+      </c>
+      <c r="M99" t="s">
+        <v>501</v>
+      </c>
+      <c r="N99" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M99" t="s">
-        <v>503</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>78</v>
@@ -8547,7 +8557,7 @@
         <v>33</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U99" t="s">
         <v>35</v>
@@ -8559,7 +8569,7 @@
         <v>352</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>643</v>
+        <v>756</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.25">
@@ -8570,19 +8580,19 @@
         <v>22</v>
       </c>
       <c r="C100" t="s">
+        <v>510</v>
+      </c>
+      <c r="D100" t="s">
+        <v>511</v>
+      </c>
+      <c r="E100" t="s">
+        <v>511</v>
+      </c>
+      <c r="F100" t="s">
+        <v>49</v>
+      </c>
+      <c r="I100" t="s">
         <v>512</v>
-      </c>
-      <c r="D100" t="s">
-        <v>513</v>
-      </c>
-      <c r="E100" t="s">
-        <v>513</v>
-      </c>
-      <c r="F100" t="s">
-        <v>49</v>
-      </c>
-      <c r="I100" t="s">
-        <v>514</v>
       </c>
       <c r="K100" t="s">
         <v>41</v>
@@ -8608,19 +8618,19 @@
         <v>22</v>
       </c>
       <c r="C101" t="s">
+        <v>513</v>
+      </c>
+      <c r="D101" t="s">
+        <v>514</v>
+      </c>
+      <c r="E101" t="s">
+        <v>514</v>
+      </c>
+      <c r="F101" t="s">
+        <v>49</v>
+      </c>
+      <c r="I101" t="s">
         <v>515</v>
-      </c>
-      <c r="D101" t="s">
-        <v>516</v>
-      </c>
-      <c r="E101" t="s">
-        <v>516</v>
-      </c>
-      <c r="F101" t="s">
-        <v>49</v>
-      </c>
-      <c r="I101" t="s">
-        <v>517</v>
       </c>
       <c r="K101" t="s">
         <v>41</v>
@@ -8646,19 +8656,19 @@
         <v>22</v>
       </c>
       <c r="C102" t="s">
+        <v>516</v>
+      </c>
+      <c r="D102" t="s">
+        <v>517</v>
+      </c>
+      <c r="E102" t="s">
+        <v>517</v>
+      </c>
+      <c r="F102" t="s">
+        <v>49</v>
+      </c>
+      <c r="I102" t="s">
         <v>518</v>
-      </c>
-      <c r="D102" t="s">
-        <v>519</v>
-      </c>
-      <c r="E102" t="s">
-        <v>519</v>
-      </c>
-      <c r="F102" t="s">
-        <v>49</v>
-      </c>
-      <c r="I102" t="s">
-        <v>520</v>
       </c>
       <c r="K102" t="s">
         <v>41</v>
@@ -8684,19 +8694,19 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
+        <v>519</v>
+      </c>
+      <c r="D103" t="s">
+        <v>520</v>
+      </c>
+      <c r="E103" t="s">
+        <v>520</v>
+      </c>
+      <c r="F103" t="s">
+        <v>49</v>
+      </c>
+      <c r="I103" t="s">
         <v>521</v>
-      </c>
-      <c r="D103" t="s">
-        <v>522</v>
-      </c>
-      <c r="E103" t="s">
-        <v>522</v>
-      </c>
-      <c r="F103" t="s">
-        <v>49</v>
-      </c>
-      <c r="I103" t="s">
-        <v>523</v>
       </c>
       <c r="K103" t="s">
         <v>41</v>
@@ -8722,19 +8732,19 @@
         <v>22</v>
       </c>
       <c r="C104" t="s">
+        <v>522</v>
+      </c>
+      <c r="D104" t="s">
+        <v>523</v>
+      </c>
+      <c r="E104" t="s">
+        <v>523</v>
+      </c>
+      <c r="F104" t="s">
+        <v>49</v>
+      </c>
+      <c r="I104" t="s">
         <v>524</v>
-      </c>
-      <c r="D104" t="s">
-        <v>525</v>
-      </c>
-      <c r="E104" t="s">
-        <v>525</v>
-      </c>
-      <c r="F104" t="s">
-        <v>49</v>
-      </c>
-      <c r="I104" t="s">
-        <v>526</v>
       </c>
       <c r="K104" t="s">
         <v>41</v>
@@ -8760,31 +8770,31 @@
         <v>22</v>
       </c>
       <c r="C105" t="s">
+        <v>525</v>
+      </c>
+      <c r="D105" t="s">
+        <v>526</v>
+      </c>
+      <c r="E105" t="s">
+        <v>526</v>
+      </c>
+      <c r="F105" t="s">
+        <v>49</v>
+      </c>
+      <c r="I105" t="s">
+        <v>515</v>
+      </c>
+      <c r="K105" t="s">
+        <v>635</v>
+      </c>
+      <c r="L105" t="s">
         <v>527</v>
       </c>
-      <c r="D105" t="s">
+      <c r="M105" t="s">
         <v>528</v>
       </c>
-      <c r="E105" t="s">
-        <v>528</v>
-      </c>
-      <c r="F105" t="s">
-        <v>49</v>
-      </c>
-      <c r="I105" t="s">
-        <v>517</v>
-      </c>
-      <c r="K105" t="s">
-        <v>644</v>
-      </c>
-      <c r="L105" t="s">
+      <c r="N105" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="M105" t="s">
-        <v>530</v>
-      </c>
-      <c r="N105" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="P105" s="1" t="s">
         <v>78</v>
@@ -8793,7 +8803,7 @@
         <v>79</v>
       </c>
       <c r="R105" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="U105" t="s">
         <v>35</v>
@@ -8816,19 +8826,19 @@
         <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D106" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E106" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F106" t="s">
         <v>49</v>
       </c>
       <c r="I106" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K106" t="s">
         <v>41</v>
@@ -8854,28 +8864,28 @@
         <v>22</v>
       </c>
       <c r="C107" t="s">
+        <v>533</v>
+      </c>
+      <c r="D107" t="s">
+        <v>534</v>
+      </c>
+      <c r="E107" t="s">
         <v>535</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
+        <v>49</v>
+      </c>
+      <c r="I107" t="s">
         <v>536</v>
       </c>
-      <c r="E107" t="s">
+      <c r="J107" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="F107" t="s">
-        <v>49</v>
-      </c>
-      <c r="I107" t="s">
-        <v>538</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="K107" t="s">
         <v>41</v>
       </c>
       <c r="T107" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="U107" t="s">
         <v>86</v>
@@ -8898,22 +8908,22 @@
         <v>22</v>
       </c>
       <c r="C108" t="s">
+        <v>539</v>
+      </c>
+      <c r="D108" t="s">
+        <v>540</v>
+      </c>
+      <c r="E108" t="s">
         <v>541</v>
       </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
+        <v>49</v>
+      </c>
+      <c r="I108" t="s">
+        <v>536</v>
+      </c>
+      <c r="J108" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="E108" t="s">
-        <v>543</v>
-      </c>
-      <c r="F108" t="s">
-        <v>49</v>
-      </c>
-      <c r="I108" t="s">
-        <v>538</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="K108" t="s">
         <v>41</v>
@@ -8939,22 +8949,22 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
+        <v>543</v>
+      </c>
+      <c r="D109" t="s">
+        <v>544</v>
+      </c>
+      <c r="E109" t="s">
         <v>545</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
+        <v>49</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E109" t="s">
+      <c r="J109" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="F109" t="s">
-        <v>49</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="K109" t="s">
         <v>41</v>
@@ -8980,34 +8990,34 @@
         <v>22</v>
       </c>
       <c r="C110" t="s">
+        <v>548</v>
+      </c>
+      <c r="D110" t="s">
+        <v>549</v>
+      </c>
+      <c r="E110" t="s">
         <v>550</v>
       </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
+        <v>49</v>
+      </c>
+      <c r="I110" t="s">
         <v>551</v>
       </c>
-      <c r="E110" t="s">
+      <c r="J110" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="K110" t="s">
+        <v>636</v>
+      </c>
+      <c r="L110" t="s">
         <v>552</v>
       </c>
-      <c r="F110" t="s">
-        <v>49</v>
-      </c>
-      <c r="I110" t="s">
+      <c r="M110" t="s">
         <v>553</v>
       </c>
-      <c r="J110" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K110" t="s">
-        <v>645</v>
-      </c>
-      <c r="L110" t="s">
+      <c r="N110" t="s">
         <v>554</v>
-      </c>
-      <c r="M110" t="s">
-        <v>555</v>
-      </c>
-      <c r="N110" t="s">
-        <v>556</v>
       </c>
       <c r="P110" s="1" t="s">
         <v>78</v>
@@ -9016,7 +9026,7 @@
         <v>33</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="U110" t="s">
         <v>35</v>
@@ -9028,7 +9038,7 @@
         <v>68</v>
       </c>
       <c r="X110" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9039,34 +9049,34 @@
         <v>22</v>
       </c>
       <c r="C111" t="s">
+        <v>557</v>
+      </c>
+      <c r="D111" t="s">
+        <v>558</v>
+      </c>
+      <c r="E111" t="s">
         <v>559</v>
       </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
+        <v>49</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E111" t="s">
+      <c r="J111" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="K111" t="s">
+        <v>637</v>
+      </c>
+      <c r="L111" t="s">
         <v>561</v>
       </c>
-      <c r="F111" t="s">
-        <v>49</v>
-      </c>
-      <c r="I111" s="1" t="s">
+      <c r="M111" t="s">
         <v>562</v>
       </c>
-      <c r="J111" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K111" t="s">
-        <v>646</v>
-      </c>
-      <c r="L111" t="s">
+      <c r="N111" t="s">
         <v>563</v>
-      </c>
-      <c r="M111" t="s">
-        <v>564</v>
-      </c>
-      <c r="N111" t="s">
-        <v>565</v>
       </c>
       <c r="P111" s="1" t="s">
         <v>78</v>
@@ -9075,10 +9085,10 @@
         <v>33</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="T111" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="U111" t="s">
         <v>35</v>
@@ -9090,7 +9100,7 @@
         <v>68</v>
       </c>
       <c r="X111" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9101,19 +9111,19 @@
         <v>22</v>
       </c>
       <c r="C112" t="s">
+        <v>567</v>
+      </c>
+      <c r="D112" t="s">
+        <v>568</v>
+      </c>
+      <c r="E112" t="s">
         <v>569</v>
-      </c>
-      <c r="D112" t="s">
-        <v>570</v>
-      </c>
-      <c r="E112" t="s">
-        <v>571</v>
       </c>
       <c r="F112" t="s">
         <v>112</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="U112" t="s">
         <v>35</v>
@@ -9125,10 +9135,10 @@
         <v>59</v>
       </c>
       <c r="X112" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="113" spans="1:24" ht="285" x14ac:dyDescent="0.25">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" ht="270" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -9136,22 +9146,22 @@
         <v>22</v>
       </c>
       <c r="C113" t="s">
+        <v>570</v>
+      </c>
+      <c r="D113" t="s">
+        <v>571</v>
+      </c>
+      <c r="E113" t="s">
         <v>572</v>
       </c>
-      <c r="D113" t="s">
+      <c r="F113" t="s">
+        <v>49</v>
+      </c>
+      <c r="G113" t="s">
         <v>573</v>
       </c>
-      <c r="E113" t="s">
-        <v>574</v>
-      </c>
-      <c r="F113" t="s">
-        <v>49</v>
-      </c>
-      <c r="G113" t="s">
-        <v>575</v>
-      </c>
       <c r="K113" s="1" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="U113" t="s">
         <v>35</v>
@@ -9163,7 +9173,7 @@
         <v>59</v>
       </c>
       <c r="X113" s="1" t="s">
-        <v>649</v>
+        <v>763</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.25">
@@ -9171,7 +9181,7 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C114" t="s">
         <v>23</v>
@@ -9192,10 +9202,10 @@
         <v>28</v>
       </c>
       <c r="L114" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M114" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="U114" t="s">
         <v>35</v>
@@ -9215,7 +9225,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C115" t="s">
         <v>38</v>
@@ -9245,7 +9255,7 @@
         <v>43</v>
       </c>
       <c r="X115" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.25">
@@ -9253,7 +9263,7 @@
         <v>3</v>
       </c>
       <c r="B116" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C116" t="s">
         <v>44</v>
@@ -9283,7 +9293,7 @@
         <v>43</v>
       </c>
       <c r="X116" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.25">
@@ -9291,7 +9301,7 @@
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C117" t="s">
         <v>47</v>
@@ -9329,7 +9339,7 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C118" t="s">
         <v>51</v>
@@ -9350,7 +9360,7 @@
         <v>56</v>
       </c>
       <c r="K118" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="L118" t="s">
         <v>57</v>
@@ -9371,7 +9381,7 @@
         <v>59</v>
       </c>
       <c r="X118" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
     </row>
     <row r="119" spans="1:24" ht="45" x14ac:dyDescent="0.25">
@@ -9379,7 +9389,7 @@
         <v>6</v>
       </c>
       <c r="B119" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C119" t="s">
         <v>60</v>
@@ -9426,7 +9436,7 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C120" t="s">
         <v>70</v>
@@ -9447,7 +9457,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="L120" t="s">
         <v>75</v>
@@ -9485,7 +9495,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C121" t="s">
         <v>81</v>
@@ -9526,7 +9536,7 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C122" t="s">
         <v>88</v>
@@ -9567,7 +9577,7 @@
         <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C123" t="s">
         <v>92</v>
@@ -9588,7 +9598,7 @@
         <v>96</v>
       </c>
       <c r="K123" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="L123" t="s">
         <v>97</v>
@@ -9629,7 +9639,7 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C124" t="s">
         <v>103</v>
@@ -9650,7 +9660,7 @@
         <v>107</v>
       </c>
       <c r="K124" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="L124" t="s">
         <v>97</v>
@@ -9691,7 +9701,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C125" t="s">
         <v>110</v>
@@ -9729,7 +9739,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C126" t="s">
         <v>114</v>
@@ -9764,7 +9774,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C127" t="s">
         <v>117</v>
@@ -9785,7 +9795,7 @@
         <v>121</v>
       </c>
       <c r="K127" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="L127" t="s">
         <v>97</v>
@@ -9826,7 +9836,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C128" t="s">
         <v>123</v>
@@ -9844,7 +9854,7 @@
         <v>125</v>
       </c>
       <c r="K128" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="L128" t="s">
         <v>126</v>
@@ -9882,7 +9892,7 @@
         <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C129" t="s">
         <v>131</v>
@@ -9923,7 +9933,7 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C130" t="s">
         <v>136</v>
@@ -9944,7 +9954,7 @@
         <v>139</v>
       </c>
       <c r="K130" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="L130" t="s">
         <v>140</v>
@@ -9985,7 +9995,7 @@
         <v>18</v>
       </c>
       <c r="B131" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C131" t="s">
         <v>144</v>
@@ -10003,7 +10013,7 @@
         <v>146</v>
       </c>
       <c r="K131" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="U131" t="s">
         <v>35</v>
@@ -10015,7 +10025,7 @@
         <v>59</v>
       </c>
       <c r="X131" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="132" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -10023,7 +10033,7 @@
         <v>19</v>
       </c>
       <c r="B132" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C132" t="s">
         <v>147</v>
@@ -10044,7 +10054,7 @@
         <v>139</v>
       </c>
       <c r="K132" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="L132" t="s">
         <v>150</v>
@@ -10085,7 +10095,7 @@
         <v>20</v>
       </c>
       <c r="B133" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C133" t="s">
         <v>153</v>
@@ -10103,7 +10113,7 @@
         <v>146</v>
       </c>
       <c r="K133" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="U133" t="s">
         <v>35</v>
@@ -10115,7 +10125,7 @@
         <v>59</v>
       </c>
       <c r="X133" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
     </row>
     <row r="134" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -10123,7 +10133,7 @@
         <v>21</v>
       </c>
       <c r="B134" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C134" t="s">
         <v>155</v>
@@ -10144,7 +10154,7 @@
         <v>158</v>
       </c>
       <c r="K134" t="s">
-        <v>579</v>
+        <v>768</v>
       </c>
       <c r="L134" t="s">
         <v>159</v>
@@ -10185,7 +10195,7 @@
         <v>22</v>
       </c>
       <c r="B135" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C135" t="s">
         <v>162</v>
@@ -10206,7 +10216,7 @@
         <v>139</v>
       </c>
       <c r="K135" t="s">
-        <v>766</v>
+        <v>749</v>
       </c>
       <c r="L135" t="s">
         <v>164</v>
@@ -10227,7 +10237,7 @@
         <v>143</v>
       </c>
       <c r="T135" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="U135" t="s">
         <v>35</v>
@@ -10247,7 +10257,7 @@
         <v>23</v>
       </c>
       <c r="B136" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C136" t="s">
         <v>169</v>
@@ -10265,7 +10275,7 @@
         <v>146</v>
       </c>
       <c r="K136" t="s">
-        <v>766</v>
+        <v>749</v>
       </c>
       <c r="L136" t="s">
         <v>164</v>
@@ -10295,7 +10305,7 @@
         <v>59</v>
       </c>
       <c r="X136" t="s">
-        <v>767</v>
+        <v>750</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.25">
@@ -10303,7 +10313,7 @@
         <v>24</v>
       </c>
       <c r="B137" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C137" t="s">
         <v>171</v>
@@ -10321,7 +10331,7 @@
         <v>173</v>
       </c>
       <c r="K137" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="L137" t="s">
         <v>174</v>
@@ -10351,7 +10361,7 @@
         <v>59</v>
       </c>
       <c r="X137" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.25">
@@ -10359,7 +10369,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C138" t="s">
         <v>178</v>
@@ -10374,7 +10384,7 @@
         <v>26</v>
       </c>
       <c r="K138" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="U138" t="s">
         <v>35</v>
@@ -10386,7 +10396,7 @@
         <v>59</v>
       </c>
       <c r="X138" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
     </row>
     <row r="139" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -10394,7 +10404,7 @@
         <v>26</v>
       </c>
       <c r="B139" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C139" t="s">
         <v>180</v>
@@ -10415,7 +10425,7 @@
         <v>184</v>
       </c>
       <c r="K139" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="L139" t="s">
         <v>185</v>
@@ -10433,7 +10443,7 @@
         <v>183</v>
       </c>
       <c r="T139" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="U139" t="s">
         <v>35</v>
@@ -10445,7 +10455,7 @@
         <v>59</v>
       </c>
       <c r="X139" t="s">
-        <v>582</v>
+        <v>769</v>
       </c>
     </row>
     <row r="140" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -10453,7 +10463,7 @@
         <v>27</v>
       </c>
       <c r="B140" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C140" t="s">
         <v>188</v>
@@ -10474,7 +10484,7 @@
         <v>184</v>
       </c>
       <c r="K140" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="L140" t="s">
         <v>191</v>
@@ -10492,7 +10502,7 @@
         <v>183</v>
       </c>
       <c r="T140" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="U140" t="s">
         <v>35</v>
@@ -10504,7 +10514,7 @@
         <v>59</v>
       </c>
       <c r="X140" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.25">
@@ -10512,7 +10522,7 @@
         <v>28</v>
       </c>
       <c r="B141" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C141" t="s">
         <v>193</v>
@@ -10553,7 +10563,7 @@
         <v>29</v>
       </c>
       <c r="B142" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C142" t="s">
         <v>196</v>
@@ -10594,7 +10604,7 @@
         <v>30</v>
       </c>
       <c r="B143" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C143" t="s">
         <v>200</v>
@@ -10632,7 +10642,7 @@
         <v>31</v>
       </c>
       <c r="B144" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C144" t="s">
         <v>203</v>
@@ -10670,7 +10680,7 @@
         <v>32</v>
       </c>
       <c r="B145" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C145" t="s">
         <v>206</v>
@@ -10708,7 +10718,7 @@
         <v>33</v>
       </c>
       <c r="B146" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C146" t="s">
         <v>209</v>
@@ -10726,7 +10736,7 @@
         <v>211</v>
       </c>
       <c r="K146" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="L146" t="s">
         <v>210</v>
@@ -10755,7 +10765,7 @@
         <v>34</v>
       </c>
       <c r="B147" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C147" t="s">
         <v>214</v>
@@ -10773,7 +10783,7 @@
         <v>211</v>
       </c>
       <c r="K147" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="L147" t="s">
         <v>215</v>
@@ -10802,7 +10812,7 @@
         <v>35</v>
       </c>
       <c r="B148" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C148" t="s">
         <v>218</v>
@@ -10820,7 +10830,7 @@
         <v>211</v>
       </c>
       <c r="K148" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="L148" t="s">
         <v>219</v>
@@ -10849,7 +10859,7 @@
         <v>36</v>
       </c>
       <c r="B149" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C149" t="s">
         <v>222</v>
@@ -10870,7 +10880,7 @@
         <v>224</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="L149" s="1" t="s">
         <v>225</v>
@@ -10885,7 +10895,7 @@
         <v>59</v>
       </c>
       <c r="X149" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.25">
@@ -10893,7 +10903,7 @@
         <v>37</v>
       </c>
       <c r="B150" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C150" t="s">
         <v>226</v>
@@ -10911,7 +10921,7 @@
         <v>211</v>
       </c>
       <c r="K150" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="L150" t="s">
         <v>227</v>
@@ -10940,7 +10950,7 @@
         <v>38</v>
       </c>
       <c r="B151" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C151" t="s">
         <v>230</v>
@@ -10958,7 +10968,7 @@
         <v>232</v>
       </c>
       <c r="K151" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="L151" t="s">
         <v>231</v>
@@ -10987,7 +10997,7 @@
         <v>39</v>
       </c>
       <c r="B152" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C152" t="s">
         <v>235</v>
@@ -11028,7 +11038,7 @@
         <v>40</v>
       </c>
       <c r="B153" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C153" t="s">
         <v>240</v>
@@ -11069,7 +11079,7 @@
         <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C154" t="s">
         <v>245</v>
@@ -11110,7 +11120,7 @@
         <v>42</v>
       </c>
       <c r="B155" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C155" t="s">
         <v>248</v>
@@ -11131,7 +11141,7 @@
         <v>244</v>
       </c>
       <c r="K155" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="L155" t="s">
         <v>252</v>
@@ -11166,7 +11176,7 @@
         <v>43</v>
       </c>
       <c r="B156" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C156" t="s">
         <v>257</v>
@@ -11204,7 +11214,7 @@
         <v>44</v>
       </c>
       <c r="B157" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C157" t="s">
         <v>260</v>
@@ -11225,7 +11235,7 @@
         <v>263</v>
       </c>
       <c r="K157" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="L157" t="s">
         <v>264</v>
@@ -11257,7 +11267,7 @@
         <v>45</v>
       </c>
       <c r="B158" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C158" t="s">
         <v>267</v>
@@ -11295,7 +11305,7 @@
         <v>46</v>
       </c>
       <c r="B159" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C159" t="s">
         <v>270</v>
@@ -11316,7 +11326,7 @@
         <v>273</v>
       </c>
       <c r="K159" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="L159" t="s">
         <v>274</v>
@@ -11354,7 +11364,7 @@
         <v>47</v>
       </c>
       <c r="B160" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C160" t="s">
         <v>279</v>
@@ -11413,7 +11423,7 @@
         <v>48</v>
       </c>
       <c r="B161" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C161" t="s">
         <v>283</v>
@@ -11454,7 +11464,7 @@
         <v>49</v>
       </c>
       <c r="B162" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C162" t="s">
         <v>287</v>
@@ -11472,7 +11482,7 @@
         <v>113</v>
       </c>
       <c r="K162" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="L162" t="s">
         <v>289</v>
@@ -11513,7 +11523,7 @@
         <v>50</v>
       </c>
       <c r="B163" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C163" t="s">
         <v>296</v>
@@ -11534,7 +11544,7 @@
         <v>299</v>
       </c>
       <c r="K163" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="L163" t="s">
         <v>289</v>
@@ -11572,7 +11582,7 @@
         <v>51</v>
       </c>
       <c r="B164" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C164" t="s">
         <v>301</v>
@@ -11593,7 +11603,7 @@
         <v>304</v>
       </c>
       <c r="K164" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="L164" t="s">
         <v>305</v>
@@ -11631,7 +11641,7 @@
         <v>52</v>
       </c>
       <c r="B165" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C165" t="s">
         <v>310</v>
@@ -11672,7 +11682,7 @@
         <v>53</v>
       </c>
       <c r="B166" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C166" t="s">
         <v>314</v>
@@ -11690,7 +11700,7 @@
         <v>313</v>
       </c>
       <c r="K166" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="L166" t="s">
         <v>316</v>
@@ -11711,7 +11721,7 @@
         <v>320</v>
       </c>
       <c r="T166" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="U166" t="s">
         <v>35</v>
@@ -11731,7 +11741,7 @@
         <v>54</v>
       </c>
       <c r="B167" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C167" t="s">
         <v>323</v>
@@ -11769,7 +11779,7 @@
         <v>55</v>
       </c>
       <c r="B168" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C168" t="s">
         <v>325</v>
@@ -11787,7 +11797,7 @@
         <v>328</v>
       </c>
       <c r="K168" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="L168" t="s">
         <v>329</v>
@@ -11808,7 +11818,7 @@
         <v>320</v>
       </c>
       <c r="T168" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="U168" t="s">
         <v>35</v>
@@ -11820,7 +11830,7 @@
         <v>59</v>
       </c>
       <c r="X168" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
     </row>
     <row r="169" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -11828,7 +11838,7 @@
         <v>56</v>
       </c>
       <c r="B169" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C169" t="s">
         <v>333</v>
@@ -11869,7 +11879,7 @@
         <v>57</v>
       </c>
       <c r="B170" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C170" t="s">
         <v>337</v>
@@ -11910,7 +11920,7 @@
         <v>58</v>
       </c>
       <c r="B171" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C171" t="s">
         <v>340</v>
@@ -11931,7 +11941,7 @@
         <v>312</v>
       </c>
       <c r="K171" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="L171" s="1" t="s">
         <v>343</v>
@@ -11961,7 +11971,7 @@
         <v>59</v>
       </c>
       <c r="X171" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
     </row>
     <row r="172" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -11969,7 +11979,7 @@
         <v>59</v>
       </c>
       <c r="B172" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C172" t="s">
         <v>347</v>
@@ -11987,7 +11997,7 @@
         <v>350</v>
       </c>
       <c r="K172" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="L172" s="1" t="s">
         <v>343</v>
@@ -12017,7 +12027,7 @@
         <v>352</v>
       </c>
       <c r="X172" s="1" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
     </row>
     <row r="173" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -12025,7 +12035,7 @@
         <v>60</v>
       </c>
       <c r="B173" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C173" t="s">
         <v>353</v>
@@ -12046,7 +12056,7 @@
         <v>356</v>
       </c>
       <c r="K173" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="L173" t="s">
         <v>358</v>
@@ -12087,7 +12097,7 @@
         <v>61</v>
       </c>
       <c r="B174" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C174" t="s">
         <v>363</v>
@@ -12108,7 +12118,7 @@
         <v>367</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="L174" t="s">
         <v>368</v>
@@ -12141,7 +12151,7 @@
         <v>352</v>
       </c>
       <c r="X174" s="1" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
     </row>
     <row r="175" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -12149,7 +12159,7 @@
         <v>62</v>
       </c>
       <c r="B175" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C175" t="s">
         <v>374</v>
@@ -12170,7 +12180,7 @@
         <v>367</v>
       </c>
       <c r="K175" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="L175" t="s">
         <v>377</v>
@@ -12211,7 +12221,7 @@
         <v>63</v>
       </c>
       <c r="B176" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C176" t="s">
         <v>381</v>
@@ -12232,7 +12242,7 @@
         <v>367</v>
       </c>
       <c r="K176" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="L176" t="s">
         <v>377</v>
@@ -12270,7 +12280,7 @@
         <v>64</v>
       </c>
       <c r="B177" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C177" t="s">
         <v>386</v>
@@ -12291,7 +12301,7 @@
         <v>367</v>
       </c>
       <c r="K177" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="L177" t="s">
         <v>389</v>
@@ -12329,7 +12339,7 @@
         <v>65</v>
       </c>
       <c r="B178" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C178" t="s">
         <v>391</v>
@@ -12350,7 +12360,7 @@
         <v>367</v>
       </c>
       <c r="K178" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="L178" t="s">
         <v>394</v>
@@ -12388,7 +12398,7 @@
         <v>66</v>
       </c>
       <c r="B179" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C179" t="s">
         <v>396</v>
@@ -12409,7 +12419,7 @@
         <v>367</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="L179" t="s">
         <v>368</v>
@@ -12447,7 +12457,7 @@
         <v>67</v>
       </c>
       <c r="B180" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C180" t="s">
         <v>400</v>
@@ -12488,7 +12498,7 @@
         <v>68</v>
       </c>
       <c r="B181" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C181" t="s">
         <v>403</v>
@@ -12509,7 +12519,7 @@
         <v>367</v>
       </c>
       <c r="K181" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="L181" t="s">
         <v>406</v>
@@ -12547,7 +12557,7 @@
         <v>69</v>
       </c>
       <c r="B182" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C182" t="s">
         <v>408</v>
@@ -12568,7 +12578,7 @@
         <v>367</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="U182" t="s">
         <v>35</v>
@@ -12580,7 +12590,7 @@
         <v>352</v>
       </c>
       <c r="X182" s="1" t="s">
-        <v>691</v>
+        <v>757</v>
       </c>
     </row>
     <row r="183" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -12588,7 +12598,7 @@
         <v>70</v>
       </c>
       <c r="B183" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C183" t="s">
         <v>411</v>
@@ -12609,7 +12619,7 @@
         <v>367</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="L183" s="1" t="s">
         <v>415</v>
@@ -12642,7 +12652,7 @@
         <v>352</v>
       </c>
       <c r="X183" s="1" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
     </row>
     <row r="184" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -12650,7 +12660,7 @@
         <v>71</v>
       </c>
       <c r="B184" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C184" t="s">
         <v>420</v>
@@ -12671,7 +12681,7 @@
         <v>367</v>
       </c>
       <c r="K184" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="L184" t="s">
         <v>425</v>
@@ -12712,7 +12722,7 @@
         <v>72</v>
       </c>
       <c r="B185" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C185" t="s">
         <v>429</v>
@@ -12733,7 +12743,7 @@
         <v>432</v>
       </c>
       <c r="K185" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="L185" t="s">
         <v>425</v>
@@ -12774,7 +12784,7 @@
         <v>73</v>
       </c>
       <c r="B186" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C186" t="s">
         <v>433</v>
@@ -12795,16 +12805,16 @@
         <v>367</v>
       </c>
       <c r="K186" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="L186" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M186" t="s">
         <v>384</v>
       </c>
       <c r="N186" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P186" s="1" t="s">
         <v>78</v>
@@ -12833,22 +12843,22 @@
         <v>74</v>
       </c>
       <c r="B187" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C187" t="s">
+        <v>438</v>
+      </c>
+      <c r="D187" t="s">
         <v>439</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
+        <v>439</v>
+      </c>
+      <c r="F187" t="s">
+        <v>49</v>
+      </c>
+      <c r="I187" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="E187" t="s">
-        <v>440</v>
-      </c>
-      <c r="F187" t="s">
-        <v>49</v>
-      </c>
-      <c r="I187" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="J187" s="1" t="s">
         <v>367</v>
@@ -12874,22 +12884,22 @@
         <v>75</v>
       </c>
       <c r="B188" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C188" t="s">
+        <v>441</v>
+      </c>
+      <c r="D188" t="s">
         <v>442</v>
       </c>
-      <c r="D188" t="s">
-        <v>443</v>
-      </c>
       <c r="E188" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F188" t="s">
         <v>49</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J188" s="1" t="s">
         <v>367</v>
@@ -12915,22 +12925,22 @@
         <v>76</v>
       </c>
       <c r="B189" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C189" t="s">
+        <v>443</v>
+      </c>
+      <c r="D189" t="s">
         <v>444</v>
       </c>
-      <c r="D189" t="s">
-        <v>445</v>
-      </c>
       <c r="E189" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F189" t="s">
         <v>49</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J189" s="1" t="s">
         <v>367</v>
@@ -12956,22 +12966,22 @@
         <v>77</v>
       </c>
       <c r="B190" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C190" t="s">
+        <v>445</v>
+      </c>
+      <c r="D190" t="s">
         <v>446</v>
       </c>
-      <c r="D190" t="s">
-        <v>447</v>
-      </c>
       <c r="E190" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F190" t="s">
         <v>49</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>367</v>
@@ -12997,22 +13007,22 @@
         <v>78</v>
       </c>
       <c r="B191" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C191" t="s">
+        <v>447</v>
+      </c>
+      <c r="D191" t="s">
         <v>448</v>
       </c>
-      <c r="D191" t="s">
-        <v>449</v>
-      </c>
       <c r="E191" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F191" t="s">
         <v>49</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J191" s="1" t="s">
         <v>367</v>
@@ -13038,22 +13048,22 @@
         <v>79</v>
       </c>
       <c r="B192" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C192" t="s">
+        <v>449</v>
+      </c>
+      <c r="D192" t="s">
         <v>450</v>
       </c>
-      <c r="D192" t="s">
-        <v>451</v>
-      </c>
       <c r="E192" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F192" t="s">
         <v>49</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J192" s="1" t="s">
         <v>367</v>
@@ -13079,22 +13089,22 @@
         <v>80</v>
       </c>
       <c r="B193" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C193" t="s">
+        <v>451</v>
+      </c>
+      <c r="D193" t="s">
         <v>452</v>
       </c>
-      <c r="D193" t="s">
-        <v>453</v>
-      </c>
       <c r="E193" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F193" t="s">
         <v>49</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J193" s="1" t="s">
         <v>367</v>
@@ -13120,22 +13130,22 @@
         <v>81</v>
       </c>
       <c r="B194" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C194" t="s">
+        <v>453</v>
+      </c>
+      <c r="D194" t="s">
         <v>454</v>
       </c>
-      <c r="D194" t="s">
-        <v>455</v>
-      </c>
       <c r="E194" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F194" t="s">
         <v>49</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J194" s="1" t="s">
         <v>367</v>
@@ -13161,22 +13171,22 @@
         <v>82</v>
       </c>
       <c r="B195" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C195" t="s">
+        <v>455</v>
+      </c>
+      <c r="D195" t="s">
         <v>456</v>
       </c>
-      <c r="D195" t="s">
-        <v>457</v>
-      </c>
       <c r="E195" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F195" t="s">
         <v>49</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>367</v>
@@ -13202,22 +13212,22 @@
         <v>83</v>
       </c>
       <c r="B196" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C196" t="s">
+        <v>457</v>
+      </c>
+      <c r="D196" t="s">
         <v>458</v>
       </c>
-      <c r="D196" t="s">
-        <v>459</v>
-      </c>
       <c r="E196" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F196" t="s">
         <v>49</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J196" s="1" t="s">
         <v>367</v>
@@ -13243,22 +13253,22 @@
         <v>84</v>
       </c>
       <c r="B197" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C197" t="s">
+        <v>459</v>
+      </c>
+      <c r="D197" t="s">
         <v>460</v>
       </c>
-      <c r="D197" t="s">
-        <v>461</v>
-      </c>
       <c r="E197" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F197" t="s">
         <v>49</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J197" s="1" t="s">
         <v>367</v>
@@ -13284,22 +13294,22 @@
         <v>85</v>
       </c>
       <c r="B198" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C198" t="s">
+        <v>461</v>
+      </c>
+      <c r="D198" t="s">
         <v>462</v>
       </c>
-      <c r="D198" t="s">
-        <v>463</v>
-      </c>
       <c r="E198" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F198" t="s">
         <v>49</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J198" s="1" t="s">
         <v>367</v>
@@ -13325,22 +13335,22 @@
         <v>86</v>
       </c>
       <c r="B199" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C199" t="s">
+        <v>463</v>
+      </c>
+      <c r="D199" t="s">
         <v>464</v>
       </c>
-      <c r="D199" t="s">
-        <v>465</v>
-      </c>
       <c r="E199" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F199" t="s">
         <v>49</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J199" s="1" t="s">
         <v>367</v>
@@ -13366,22 +13376,22 @@
         <v>87</v>
       </c>
       <c r="B200" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C200" t="s">
+        <v>465</v>
+      </c>
+      <c r="D200" t="s">
         <v>466</v>
       </c>
-      <c r="D200" t="s">
-        <v>467</v>
-      </c>
       <c r="E200" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F200" t="s">
         <v>49</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J200" s="1" t="s">
         <v>367</v>
@@ -13407,22 +13417,22 @@
         <v>88</v>
       </c>
       <c r="B201" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C201" t="s">
+        <v>467</v>
+      </c>
+      <c r="D201" t="s">
         <v>468</v>
       </c>
-      <c r="D201" t="s">
-        <v>469</v>
-      </c>
       <c r="E201" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F201" t="s">
         <v>49</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J201" s="1" t="s">
         <v>367</v>
@@ -13448,22 +13458,22 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C202" t="s">
+        <v>469</v>
+      </c>
+      <c r="D202" t="s">
         <v>470</v>
       </c>
-      <c r="D202" t="s">
-        <v>471</v>
-      </c>
       <c r="E202" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F202" t="s">
         <v>49</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J202" s="1" t="s">
         <v>367</v>
@@ -13489,22 +13499,22 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C203" t="s">
+        <v>471</v>
+      </c>
+      <c r="D203" t="s">
         <v>472</v>
       </c>
-      <c r="D203" t="s">
-        <v>473</v>
-      </c>
       <c r="E203" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F203" t="s">
         <v>49</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J203" s="1" t="s">
         <v>367</v>
@@ -13530,22 +13540,22 @@
         <v>91</v>
       </c>
       <c r="B204" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C204" t="s">
+        <v>473</v>
+      </c>
+      <c r="D204" t="s">
         <v>474</v>
       </c>
-      <c r="D204" t="s">
-        <v>475</v>
-      </c>
       <c r="E204" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F204" t="s">
         <v>49</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J204" s="1" t="s">
         <v>367</v>
@@ -13571,22 +13581,22 @@
         <v>92</v>
       </c>
       <c r="B205" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C205" t="s">
+        <v>475</v>
+      </c>
+      <c r="D205" t="s">
         <v>476</v>
       </c>
-      <c r="D205" t="s">
-        <v>477</v>
-      </c>
       <c r="E205" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F205" t="s">
         <v>49</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J205" s="1" t="s">
         <v>367</v>
@@ -13612,37 +13622,37 @@
         <v>93</v>
       </c>
       <c r="B206" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C206" t="s">
+        <v>477</v>
+      </c>
+      <c r="D206" t="s">
         <v>478</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
+        <v>478</v>
+      </c>
+      <c r="F206" t="s">
+        <v>49</v>
+      </c>
+      <c r="I206" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="E206" t="s">
-        <v>479</v>
-      </c>
-      <c r="F206" t="s">
-        <v>49</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K206" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="L206" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M206" t="s">
         <v>384</v>
       </c>
       <c r="N206" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="P206" s="1" t="s">
         <v>78</v>
@@ -13671,37 +13681,37 @@
         <v>94</v>
       </c>
       <c r="B207" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C207" t="s">
+        <v>482</v>
+      </c>
+      <c r="D207" t="s">
+        <v>483</v>
+      </c>
+      <c r="E207" t="s">
         <v>484</v>
       </c>
-      <c r="D207" t="s">
+      <c r="F207" t="s">
+        <v>49</v>
+      </c>
+      <c r="I207" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="E207" t="s">
-        <v>486</v>
-      </c>
-      <c r="F207" t="s">
-        <v>49</v>
-      </c>
-      <c r="I207" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K207" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="L207" t="s">
+        <v>486</v>
+      </c>
+      <c r="M207" t="s">
+        <v>487</v>
+      </c>
+      <c r="N207" t="s">
         <v>488</v>
-      </c>
-      <c r="M207" t="s">
-        <v>489</v>
-      </c>
-      <c r="N207" t="s">
-        <v>490</v>
       </c>
       <c r="P207" s="1" t="s">
         <v>78</v>
@@ -13730,37 +13740,37 @@
         <v>95</v>
       </c>
       <c r="B208" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C208" t="s">
+        <v>489</v>
+      </c>
+      <c r="D208" t="s">
+        <v>490</v>
+      </c>
+      <c r="E208" t="s">
         <v>491</v>
       </c>
-      <c r="D208" t="s">
+      <c r="F208" t="s">
+        <v>49</v>
+      </c>
+      <c r="I208" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E208" t="s">
+      <c r="J208" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F208" t="s">
-        <v>49</v>
-      </c>
-      <c r="I208" s="1" t="s">
+      <c r="K208" t="s">
+        <v>686</v>
+      </c>
+      <c r="L208" t="s">
         <v>494</v>
       </c>
-      <c r="J208" s="1" t="s">
+      <c r="M208" t="s">
         <v>495</v>
       </c>
-      <c r="K208" t="s">
-        <v>698</v>
-      </c>
-      <c r="L208" t="s">
+      <c r="N208" t="s">
         <v>496</v>
-      </c>
-      <c r="M208" t="s">
-        <v>497</v>
-      </c>
-      <c r="N208" t="s">
-        <v>498</v>
       </c>
       <c r="P208" s="1" t="s">
         <v>78</v>
@@ -13789,37 +13799,37 @@
         <v>96</v>
       </c>
       <c r="B209" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C209" t="s">
+        <v>497</v>
+      </c>
+      <c r="D209" t="s">
+        <v>498</v>
+      </c>
+      <c r="E209" t="s">
+        <v>498</v>
+      </c>
+      <c r="F209" t="s">
+        <v>49</v>
+      </c>
+      <c r="I209" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="D209" t="s">
-        <v>500</v>
-      </c>
-      <c r="E209" t="s">
-        <v>500</v>
-      </c>
-      <c r="F209" t="s">
-        <v>49</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="L209" t="s">
+        <v>500</v>
+      </c>
+      <c r="M209" t="s">
+        <v>501</v>
+      </c>
+      <c r="N209" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M209" t="s">
-        <v>503</v>
-      </c>
-      <c r="N209" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P209" s="1" t="s">
         <v>78</v>
@@ -13828,7 +13838,7 @@
         <v>33</v>
       </c>
       <c r="R209" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U209" t="s">
         <v>35</v>
@@ -13840,7 +13850,7 @@
         <v>352</v>
       </c>
       <c r="X209" s="1" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
     </row>
     <row r="210" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -13848,37 +13858,37 @@
         <v>97</v>
       </c>
       <c r="B210" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C210" t="s">
+        <v>504</v>
+      </c>
+      <c r="D210" t="s">
+        <v>505</v>
+      </c>
+      <c r="E210" t="s">
+        <v>505</v>
+      </c>
+      <c r="F210" t="s">
+        <v>49</v>
+      </c>
+      <c r="I210" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="D210" t="s">
-        <v>507</v>
-      </c>
-      <c r="E210" t="s">
-        <v>507</v>
-      </c>
-      <c r="F210" t="s">
-        <v>49</v>
-      </c>
-      <c r="I210" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="L210" t="s">
+        <v>500</v>
+      </c>
+      <c r="M210" t="s">
+        <v>501</v>
+      </c>
+      <c r="N210" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M210" t="s">
-        <v>503</v>
-      </c>
-      <c r="N210" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P210" s="1" t="s">
         <v>78</v>
@@ -13887,7 +13897,7 @@
         <v>33</v>
       </c>
       <c r="R210" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U210" t="s">
         <v>35</v>
@@ -13899,7 +13909,7 @@
         <v>352</v>
       </c>
       <c r="X210" s="1" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
     </row>
     <row r="211" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -13907,37 +13917,37 @@
         <v>98</v>
       </c>
       <c r="B211" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C211" t="s">
+        <v>507</v>
+      </c>
+      <c r="D211" t="s">
+        <v>508</v>
+      </c>
+      <c r="E211" t="s">
+        <v>508</v>
+      </c>
+      <c r="F211" t="s">
+        <v>49</v>
+      </c>
+      <c r="I211" t="s">
         <v>509</v>
-      </c>
-      <c r="D211" t="s">
-        <v>510</v>
-      </c>
-      <c r="E211" t="s">
-        <v>510</v>
-      </c>
-      <c r="F211" t="s">
-        <v>49</v>
-      </c>
-      <c r="I211" t="s">
-        <v>511</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="L211" t="s">
+        <v>500</v>
+      </c>
+      <c r="M211" t="s">
+        <v>501</v>
+      </c>
+      <c r="N211" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M211" t="s">
-        <v>503</v>
-      </c>
-      <c r="N211" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P211" s="1" t="s">
         <v>78</v>
@@ -13946,7 +13956,7 @@
         <v>33</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U211" t="s">
         <v>35</v>
@@ -13958,7 +13968,7 @@
         <v>352</v>
       </c>
       <c r="X211" s="1" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.25">
@@ -13966,22 +13976,22 @@
         <v>99</v>
       </c>
       <c r="B212" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C212" t="s">
+        <v>510</v>
+      </c>
+      <c r="D212" t="s">
+        <v>511</v>
+      </c>
+      <c r="E212" t="s">
+        <v>511</v>
+      </c>
+      <c r="F212" t="s">
+        <v>49</v>
+      </c>
+      <c r="I212" t="s">
         <v>512</v>
-      </c>
-      <c r="D212" t="s">
-        <v>513</v>
-      </c>
-      <c r="E212" t="s">
-        <v>513</v>
-      </c>
-      <c r="F212" t="s">
-        <v>49</v>
-      </c>
-      <c r="I212" t="s">
-        <v>514</v>
       </c>
       <c r="K212" t="s">
         <v>41</v>
@@ -14004,22 +14014,22 @@
         <v>100</v>
       </c>
       <c r="B213" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C213" t="s">
+        <v>513</v>
+      </c>
+      <c r="D213" t="s">
+        <v>514</v>
+      </c>
+      <c r="E213" t="s">
+        <v>514</v>
+      </c>
+      <c r="F213" t="s">
+        <v>49</v>
+      </c>
+      <c r="I213" t="s">
         <v>515</v>
-      </c>
-      <c r="D213" t="s">
-        <v>516</v>
-      </c>
-      <c r="E213" t="s">
-        <v>516</v>
-      </c>
-      <c r="F213" t="s">
-        <v>49</v>
-      </c>
-      <c r="I213" t="s">
-        <v>517</v>
       </c>
       <c r="K213" t="s">
         <v>41</v>
@@ -14042,22 +14052,22 @@
         <v>101</v>
       </c>
       <c r="B214" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C214" t="s">
+        <v>516</v>
+      </c>
+      <c r="D214" t="s">
+        <v>517</v>
+      </c>
+      <c r="E214" t="s">
+        <v>517</v>
+      </c>
+      <c r="F214" t="s">
+        <v>49</v>
+      </c>
+      <c r="I214" t="s">
         <v>518</v>
-      </c>
-      <c r="D214" t="s">
-        <v>519</v>
-      </c>
-      <c r="E214" t="s">
-        <v>519</v>
-      </c>
-      <c r="F214" t="s">
-        <v>49</v>
-      </c>
-      <c r="I214" t="s">
-        <v>520</v>
       </c>
       <c r="K214" t="s">
         <v>41</v>
@@ -14080,22 +14090,22 @@
         <v>102</v>
       </c>
       <c r="B215" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C215" t="s">
+        <v>519</v>
+      </c>
+      <c r="D215" t="s">
+        <v>520</v>
+      </c>
+      <c r="E215" t="s">
+        <v>520</v>
+      </c>
+      <c r="F215" t="s">
+        <v>49</v>
+      </c>
+      <c r="I215" t="s">
         <v>521</v>
-      </c>
-      <c r="D215" t="s">
-        <v>522</v>
-      </c>
-      <c r="E215" t="s">
-        <v>522</v>
-      </c>
-      <c r="F215" t="s">
-        <v>49</v>
-      </c>
-      <c r="I215" t="s">
-        <v>523</v>
       </c>
       <c r="K215" t="s">
         <v>41</v>
@@ -14118,22 +14128,22 @@
         <v>103</v>
       </c>
       <c r="B216" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C216" t="s">
+        <v>522</v>
+      </c>
+      <c r="D216" t="s">
+        <v>523</v>
+      </c>
+      <c r="E216" t="s">
+        <v>523</v>
+      </c>
+      <c r="F216" t="s">
+        <v>49</v>
+      </c>
+      <c r="I216" t="s">
         <v>524</v>
-      </c>
-      <c r="D216" t="s">
-        <v>525</v>
-      </c>
-      <c r="E216" t="s">
-        <v>525</v>
-      </c>
-      <c r="F216" t="s">
-        <v>49</v>
-      </c>
-      <c r="I216" t="s">
-        <v>526</v>
       </c>
       <c r="K216" t="s">
         <v>41</v>
@@ -14156,34 +14166,34 @@
         <v>104</v>
       </c>
       <c r="B217" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C217" t="s">
+        <v>525</v>
+      </c>
+      <c r="D217" t="s">
+        <v>526</v>
+      </c>
+      <c r="E217" t="s">
+        <v>526</v>
+      </c>
+      <c r="F217" t="s">
+        <v>49</v>
+      </c>
+      <c r="I217" t="s">
+        <v>515</v>
+      </c>
+      <c r="K217" t="s">
+        <v>770</v>
+      </c>
+      <c r="L217" t="s">
         <v>527</v>
       </c>
-      <c r="D217" t="s">
+      <c r="M217" t="s">
         <v>528</v>
       </c>
-      <c r="E217" t="s">
-        <v>528</v>
-      </c>
-      <c r="F217" t="s">
-        <v>49</v>
-      </c>
-      <c r="I217" t="s">
-        <v>517</v>
-      </c>
-      <c r="K217" t="s">
-        <v>585</v>
-      </c>
-      <c r="L217" t="s">
+      <c r="N217" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="M217" t="s">
-        <v>530</v>
-      </c>
-      <c r="N217" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="P217" s="1" t="s">
         <v>78</v>
@@ -14192,7 +14202,7 @@
         <v>79</v>
       </c>
       <c r="R217" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="U217" t="s">
         <v>35</v>
@@ -14212,22 +14222,22 @@
         <v>105</v>
       </c>
       <c r="B218" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C218" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D218" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E218" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F218" t="s">
         <v>49</v>
       </c>
       <c r="I218" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K218" t="s">
         <v>41</v>
@@ -14250,25 +14260,25 @@
         <v>106</v>
       </c>
       <c r="B219" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C219" t="s">
+        <v>533</v>
+      </c>
+      <c r="D219" t="s">
+        <v>534</v>
+      </c>
+      <c r="E219" t="s">
         <v>535</v>
       </c>
-      <c r="D219" t="s">
+      <c r="F219" t="s">
+        <v>49</v>
+      </c>
+      <c r="I219" t="s">
         <v>536</v>
       </c>
-      <c r="E219" t="s">
+      <c r="J219" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="F219" t="s">
-        <v>49</v>
-      </c>
-      <c r="I219" t="s">
-        <v>538</v>
-      </c>
-      <c r="J219" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="K219" t="s">
         <v>41</v>
@@ -14291,25 +14301,25 @@
         <v>107</v>
       </c>
       <c r="B220" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C220" t="s">
+        <v>539</v>
+      </c>
+      <c r="D220" t="s">
+        <v>540</v>
+      </c>
+      <c r="E220" t="s">
         <v>541</v>
       </c>
-      <c r="D220" t="s">
+      <c r="F220" t="s">
+        <v>49</v>
+      </c>
+      <c r="I220" t="s">
+        <v>536</v>
+      </c>
+      <c r="J220" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="E220" t="s">
-        <v>543</v>
-      </c>
-      <c r="F220" t="s">
-        <v>49</v>
-      </c>
-      <c r="I220" t="s">
-        <v>538</v>
-      </c>
-      <c r="J220" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="K220" t="s">
         <v>41</v>
@@ -14332,25 +14342,25 @@
         <v>108</v>
       </c>
       <c r="B221" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C221" t="s">
+        <v>543</v>
+      </c>
+      <c r="D221" t="s">
+        <v>544</v>
+      </c>
+      <c r="E221" t="s">
         <v>545</v>
       </c>
-      <c r="D221" t="s">
+      <c r="F221" t="s">
+        <v>49</v>
+      </c>
+      <c r="I221" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E221" t="s">
+      <c r="J221" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="F221" t="s">
-        <v>49</v>
-      </c>
-      <c r="I221" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J221" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="K221" t="s">
         <v>41</v>
@@ -14373,37 +14383,37 @@
         <v>109</v>
       </c>
       <c r="B222" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C222" t="s">
+        <v>548</v>
+      </c>
+      <c r="D222" t="s">
+        <v>549</v>
+      </c>
+      <c r="E222" t="s">
         <v>550</v>
       </c>
-      <c r="D222" t="s">
+      <c r="F222" t="s">
+        <v>49</v>
+      </c>
+      <c r="I222" t="s">
         <v>551</v>
       </c>
-      <c r="E222" t="s">
+      <c r="J222" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="K222" t="s">
+        <v>691</v>
+      </c>
+      <c r="L222" t="s">
         <v>552</v>
       </c>
-      <c r="F222" t="s">
-        <v>49</v>
-      </c>
-      <c r="I222" t="s">
+      <c r="M222" t="s">
         <v>553</v>
       </c>
-      <c r="J222" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K222" t="s">
-        <v>703</v>
-      </c>
-      <c r="L222" t="s">
+      <c r="N222" t="s">
         <v>554</v>
-      </c>
-      <c r="M222" t="s">
-        <v>555</v>
-      </c>
-      <c r="N222" t="s">
-        <v>556</v>
       </c>
       <c r="P222" s="1" t="s">
         <v>78</v>
@@ -14412,7 +14422,7 @@
         <v>33</v>
       </c>
       <c r="R222" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="U222" t="s">
         <v>35</v>
@@ -14424,7 +14434,7 @@
         <v>68</v>
       </c>
       <c r="X222" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="223" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -14432,37 +14442,37 @@
         <v>110</v>
       </c>
       <c r="B223" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C223" t="s">
+        <v>557</v>
+      </c>
+      <c r="D223" t="s">
+        <v>558</v>
+      </c>
+      <c r="E223" t="s">
         <v>559</v>
       </c>
-      <c r="D223" t="s">
+      <c r="F223" t="s">
+        <v>49</v>
+      </c>
+      <c r="I223" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E223" t="s">
+      <c r="J223" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="K223" t="s">
+        <v>692</v>
+      </c>
+      <c r="L223" t="s">
         <v>561</v>
       </c>
-      <c r="F223" t="s">
-        <v>49</v>
-      </c>
-      <c r="I223" s="1" t="s">
+      <c r="M223" t="s">
         <v>562</v>
       </c>
-      <c r="J223" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K223" t="s">
-        <v>704</v>
-      </c>
-      <c r="L223" t="s">
+      <c r="N223" t="s">
         <v>563</v>
-      </c>
-      <c r="M223" t="s">
-        <v>564</v>
-      </c>
-      <c r="N223" t="s">
-        <v>565</v>
       </c>
       <c r="P223" s="1" t="s">
         <v>78</v>
@@ -14471,10 +14481,10 @@
         <v>33</v>
       </c>
       <c r="R223" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="T223" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="U223" t="s">
         <v>35</v>
@@ -14486,7 +14496,7 @@
         <v>68</v>
       </c>
       <c r="X223" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="224" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -14494,22 +14504,22 @@
         <v>111</v>
       </c>
       <c r="B224" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C224" t="s">
+        <v>567</v>
+      </c>
+      <c r="D224" t="s">
+        <v>568</v>
+      </c>
+      <c r="E224" t="s">
         <v>569</v>
-      </c>
-      <c r="D224" t="s">
-        <v>570</v>
-      </c>
-      <c r="E224" t="s">
-        <v>571</v>
       </c>
       <c r="F224" t="s">
         <v>112</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="U224" t="s">
         <v>35</v>
@@ -14521,33 +14531,33 @@
         <v>59</v>
       </c>
       <c r="X224" s="1" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="225" spans="1:24" ht="285" x14ac:dyDescent="0.25">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="225" spans="1:24" ht="270" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>112</v>
       </c>
       <c r="B225" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C225" t="s">
+        <v>570</v>
+      </c>
+      <c r="D225" t="s">
+        <v>571</v>
+      </c>
+      <c r="E225" t="s">
         <v>572</v>
       </c>
-      <c r="D225" t="s">
+      <c r="F225" t="s">
+        <v>49</v>
+      </c>
+      <c r="G225" t="s">
         <v>573</v>
       </c>
-      <c r="E225" t="s">
-        <v>574</v>
-      </c>
-      <c r="F225" t="s">
-        <v>49</v>
-      </c>
-      <c r="G225" t="s">
-        <v>575</v>
-      </c>
       <c r="K225" s="1" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="U225" t="s">
         <v>35</v>
@@ -14559,7 +14569,7 @@
         <v>59</v>
       </c>
       <c r="X225" s="1" t="s">
-        <v>707</v>
+        <v>765</v>
       </c>
     </row>
     <row r="226" spans="1:24" x14ac:dyDescent="0.25">
@@ -14567,7 +14577,7 @@
         <v>1</v>
       </c>
       <c r="B226" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C226" t="s">
         <v>23</v>
@@ -14588,10 +14598,10 @@
         <v>28</v>
       </c>
       <c r="L226" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M226" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="U226" t="s">
         <v>35</v>
@@ -14611,7 +14621,7 @@
         <v>2</v>
       </c>
       <c r="B227" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C227" t="s">
         <v>38</v>
@@ -14641,7 +14651,7 @@
         <v>43</v>
       </c>
       <c r="X227" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="228" spans="1:24" x14ac:dyDescent="0.25">
@@ -14649,7 +14659,7 @@
         <v>3</v>
       </c>
       <c r="B228" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C228" t="s">
         <v>44</v>
@@ -14679,7 +14689,7 @@
         <v>43</v>
       </c>
       <c r="X228" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="229" spans="1:24" x14ac:dyDescent="0.25">
@@ -14687,7 +14697,7 @@
         <v>4</v>
       </c>
       <c r="B229" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C229" t="s">
         <v>47</v>
@@ -14725,7 +14735,7 @@
         <v>5</v>
       </c>
       <c r="B230" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C230" t="s">
         <v>51</v>
@@ -14746,7 +14756,7 @@
         <v>56</v>
       </c>
       <c r="K230" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="L230" t="s">
         <v>57</v>
@@ -14767,7 +14777,7 @@
         <v>59</v>
       </c>
       <c r="X230" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
     </row>
     <row r="231" spans="1:24" ht="45" x14ac:dyDescent="0.25">
@@ -14775,7 +14785,7 @@
         <v>6</v>
       </c>
       <c r="B231" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C231" t="s">
         <v>60</v>
@@ -14822,7 +14832,7 @@
         <v>7</v>
       </c>
       <c r="B232" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C232" t="s">
         <v>70</v>
@@ -14843,7 +14853,7 @@
         <v>74</v>
       </c>
       <c r="K232" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="L232" t="s">
         <v>75</v>
@@ -14881,7 +14891,7 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C233" t="s">
         <v>81</v>
@@ -14922,7 +14932,7 @@
         <v>9</v>
       </c>
       <c r="B234" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C234" t="s">
         <v>88</v>
@@ -14963,7 +14973,7 @@
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C235" t="s">
         <v>92</v>
@@ -14984,7 +14994,7 @@
         <v>96</v>
       </c>
       <c r="K235" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="L235" t="s">
         <v>97</v>
@@ -15025,7 +15035,7 @@
         <v>11</v>
       </c>
       <c r="B236" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C236" t="s">
         <v>103</v>
@@ -15046,7 +15056,7 @@
         <v>107</v>
       </c>
       <c r="K236" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="L236" t="s">
         <v>97</v>
@@ -15087,7 +15097,7 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C237" t="s">
         <v>110</v>
@@ -15125,7 +15135,7 @@
         <v>13</v>
       </c>
       <c r="B238" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C238" t="s">
         <v>114</v>
@@ -15160,7 +15170,7 @@
         <v>14</v>
       </c>
       <c r="B239" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C239" t="s">
         <v>117</v>
@@ -15181,7 +15191,7 @@
         <v>121</v>
       </c>
       <c r="K239" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="L239" t="s">
         <v>97</v>
@@ -15222,7 +15232,7 @@
         <v>15</v>
       </c>
       <c r="B240" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C240" t="s">
         <v>123</v>
@@ -15240,7 +15250,7 @@
         <v>125</v>
       </c>
       <c r="K240" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="L240" t="s">
         <v>126</v>
@@ -15278,7 +15288,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C241" t="s">
         <v>131</v>
@@ -15319,7 +15329,7 @@
         <v>17</v>
       </c>
       <c r="B242" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C242" t="s">
         <v>136</v>
@@ -15340,7 +15350,7 @@
         <v>139</v>
       </c>
       <c r="K242" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="L242" t="s">
         <v>140</v>
@@ -15381,7 +15391,7 @@
         <v>18</v>
       </c>
       <c r="B243" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C243" t="s">
         <v>144</v>
@@ -15399,7 +15409,7 @@
         <v>146</v>
       </c>
       <c r="K243" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="U243" t="s">
         <v>35</v>
@@ -15411,7 +15421,7 @@
         <v>59</v>
       </c>
       <c r="X243" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
     </row>
     <row r="244" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -15419,7 +15429,7 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C244" t="s">
         <v>147</v>
@@ -15440,7 +15450,7 @@
         <v>139</v>
       </c>
       <c r="K244" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="L244" t="s">
         <v>150</v>
@@ -15481,7 +15491,7 @@
         <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C245" t="s">
         <v>153</v>
@@ -15499,7 +15509,7 @@
         <v>146</v>
       </c>
       <c r="K245" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="U245" t="s">
         <v>35</v>
@@ -15511,7 +15521,7 @@
         <v>59</v>
       </c>
       <c r="X245" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="246" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -15519,7 +15529,7 @@
         <v>21</v>
       </c>
       <c r="B246" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C246" t="s">
         <v>155</v>
@@ -15540,7 +15550,7 @@
         <v>158</v>
       </c>
       <c r="K246" t="s">
-        <v>579</v>
+        <v>772</v>
       </c>
       <c r="L246" t="s">
         <v>159</v>
@@ -15581,7 +15591,7 @@
         <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C247" t="s">
         <v>162</v>
@@ -15602,7 +15612,7 @@
         <v>139</v>
       </c>
       <c r="K247" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="L247" t="s">
         <v>164</v>
@@ -15623,7 +15633,7 @@
         <v>143</v>
       </c>
       <c r="T247" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="U247" t="s">
         <v>35</v>
@@ -15643,7 +15653,7 @@
         <v>23</v>
       </c>
       <c r="B248" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C248" t="s">
         <v>169</v>
@@ -15661,7 +15671,7 @@
         <v>146</v>
       </c>
       <c r="K248" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="L248" t="s">
         <v>164</v>
@@ -15691,7 +15701,7 @@
         <v>59</v>
       </c>
       <c r="X248" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="249" spans="1:24" x14ac:dyDescent="0.25">
@@ -15699,7 +15709,7 @@
         <v>24</v>
       </c>
       <c r="B249" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C249" t="s">
         <v>171</v>
@@ -15717,7 +15727,7 @@
         <v>173</v>
       </c>
       <c r="K249" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="L249" t="s">
         <v>174</v>
@@ -15747,7 +15757,7 @@
         <v>59</v>
       </c>
       <c r="X249" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
     </row>
     <row r="250" spans="1:24" x14ac:dyDescent="0.25">
@@ -15755,7 +15765,7 @@
         <v>25</v>
       </c>
       <c r="B250" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C250" t="s">
         <v>178</v>
@@ -15770,7 +15780,7 @@
         <v>26</v>
       </c>
       <c r="K250" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="U250" t="s">
         <v>35</v>
@@ -15782,7 +15792,7 @@
         <v>59</v>
       </c>
       <c r="X250" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
     </row>
     <row r="251" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -15790,7 +15800,7 @@
         <v>26</v>
       </c>
       <c r="B251" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C251" t="s">
         <v>180</v>
@@ -15811,7 +15821,7 @@
         <v>184</v>
       </c>
       <c r="K251" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="L251" t="s">
         <v>185</v>
@@ -15829,7 +15839,7 @@
         <v>183</v>
       </c>
       <c r="T251" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="U251" t="s">
         <v>35</v>
@@ -15841,7 +15851,7 @@
         <v>59</v>
       </c>
       <c r="X251" t="s">
-        <v>582</v>
+        <v>774</v>
       </c>
     </row>
     <row r="252" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -15849,7 +15859,7 @@
         <v>27</v>
       </c>
       <c r="B252" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C252" t="s">
         <v>188</v>
@@ -15870,7 +15880,7 @@
         <v>184</v>
       </c>
       <c r="K252" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="L252" t="s">
         <v>191</v>
@@ -15888,7 +15898,7 @@
         <v>183</v>
       </c>
       <c r="T252" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="U252" t="s">
         <v>35</v>
@@ -15900,7 +15910,7 @@
         <v>59</v>
       </c>
       <c r="X252" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
     </row>
     <row r="253" spans="1:24" x14ac:dyDescent="0.25">
@@ -15908,7 +15918,7 @@
         <v>28</v>
       </c>
       <c r="B253" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C253" t="s">
         <v>193</v>
@@ -15949,7 +15959,7 @@
         <v>29</v>
       </c>
       <c r="B254" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C254" t="s">
         <v>196</v>
@@ -15990,7 +16000,7 @@
         <v>30</v>
       </c>
       <c r="B255" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C255" t="s">
         <v>200</v>
@@ -16028,7 +16038,7 @@
         <v>31</v>
       </c>
       <c r="B256" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C256" t="s">
         <v>203</v>
@@ -16066,7 +16076,7 @@
         <v>32</v>
       </c>
       <c r="B257" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C257" t="s">
         <v>206</v>
@@ -16104,7 +16114,7 @@
         <v>33</v>
       </c>
       <c r="B258" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C258" t="s">
         <v>209</v>
@@ -16122,7 +16132,7 @@
         <v>211</v>
       </c>
       <c r="K258" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="L258" t="s">
         <v>210</v>
@@ -16151,7 +16161,7 @@
         <v>34</v>
       </c>
       <c r="B259" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C259" t="s">
         <v>214</v>
@@ -16169,7 +16179,7 @@
         <v>211</v>
       </c>
       <c r="K259" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="L259" t="s">
         <v>215</v>
@@ -16198,7 +16208,7 @@
         <v>35</v>
       </c>
       <c r="B260" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C260" t="s">
         <v>218</v>
@@ -16216,7 +16226,7 @@
         <v>211</v>
       </c>
       <c r="K260" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="L260" t="s">
         <v>219</v>
@@ -16245,7 +16255,7 @@
         <v>36</v>
       </c>
       <c r="B261" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C261" t="s">
         <v>222</v>
@@ -16266,7 +16276,7 @@
         <v>224</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="L261" s="1" t="s">
         <v>225</v>
@@ -16281,7 +16291,7 @@
         <v>59</v>
       </c>
       <c r="X261" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
     </row>
     <row r="262" spans="1:24" x14ac:dyDescent="0.25">
@@ -16289,7 +16299,7 @@
         <v>37</v>
       </c>
       <c r="B262" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C262" t="s">
         <v>226</v>
@@ -16307,7 +16317,7 @@
         <v>211</v>
       </c>
       <c r="K262" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="L262" t="s">
         <v>227</v>
@@ -16336,7 +16346,7 @@
         <v>38</v>
       </c>
       <c r="B263" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C263" t="s">
         <v>230</v>
@@ -16354,7 +16364,7 @@
         <v>232</v>
       </c>
       <c r="K263" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="L263" t="s">
         <v>231</v>
@@ -16383,7 +16393,7 @@
         <v>39</v>
       </c>
       <c r="B264" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C264" t="s">
         <v>235</v>
@@ -16424,7 +16434,7 @@
         <v>40</v>
       </c>
       <c r="B265" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C265" t="s">
         <v>240</v>
@@ -16465,7 +16475,7 @@
         <v>41</v>
       </c>
       <c r="B266" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C266" t="s">
         <v>245</v>
@@ -16506,7 +16516,7 @@
         <v>42</v>
       </c>
       <c r="B267" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C267" t="s">
         <v>248</v>
@@ -16527,7 +16537,7 @@
         <v>244</v>
       </c>
       <c r="K267" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="L267" t="s">
         <v>252</v>
@@ -16562,7 +16572,7 @@
         <v>43</v>
       </c>
       <c r="B268" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C268" t="s">
         <v>257</v>
@@ -16600,7 +16610,7 @@
         <v>44</v>
       </c>
       <c r="B269" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C269" t="s">
         <v>260</v>
@@ -16621,7 +16631,7 @@
         <v>263</v>
       </c>
       <c r="K269" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="L269" t="s">
         <v>264</v>
@@ -16653,7 +16663,7 @@
         <v>45</v>
       </c>
       <c r="B270" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C270" t="s">
         <v>267</v>
@@ -16691,7 +16701,7 @@
         <v>46</v>
       </c>
       <c r="B271" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C271" t="s">
         <v>270</v>
@@ -16712,7 +16722,7 @@
         <v>273</v>
       </c>
       <c r="K271" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="L271" t="s">
         <v>274</v>
@@ -16750,7 +16760,7 @@
         <v>47</v>
       </c>
       <c r="B272" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C272" t="s">
         <v>279</v>
@@ -16809,7 +16819,7 @@
         <v>48</v>
       </c>
       <c r="B273" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C273" t="s">
         <v>283</v>
@@ -16850,7 +16860,7 @@
         <v>49</v>
       </c>
       <c r="B274" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C274" t="s">
         <v>287</v>
@@ -16868,7 +16878,7 @@
         <v>113</v>
       </c>
       <c r="K274" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="L274" t="s">
         <v>289</v>
@@ -16909,7 +16919,7 @@
         <v>50</v>
       </c>
       <c r="B275" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C275" t="s">
         <v>296</v>
@@ -16930,7 +16940,7 @@
         <v>299</v>
       </c>
       <c r="K275" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="L275" t="s">
         <v>289</v>
@@ -16968,7 +16978,7 @@
         <v>51</v>
       </c>
       <c r="B276" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C276" t="s">
         <v>301</v>
@@ -16989,7 +16999,7 @@
         <v>304</v>
       </c>
       <c r="K276" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="L276" t="s">
         <v>305</v>
@@ -17027,7 +17037,7 @@
         <v>52</v>
       </c>
       <c r="B277" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C277" t="s">
         <v>310</v>
@@ -17068,7 +17078,7 @@
         <v>53</v>
       </c>
       <c r="B278" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C278" t="s">
         <v>314</v>
@@ -17086,7 +17096,7 @@
         <v>313</v>
       </c>
       <c r="K278" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="L278" t="s">
         <v>316</v>
@@ -17107,7 +17117,7 @@
         <v>320</v>
       </c>
       <c r="T278" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="U278" t="s">
         <v>35</v>
@@ -17127,7 +17137,7 @@
         <v>54</v>
       </c>
       <c r="B279" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C279" t="s">
         <v>323</v>
@@ -17165,7 +17175,7 @@
         <v>55</v>
       </c>
       <c r="B280" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C280" t="s">
         <v>325</v>
@@ -17183,7 +17193,7 @@
         <v>328</v>
       </c>
       <c r="K280" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="L280" t="s">
         <v>329</v>
@@ -17204,7 +17214,7 @@
         <v>320</v>
       </c>
       <c r="T280" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="U280" t="s">
         <v>35</v>
@@ -17216,7 +17226,7 @@
         <v>59</v>
       </c>
       <c r="X280" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
     </row>
     <row r="281" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -17224,7 +17234,7 @@
         <v>56</v>
       </c>
       <c r="B281" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C281" t="s">
         <v>333</v>
@@ -17265,7 +17275,7 @@
         <v>57</v>
       </c>
       <c r="B282" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C282" t="s">
         <v>337</v>
@@ -17306,7 +17316,7 @@
         <v>58</v>
       </c>
       <c r="B283" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C283" t="s">
         <v>340</v>
@@ -17327,7 +17337,7 @@
         <v>312</v>
       </c>
       <c r="K283" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="L283" s="1" t="s">
         <v>343</v>
@@ -17357,7 +17367,7 @@
         <v>59</v>
       </c>
       <c r="X283" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
     </row>
     <row r="284" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -17365,7 +17375,7 @@
         <v>59</v>
       </c>
       <c r="B284" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C284" t="s">
         <v>347</v>
@@ -17383,7 +17393,7 @@
         <v>350</v>
       </c>
       <c r="K284" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="L284" s="1" t="s">
         <v>343</v>
@@ -17413,7 +17423,7 @@
         <v>352</v>
       </c>
       <c r="X284" s="1" t="s">
-        <v>740</v>
+        <v>726</v>
       </c>
     </row>
     <row r="285" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -17421,7 +17431,7 @@
         <v>60</v>
       </c>
       <c r="B285" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C285" t="s">
         <v>353</v>
@@ -17442,7 +17452,7 @@
         <v>356</v>
       </c>
       <c r="K285" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
       <c r="L285" t="s">
         <v>358</v>
@@ -17483,7 +17493,7 @@
         <v>61</v>
       </c>
       <c r="B286" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C286" t="s">
         <v>363</v>
@@ -17504,7 +17514,7 @@
         <v>367</v>
       </c>
       <c r="K286" s="1" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="L286" t="s">
         <v>368</v>
@@ -17537,7 +17547,7 @@
         <v>352</v>
       </c>
       <c r="X286" s="1" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
     </row>
     <row r="287" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -17545,7 +17555,7 @@
         <v>62</v>
       </c>
       <c r="B287" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C287" t="s">
         <v>374</v>
@@ -17566,7 +17576,7 @@
         <v>367</v>
       </c>
       <c r="K287" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="L287" t="s">
         <v>377</v>
@@ -17607,7 +17617,7 @@
         <v>63</v>
       </c>
       <c r="B288" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C288" t="s">
         <v>381</v>
@@ -17628,7 +17638,7 @@
         <v>367</v>
       </c>
       <c r="K288" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="L288" t="s">
         <v>377</v>
@@ -17666,7 +17676,7 @@
         <v>64</v>
       </c>
       <c r="B289" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C289" t="s">
         <v>386</v>
@@ -17687,7 +17697,7 @@
         <v>367</v>
       </c>
       <c r="K289" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="L289" t="s">
         <v>389</v>
@@ -17725,7 +17735,7 @@
         <v>65</v>
       </c>
       <c r="B290" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C290" t="s">
         <v>391</v>
@@ -17746,7 +17756,7 @@
         <v>367</v>
       </c>
       <c r="K290" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="L290" t="s">
         <v>394</v>
@@ -17784,7 +17794,7 @@
         <v>66</v>
       </c>
       <c r="B291" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C291" t="s">
         <v>396</v>
@@ -17805,7 +17815,7 @@
         <v>367</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="L291" t="s">
         <v>368</v>
@@ -17843,7 +17853,7 @@
         <v>67</v>
       </c>
       <c r="B292" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C292" t="s">
         <v>400</v>
@@ -17884,7 +17894,7 @@
         <v>68</v>
       </c>
       <c r="B293" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C293" t="s">
         <v>403</v>
@@ -17905,7 +17915,7 @@
         <v>367</v>
       </c>
       <c r="K293" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="L293" t="s">
         <v>406</v>
@@ -17943,7 +17953,7 @@
         <v>69</v>
       </c>
       <c r="B294" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C294" t="s">
         <v>408</v>
@@ -17964,7 +17974,7 @@
         <v>367</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="U294" t="s">
         <v>35</v>
@@ -17976,7 +17986,7 @@
         <v>352</v>
       </c>
       <c r="X294" s="1" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
     </row>
     <row r="295" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -17984,7 +17994,7 @@
         <v>70</v>
       </c>
       <c r="B295" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C295" t="s">
         <v>411</v>
@@ -18005,7 +18015,7 @@
         <v>367</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="L295" s="1" t="s">
         <v>415</v>
@@ -18038,7 +18048,7 @@
         <v>352</v>
       </c>
       <c r="X295" s="1" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
     </row>
     <row r="296" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -18046,7 +18056,7 @@
         <v>71</v>
       </c>
       <c r="B296" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C296" t="s">
         <v>420</v>
@@ -18067,7 +18077,7 @@
         <v>367</v>
       </c>
       <c r="K296" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="L296" t="s">
         <v>425</v>
@@ -18108,7 +18118,7 @@
         <v>72</v>
       </c>
       <c r="B297" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C297" t="s">
         <v>429</v>
@@ -18129,7 +18139,7 @@
         <v>432</v>
       </c>
       <c r="K297" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="L297" t="s">
         <v>425</v>
@@ -18170,7 +18180,7 @@
         <v>73</v>
       </c>
       <c r="B298" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C298" t="s">
         <v>433</v>
@@ -18191,16 +18201,16 @@
         <v>367</v>
       </c>
       <c r="K298" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="L298" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M298" t="s">
         <v>384</v>
       </c>
       <c r="N298" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P298" s="1" t="s">
         <v>78</v>
@@ -18229,22 +18239,22 @@
         <v>74</v>
       </c>
       <c r="B299" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C299" t="s">
+        <v>438</v>
+      </c>
+      <c r="D299" t="s">
         <v>439</v>
       </c>
-      <c r="D299" t="s">
+      <c r="E299" t="s">
+        <v>439</v>
+      </c>
+      <c r="F299" t="s">
+        <v>49</v>
+      </c>
+      <c r="I299" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="E299" t="s">
-        <v>440</v>
-      </c>
-      <c r="F299" t="s">
-        <v>49</v>
-      </c>
-      <c r="I299" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>367</v>
@@ -18270,22 +18280,22 @@
         <v>75</v>
       </c>
       <c r="B300" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C300" t="s">
+        <v>441</v>
+      </c>
+      <c r="D300" t="s">
         <v>442</v>
       </c>
-      <c r="D300" t="s">
-        <v>443</v>
-      </c>
       <c r="E300" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F300" t="s">
         <v>49</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>367</v>
@@ -18311,22 +18321,22 @@
         <v>76</v>
       </c>
       <c r="B301" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C301" t="s">
+        <v>443</v>
+      </c>
+      <c r="D301" t="s">
         <v>444</v>
       </c>
-      <c r="D301" t="s">
-        <v>445</v>
-      </c>
       <c r="E301" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F301" t="s">
         <v>49</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>367</v>
@@ -18352,22 +18362,22 @@
         <v>77</v>
       </c>
       <c r="B302" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C302" t="s">
+        <v>445</v>
+      </c>
+      <c r="D302" t="s">
         <v>446</v>
       </c>
-      <c r="D302" t="s">
-        <v>447</v>
-      </c>
       <c r="E302" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F302" t="s">
         <v>49</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J302" s="1" t="s">
         <v>367</v>
@@ -18393,22 +18403,22 @@
         <v>78</v>
       </c>
       <c r="B303" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C303" t="s">
+        <v>447</v>
+      </c>
+      <c r="D303" t="s">
         <v>448</v>
       </c>
-      <c r="D303" t="s">
-        <v>449</v>
-      </c>
       <c r="E303" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F303" t="s">
         <v>49</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>367</v>
@@ -18434,22 +18444,22 @@
         <v>79</v>
       </c>
       <c r="B304" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C304" t="s">
+        <v>449</v>
+      </c>
+      <c r="D304" t="s">
         <v>450</v>
       </c>
-      <c r="D304" t="s">
-        <v>451</v>
-      </c>
       <c r="E304" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F304" t="s">
         <v>49</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J304" s="1" t="s">
         <v>367</v>
@@ -18475,22 +18485,22 @@
         <v>80</v>
       </c>
       <c r="B305" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C305" t="s">
+        <v>451</v>
+      </c>
+      <c r="D305" t="s">
         <v>452</v>
       </c>
-      <c r="D305" t="s">
-        <v>453</v>
-      </c>
       <c r="E305" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F305" t="s">
         <v>49</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>367</v>
@@ -18516,22 +18526,22 @@
         <v>81</v>
       </c>
       <c r="B306" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C306" t="s">
+        <v>453</v>
+      </c>
+      <c r="D306" t="s">
         <v>454</v>
       </c>
-      <c r="D306" t="s">
-        <v>455</v>
-      </c>
       <c r="E306" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F306" t="s">
         <v>49</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>367</v>
@@ -18557,22 +18567,22 @@
         <v>82</v>
       </c>
       <c r="B307" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C307" t="s">
+        <v>455</v>
+      </c>
+      <c r="D307" t="s">
         <v>456</v>
       </c>
-      <c r="D307" t="s">
-        <v>457</v>
-      </c>
       <c r="E307" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F307" t="s">
         <v>49</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>367</v>
@@ -18598,22 +18608,22 @@
         <v>83</v>
       </c>
       <c r="B308" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C308" t="s">
+        <v>457</v>
+      </c>
+      <c r="D308" t="s">
         <v>458</v>
       </c>
-      <c r="D308" t="s">
-        <v>459</v>
-      </c>
       <c r="E308" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F308" t="s">
         <v>49</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>367</v>
@@ -18639,22 +18649,22 @@
         <v>84</v>
       </c>
       <c r="B309" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C309" t="s">
+        <v>459</v>
+      </c>
+      <c r="D309" t="s">
         <v>460</v>
       </c>
-      <c r="D309" t="s">
-        <v>461</v>
-      </c>
       <c r="E309" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F309" t="s">
         <v>49</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>367</v>
@@ -18680,22 +18690,22 @@
         <v>85</v>
       </c>
       <c r="B310" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C310" t="s">
+        <v>461</v>
+      </c>
+      <c r="D310" t="s">
         <v>462</v>
       </c>
-      <c r="D310" t="s">
-        <v>463</v>
-      </c>
       <c r="E310" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F310" t="s">
         <v>49</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>367</v>
@@ -18721,22 +18731,22 @@
         <v>86</v>
       </c>
       <c r="B311" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C311" t="s">
+        <v>463</v>
+      </c>
+      <c r="D311" t="s">
         <v>464</v>
       </c>
-      <c r="D311" t="s">
-        <v>465</v>
-      </c>
       <c r="E311" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F311" t="s">
         <v>49</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>367</v>
@@ -18762,22 +18772,22 @@
         <v>87</v>
       </c>
       <c r="B312" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C312" t="s">
+        <v>465</v>
+      </c>
+      <c r="D312" t="s">
         <v>466</v>
       </c>
-      <c r="D312" t="s">
-        <v>467</v>
-      </c>
       <c r="E312" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F312" t="s">
         <v>49</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>367</v>
@@ -18803,22 +18813,22 @@
         <v>88</v>
       </c>
       <c r="B313" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C313" t="s">
+        <v>467</v>
+      </c>
+      <c r="D313" t="s">
         <v>468</v>
       </c>
-      <c r="D313" t="s">
-        <v>469</v>
-      </c>
       <c r="E313" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F313" t="s">
         <v>49</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>367</v>
@@ -18844,22 +18854,22 @@
         <v>89</v>
       </c>
       <c r="B314" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C314" t="s">
+        <v>469</v>
+      </c>
+      <c r="D314" t="s">
         <v>470</v>
       </c>
-      <c r="D314" t="s">
-        <v>471</v>
-      </c>
       <c r="E314" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F314" t="s">
         <v>49</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>367</v>
@@ -18885,22 +18895,22 @@
         <v>90</v>
       </c>
       <c r="B315" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C315" t="s">
+        <v>471</v>
+      </c>
+      <c r="D315" t="s">
         <v>472</v>
       </c>
-      <c r="D315" t="s">
-        <v>473</v>
-      </c>
       <c r="E315" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F315" t="s">
         <v>49</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>367</v>
@@ -18926,22 +18936,22 @@
         <v>91</v>
       </c>
       <c r="B316" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C316" t="s">
+        <v>473</v>
+      </c>
+      <c r="D316" t="s">
         <v>474</v>
       </c>
-      <c r="D316" t="s">
-        <v>475</v>
-      </c>
       <c r="E316" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F316" t="s">
         <v>49</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>367</v>
@@ -18967,22 +18977,22 @@
         <v>92</v>
       </c>
       <c r="B317" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C317" t="s">
+        <v>475</v>
+      </c>
+      <c r="D317" t="s">
         <v>476</v>
       </c>
-      <c r="D317" t="s">
-        <v>477</v>
-      </c>
       <c r="E317" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F317" t="s">
         <v>49</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J317" s="1" t="s">
         <v>367</v>
@@ -19008,37 +19018,37 @@
         <v>93</v>
       </c>
       <c r="B318" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C318" t="s">
+        <v>477</v>
+      </c>
+      <c r="D318" t="s">
         <v>478</v>
       </c>
-      <c r="D318" t="s">
+      <c r="E318" t="s">
+        <v>478</v>
+      </c>
+      <c r="F318" t="s">
+        <v>49</v>
+      </c>
+      <c r="I318" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="E318" t="s">
-        <v>479</v>
-      </c>
-      <c r="F318" t="s">
-        <v>49</v>
-      </c>
-      <c r="I318" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K318" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="L318" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M318" t="s">
         <v>384</v>
       </c>
       <c r="N318" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="P318" s="1" t="s">
         <v>78</v>
@@ -19067,37 +19077,37 @@
         <v>94</v>
       </c>
       <c r="B319" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C319" t="s">
+        <v>482</v>
+      </c>
+      <c r="D319" t="s">
+        <v>483</v>
+      </c>
+      <c r="E319" t="s">
         <v>484</v>
       </c>
-      <c r="D319" t="s">
+      <c r="F319" t="s">
+        <v>49</v>
+      </c>
+      <c r="I319" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="E319" t="s">
-        <v>486</v>
-      </c>
-      <c r="F319" t="s">
-        <v>49</v>
-      </c>
-      <c r="I319" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="J319" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K319" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="L319" t="s">
+        <v>486</v>
+      </c>
+      <c r="M319" t="s">
+        <v>487</v>
+      </c>
+      <c r="N319" t="s">
         <v>488</v>
-      </c>
-      <c r="M319" t="s">
-        <v>489</v>
-      </c>
-      <c r="N319" t="s">
-        <v>490</v>
       </c>
       <c r="P319" s="1" t="s">
         <v>78</v>
@@ -19126,37 +19136,37 @@
         <v>95</v>
       </c>
       <c r="B320" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C320" t="s">
+        <v>489</v>
+      </c>
+      <c r="D320" t="s">
+        <v>490</v>
+      </c>
+      <c r="E320" t="s">
         <v>491</v>
       </c>
-      <c r="D320" t="s">
+      <c r="F320" t="s">
+        <v>49</v>
+      </c>
+      <c r="I320" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E320" t="s">
+      <c r="J320" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F320" t="s">
-        <v>49</v>
-      </c>
-      <c r="I320" s="1" t="s">
+      <c r="K320" t="s">
+        <v>741</v>
+      </c>
+      <c r="L320" t="s">
         <v>494</v>
       </c>
-      <c r="J320" s="1" t="s">
+      <c r="M320" t="s">
         <v>495</v>
       </c>
-      <c r="K320" t="s">
-        <v>756</v>
-      </c>
-      <c r="L320" t="s">
+      <c r="N320" t="s">
         <v>496</v>
-      </c>
-      <c r="M320" t="s">
-        <v>497</v>
-      </c>
-      <c r="N320" t="s">
-        <v>498</v>
       </c>
       <c r="P320" s="1" t="s">
         <v>78</v>
@@ -19185,37 +19195,37 @@
         <v>96</v>
       </c>
       <c r="B321" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C321" t="s">
+        <v>497</v>
+      </c>
+      <c r="D321" t="s">
+        <v>498</v>
+      </c>
+      <c r="E321" t="s">
+        <v>498</v>
+      </c>
+      <c r="F321" t="s">
+        <v>49</v>
+      </c>
+      <c r="I321" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="D321" t="s">
-        <v>500</v>
-      </c>
-      <c r="E321" t="s">
-        <v>500</v>
-      </c>
-      <c r="F321" t="s">
-        <v>49</v>
-      </c>
-      <c r="I321" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="J321" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="L321" t="s">
+        <v>500</v>
+      </c>
+      <c r="M321" t="s">
+        <v>501</v>
+      </c>
+      <c r="N321" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M321" t="s">
-        <v>503</v>
-      </c>
-      <c r="N321" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P321" s="1" t="s">
         <v>78</v>
@@ -19224,7 +19234,7 @@
         <v>33</v>
       </c>
       <c r="R321" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U321" t="s">
         <v>35</v>
@@ -19236,7 +19246,7 @@
         <v>352</v>
       </c>
       <c r="X321" s="1" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
     </row>
     <row r="322" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19244,37 +19254,37 @@
         <v>97</v>
       </c>
       <c r="B322" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C322" t="s">
+        <v>504</v>
+      </c>
+      <c r="D322" t="s">
+        <v>505</v>
+      </c>
+      <c r="E322" t="s">
+        <v>505</v>
+      </c>
+      <c r="F322" t="s">
+        <v>49</v>
+      </c>
+      <c r="I322" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="D322" t="s">
-        <v>507</v>
-      </c>
-      <c r="E322" t="s">
-        <v>507</v>
-      </c>
-      <c r="F322" t="s">
-        <v>49</v>
-      </c>
-      <c r="I322" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K322" s="1" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="L322" t="s">
+        <v>500</v>
+      </c>
+      <c r="M322" t="s">
+        <v>501</v>
+      </c>
+      <c r="N322" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M322" t="s">
-        <v>503</v>
-      </c>
-      <c r="N322" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P322" s="1" t="s">
         <v>78</v>
@@ -19283,7 +19293,7 @@
         <v>33</v>
       </c>
       <c r="R322" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U322" t="s">
         <v>35</v>
@@ -19295,7 +19305,7 @@
         <v>352</v>
       </c>
       <c r="X322" s="1" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
     </row>
     <row r="323" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19303,37 +19313,37 @@
         <v>98</v>
       </c>
       <c r="B323" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C323" t="s">
+        <v>507</v>
+      </c>
+      <c r="D323" t="s">
+        <v>508</v>
+      </c>
+      <c r="E323" t="s">
+        <v>508</v>
+      </c>
+      <c r="F323" t="s">
+        <v>49</v>
+      </c>
+      <c r="I323" t="s">
         <v>509</v>
-      </c>
-      <c r="D323" t="s">
-        <v>510</v>
-      </c>
-      <c r="E323" t="s">
-        <v>510</v>
-      </c>
-      <c r="F323" t="s">
-        <v>49</v>
-      </c>
-      <c r="I323" t="s">
-        <v>511</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K323" s="1" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="L323" t="s">
+        <v>500</v>
+      </c>
+      <c r="M323" t="s">
+        <v>501</v>
+      </c>
+      <c r="N323" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="M323" t="s">
-        <v>503</v>
-      </c>
-      <c r="N323" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="P323" s="1" t="s">
         <v>78</v>
@@ -19342,7 +19352,7 @@
         <v>33</v>
       </c>
       <c r="R323" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="U323" t="s">
         <v>35</v>
@@ -19354,7 +19364,7 @@
         <v>352</v>
       </c>
       <c r="X323" s="1" t="s">
-        <v>760</v>
+        <v>745</v>
       </c>
     </row>
     <row r="324" spans="1:24" x14ac:dyDescent="0.25">
@@ -19362,22 +19372,22 @@
         <v>99</v>
       </c>
       <c r="B324" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C324" t="s">
+        <v>510</v>
+      </c>
+      <c r="D324" t="s">
+        <v>511</v>
+      </c>
+      <c r="E324" t="s">
+        <v>511</v>
+      </c>
+      <c r="F324" t="s">
+        <v>49</v>
+      </c>
+      <c r="I324" t="s">
         <v>512</v>
-      </c>
-      <c r="D324" t="s">
-        <v>513</v>
-      </c>
-      <c r="E324" t="s">
-        <v>513</v>
-      </c>
-      <c r="F324" t="s">
-        <v>49</v>
-      </c>
-      <c r="I324" t="s">
-        <v>514</v>
       </c>
       <c r="K324" t="s">
         <v>41</v>
@@ -19400,22 +19410,22 @@
         <v>100</v>
       </c>
       <c r="B325" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C325" t="s">
+        <v>513</v>
+      </c>
+      <c r="D325" t="s">
+        <v>514</v>
+      </c>
+      <c r="E325" t="s">
+        <v>514</v>
+      </c>
+      <c r="F325" t="s">
+        <v>49</v>
+      </c>
+      <c r="I325" t="s">
         <v>515</v>
-      </c>
-      <c r="D325" t="s">
-        <v>516</v>
-      </c>
-      <c r="E325" t="s">
-        <v>516</v>
-      </c>
-      <c r="F325" t="s">
-        <v>49</v>
-      </c>
-      <c r="I325" t="s">
-        <v>517</v>
       </c>
       <c r="K325" t="s">
         <v>41</v>
@@ -19438,22 +19448,22 @@
         <v>101</v>
       </c>
       <c r="B326" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C326" t="s">
+        <v>516</v>
+      </c>
+      <c r="D326" t="s">
+        <v>517</v>
+      </c>
+      <c r="E326" t="s">
+        <v>517</v>
+      </c>
+      <c r="F326" t="s">
+        <v>49</v>
+      </c>
+      <c r="I326" t="s">
         <v>518</v>
-      </c>
-      <c r="D326" t="s">
-        <v>519</v>
-      </c>
-      <c r="E326" t="s">
-        <v>519</v>
-      </c>
-      <c r="F326" t="s">
-        <v>49</v>
-      </c>
-      <c r="I326" t="s">
-        <v>520</v>
       </c>
       <c r="K326" t="s">
         <v>41</v>
@@ -19476,22 +19486,22 @@
         <v>102</v>
       </c>
       <c r="B327" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C327" t="s">
+        <v>519</v>
+      </c>
+      <c r="D327" t="s">
+        <v>520</v>
+      </c>
+      <c r="E327" t="s">
+        <v>520</v>
+      </c>
+      <c r="F327" t="s">
+        <v>49</v>
+      </c>
+      <c r="I327" t="s">
         <v>521</v>
-      </c>
-      <c r="D327" t="s">
-        <v>522</v>
-      </c>
-      <c r="E327" t="s">
-        <v>522</v>
-      </c>
-      <c r="F327" t="s">
-        <v>49</v>
-      </c>
-      <c r="I327" t="s">
-        <v>523</v>
       </c>
       <c r="K327" t="s">
         <v>41</v>
@@ -19514,22 +19524,22 @@
         <v>103</v>
       </c>
       <c r="B328" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C328" t="s">
+        <v>522</v>
+      </c>
+      <c r="D328" t="s">
+        <v>523</v>
+      </c>
+      <c r="E328" t="s">
+        <v>523</v>
+      </c>
+      <c r="F328" t="s">
+        <v>49</v>
+      </c>
+      <c r="I328" t="s">
         <v>524</v>
-      </c>
-      <c r="D328" t="s">
-        <v>525</v>
-      </c>
-      <c r="E328" t="s">
-        <v>525</v>
-      </c>
-      <c r="F328" t="s">
-        <v>49</v>
-      </c>
-      <c r="I328" t="s">
-        <v>526</v>
       </c>
       <c r="K328" t="s">
         <v>41</v>
@@ -19552,34 +19562,34 @@
         <v>104</v>
       </c>
       <c r="B329" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C329" t="s">
+        <v>525</v>
+      </c>
+      <c r="D329" t="s">
+        <v>526</v>
+      </c>
+      <c r="E329" t="s">
+        <v>526</v>
+      </c>
+      <c r="F329" t="s">
+        <v>49</v>
+      </c>
+      <c r="I329" t="s">
+        <v>515</v>
+      </c>
+      <c r="K329" t="s">
+        <v>771</v>
+      </c>
+      <c r="L329" t="s">
         <v>527</v>
       </c>
-      <c r="D329" t="s">
+      <c r="M329" t="s">
         <v>528</v>
       </c>
-      <c r="E329" t="s">
-        <v>528</v>
-      </c>
-      <c r="F329" t="s">
-        <v>49</v>
-      </c>
-      <c r="I329" t="s">
-        <v>517</v>
-      </c>
-      <c r="K329" t="s">
-        <v>585</v>
-      </c>
-      <c r="L329" t="s">
+      <c r="N329" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="M329" t="s">
-        <v>530</v>
-      </c>
-      <c r="N329" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="P329" s="1" t="s">
         <v>78</v>
@@ -19588,7 +19598,7 @@
         <v>79</v>
       </c>
       <c r="R329" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="U329" t="s">
         <v>35</v>
@@ -19608,22 +19618,22 @@
         <v>105</v>
       </c>
       <c r="B330" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C330" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D330" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E330" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F330" t="s">
         <v>49</v>
       </c>
       <c r="I330" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K330" t="s">
         <v>41</v>
@@ -19646,25 +19656,25 @@
         <v>106</v>
       </c>
       <c r="B331" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C331" t="s">
+        <v>533</v>
+      </c>
+      <c r="D331" t="s">
+        <v>534</v>
+      </c>
+      <c r="E331" t="s">
         <v>535</v>
       </c>
-      <c r="D331" t="s">
+      <c r="F331" t="s">
+        <v>49</v>
+      </c>
+      <c r="I331" t="s">
         <v>536</v>
       </c>
-      <c r="E331" t="s">
+      <c r="J331" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="F331" t="s">
-        <v>49</v>
-      </c>
-      <c r="I331" t="s">
-        <v>538</v>
-      </c>
-      <c r="J331" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="K331" t="s">
         <v>41</v>
@@ -19687,25 +19697,25 @@
         <v>107</v>
       </c>
       <c r="B332" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C332" t="s">
+        <v>539</v>
+      </c>
+      <c r="D332" t="s">
+        <v>540</v>
+      </c>
+      <c r="E332" t="s">
         <v>541</v>
       </c>
-      <c r="D332" t="s">
+      <c r="F332" t="s">
+        <v>49</v>
+      </c>
+      <c r="I332" t="s">
+        <v>536</v>
+      </c>
+      <c r="J332" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="E332" t="s">
-        <v>543</v>
-      </c>
-      <c r="F332" t="s">
-        <v>49</v>
-      </c>
-      <c r="I332" t="s">
-        <v>538</v>
-      </c>
-      <c r="J332" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="K332" t="s">
         <v>41</v>
@@ -19728,25 +19738,25 @@
         <v>108</v>
       </c>
       <c r="B333" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C333" t="s">
+        <v>543</v>
+      </c>
+      <c r="D333" t="s">
+        <v>544</v>
+      </c>
+      <c r="E333" t="s">
         <v>545</v>
       </c>
-      <c r="D333" t="s">
+      <c r="F333" t="s">
+        <v>49</v>
+      </c>
+      <c r="I333" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E333" t="s">
+      <c r="J333" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="F333" t="s">
-        <v>49</v>
-      </c>
-      <c r="I333" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J333" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="K333" t="s">
         <v>41</v>
@@ -19769,37 +19779,37 @@
         <v>109</v>
       </c>
       <c r="B334" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C334" t="s">
+        <v>548</v>
+      </c>
+      <c r="D334" t="s">
+        <v>549</v>
+      </c>
+      <c r="E334" t="s">
         <v>550</v>
       </c>
-      <c r="D334" t="s">
+      <c r="F334" t="s">
+        <v>49</v>
+      </c>
+      <c r="I334" t="s">
         <v>551</v>
       </c>
-      <c r="E334" t="s">
+      <c r="J334" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="K334" t="s">
+        <v>746</v>
+      </c>
+      <c r="L334" t="s">
         <v>552</v>
       </c>
-      <c r="F334" t="s">
-        <v>49</v>
-      </c>
-      <c r="I334" t="s">
+      <c r="M334" t="s">
         <v>553</v>
       </c>
-      <c r="J334" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K334" t="s">
-        <v>761</v>
-      </c>
-      <c r="L334" t="s">
+      <c r="N334" t="s">
         <v>554</v>
-      </c>
-      <c r="M334" t="s">
-        <v>555</v>
-      </c>
-      <c r="N334" t="s">
-        <v>556</v>
       </c>
       <c r="P334" s="1" t="s">
         <v>78</v>
@@ -19808,7 +19818,7 @@
         <v>33</v>
       </c>
       <c r="R334" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="U334" t="s">
         <v>35</v>
@@ -19820,7 +19830,7 @@
         <v>68</v>
       </c>
       <c r="X334" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="335" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19828,37 +19838,37 @@
         <v>110</v>
       </c>
       <c r="B335" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C335" t="s">
+        <v>557</v>
+      </c>
+      <c r="D335" t="s">
+        <v>558</v>
+      </c>
+      <c r="E335" t="s">
         <v>559</v>
       </c>
-      <c r="D335" t="s">
+      <c r="F335" t="s">
+        <v>49</v>
+      </c>
+      <c r="I335" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E335" t="s">
+      <c r="J335" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="K335" t="s">
+        <v>747</v>
+      </c>
+      <c r="L335" t="s">
         <v>561</v>
       </c>
-      <c r="F335" t="s">
-        <v>49</v>
-      </c>
-      <c r="I335" s="1" t="s">
+      <c r="M335" t="s">
         <v>562</v>
       </c>
-      <c r="J335" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K335" t="s">
-        <v>762</v>
-      </c>
-      <c r="L335" t="s">
+      <c r="N335" t="s">
         <v>563</v>
-      </c>
-      <c r="M335" t="s">
-        <v>564</v>
-      </c>
-      <c r="N335" t="s">
-        <v>565</v>
       </c>
       <c r="P335" s="1" t="s">
         <v>78</v>
@@ -19867,10 +19877,10 @@
         <v>33</v>
       </c>
       <c r="R335" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="T335" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="U335" t="s">
         <v>35</v>
@@ -19882,7 +19892,7 @@
         <v>68</v>
       </c>
       <c r="X335" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="336" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19890,22 +19900,22 @@
         <v>111</v>
       </c>
       <c r="B336" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C336" t="s">
+        <v>567</v>
+      </c>
+      <c r="D336" t="s">
+        <v>568</v>
+      </c>
+      <c r="E336" t="s">
         <v>569</v>
-      </c>
-      <c r="D336" t="s">
-        <v>570</v>
-      </c>
-      <c r="E336" t="s">
-        <v>571</v>
       </c>
       <c r="F336" t="s">
         <v>112</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="U336" t="s">
         <v>35</v>
@@ -19917,33 +19927,33 @@
         <v>59</v>
       </c>
       <c r="X336" s="1" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="337" spans="1:24" ht="285" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="337" spans="1:24" ht="270" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>112</v>
       </c>
       <c r="B337" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C337" t="s">
+        <v>570</v>
+      </c>
+      <c r="D337" t="s">
+        <v>571</v>
+      </c>
+      <c r="E337" t="s">
         <v>572</v>
       </c>
-      <c r="D337" t="s">
+      <c r="F337" t="s">
+        <v>49</v>
+      </c>
+      <c r="G337" t="s">
         <v>573</v>
       </c>
-      <c r="E337" t="s">
-        <v>574</v>
-      </c>
-      <c r="F337" t="s">
-        <v>49</v>
-      </c>
-      <c r="G337" t="s">
-        <v>575</v>
-      </c>
       <c r="K337" s="1" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="U337" t="s">
         <v>35</v>
@@ -19955,7 +19965,7 @@
         <v>59</v>
       </c>
       <c r="X337" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
   </sheetData>

--- a/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA1C5AB-0FD5-4484-A21C-B1A99AE19AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D478739-D2F8-4F06-B5BF-457DD2E2C657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95E6C139-84C6-42BA-8CBB-FF1D79072BFF}"/>
   </bookViews>
@@ -2274,18 +2274,6 @@
     <t>pa_running_w2</t>
   </si>
   <si>
-    <t>dis_vigorous_w2;
-dis_moderate_w2;
-dis_lift_w2;
-dis_climbseveral_w2;
-dis_climbone_w2;
-dis_bending_w2;
-dis_walk2km__w2;
-dis_walk1km__w2;
-dis_walk100m__w2;
-dis_bath_w2</t>
-  </si>
-  <si>
     <t>DOM_w3</t>
   </si>
   <si>
@@ -2544,18 +2532,6 @@
     <t>pa_running_w3</t>
   </si>
   <si>
-    <t>dis_vigorous_w3;
-dis_moderate_w3;
-dis_lift_w3;
-dis_climbseveral_w3;
-dis_climbone_w3;
-dis_bending_w3;
-dis_walk2km__w3;
-dis_walk1km__w3;
-dis_walk100m__w3;
-dis_bath_w3</t>
-  </si>
-  <si>
     <t>DOM_w4</t>
   </si>
   <si>
@@ -2812,18 +2788,6 @@
   </si>
   <si>
     <t>pa_running_w4</t>
-  </si>
-  <si>
-    <t>dis_vigorous_w4;
-dis_moderate_w4;
-dis_lift_w4;
-dis_climbseveral_w4;
-dis_climbone_w4;
-dis_bending_w4;
-dis_walk2km__w4;
-dis_walk1km__w4;
-dis_walk100m__w4;
-dis_bath_w4</t>
   </si>
   <si>
     <t>waist_mean_w3</t>
@@ -3313,6 +3277,42 @@
   </si>
   <si>
     <t>round(rowMeans(select(., systolicBP_right_w4, systolicBP_left_w4), na.rm=TRUE), 2)</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w2;
+dis_moderate_w2;
+dis_lift_w2;
+dis_climbseveral_w2;
+dis_climbone_w2;
+dis_bending_w2;
+dis_walk2km_w2;
+dis_walk1km_w2;
+dis_walk100m_w2;
+dis_bath_w2</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w3;
+dis_moderate_w3;
+dis_lift_w3;
+dis_climbseveral_w3;
+dis_climbone_w3;
+dis_bending_w3;
+dis_walk2km_w3;
+dis_walk1km_w3;
+dis_walk100m_w3;
+dis_bath_w3</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w4;
+dis_moderate_w4;
+dis_lift_w4;
+dis_climbseveral_w4;
+dis_climbone_w4;
+dis_bending_w4;
+dis_walk2km_w4;
+dis_walk1km_w4;
+dis_walk100m_w4;
+dis_bath_w4</t>
   </si>
 </sst>
 </file>
@@ -3687,6 +3687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F369A59-9712-47DB-8DA9-54F6F198C8F2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X337"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3768,7 +3769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3824,7 +3825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3862,7 +3863,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3900,7 +3901,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3938,7 +3939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3988,7 +3989,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4035,7 +4036,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4094,7 +4095,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="345" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4176,7 +4177,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4238,7 +4239,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4300,7 +4301,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4338,7 +4339,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4373,7 +4374,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4435,7 +4436,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4491,7 +4492,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4532,7 +4533,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4594,7 +4595,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4632,7 +4633,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4694,7 +4695,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4732,7 +4733,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4794,7 +4795,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4859,7 +4860,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4918,7 +4919,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4977,7 +4978,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5012,7 +5013,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5071,7 +5072,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5130,7 +5131,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5171,7 +5172,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5212,7 +5213,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5250,7 +5251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5288,7 +5289,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5326,7 +5327,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5373,7 +5374,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5420,7 +5421,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5467,7 +5468,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5511,7 +5512,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5558,7 +5559,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5605,7 +5606,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5646,7 +5647,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5687,7 +5688,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5728,7 +5729,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5784,7 +5785,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5822,7 +5823,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5913,7 +5914,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="270" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5972,7 +5973,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6013,7 +6014,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="240" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6054,7 +6055,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6113,7 +6114,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="390" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6172,7 +6173,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6231,7 +6232,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6272,7 +6273,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6331,7 +6332,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6428,7 +6429,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6469,7 +6470,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6510,7 +6511,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6572,7 +6573,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="60" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6631,7 +6632,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="61" spans="1:24" ht="390" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6693,7 +6694,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6755,7 +6756,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6817,7 +6818,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6876,7 +6877,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6935,7 +6936,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6994,7 +6995,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7053,7 +7054,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7094,7 +7095,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7153,7 +7154,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="70" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7191,10 +7192,10 @@
         <v>352</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="71" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7256,7 +7257,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="72" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7318,7 +7319,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7380,7 +7381,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7406,7 +7407,7 @@
         <v>367</v>
       </c>
       <c r="K74" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="L74" t="s">
         <v>436</v>
@@ -7439,7 +7440,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="75" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7480,7 +7481,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7521,7 +7522,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7562,7 +7563,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7603,7 +7604,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7644,7 +7645,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7685,7 +7686,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7726,7 +7727,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7767,7 +7768,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7808,7 +7809,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7849,7 +7850,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7890,7 +7891,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7931,7 +7932,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7972,7 +7973,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -8013,7 +8014,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="90" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8095,7 +8096,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -8136,7 +8137,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="92" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -8177,7 +8178,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -8218,7 +8219,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -8244,7 +8245,7 @@
         <v>367</v>
       </c>
       <c r="K94" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L94" t="s">
         <v>480</v>
@@ -8277,7 +8278,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -8336,7 +8337,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -8395,7 +8396,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -8451,10 +8452,10 @@
         <v>352</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="98" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -8510,10 +8511,10 @@
         <v>352</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="99" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -8569,10 +8570,10 @@
         <v>352</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8610,7 +8611,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8648,7 +8649,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8686,7 +8687,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8724,7 +8725,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8762,7 +8763,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="105" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8818,7 +8819,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8856,7 +8857,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="107" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8900,7 +8901,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="108" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8941,7 +8942,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8982,7 +8983,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="110" spans="1:24" ht="285" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:24" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -9041,7 +9042,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="111" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -9123,7 +9124,7 @@
         <v>112</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>638</v>
+        <v>772</v>
       </c>
       <c r="U112" t="s">
         <v>35</v>
@@ -9135,7 +9136,7 @@
         <v>59</v>
       </c>
       <c r="X112" s="1" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="113" spans="1:24" ht="270" x14ac:dyDescent="0.25">
@@ -9161,7 +9162,7 @@
         <v>573</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>638</v>
+        <v>772</v>
       </c>
       <c r="U113" t="s">
         <v>35</v>
@@ -9173,10 +9174,10 @@
         <v>59</v>
       </c>
       <c r="X113" s="1" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1</v>
       </c>
@@ -9220,7 +9221,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2</v>
       </c>
@@ -9258,7 +9259,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>3</v>
       </c>
@@ -9296,7 +9297,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>4</v>
       </c>
@@ -9334,7 +9335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>5</v>
       </c>
@@ -9360,7 +9361,7 @@
         <v>56</v>
       </c>
       <c r="K118" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L118" t="s">
         <v>57</v>
@@ -9381,10 +9382,10 @@
         <v>59</v>
       </c>
       <c r="X118" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="119" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>6</v>
       </c>
@@ -9431,7 +9432,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>7</v>
       </c>
@@ -9457,7 +9458,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L120" t="s">
         <v>75</v>
@@ -9490,7 +9491,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" spans="1:24" ht="345" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:24" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>8</v>
       </c>
@@ -9531,7 +9532,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="122" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>9</v>
       </c>
@@ -9572,7 +9573,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>10</v>
       </c>
@@ -9598,7 +9599,7 @@
         <v>96</v>
       </c>
       <c r="K123" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L123" t="s">
         <v>97</v>
@@ -9634,7 +9635,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="124" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>11</v>
       </c>
@@ -9660,7 +9661,7 @@
         <v>107</v>
       </c>
       <c r="K124" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L124" t="s">
         <v>97</v>
@@ -9696,7 +9697,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>12</v>
       </c>
@@ -9734,7 +9735,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>13</v>
       </c>
@@ -9769,7 +9770,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>14</v>
       </c>
@@ -9795,7 +9796,7 @@
         <v>121</v>
       </c>
       <c r="K127" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L127" t="s">
         <v>97</v>
@@ -9831,7 +9832,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>15</v>
       </c>
@@ -9854,7 +9855,7 @@
         <v>125</v>
       </c>
       <c r="K128" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L128" t="s">
         <v>126</v>
@@ -9887,7 +9888,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="129" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>16</v>
       </c>
@@ -9928,7 +9929,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="130" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>17</v>
       </c>
@@ -9954,7 +9955,7 @@
         <v>139</v>
       </c>
       <c r="K130" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L130" t="s">
         <v>140</v>
@@ -9990,7 +9991,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>18</v>
       </c>
@@ -10013,7 +10014,7 @@
         <v>146</v>
       </c>
       <c r="K131" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="U131" t="s">
         <v>35</v>
@@ -10025,10 +10026,10 @@
         <v>59</v>
       </c>
       <c r="X131" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="132" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>19</v>
       </c>
@@ -10054,7 +10055,7 @@
         <v>139</v>
       </c>
       <c r="K132" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="L132" t="s">
         <v>150</v>
@@ -10090,7 +10091,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>20</v>
       </c>
@@ -10113,7 +10114,7 @@
         <v>146</v>
       </c>
       <c r="K133" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="U133" t="s">
         <v>35</v>
@@ -10125,10 +10126,10 @@
         <v>59</v>
       </c>
       <c r="X133" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="134" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>21</v>
       </c>
@@ -10154,7 +10155,7 @@
         <v>158</v>
       </c>
       <c r="K134" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="L134" t="s">
         <v>159</v>
@@ -10190,7 +10191,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>22</v>
       </c>
@@ -10216,7 +10217,7 @@
         <v>139</v>
       </c>
       <c r="K135" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="L135" t="s">
         <v>164</v>
@@ -10252,7 +10253,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>23</v>
       </c>
@@ -10275,7 +10276,7 @@
         <v>146</v>
       </c>
       <c r="K136" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="L136" t="s">
         <v>164</v>
@@ -10305,10 +10306,10 @@
         <v>59</v>
       </c>
       <c r="X136" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>24</v>
       </c>
@@ -10331,7 +10332,7 @@
         <v>173</v>
       </c>
       <c r="K137" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="L137" t="s">
         <v>174</v>
@@ -10361,10 +10362,10 @@
         <v>59</v>
       </c>
       <c r="X137" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>25</v>
       </c>
@@ -10384,7 +10385,7 @@
         <v>26</v>
       </c>
       <c r="K138" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="U138" t="s">
         <v>35</v>
@@ -10396,10 +10397,10 @@
         <v>59</v>
       </c>
       <c r="X138" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="139" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>26</v>
       </c>
@@ -10425,7 +10426,7 @@
         <v>184</v>
       </c>
       <c r="K139" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L139" t="s">
         <v>185</v>
@@ -10455,10 +10456,10 @@
         <v>59</v>
       </c>
       <c r="X139" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="140" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>27</v>
       </c>
@@ -10484,7 +10485,7 @@
         <v>184</v>
       </c>
       <c r="K140" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L140" t="s">
         <v>191</v>
@@ -10514,10 +10515,10 @@
         <v>59</v>
       </c>
       <c r="X140" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>28</v>
       </c>
@@ -10558,7 +10559,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>29</v>
       </c>
@@ -10599,7 +10600,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="143" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>30</v>
       </c>
@@ -10637,7 +10638,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>31</v>
       </c>
@@ -10675,7 +10676,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>32</v>
       </c>
@@ -10713,7 +10714,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>33</v>
       </c>
@@ -10736,7 +10737,7 @@
         <v>211</v>
       </c>
       <c r="K146" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L146" t="s">
         <v>210</v>
@@ -10760,7 +10761,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>34</v>
       </c>
@@ -10783,7 +10784,7 @@
         <v>211</v>
       </c>
       <c r="K147" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L147" t="s">
         <v>215</v>
@@ -10807,7 +10808,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>35</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>211</v>
       </c>
       <c r="K148" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L148" t="s">
         <v>219</v>
@@ -10854,7 +10855,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>36</v>
       </c>
@@ -10880,7 +10881,7 @@
         <v>224</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L149" s="1" t="s">
         <v>225</v>
@@ -10895,10 +10896,10 @@
         <v>59</v>
       </c>
       <c r="X149" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>37</v>
       </c>
@@ -10921,7 +10922,7 @@
         <v>211</v>
       </c>
       <c r="K150" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="L150" t="s">
         <v>227</v>
@@ -10945,7 +10946,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>38</v>
       </c>
@@ -10968,7 +10969,7 @@
         <v>232</v>
       </c>
       <c r="K151" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L151" t="s">
         <v>231</v>
@@ -10992,7 +10993,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="152" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>39</v>
       </c>
@@ -11033,7 +11034,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="153" spans="1:24" ht="75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>40</v>
       </c>
@@ -11074,7 +11075,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>41</v>
       </c>
@@ -11115,7 +11116,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="155" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>42</v>
       </c>
@@ -11141,7 +11142,7 @@
         <v>244</v>
       </c>
       <c r="K155" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L155" t="s">
         <v>252</v>
@@ -11171,7 +11172,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>43</v>
       </c>
@@ -11209,7 +11210,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>44</v>
       </c>
@@ -11235,7 +11236,7 @@
         <v>263</v>
       </c>
       <c r="K157" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L157" t="s">
         <v>264</v>
@@ -11262,7 +11263,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="158" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>45</v>
       </c>
@@ -11300,7 +11301,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="159" spans="1:24" ht="270" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:24" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>46</v>
       </c>
@@ -11326,7 +11327,7 @@
         <v>273</v>
       </c>
       <c r="K159" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="L159" t="s">
         <v>274</v>
@@ -11359,7 +11360,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="160" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>47</v>
       </c>
@@ -11418,7 +11419,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" spans="1:24" ht="240" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:24" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>48</v>
       </c>
@@ -11459,7 +11460,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="162" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>49</v>
       </c>
@@ -11482,7 +11483,7 @@
         <v>113</v>
       </c>
       <c r="K162" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L162" t="s">
         <v>289</v>
@@ -11518,7 +11519,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="163" spans="1:24" ht="390" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>50</v>
       </c>
@@ -11544,7 +11545,7 @@
         <v>299</v>
       </c>
       <c r="K163" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L163" t="s">
         <v>289</v>
@@ -11577,7 +11578,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="164" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>51</v>
       </c>
@@ -11603,7 +11604,7 @@
         <v>304</v>
       </c>
       <c r="K164" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L164" t="s">
         <v>305</v>
@@ -11636,7 +11637,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="165" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>52</v>
       </c>
@@ -11677,7 +11678,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="166" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>53</v>
       </c>
@@ -11700,7 +11701,7 @@
         <v>313</v>
       </c>
       <c r="K166" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L166" t="s">
         <v>316</v>
@@ -11736,7 +11737,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>54</v>
       </c>
@@ -11774,7 +11775,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="168" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>55</v>
       </c>
@@ -11797,7 +11798,7 @@
         <v>328</v>
       </c>
       <c r="K168" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L168" t="s">
         <v>329</v>
@@ -11830,10 +11831,10 @@
         <v>59</v>
       </c>
       <c r="X168" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="169" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>56</v>
       </c>
@@ -11874,7 +11875,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="170" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>57</v>
       </c>
@@ -11915,7 +11916,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="171" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>58</v>
       </c>
@@ -11941,7 +11942,7 @@
         <v>312</v>
       </c>
       <c r="K171" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L171" s="1" t="s">
         <v>343</v>
@@ -11971,10 +11972,10 @@
         <v>59</v>
       </c>
       <c r="X171" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="172" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>59</v>
       </c>
@@ -11997,7 +11998,7 @@
         <v>350</v>
       </c>
       <c r="K172" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L172" s="1" t="s">
         <v>343</v>
@@ -12027,10 +12028,10 @@
         <v>352</v>
       </c>
       <c r="X172" s="1" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="173" spans="1:24" ht="390" x14ac:dyDescent="0.25">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>60</v>
       </c>
@@ -12056,7 +12057,7 @@
         <v>356</v>
       </c>
       <c r="K173" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L173" t="s">
         <v>358</v>
@@ -12092,7 +12093,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="174" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>61</v>
       </c>
@@ -12118,7 +12119,7 @@
         <v>367</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L174" t="s">
         <v>368</v>
@@ -12151,10 +12152,10 @@
         <v>352</v>
       </c>
       <c r="X174" s="1" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="175" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>62</v>
       </c>
@@ -12180,7 +12181,7 @@
         <v>367</v>
       </c>
       <c r="K175" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L175" t="s">
         <v>377</v>
@@ -12216,7 +12217,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="176" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>63</v>
       </c>
@@ -12242,7 +12243,7 @@
         <v>367</v>
       </c>
       <c r="K176" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L176" t="s">
         <v>377</v>
@@ -12275,7 +12276,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="177" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>64</v>
       </c>
@@ -12301,7 +12302,7 @@
         <v>367</v>
       </c>
       <c r="K177" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="L177" t="s">
         <v>389</v>
@@ -12334,7 +12335,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="178" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>65</v>
       </c>
@@ -12360,7 +12361,7 @@
         <v>367</v>
       </c>
       <c r="K178" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="L178" t="s">
         <v>394</v>
@@ -12393,7 +12394,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="179" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>66</v>
       </c>
@@ -12419,7 +12420,7 @@
         <v>367</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L179" t="s">
         <v>368</v>
@@ -12452,7 +12453,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>67</v>
       </c>
@@ -12493,7 +12494,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="181" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>68</v>
       </c>
@@ -12519,7 +12520,7 @@
         <v>367</v>
       </c>
       <c r="K181" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L181" t="s">
         <v>406</v>
@@ -12552,7 +12553,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="182" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>69</v>
       </c>
@@ -12578,7 +12579,7 @@
         <v>367</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="U182" t="s">
         <v>35</v>
@@ -12590,10 +12591,10 @@
         <v>352</v>
       </c>
       <c r="X182" s="1" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="183" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>70</v>
       </c>
@@ -12619,7 +12620,7 @@
         <v>367</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L183" s="1" t="s">
         <v>415</v>
@@ -12652,10 +12653,10 @@
         <v>352</v>
       </c>
       <c r="X183" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="184" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>71</v>
       </c>
@@ -12681,7 +12682,7 @@
         <v>367</v>
       </c>
       <c r="K184" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L184" t="s">
         <v>425</v>
@@ -12717,7 +12718,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="185" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>72</v>
       </c>
@@ -12743,7 +12744,7 @@
         <v>432</v>
       </c>
       <c r="K185" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L185" t="s">
         <v>425</v>
@@ -12779,7 +12780,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="186" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>73</v>
       </c>
@@ -12805,7 +12806,7 @@
         <v>367</v>
       </c>
       <c r="K186" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L186" t="s">
         <v>436</v>
@@ -12838,7 +12839,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="187" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>74</v>
       </c>
@@ -12879,7 +12880,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="188" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>75</v>
       </c>
@@ -12920,7 +12921,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="189" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>76</v>
       </c>
@@ -12961,7 +12962,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="190" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>77</v>
       </c>
@@ -13002,7 +13003,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>78</v>
       </c>
@@ -13043,7 +13044,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="192" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>79</v>
       </c>
@@ -13084,7 +13085,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="193" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>80</v>
       </c>
@@ -13125,7 +13126,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="194" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>81</v>
       </c>
@@ -13166,7 +13167,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="195" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>82</v>
       </c>
@@ -13207,7 +13208,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="196" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>83</v>
       </c>
@@ -13248,7 +13249,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="197" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>84</v>
       </c>
@@ -13289,7 +13290,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="198" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>85</v>
       </c>
@@ -13330,7 +13331,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="199" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>86</v>
       </c>
@@ -13371,7 +13372,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="200" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>87</v>
       </c>
@@ -13412,7 +13413,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="201" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>88</v>
       </c>
@@ -13453,7 +13454,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="202" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>89</v>
       </c>
@@ -13494,7 +13495,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="203" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>90</v>
       </c>
@@ -13535,7 +13536,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="204" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>91</v>
       </c>
@@ -13576,7 +13577,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="205" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>92</v>
       </c>
@@ -13617,7 +13618,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>93</v>
       </c>
@@ -13643,7 +13644,7 @@
         <v>367</v>
       </c>
       <c r="K206" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L206" t="s">
         <v>480</v>
@@ -13676,7 +13677,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="207" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>94</v>
       </c>
@@ -13702,7 +13703,7 @@
         <v>367</v>
       </c>
       <c r="K207" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L207" t="s">
         <v>486</v>
@@ -13735,7 +13736,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="208" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>95</v>
       </c>
@@ -13761,7 +13762,7 @@
         <v>493</v>
       </c>
       <c r="K208" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L208" t="s">
         <v>494</v>
@@ -13794,7 +13795,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="209" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>96</v>
       </c>
@@ -13820,7 +13821,7 @@
         <v>367</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L209" t="s">
         <v>500</v>
@@ -13850,10 +13851,10 @@
         <v>352</v>
       </c>
       <c r="X209" s="1" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="210" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="210" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>97</v>
       </c>
@@ -13879,7 +13880,7 @@
         <v>367</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L210" t="s">
         <v>500</v>
@@ -13909,10 +13910,10 @@
         <v>352</v>
       </c>
       <c r="X210" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="211" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="211" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>98</v>
       </c>
@@ -13938,7 +13939,7 @@
         <v>367</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L211" t="s">
         <v>500</v>
@@ -13968,10 +13969,10 @@
         <v>352</v>
       </c>
       <c r="X211" s="1" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="212" spans="1:24" x14ac:dyDescent="0.25">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="212" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>99</v>
       </c>
@@ -14009,7 +14010,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="213" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>100</v>
       </c>
@@ -14047,7 +14048,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="214" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>101</v>
       </c>
@@ -14085,7 +14086,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="215" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>102</v>
       </c>
@@ -14123,7 +14124,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="216" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>103</v>
       </c>
@@ -14161,7 +14162,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="217" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>104</v>
       </c>
@@ -14184,7 +14185,7 @@
         <v>515</v>
       </c>
       <c r="K217" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L217" t="s">
         <v>527</v>
@@ -14217,7 +14218,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>105</v>
       </c>
@@ -14255,7 +14256,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="219" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>106</v>
       </c>
@@ -14296,7 +14297,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="220" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>107</v>
       </c>
@@ -14337,7 +14338,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="221" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>108</v>
       </c>
@@ -14378,7 +14379,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="222" spans="1:24" ht="285" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:24" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>109</v>
       </c>
@@ -14404,7 +14405,7 @@
         <v>547</v>
       </c>
       <c r="K222" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="L222" t="s">
         <v>552</v>
@@ -14437,7 +14438,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="223" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>110</v>
       </c>
@@ -14463,7 +14464,7 @@
         <v>547</v>
       </c>
       <c r="K223" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="L223" t="s">
         <v>561</v>
@@ -14519,7 +14520,7 @@
         <v>112</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>693</v>
+        <v>773</v>
       </c>
       <c r="U224" t="s">
         <v>35</v>
@@ -14531,7 +14532,7 @@
         <v>59</v>
       </c>
       <c r="X224" s="1" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="225" spans="1:24" ht="270" x14ac:dyDescent="0.25">
@@ -14557,7 +14558,7 @@
         <v>573</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>693</v>
+        <v>773</v>
       </c>
       <c r="U225" t="s">
         <v>35</v>
@@ -14569,10 +14570,10 @@
         <v>59</v>
       </c>
       <c r="X225" s="1" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="226" spans="1:24" x14ac:dyDescent="0.25">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="226" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1</v>
       </c>
@@ -14616,7 +14617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2</v>
       </c>
@@ -14654,7 +14655,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="228" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>3</v>
       </c>
@@ -14692,7 +14693,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>4</v>
       </c>
@@ -14730,7 +14731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>5</v>
       </c>
@@ -14756,7 +14757,7 @@
         <v>56</v>
       </c>
       <c r="K230" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="L230" t="s">
         <v>57</v>
@@ -14777,10 +14778,10 @@
         <v>59</v>
       </c>
       <c r="X230" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="231" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="231" spans="1:24" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>6</v>
       </c>
@@ -14827,7 +14828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="232" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>7</v>
       </c>
@@ -14853,7 +14854,7 @@
         <v>74</v>
       </c>
       <c r="K232" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L232" t="s">
         <v>75</v>
@@ -14886,7 +14887,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="233" spans="1:24" ht="345" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:24" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>8</v>
       </c>
@@ -14927,7 +14928,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="234" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>9</v>
       </c>
@@ -14968,7 +14969,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="235" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>10</v>
       </c>
@@ -14994,7 +14995,7 @@
         <v>96</v>
       </c>
       <c r="K235" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L235" t="s">
         <v>97</v>
@@ -15030,7 +15031,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="236" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>11</v>
       </c>
@@ -15056,7 +15057,7 @@
         <v>107</v>
       </c>
       <c r="K236" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L236" t="s">
         <v>97</v>
@@ -15092,7 +15093,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="237" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>12</v>
       </c>
@@ -15130,7 +15131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="238" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>13</v>
       </c>
@@ -15165,7 +15166,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="239" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>14</v>
       </c>
@@ -15191,7 +15192,7 @@
         <v>121</v>
       </c>
       <c r="K239" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L239" t="s">
         <v>97</v>
@@ -15227,7 +15228,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="240" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>15</v>
       </c>
@@ -15250,7 +15251,7 @@
         <v>125</v>
       </c>
       <c r="K240" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="L240" t="s">
         <v>126</v>
@@ -15283,7 +15284,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="241" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>16</v>
       </c>
@@ -15324,7 +15325,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="242" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>17</v>
       </c>
@@ -15350,7 +15351,7 @@
         <v>139</v>
       </c>
       <c r="K242" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="L242" t="s">
         <v>140</v>
@@ -15386,7 +15387,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="243" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>18</v>
       </c>
@@ -15409,7 +15410,7 @@
         <v>146</v>
       </c>
       <c r="K243" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="U243" t="s">
         <v>35</v>
@@ -15421,10 +15422,10 @@
         <v>59</v>
       </c>
       <c r="X243" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="244" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="244" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>19</v>
       </c>
@@ -15450,7 +15451,7 @@
         <v>139</v>
       </c>
       <c r="K244" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="L244" t="s">
         <v>150</v>
@@ -15486,7 +15487,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="245" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>20</v>
       </c>
@@ -15509,7 +15510,7 @@
         <v>146</v>
       </c>
       <c r="K245" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="U245" t="s">
         <v>35</v>
@@ -15521,10 +15522,10 @@
         <v>59</v>
       </c>
       <c r="X245" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="246" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="246" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>21</v>
       </c>
@@ -15550,7 +15551,7 @@
         <v>158</v>
       </c>
       <c r="K246" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="L246" t="s">
         <v>159</v>
@@ -15586,7 +15587,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="247" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>22</v>
       </c>
@@ -15612,7 +15613,7 @@
         <v>139</v>
       </c>
       <c r="K247" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="L247" t="s">
         <v>164</v>
@@ -15648,7 +15649,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="248" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>23</v>
       </c>
@@ -15671,7 +15672,7 @@
         <v>146</v>
       </c>
       <c r="K248" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="L248" t="s">
         <v>164</v>
@@ -15701,10 +15702,10 @@
         <v>59</v>
       </c>
       <c r="X248" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="249" spans="1:24" x14ac:dyDescent="0.25">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="249" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>24</v>
       </c>
@@ -15727,7 +15728,7 @@
         <v>173</v>
       </c>
       <c r="K249" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="L249" t="s">
         <v>174</v>
@@ -15757,10 +15758,10 @@
         <v>59</v>
       </c>
       <c r="X249" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="250" spans="1:24" x14ac:dyDescent="0.25">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="250" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>25</v>
       </c>
@@ -15780,7 +15781,7 @@
         <v>26</v>
       </c>
       <c r="K250" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="U250" t="s">
         <v>35</v>
@@ -15792,10 +15793,10 @@
         <v>59</v>
       </c>
       <c r="X250" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="251" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="251" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>26</v>
       </c>
@@ -15821,7 +15822,7 @@
         <v>184</v>
       </c>
       <c r="K251" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="L251" t="s">
         <v>185</v>
@@ -15851,10 +15852,10 @@
         <v>59</v>
       </c>
       <c r="X251" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="252" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="252" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>27</v>
       </c>
@@ -15880,7 +15881,7 @@
         <v>184</v>
       </c>
       <c r="K252" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="L252" t="s">
         <v>191</v>
@@ -15910,10 +15911,10 @@
         <v>59</v>
       </c>
       <c r="X252" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="253" spans="1:24" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="253" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>28</v>
       </c>
@@ -15954,7 +15955,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="254" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>29</v>
       </c>
@@ -15995,7 +15996,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="255" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>30</v>
       </c>
@@ -16033,7 +16034,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="256" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>31</v>
       </c>
@@ -16071,7 +16072,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="257" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>32</v>
       </c>
@@ -16109,7 +16110,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>33</v>
       </c>
@@ -16132,7 +16133,7 @@
         <v>211</v>
       </c>
       <c r="K258" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="L258" t="s">
         <v>210</v>
@@ -16156,7 +16157,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="259" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>34</v>
       </c>
@@ -16179,7 +16180,7 @@
         <v>211</v>
       </c>
       <c r="K259" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="L259" t="s">
         <v>215</v>
@@ -16203,7 +16204,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>35</v>
       </c>
@@ -16226,7 +16227,7 @@
         <v>211</v>
       </c>
       <c r="K260" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="L260" t="s">
         <v>219</v>
@@ -16250,7 +16251,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="261" spans="1:24" ht="180" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>36</v>
       </c>
@@ -16276,7 +16277,7 @@
         <v>224</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="L261" s="1" t="s">
         <v>225</v>
@@ -16291,10 +16292,10 @@
         <v>59</v>
       </c>
       <c r="X261" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="262" spans="1:24" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="262" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>37</v>
       </c>
@@ -16317,7 +16318,7 @@
         <v>211</v>
       </c>
       <c r="K262" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="L262" t="s">
         <v>227</v>
@@ -16341,7 +16342,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="263" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>38</v>
       </c>
@@ -16364,7 +16365,7 @@
         <v>232</v>
       </c>
       <c r="K263" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="L263" t="s">
         <v>231</v>
@@ -16388,7 +16389,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="264" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>39</v>
       </c>
@@ -16429,7 +16430,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="265" spans="1:24" ht="75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>40</v>
       </c>
@@ -16470,7 +16471,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="266" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>41</v>
       </c>
@@ -16511,7 +16512,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="267" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>42</v>
       </c>
@@ -16537,7 +16538,7 @@
         <v>244</v>
       </c>
       <c r="K267" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="L267" t="s">
         <v>252</v>
@@ -16567,7 +16568,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="268" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>43</v>
       </c>
@@ -16605,7 +16606,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="269" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>44</v>
       </c>
@@ -16631,7 +16632,7 @@
         <v>263</v>
       </c>
       <c r="K269" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L269" t="s">
         <v>264</v>
@@ -16658,7 +16659,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="270" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>45</v>
       </c>
@@ -16696,7 +16697,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="271" spans="1:24" ht="270" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:24" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>46</v>
       </c>
@@ -16722,7 +16723,7 @@
         <v>273</v>
       </c>
       <c r="K271" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="L271" t="s">
         <v>274</v>
@@ -16755,7 +16756,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="272" spans="1:24" ht="120" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>47</v>
       </c>
@@ -16814,7 +16815,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="273" spans="1:24" ht="240" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:24" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>48</v>
       </c>
@@ -16855,7 +16856,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="274" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>49</v>
       </c>
@@ -16878,7 +16879,7 @@
         <v>113</v>
       </c>
       <c r="K274" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="L274" t="s">
         <v>289</v>
@@ -16914,7 +16915,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="275" spans="1:24" ht="390" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>50</v>
       </c>
@@ -16940,7 +16941,7 @@
         <v>299</v>
       </c>
       <c r="K275" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="L275" t="s">
         <v>289</v>
@@ -16973,7 +16974,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="276" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>51</v>
       </c>
@@ -16999,7 +17000,7 @@
         <v>304</v>
       </c>
       <c r="K276" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="L276" t="s">
         <v>305</v>
@@ -17032,7 +17033,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="277" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>52</v>
       </c>
@@ -17073,7 +17074,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="278" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>53</v>
       </c>
@@ -17096,7 +17097,7 @@
         <v>313</v>
       </c>
       <c r="K278" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="L278" t="s">
         <v>316</v>
@@ -17132,7 +17133,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="279" spans="1:24" ht="150" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>54</v>
       </c>
@@ -17170,7 +17171,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="280" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>55</v>
       </c>
@@ -17193,7 +17194,7 @@
         <v>328</v>
       </c>
       <c r="K280" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="L280" t="s">
         <v>329</v>
@@ -17226,10 +17227,10 @@
         <v>59</v>
       </c>
       <c r="X280" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="281" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="281" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>56</v>
       </c>
@@ -17270,7 +17271,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="282" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>57</v>
       </c>
@@ -17311,7 +17312,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="283" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>58</v>
       </c>
@@ -17337,7 +17338,7 @@
         <v>312</v>
       </c>
       <c r="K283" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="L283" s="1" t="s">
         <v>343</v>
@@ -17367,10 +17368,10 @@
         <v>59</v>
       </c>
       <c r="X283" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="284" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="284" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>59</v>
       </c>
@@ -17393,7 +17394,7 @@
         <v>350</v>
       </c>
       <c r="K284" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="L284" s="1" t="s">
         <v>343</v>
@@ -17423,10 +17424,10 @@
         <v>352</v>
       </c>
       <c r="X284" s="1" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="285" spans="1:24" ht="390" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="285" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>60</v>
       </c>
@@ -17452,7 +17453,7 @@
         <v>356</v>
       </c>
       <c r="K285" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="L285" t="s">
         <v>358</v>
@@ -17488,7 +17489,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="286" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>61</v>
       </c>
@@ -17514,7 +17515,7 @@
         <v>367</v>
       </c>
       <c r="K286" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="L286" t="s">
         <v>368</v>
@@ -17547,10 +17548,10 @@
         <v>352</v>
       </c>
       <c r="X286" s="1" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="287" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="287" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>62</v>
       </c>
@@ -17576,7 +17577,7 @@
         <v>367</v>
       </c>
       <c r="K287" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="L287" t="s">
         <v>377</v>
@@ -17612,7 +17613,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="288" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>63</v>
       </c>
@@ -17638,7 +17639,7 @@
         <v>367</v>
       </c>
       <c r="K288" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="L288" t="s">
         <v>377</v>
@@ -17671,7 +17672,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="289" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>64</v>
       </c>
@@ -17697,7 +17698,7 @@
         <v>367</v>
       </c>
       <c r="K289" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="L289" t="s">
         <v>389</v>
@@ -17730,7 +17731,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="290" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>65</v>
       </c>
@@ -17756,7 +17757,7 @@
         <v>367</v>
       </c>
       <c r="K290" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="L290" t="s">
         <v>394</v>
@@ -17789,7 +17790,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="291" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>66</v>
       </c>
@@ -17815,7 +17816,7 @@
         <v>367</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="L291" t="s">
         <v>368</v>
@@ -17848,7 +17849,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="292" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>67</v>
       </c>
@@ -17889,7 +17890,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="293" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>68</v>
       </c>
@@ -17915,7 +17916,7 @@
         <v>367</v>
       </c>
       <c r="K293" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="L293" t="s">
         <v>406</v>
@@ -17948,7 +17949,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="294" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>69</v>
       </c>
@@ -17974,7 +17975,7 @@
         <v>367</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="U294" t="s">
         <v>35</v>
@@ -17986,10 +17987,10 @@
         <v>352</v>
       </c>
       <c r="X294" s="1" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="295" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="295" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>70</v>
       </c>
@@ -18015,7 +18016,7 @@
         <v>367</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="L295" s="1" t="s">
         <v>415</v>
@@ -18048,10 +18049,10 @@
         <v>352</v>
       </c>
       <c r="X295" s="1" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="296" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="296" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>71</v>
       </c>
@@ -18077,7 +18078,7 @@
         <v>367</v>
       </c>
       <c r="K296" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="L296" t="s">
         <v>425</v>
@@ -18113,7 +18114,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="297" spans="1:24" ht="105" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>72</v>
       </c>
@@ -18139,7 +18140,7 @@
         <v>432</v>
       </c>
       <c r="K297" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="L297" t="s">
         <v>425</v>
@@ -18175,7 +18176,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="298" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>73</v>
       </c>
@@ -18201,7 +18202,7 @@
         <v>367</v>
       </c>
       <c r="K298" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="L298" t="s">
         <v>436</v>
@@ -18234,7 +18235,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="299" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>74</v>
       </c>
@@ -18275,7 +18276,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="300" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>75</v>
       </c>
@@ -18316,7 +18317,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="301" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>76</v>
       </c>
@@ -18357,7 +18358,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="302" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>77</v>
       </c>
@@ -18398,7 +18399,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="303" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>78</v>
       </c>
@@ -18439,7 +18440,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="304" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>79</v>
       </c>
@@ -18480,7 +18481,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="305" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>80</v>
       </c>
@@ -18521,7 +18522,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="306" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>81</v>
       </c>
@@ -18562,7 +18563,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="307" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>82</v>
       </c>
@@ -18603,7 +18604,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="308" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>83</v>
       </c>
@@ -18644,7 +18645,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="309" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>84</v>
       </c>
@@ -18685,7 +18686,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="310" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>85</v>
       </c>
@@ -18726,7 +18727,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="311" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>86</v>
       </c>
@@ -18767,7 +18768,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="312" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>87</v>
       </c>
@@ -18808,7 +18809,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="313" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>88</v>
       </c>
@@ -18849,7 +18850,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="314" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>89</v>
       </c>
@@ -18890,7 +18891,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="315" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>90</v>
       </c>
@@ -18931,7 +18932,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="316" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>91</v>
       </c>
@@ -18972,7 +18973,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="317" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>92</v>
       </c>
@@ -19013,7 +19014,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="318" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>93</v>
       </c>
@@ -19039,7 +19040,7 @@
         <v>367</v>
       </c>
       <c r="K318" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="L318" t="s">
         <v>480</v>
@@ -19072,7 +19073,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="319" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>94</v>
       </c>
@@ -19098,7 +19099,7 @@
         <v>367</v>
       </c>
       <c r="K319" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="L319" t="s">
         <v>486</v>
@@ -19131,7 +19132,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="320" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>95</v>
       </c>
@@ -19157,7 +19158,7 @@
         <v>493</v>
       </c>
       <c r="K320" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="L320" t="s">
         <v>494</v>
@@ -19190,7 +19191,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="321" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>96</v>
       </c>
@@ -19216,7 +19217,7 @@
         <v>367</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="L321" t="s">
         <v>500</v>
@@ -19246,10 +19247,10 @@
         <v>352</v>
       </c>
       <c r="X321" s="1" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="322" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="322" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>97</v>
       </c>
@@ -19275,7 +19276,7 @@
         <v>367</v>
       </c>
       <c r="K322" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="L322" t="s">
         <v>500</v>
@@ -19305,10 +19306,10 @@
         <v>352</v>
       </c>
       <c r="X322" s="1" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="323" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="323" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>98</v>
       </c>
@@ -19334,7 +19335,7 @@
         <v>367</v>
       </c>
       <c r="K323" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="L323" t="s">
         <v>500</v>
@@ -19364,10 +19365,10 @@
         <v>352</v>
       </c>
       <c r="X323" s="1" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="324" spans="1:24" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="324" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>99</v>
       </c>
@@ -19405,7 +19406,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="325" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>100</v>
       </c>
@@ -19443,7 +19444,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="326" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>101</v>
       </c>
@@ -19481,7 +19482,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="327" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>102</v>
       </c>
@@ -19519,7 +19520,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="328" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>103</v>
       </c>
@@ -19557,7 +19558,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="329" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>104</v>
       </c>
@@ -19580,7 +19581,7 @@
         <v>515</v>
       </c>
       <c r="K329" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="L329" t="s">
         <v>527</v>
@@ -19613,7 +19614,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="330" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>105</v>
       </c>
@@ -19651,7 +19652,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="331" spans="1:24" ht="135" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>106</v>
       </c>
@@ -19692,7 +19693,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="332" spans="1:24" ht="225" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>107</v>
       </c>
@@ -19733,7 +19734,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="333" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>108</v>
       </c>
@@ -19774,7 +19775,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="334" spans="1:24" ht="285" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:24" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>109</v>
       </c>
@@ -19800,7 +19801,7 @@
         <v>547</v>
       </c>
       <c r="K334" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="L334" t="s">
         <v>552</v>
@@ -19833,7 +19834,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="335" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>110</v>
       </c>
@@ -19859,7 +19860,7 @@
         <v>547</v>
       </c>
       <c r="K335" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="L335" t="s">
         <v>561</v>
@@ -19915,7 +19916,7 @@
         <v>112</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>748</v>
+        <v>774</v>
       </c>
       <c r="U336" t="s">
         <v>35</v>
@@ -19927,7 +19928,7 @@
         <v>59</v>
       </c>
       <c r="X336" s="1" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="337" spans="1:24" ht="270" x14ac:dyDescent="0.25">
@@ -19953,7 +19954,7 @@
         <v>573</v>
       </c>
       <c r="K337" s="1" t="s">
-        <v>748</v>
+        <v>774</v>
       </c>
       <c r="U337" t="s">
         <v>35</v>
@@ -19965,11 +19966,18 @@
         <v>59</v>
       </c>
       <c r="X337" s="1" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X337" xr:uid="{8F369A59-9712-47DB-8DA9-54F6F198C8F2}"/>
+  <autoFilter ref="A1:X337" xr:uid="{8F369A59-9712-47DB-8DA9-54F6F198C8F2}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="phy_mobility_limitation_SF36"/>
+        <filter val="phy_SF36_nb_items"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D478739-D2F8-4F06-B5BF-457DD2E2C657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3413A9C9-08A9-486F-A382-C9E5438B68F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95E6C139-84C6-42BA-8CBB-FF1D79072BFF}"/>
   </bookViews>
@@ -3687,7 +3687,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F369A59-9712-47DB-8DA9-54F6F198C8F2}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X337"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3769,7 +3768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3825,7 +3824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3863,7 +3862,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3901,7 +3900,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3939,7 +3938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3989,7 +3988,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4036,7 +4035,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4095,7 +4094,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="345" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4136,7 +4135,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4239,7 +4238,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4301,7 +4300,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4339,7 +4338,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4374,7 +4373,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4436,7 +4435,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4492,7 +4491,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4533,7 +4532,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4595,7 +4594,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4633,7 +4632,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4695,7 +4694,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4733,7 +4732,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4795,7 +4794,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4860,7 +4859,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4919,7 +4918,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4978,7 +4977,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5013,7 +5012,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5072,7 +5071,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5131,7 +5130,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5172,7 +5171,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5213,7 +5212,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5251,7 +5250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5289,7 +5288,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5327,7 +5326,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5374,7 +5373,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5421,7 +5420,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5468,7 +5467,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5512,7 +5511,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5559,7 +5558,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5606,7 +5605,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5647,7 +5646,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5688,7 +5687,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5729,7 +5728,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5785,7 +5784,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5823,7 +5822,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5876,7 +5875,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5914,7 +5913,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="270" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5973,7 +5972,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6014,7 +6013,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" ht="240" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6055,7 +6054,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6114,7 +6113,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="390" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6173,7 +6172,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6232,7 +6231,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6273,7 +6272,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6370,7 +6369,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6429,7 +6428,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6470,7 +6469,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6511,7 +6510,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6573,7 +6572,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="60" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6632,7 +6631,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="61" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" ht="390" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6694,7 +6693,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6756,7 +6755,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6818,7 +6817,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6877,7 +6876,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="65" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6936,7 +6935,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="66" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6995,7 +6994,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="67" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7054,7 +7053,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" ht="60" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7095,7 +7094,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7154,7 +7153,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="70" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7195,7 +7194,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="71" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7257,7 +7256,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="72" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7319,7 +7318,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7381,7 +7380,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7440,7 +7439,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="75" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7481,7 +7480,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7522,7 +7521,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7563,7 +7562,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7604,7 +7603,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="79" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7645,7 +7644,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7686,7 +7685,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7727,7 +7726,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7768,7 +7767,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7809,7 +7808,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7850,7 +7849,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7891,7 +7890,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7932,7 +7931,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7973,7 +7972,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -8014,7 +8013,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -8055,7 +8054,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="90" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8096,7 +8095,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -8137,7 +8136,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="92" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -8178,7 +8177,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="93" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -8219,7 +8218,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -8278,7 +8277,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -8337,7 +8336,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -8396,7 +8395,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="97" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -8455,7 +8454,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="98" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -8514,7 +8513,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="99" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -8573,7 +8572,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8611,7 +8610,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8649,7 +8648,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8687,7 +8686,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8725,7 +8724,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8763,7 +8762,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="105" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8819,7 +8818,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8857,7 +8856,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="107" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8901,7 +8900,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="108" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8942,7 +8941,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8983,7 +8982,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="110" spans="1:24" ht="285" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -9042,7 +9041,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="111" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -9177,7 +9176,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1</v>
       </c>
@@ -9221,7 +9220,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2</v>
       </c>
@@ -9259,7 +9258,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="116" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>3</v>
       </c>
@@ -9297,7 +9296,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>4</v>
       </c>
@@ -9335,7 +9334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>5</v>
       </c>
@@ -9385,7 +9384,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="119" spans="1:24" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>6</v>
       </c>
@@ -9432,7 +9431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>7</v>
       </c>
@@ -9491,7 +9490,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" spans="1:24" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:24" ht="345" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>8</v>
       </c>
@@ -9532,7 +9531,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="122" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>9</v>
       </c>
@@ -9573,7 +9572,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>10</v>
       </c>
@@ -9635,7 +9634,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="124" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>11</v>
       </c>
@@ -9697,7 +9696,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>12</v>
       </c>
@@ -9735,7 +9734,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>13</v>
       </c>
@@ -9770,7 +9769,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>14</v>
       </c>
@@ -9832,7 +9831,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>15</v>
       </c>
@@ -9888,7 +9887,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="129" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>16</v>
       </c>
@@ -9929,7 +9928,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="130" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>17</v>
       </c>
@@ -9991,7 +9990,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="131" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>18</v>
       </c>
@@ -10029,7 +10028,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>19</v>
       </c>
@@ -10091,7 +10090,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>20</v>
       </c>
@@ -10129,7 +10128,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="134" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>21</v>
       </c>
@@ -10191,7 +10190,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>22</v>
       </c>
@@ -10253,7 +10252,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>23</v>
       </c>
@@ -10309,7 +10308,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="137" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>24</v>
       </c>
@@ -10365,7 +10364,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="138" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>25</v>
       </c>
@@ -10400,7 +10399,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="139" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>26</v>
       </c>
@@ -10459,7 +10458,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="140" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>27</v>
       </c>
@@ -10518,7 +10517,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="141" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>28</v>
       </c>
@@ -10559,7 +10558,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="142" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>29</v>
       </c>
@@ -10600,7 +10599,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="143" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>30</v>
       </c>
@@ -10638,7 +10637,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="144" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>31</v>
       </c>
@@ -10676,7 +10675,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="145" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>32</v>
       </c>
@@ -10714,7 +10713,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="146" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>33</v>
       </c>
@@ -10761,7 +10760,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>34</v>
       </c>
@@ -10808,7 +10807,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="148" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>35</v>
       </c>
@@ -10855,7 +10854,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>36</v>
       </c>
@@ -10899,7 +10898,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="150" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>37</v>
       </c>
@@ -10946,7 +10945,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>38</v>
       </c>
@@ -10993,7 +10992,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="152" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>39</v>
       </c>
@@ -11034,7 +11033,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="153" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:24" ht="75" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>40</v>
       </c>
@@ -11075,7 +11074,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="154" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>41</v>
       </c>
@@ -11116,7 +11115,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="155" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>42</v>
       </c>
@@ -11172,7 +11171,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="156" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>43</v>
       </c>
@@ -11210,7 +11209,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>44</v>
       </c>
@@ -11263,7 +11262,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="158" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>45</v>
       </c>
@@ -11301,7 +11300,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="159" spans="1:24" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:24" ht="270" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>46</v>
       </c>
@@ -11360,7 +11359,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="160" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>47</v>
       </c>
@@ -11419,7 +11418,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" spans="1:24" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:24" ht="240" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>48</v>
       </c>
@@ -11460,7 +11459,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="162" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>49</v>
       </c>
@@ -11519,7 +11518,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="163" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:24" ht="390" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>50</v>
       </c>
@@ -11578,7 +11577,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="164" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>51</v>
       </c>
@@ -11637,7 +11636,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="165" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>52</v>
       </c>
@@ -11678,7 +11677,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="166" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>53</v>
       </c>
@@ -11737,7 +11736,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>54</v>
       </c>
@@ -11775,7 +11774,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="168" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>55</v>
       </c>
@@ -11834,7 +11833,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="169" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>56</v>
       </c>
@@ -11875,7 +11874,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="170" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>57</v>
       </c>
@@ -11916,7 +11915,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="171" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>58</v>
       </c>
@@ -11975,7 +11974,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="172" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>59</v>
       </c>
@@ -12031,7 +12030,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="173" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:24" ht="390" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>60</v>
       </c>
@@ -12093,7 +12092,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="174" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>61</v>
       </c>
@@ -12155,7 +12154,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="175" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>62</v>
       </c>
@@ -12217,7 +12216,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="176" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>63</v>
       </c>
@@ -12276,7 +12275,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="177" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>64</v>
       </c>
@@ -12335,7 +12334,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="178" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>65</v>
       </c>
@@ -12394,7 +12393,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="179" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>66</v>
       </c>
@@ -12453,7 +12452,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:24" ht="60" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>67</v>
       </c>
@@ -12494,7 +12493,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="181" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>68</v>
       </c>
@@ -12553,7 +12552,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="182" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>69</v>
       </c>
@@ -12594,7 +12593,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="183" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>70</v>
       </c>
@@ -12656,7 +12655,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="184" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>71</v>
       </c>
@@ -12718,7 +12717,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="185" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>72</v>
       </c>
@@ -12780,7 +12779,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="186" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>73</v>
       </c>
@@ -12839,7 +12838,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="187" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>74</v>
       </c>
@@ -12880,7 +12879,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="188" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>75</v>
       </c>
@@ -12921,7 +12920,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="189" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>76</v>
       </c>
@@ -12962,7 +12961,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="190" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>77</v>
       </c>
@@ -13003,7 +13002,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>78</v>
       </c>
@@ -13044,7 +13043,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="192" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>79</v>
       </c>
@@ -13085,7 +13084,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="193" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>80</v>
       </c>
@@ -13126,7 +13125,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="194" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>81</v>
       </c>
@@ -13167,7 +13166,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="195" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>82</v>
       </c>
@@ -13208,7 +13207,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="196" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>83</v>
       </c>
@@ -13249,7 +13248,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="197" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>84</v>
       </c>
@@ -13290,7 +13289,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="198" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>85</v>
       </c>
@@ -13331,7 +13330,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="199" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>86</v>
       </c>
@@ -13372,7 +13371,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="200" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>87</v>
       </c>
@@ -13413,7 +13412,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="201" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>88</v>
       </c>
@@ -13454,7 +13453,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="202" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>89</v>
       </c>
@@ -13495,7 +13494,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="203" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>90</v>
       </c>
@@ -13536,7 +13535,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="204" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>91</v>
       </c>
@@ -13577,7 +13576,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="205" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>92</v>
       </c>
@@ -13618,7 +13617,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>93</v>
       </c>
@@ -13677,7 +13676,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="207" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>94</v>
       </c>
@@ -13736,7 +13735,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="208" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>95</v>
       </c>
@@ -13795,7 +13794,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="209" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>96</v>
       </c>
@@ -13854,7 +13853,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="210" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>97</v>
       </c>
@@ -13913,7 +13912,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="211" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>98</v>
       </c>
@@ -13972,7 +13971,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="212" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>99</v>
       </c>
@@ -14010,7 +14009,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="213" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>100</v>
       </c>
@@ -14048,7 +14047,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="214" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>101</v>
       </c>
@@ -14086,7 +14085,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="215" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>102</v>
       </c>
@@ -14124,7 +14123,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="216" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>103</v>
       </c>
@@ -14162,7 +14161,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="217" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>104</v>
       </c>
@@ -14218,7 +14217,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>105</v>
       </c>
@@ -14256,7 +14255,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="219" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>106</v>
       </c>
@@ -14297,7 +14296,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="220" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>107</v>
       </c>
@@ -14338,7 +14337,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="221" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>108</v>
       </c>
@@ -14379,7 +14378,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="222" spans="1:24" ht="285" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>109</v>
       </c>
@@ -14438,7 +14437,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="223" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>110</v>
       </c>
@@ -14573,7 +14572,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="226" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1</v>
       </c>
@@ -14617,7 +14616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2</v>
       </c>
@@ -14655,7 +14654,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="228" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>3</v>
       </c>
@@ -14693,7 +14692,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="229" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>4</v>
       </c>
@@ -14731,7 +14730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>5</v>
       </c>
@@ -14781,7 +14780,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="231" spans="1:24" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>6</v>
       </c>
@@ -14828,7 +14827,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="232" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>7</v>
       </c>
@@ -14887,7 +14886,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="233" spans="1:24" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:24" ht="345" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>8</v>
       </c>
@@ -14928,7 +14927,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="234" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>9</v>
       </c>
@@ -14969,7 +14968,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="235" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>10</v>
       </c>
@@ -15031,7 +15030,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="236" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>11</v>
       </c>
@@ -15093,7 +15092,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="237" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>12</v>
       </c>
@@ -15131,7 +15130,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="238" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>13</v>
       </c>
@@ -15166,7 +15165,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="239" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>14</v>
       </c>
@@ -15228,7 +15227,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="240" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>15</v>
       </c>
@@ -15284,7 +15283,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="241" spans="1:24" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>16</v>
       </c>
@@ -15325,7 +15324,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="242" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>17</v>
       </c>
@@ -15387,7 +15386,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="243" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>18</v>
       </c>
@@ -15425,7 +15424,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="244" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>19</v>
       </c>
@@ -15487,7 +15486,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="245" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>20</v>
       </c>
@@ -15525,7 +15524,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="246" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>21</v>
       </c>
@@ -15587,7 +15586,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="247" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>22</v>
       </c>
@@ -15649,7 +15648,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="248" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>23</v>
       </c>
@@ -15705,7 +15704,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="249" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>24</v>
       </c>
@@ -15761,7 +15760,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="250" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>25</v>
       </c>
@@ -15796,7 +15795,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="251" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>26</v>
       </c>
@@ -15855,7 +15854,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="252" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>27</v>
       </c>
@@ -15914,7 +15913,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="253" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>28</v>
       </c>
@@ -15955,7 +15954,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="254" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>29</v>
       </c>
@@ -15996,7 +15995,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="255" spans="1:24" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:24" ht="90" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>30</v>
       </c>
@@ -16034,7 +16033,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="256" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>31</v>
       </c>
@@ -16072,7 +16071,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="257" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>32</v>
       </c>
@@ -16110,7 +16109,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>33</v>
       </c>
@@ -16157,7 +16156,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="259" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>34</v>
       </c>
@@ -16204,7 +16203,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>35</v>
       </c>
@@ -16251,7 +16250,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="261" spans="1:24" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:24" ht="180" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>36</v>
       </c>
@@ -16295,7 +16294,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="262" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>37</v>
       </c>
@@ -16342,7 +16341,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="263" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>38</v>
       </c>
@@ -16389,7 +16388,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="264" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>39</v>
       </c>
@@ -16430,7 +16429,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="265" spans="1:24" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:24" ht="75" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>40</v>
       </c>
@@ -16471,7 +16470,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="266" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>41</v>
       </c>
@@ -16512,7 +16511,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="267" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>42</v>
       </c>
@@ -16568,7 +16567,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="268" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>43</v>
       </c>
@@ -16606,7 +16605,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="269" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>44</v>
       </c>
@@ -16659,7 +16658,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="270" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>45</v>
       </c>
@@ -16697,7 +16696,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="271" spans="1:24" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:24" ht="270" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>46</v>
       </c>
@@ -16756,7 +16755,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="272" spans="1:24" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:24" ht="120" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>47</v>
       </c>
@@ -16815,7 +16814,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="273" spans="1:24" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:24" ht="240" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>48</v>
       </c>
@@ -16856,7 +16855,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="274" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>49</v>
       </c>
@@ -16915,7 +16914,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="275" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:24" ht="390" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>50</v>
       </c>
@@ -16974,7 +16973,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="276" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>51</v>
       </c>
@@ -17033,7 +17032,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="277" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>52</v>
       </c>
@@ -17074,7 +17073,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="278" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>53</v>
       </c>
@@ -17133,7 +17132,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="279" spans="1:24" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:24" ht="150" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>54</v>
       </c>
@@ -17171,7 +17170,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="280" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>55</v>
       </c>
@@ -17230,7 +17229,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="281" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>56</v>
       </c>
@@ -17271,7 +17270,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="282" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>57</v>
       </c>
@@ -17312,7 +17311,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="283" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>58</v>
       </c>
@@ -17371,7 +17370,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="284" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>59</v>
       </c>
@@ -17427,7 +17426,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="285" spans="1:24" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:24" ht="390" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>60</v>
       </c>
@@ -17489,7 +17488,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="286" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>61</v>
       </c>
@@ -17551,7 +17550,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="287" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>62</v>
       </c>
@@ -17613,7 +17612,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="288" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>63</v>
       </c>
@@ -17672,7 +17671,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="289" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>64</v>
       </c>
@@ -17731,7 +17730,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="290" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>65</v>
       </c>
@@ -17790,7 +17789,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="291" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>66</v>
       </c>
@@ -17849,7 +17848,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="292" spans="1:24" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:24" ht="60" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>67</v>
       </c>
@@ -17890,7 +17889,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="293" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>68</v>
       </c>
@@ -17949,7 +17948,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="294" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>69</v>
       </c>
@@ -17990,7 +17989,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="295" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>70</v>
       </c>
@@ -18052,7 +18051,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="296" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>71</v>
       </c>
@@ -18114,7 +18113,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="297" spans="1:24" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:24" ht="105" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>72</v>
       </c>
@@ -18176,7 +18175,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="298" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>73</v>
       </c>
@@ -18235,7 +18234,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="299" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>74</v>
       </c>
@@ -18276,7 +18275,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="300" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>75</v>
       </c>
@@ -18317,7 +18316,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="301" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>76</v>
       </c>
@@ -18358,7 +18357,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="302" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>77</v>
       </c>
@@ -18399,7 +18398,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="303" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>78</v>
       </c>
@@ -18440,7 +18439,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="304" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>79</v>
       </c>
@@ -18481,7 +18480,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="305" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>80</v>
       </c>
@@ -18522,7 +18521,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="306" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>81</v>
       </c>
@@ -18563,7 +18562,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="307" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>82</v>
       </c>
@@ -18604,7 +18603,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="308" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>83</v>
       </c>
@@ -18645,7 +18644,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="309" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>84</v>
       </c>
@@ -18686,7 +18685,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="310" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>85</v>
       </c>
@@ -18727,7 +18726,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="311" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>86</v>
       </c>
@@ -18768,7 +18767,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="312" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>87</v>
       </c>
@@ -18809,7 +18808,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="313" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>88</v>
       </c>
@@ -18850,7 +18849,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="314" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>89</v>
       </c>
@@ -18891,7 +18890,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="315" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>90</v>
       </c>
@@ -18932,7 +18931,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="316" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>91</v>
       </c>
@@ -18973,7 +18972,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="317" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>92</v>
       </c>
@@ -19014,7 +19013,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="318" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>93</v>
       </c>
@@ -19073,7 +19072,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="319" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>94</v>
       </c>
@@ -19132,7 +19131,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="320" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>95</v>
       </c>
@@ -19191,7 +19190,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="321" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>96</v>
       </c>
@@ -19250,7 +19249,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="322" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>97</v>
       </c>
@@ -19309,7 +19308,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="323" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>98</v>
       </c>
@@ -19368,7 +19367,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="324" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>99</v>
       </c>
@@ -19406,7 +19405,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="325" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>100</v>
       </c>
@@ -19444,7 +19443,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="326" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>101</v>
       </c>
@@ -19482,7 +19481,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="327" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>102</v>
       </c>
@@ -19520,7 +19519,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="328" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>103</v>
       </c>
@@ -19558,7 +19557,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="329" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>104</v>
       </c>
@@ -19614,7 +19613,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="330" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>105</v>
       </c>
@@ -19652,7 +19651,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="331" spans="1:24" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:24" ht="135" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>106</v>
       </c>
@@ -19693,7 +19692,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="332" spans="1:24" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:24" ht="225" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>107</v>
       </c>
@@ -19734,7 +19733,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="333" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>108</v>
       </c>
@@ -19775,7 +19774,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="334" spans="1:24" ht="285" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:24" ht="285" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>109</v>
       </c>
@@ -19834,7 +19833,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="335" spans="1:24" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>110</v>
       </c>
@@ -19970,14 +19969,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X337" xr:uid="{8F369A59-9712-47DB-8DA9-54F6F198C8F2}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="phy_mobility_limitation_SF36"/>
-        <filter val="phy_SF36_nb_items"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:X337" xr:uid="{8F369A59-9712-47DB-8DA9-54F6F198C8F2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabiogo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3413A9C9-08A9-486F-A382-C9E5438B68F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC741CA-99DB-4521-8620-E5F81A04EB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95E6C139-84C6-42BA-8CBB-FF1D79072BFF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{95E6C139-84C6-42BA-8CBB-FF1D79072BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1504,9 +1504,6 @@
     <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
 If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned. 
 Add a harmonization comment about any study-specific wording for collecting information about diabetes (e.g., only Type 2 diabetes, excluding gestational diabetes).</t>
-  </si>
-  <si>
-    <t>diabetes1</t>
   </si>
   <si>
     <t>Type 2 diabetes</t>
@@ -3314,6 +3311,9 @@
 dis_walk100m_w4;
 dis_bath_w4</t>
   </si>
+  <si>
+    <t>diabetes_w2</t>
+  </si>
 </sst>
 </file>
 
@@ -3371,7 +3371,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3688,7 +3688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F369A59-9712-47DB-8DA9-54F6F198C8F2}">
   <dimension ref="A1:X337"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="11" max="11" width="40.140625" customWidth="1"/>
     <col min="24" max="24" width="71" customWidth="1"/>
@@ -3753,10 +3753,10 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="U1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="V1" t="s">
         <v>19</v>
@@ -3859,7 +3859,7 @@
         <v>43</v>
       </c>
       <c r="X3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3897,7 +3897,7 @@
         <v>43</v>
       </c>
       <c r="X4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -3964,7 +3964,7 @@
         <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -3985,7 +3985,7 @@
         <v>59</v>
       </c>
       <c r="X6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.25">
@@ -4061,7 +4061,7 @@
         <v>74</v>
       </c>
       <c r="K8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L8" t="s">
         <v>75</v>
@@ -4202,7 +4202,7 @@
         <v>96</v>
       </c>
       <c r="K11" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L11" t="s">
         <v>97</v>
@@ -4264,7 +4264,7 @@
         <v>107</v>
       </c>
       <c r="K12" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L12" t="s">
         <v>97</v>
@@ -4399,7 +4399,7 @@
         <v>121</v>
       </c>
       <c r="K15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L15" t="s">
         <v>97</v>
@@ -4458,7 +4458,7 @@
         <v>125</v>
       </c>
       <c r="K16" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L16" t="s">
         <v>126</v>
@@ -4558,7 +4558,7 @@
         <v>139</v>
       </c>
       <c r="K18" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="L18" t="s">
         <v>140</v>
@@ -4617,7 +4617,7 @@
         <v>146</v>
       </c>
       <c r="K19" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="U19" t="s">
         <v>35</v>
@@ -4629,7 +4629,7 @@
         <v>59</v>
       </c>
       <c r="X19" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -4658,7 +4658,7 @@
         <v>139</v>
       </c>
       <c r="K20" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L20" t="s">
         <v>150</v>
@@ -4717,7 +4717,7 @@
         <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U21" t="s">
         <v>35</v>
@@ -4729,7 +4729,7 @@
         <v>59</v>
       </c>
       <c r="X21" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -4758,7 +4758,7 @@
         <v>158</v>
       </c>
       <c r="K22" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L22" t="s">
         <v>159</v>
@@ -4820,7 +4820,7 @@
         <v>139</v>
       </c>
       <c r="K23" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L23" t="s">
         <v>164</v>
@@ -4882,7 +4882,7 @@
         <v>146</v>
       </c>
       <c r="K24" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L24" t="s">
         <v>164</v>
@@ -4915,7 +4915,7 @@
         <v>59</v>
       </c>
       <c r="X24" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="30" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>173</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L25" t="s">
         <v>174</v>
@@ -4974,7 +4974,7 @@
         <v>59</v>
       </c>
       <c r="X25" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -4997,7 +4997,7 @@
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="U26" t="s">
         <v>35</v>
@@ -5009,7 +5009,7 @@
         <v>59</v>
       </c>
       <c r="X26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -5038,7 +5038,7 @@
         <v>184</v>
       </c>
       <c r="K27" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L27" t="s">
         <v>185</v>
@@ -5068,7 +5068,7 @@
         <v>59</v>
       </c>
       <c r="X27" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -5097,7 +5097,7 @@
         <v>184</v>
       </c>
       <c r="K28" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L28" t="s">
         <v>191</v>
@@ -5127,7 +5127,7 @@
         <v>59</v>
       </c>
       <c r="X28" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -5349,7 +5349,7 @@
         <v>211</v>
       </c>
       <c r="K34" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L34" t="s">
         <v>210</v>
@@ -5396,7 +5396,7 @@
         <v>211</v>
       </c>
       <c r="K35" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L35" t="s">
         <v>215</v>
@@ -5443,7 +5443,7 @@
         <v>211</v>
       </c>
       <c r="K36" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L36" t="s">
         <v>219</v>
@@ -5493,7 +5493,7 @@
         <v>224</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>225</v>
@@ -5508,7 +5508,7 @@
         <v>59</v>
       </c>
       <c r="X37" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -5534,7 +5534,7 @@
         <v>211</v>
       </c>
       <c r="K38" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="L38" t="s">
         <v>227</v>
@@ -5581,7 +5581,7 @@
         <v>232</v>
       </c>
       <c r="K39" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="L39" t="s">
         <v>231</v>
@@ -5754,7 +5754,7 @@
         <v>244</v>
       </c>
       <c r="K43" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L43" t="s">
         <v>252</v>
@@ -5848,7 +5848,7 @@
         <v>263</v>
       </c>
       <c r="K45" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L45" t="s">
         <v>264</v>
@@ -5939,7 +5939,7 @@
         <v>273</v>
       </c>
       <c r="K47" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L47" t="s">
         <v>274</v>
@@ -6077,7 +6077,7 @@
         <v>113</v>
       </c>
       <c r="K50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L50" t="s">
         <v>289</v>
@@ -6139,7 +6139,7 @@
         <v>299</v>
       </c>
       <c r="K51" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L51" t="s">
         <v>289</v>
@@ -6198,7 +6198,7 @@
         <v>304</v>
       </c>
       <c r="K52" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="L52" t="s">
         <v>305</v>
@@ -6295,7 +6295,7 @@
         <v>313</v>
       </c>
       <c r="K54" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="L54" t="s">
         <v>316</v>
@@ -6392,7 +6392,7 @@
         <v>328</v>
       </c>
       <c r="K56" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L56" t="s">
         <v>329</v>
@@ -6425,7 +6425,7 @@
         <v>59</v>
       </c>
       <c r="X56" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -6536,7 +6536,7 @@
         <v>312</v>
       </c>
       <c r="K59" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>343</v>
@@ -6569,7 +6569,7 @@
         <v>59</v>
       </c>
       <c r="X59" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6595,7 +6595,7 @@
         <v>350</v>
       </c>
       <c r="K60" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>343</v>
@@ -6628,7 +6628,7 @@
         <v>352</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -6719,7 +6719,7 @@
         <v>367</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L62" t="s">
         <v>368</v>
@@ -6752,7 +6752,7 @@
         <v>352</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="63" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6781,7 +6781,7 @@
         <v>367</v>
       </c>
       <c r="K63" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L63" t="s">
         <v>377</v>
@@ -6843,7 +6843,7 @@
         <v>367</v>
       </c>
       <c r="K64" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L64" t="s">
         <v>377</v>
@@ -6902,7 +6902,7 @@
         <v>367</v>
       </c>
       <c r="K65" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L65" t="s">
         <v>389</v>
@@ -6961,7 +6961,7 @@
         <v>367</v>
       </c>
       <c r="K66" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="L66" t="s">
         <v>394</v>
@@ -7020,7 +7020,7 @@
         <v>367</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L67" t="s">
         <v>368</v>
@@ -7120,7 +7120,7 @@
         <v>367</v>
       </c>
       <c r="K69" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="L69" t="s">
         <v>406</v>
@@ -7179,7 +7179,7 @@
         <v>367</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="U70" t="s">
         <v>35</v>
@@ -7191,7 +7191,7 @@
         <v>352</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>367</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>415</v>
@@ -7253,7 +7253,7 @@
         <v>352</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7282,16 +7282,16 @@
         <v>367</v>
       </c>
       <c r="K72" t="s">
+        <v>774</v>
+      </c>
+      <c r="L72" t="s">
         <v>424</v>
-      </c>
-      <c r="L72" t="s">
-        <v>425</v>
       </c>
       <c r="M72" t="s">
         <v>384</v>
       </c>
       <c r="N72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>78</v>
@@ -7300,10 +7300,10 @@
         <v>33</v>
       </c>
       <c r="R72" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="T72" t="s">
         <v>427</v>
-      </c>
-      <c r="T72" t="s">
-        <v>428</v>
       </c>
       <c r="U72" t="s">
         <v>86</v>
@@ -7326,34 +7326,34 @@
         <v>22</v>
       </c>
       <c r="C73" t="s">
+        <v>428</v>
+      </c>
+      <c r="D73" t="s">
         <v>429</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
+        <v>429</v>
+      </c>
+      <c r="F73" t="s">
+        <v>49</v>
+      </c>
+      <c r="I73" t="s">
         <v>430</v>
       </c>
-      <c r="E73" t="s">
-        <v>430</v>
-      </c>
-      <c r="F73" t="s">
-        <v>49</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="J73" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="K73" t="s">
+        <v>774</v>
+      </c>
+      <c r="L73" t="s">
         <v>424</v>
-      </c>
-      <c r="L73" t="s">
-        <v>425</v>
       </c>
       <c r="M73" t="s">
         <v>384</v>
       </c>
       <c r="N73" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>78</v>
@@ -7362,10 +7362,10 @@
         <v>33</v>
       </c>
       <c r="R73" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="T73" t="s">
         <v>427</v>
-      </c>
-      <c r="T73" t="s">
-        <v>428</v>
       </c>
       <c r="U73" t="s">
         <v>86</v>
@@ -7388,34 +7388,34 @@
         <v>22</v>
       </c>
       <c r="C74" t="s">
+        <v>432</v>
+      </c>
+      <c r="D74" t="s">
         <v>433</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
+        <v>433</v>
+      </c>
+      <c r="F74" t="s">
+        <v>49</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="E74" t="s">
-        <v>434</v>
-      </c>
-      <c r="F74" t="s">
-        <v>49</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K74" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L74" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M74" t="s">
         <v>384</v>
       </c>
       <c r="N74" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>78</v>
@@ -7424,7 +7424,7 @@
         <v>33</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U74" t="s">
         <v>35</v>
@@ -7447,19 +7447,19 @@
         <v>22</v>
       </c>
       <c r="C75" t="s">
+        <v>437</v>
+      </c>
+      <c r="D75" t="s">
         <v>438</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>438</v>
+      </c>
+      <c r="F75" t="s">
+        <v>49</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E75" t="s">
-        <v>439</v>
-      </c>
-      <c r="F75" t="s">
-        <v>49</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>367</v>
@@ -7488,19 +7488,19 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
+        <v>440</v>
+      </c>
+      <c r="D76" t="s">
         <v>441</v>
       </c>
-      <c r="D76" t="s">
-        <v>442</v>
-      </c>
       <c r="E76" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F76" t="s">
         <v>49</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>367</v>
@@ -7529,19 +7529,19 @@
         <v>22</v>
       </c>
       <c r="C77" t="s">
+        <v>442</v>
+      </c>
+      <c r="D77" t="s">
         <v>443</v>
       </c>
-      <c r="D77" t="s">
-        <v>444</v>
-      </c>
       <c r="E77" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F77" t="s">
         <v>49</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>367</v>
@@ -7570,19 +7570,19 @@
         <v>22</v>
       </c>
       <c r="C78" t="s">
+        <v>444</v>
+      </c>
+      <c r="D78" t="s">
         <v>445</v>
       </c>
-      <c r="D78" t="s">
-        <v>446</v>
-      </c>
       <c r="E78" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F78" t="s">
         <v>49</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>367</v>
@@ -7611,19 +7611,19 @@
         <v>22</v>
       </c>
       <c r="C79" t="s">
+        <v>446</v>
+      </c>
+      <c r="D79" t="s">
         <v>447</v>
       </c>
-      <c r="D79" t="s">
-        <v>448</v>
-      </c>
       <c r="E79" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F79" t="s">
         <v>49</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>367</v>
@@ -7652,19 +7652,19 @@
         <v>22</v>
       </c>
       <c r="C80" t="s">
+        <v>448</v>
+      </c>
+      <c r="D80" t="s">
         <v>449</v>
       </c>
-      <c r="D80" t="s">
-        <v>450</v>
-      </c>
       <c r="E80" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F80" t="s">
         <v>49</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>367</v>
@@ -7693,19 +7693,19 @@
         <v>22</v>
       </c>
       <c r="C81" t="s">
+        <v>450</v>
+      </c>
+      <c r="D81" t="s">
         <v>451</v>
       </c>
-      <c r="D81" t="s">
-        <v>452</v>
-      </c>
       <c r="E81" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F81" t="s">
         <v>49</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>367</v>
@@ -7734,19 +7734,19 @@
         <v>22</v>
       </c>
       <c r="C82" t="s">
+        <v>452</v>
+      </c>
+      <c r="D82" t="s">
         <v>453</v>
       </c>
-      <c r="D82" t="s">
-        <v>454</v>
-      </c>
       <c r="E82" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F82" t="s">
         <v>49</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>367</v>
@@ -7775,19 +7775,19 @@
         <v>22</v>
       </c>
       <c r="C83" t="s">
+        <v>454</v>
+      </c>
+      <c r="D83" t="s">
         <v>455</v>
       </c>
-      <c r="D83" t="s">
-        <v>456</v>
-      </c>
       <c r="E83" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F83" t="s">
         <v>49</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>367</v>
@@ -7816,19 +7816,19 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
+        <v>456</v>
+      </c>
+      <c r="D84" t="s">
         <v>457</v>
       </c>
-      <c r="D84" t="s">
-        <v>458</v>
-      </c>
       <c r="E84" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F84" t="s">
         <v>49</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>367</v>
@@ -7857,19 +7857,19 @@
         <v>22</v>
       </c>
       <c r="C85" t="s">
+        <v>458</v>
+      </c>
+      <c r="D85" t="s">
         <v>459</v>
       </c>
-      <c r="D85" t="s">
-        <v>460</v>
-      </c>
       <c r="E85" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F85" t="s">
         <v>49</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>367</v>
@@ -7898,19 +7898,19 @@
         <v>22</v>
       </c>
       <c r="C86" t="s">
+        <v>460</v>
+      </c>
+      <c r="D86" t="s">
         <v>461</v>
       </c>
-      <c r="D86" t="s">
-        <v>462</v>
-      </c>
       <c r="E86" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F86" t="s">
         <v>49</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>367</v>
@@ -7939,19 +7939,19 @@
         <v>22</v>
       </c>
       <c r="C87" t="s">
+        <v>462</v>
+      </c>
+      <c r="D87" t="s">
         <v>463</v>
       </c>
-      <c r="D87" t="s">
-        <v>464</v>
-      </c>
       <c r="E87" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F87" t="s">
         <v>49</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>367</v>
@@ -7980,19 +7980,19 @@
         <v>22</v>
       </c>
       <c r="C88" t="s">
+        <v>464</v>
+      </c>
+      <c r="D88" t="s">
         <v>465</v>
       </c>
-      <c r="D88" t="s">
-        <v>466</v>
-      </c>
       <c r="E88" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F88" t="s">
         <v>49</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>367</v>
@@ -8021,19 +8021,19 @@
         <v>22</v>
       </c>
       <c r="C89" t="s">
+        <v>466</v>
+      </c>
+      <c r="D89" t="s">
         <v>467</v>
       </c>
-      <c r="D89" t="s">
-        <v>468</v>
-      </c>
       <c r="E89" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F89" t="s">
         <v>49</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>367</v>
@@ -8062,19 +8062,19 @@
         <v>22</v>
       </c>
       <c r="C90" t="s">
+        <v>468</v>
+      </c>
+      <c r="D90" t="s">
         <v>469</v>
       </c>
-      <c r="D90" t="s">
-        <v>470</v>
-      </c>
       <c r="E90" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F90" t="s">
         <v>49</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>367</v>
@@ -8103,19 +8103,19 @@
         <v>22</v>
       </c>
       <c r="C91" t="s">
+        <v>470</v>
+      </c>
+      <c r="D91" t="s">
         <v>471</v>
       </c>
-      <c r="D91" t="s">
-        <v>472</v>
-      </c>
       <c r="E91" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F91" t="s">
         <v>49</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>367</v>
@@ -8144,19 +8144,19 @@
         <v>22</v>
       </c>
       <c r="C92" t="s">
+        <v>472</v>
+      </c>
+      <c r="D92" t="s">
         <v>473</v>
       </c>
-      <c r="D92" t="s">
-        <v>474</v>
-      </c>
       <c r="E92" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F92" t="s">
         <v>49</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>367</v>
@@ -8185,19 +8185,19 @@
         <v>22</v>
       </c>
       <c r="C93" t="s">
+        <v>474</v>
+      </c>
+      <c r="D93" t="s">
         <v>475</v>
       </c>
-      <c r="D93" t="s">
-        <v>476</v>
-      </c>
       <c r="E93" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F93" t="s">
         <v>49</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>367</v>
@@ -8226,34 +8226,34 @@
         <v>22</v>
       </c>
       <c r="C94" t="s">
+        <v>476</v>
+      </c>
+      <c r="D94" t="s">
         <v>477</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>477</v>
+      </c>
+      <c r="F94" t="s">
+        <v>49</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="E94" t="s">
-        <v>478</v>
-      </c>
-      <c r="F94" t="s">
-        <v>49</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K94" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L94" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M94" t="s">
         <v>384</v>
       </c>
       <c r="N94" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P94" s="1" t="s">
         <v>78</v>
@@ -8262,7 +8262,7 @@
         <v>33</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U94" t="s">
         <v>35</v>
@@ -8285,34 +8285,34 @@
         <v>22</v>
       </c>
       <c r="C95" t="s">
+        <v>481</v>
+      </c>
+      <c r="D95" t="s">
         <v>482</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>483</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
+        <v>49</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="F95" t="s">
-        <v>49</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K95" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="L95" t="s">
+        <v>485</v>
+      </c>
+      <c r="M95" t="s">
         <v>486</v>
       </c>
-      <c r="M95" t="s">
+      <c r="N95" t="s">
         <v>487</v>
-      </c>
-      <c r="N95" t="s">
-        <v>488</v>
       </c>
       <c r="P95" s="1" t="s">
         <v>78</v>
@@ -8321,7 +8321,7 @@
         <v>33</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U95" t="s">
         <v>35</v>
@@ -8344,34 +8344,34 @@
         <v>22</v>
       </c>
       <c r="C96" t="s">
+        <v>488</v>
+      </c>
+      <c r="D96" t="s">
         <v>489</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>490</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>49</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F96" t="s">
-        <v>49</v>
-      </c>
-      <c r="I96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="K96" t="s">
+        <v>632</v>
+      </c>
+      <c r="L96" t="s">
         <v>493</v>
       </c>
-      <c r="K96" t="s">
-        <v>633</v>
-      </c>
-      <c r="L96" t="s">
+      <c r="M96" t="s">
         <v>494</v>
       </c>
-      <c r="M96" t="s">
+      <c r="N96" t="s">
         <v>495</v>
-      </c>
-      <c r="N96" t="s">
-        <v>496</v>
       </c>
       <c r="P96" s="1" t="s">
         <v>78</v>
@@ -8380,7 +8380,7 @@
         <v>33</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U96" t="s">
         <v>35</v>
@@ -8403,34 +8403,34 @@
         <v>22</v>
       </c>
       <c r="C97" t="s">
+        <v>496</v>
+      </c>
+      <c r="D97" t="s">
         <v>497</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
+        <v>497</v>
+      </c>
+      <c r="F97" t="s">
+        <v>49</v>
+      </c>
+      <c r="I97" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="E97" t="s">
-        <v>498</v>
-      </c>
-      <c r="F97" t="s">
-        <v>49</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L97" t="s">
+        <v>499</v>
+      </c>
+      <c r="M97" t="s">
         <v>500</v>
       </c>
-      <c r="M97" t="s">
+      <c r="N97" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P97" s="1" t="s">
         <v>78</v>
@@ -8439,7 +8439,7 @@
         <v>33</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U97" t="s">
         <v>35</v>
@@ -8451,7 +8451,7 @@
         <v>352</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8462,34 +8462,34 @@
         <v>22</v>
       </c>
       <c r="C98" t="s">
+        <v>503</v>
+      </c>
+      <c r="D98" t="s">
         <v>504</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>504</v>
+      </c>
+      <c r="F98" t="s">
+        <v>49</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="E98" t="s">
-        <v>505</v>
-      </c>
-      <c r="F98" t="s">
-        <v>49</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L98" t="s">
+        <v>499</v>
+      </c>
+      <c r="M98" t="s">
         <v>500</v>
       </c>
-      <c r="M98" t="s">
+      <c r="N98" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P98" s="1" t="s">
         <v>78</v>
@@ -8498,7 +8498,7 @@
         <v>33</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U98" t="s">
         <v>35</v>
@@ -8510,7 +8510,7 @@
         <v>352</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8521,34 +8521,34 @@
         <v>22</v>
       </c>
       <c r="C99" t="s">
+        <v>506</v>
+      </c>
+      <c r="D99" t="s">
         <v>507</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
+        <v>507</v>
+      </c>
+      <c r="F99" t="s">
+        <v>49</v>
+      </c>
+      <c r="I99" t="s">
         <v>508</v>
-      </c>
-      <c r="E99" t="s">
-        <v>508</v>
-      </c>
-      <c r="F99" t="s">
-        <v>49</v>
-      </c>
-      <c r="I99" t="s">
-        <v>509</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L99" t="s">
+        <v>499</v>
+      </c>
+      <c r="M99" t="s">
         <v>500</v>
       </c>
-      <c r="M99" t="s">
+      <c r="N99" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>78</v>
@@ -8557,7 +8557,7 @@
         <v>33</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U99" t="s">
         <v>35</v>
@@ -8569,7 +8569,7 @@
         <v>352</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.25">
@@ -8580,19 +8580,19 @@
         <v>22</v>
       </c>
       <c r="C100" t="s">
+        <v>509</v>
+      </c>
+      <c r="D100" t="s">
         <v>510</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>510</v>
+      </c>
+      <c r="F100" t="s">
+        <v>49</v>
+      </c>
+      <c r="I100" t="s">
         <v>511</v>
-      </c>
-      <c r="E100" t="s">
-        <v>511</v>
-      </c>
-      <c r="F100" t="s">
-        <v>49</v>
-      </c>
-      <c r="I100" t="s">
-        <v>512</v>
       </c>
       <c r="K100" t="s">
         <v>41</v>
@@ -8618,19 +8618,19 @@
         <v>22</v>
       </c>
       <c r="C101" t="s">
+        <v>512</v>
+      </c>
+      <c r="D101" t="s">
         <v>513</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
+        <v>513</v>
+      </c>
+      <c r="F101" t="s">
+        <v>49</v>
+      </c>
+      <c r="I101" t="s">
         <v>514</v>
-      </c>
-      <c r="E101" t="s">
-        <v>514</v>
-      </c>
-      <c r="F101" t="s">
-        <v>49</v>
-      </c>
-      <c r="I101" t="s">
-        <v>515</v>
       </c>
       <c r="K101" t="s">
         <v>41</v>
@@ -8656,19 +8656,19 @@
         <v>22</v>
       </c>
       <c r="C102" t="s">
+        <v>515</v>
+      </c>
+      <c r="D102" t="s">
         <v>516</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>516</v>
+      </c>
+      <c r="F102" t="s">
+        <v>49</v>
+      </c>
+      <c r="I102" t="s">
         <v>517</v>
-      </c>
-      <c r="E102" t="s">
-        <v>517</v>
-      </c>
-      <c r="F102" t="s">
-        <v>49</v>
-      </c>
-      <c r="I102" t="s">
-        <v>518</v>
       </c>
       <c r="K102" t="s">
         <v>41</v>
@@ -8694,19 +8694,19 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
+        <v>518</v>
+      </c>
+      <c r="D103" t="s">
         <v>519</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>519</v>
+      </c>
+      <c r="F103" t="s">
+        <v>49</v>
+      </c>
+      <c r="I103" t="s">
         <v>520</v>
-      </c>
-      <c r="E103" t="s">
-        <v>520</v>
-      </c>
-      <c r="F103" t="s">
-        <v>49</v>
-      </c>
-      <c r="I103" t="s">
-        <v>521</v>
       </c>
       <c r="K103" t="s">
         <v>41</v>
@@ -8732,19 +8732,19 @@
         <v>22</v>
       </c>
       <c r="C104" t="s">
+        <v>521</v>
+      </c>
+      <c r="D104" t="s">
         <v>522</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
+        <v>522</v>
+      </c>
+      <c r="F104" t="s">
+        <v>49</v>
+      </c>
+      <c r="I104" t="s">
         <v>523</v>
-      </c>
-      <c r="E104" t="s">
-        <v>523</v>
-      </c>
-      <c r="F104" t="s">
-        <v>49</v>
-      </c>
-      <c r="I104" t="s">
-        <v>524</v>
       </c>
       <c r="K104" t="s">
         <v>41</v>
@@ -8770,31 +8770,31 @@
         <v>22</v>
       </c>
       <c r="C105" t="s">
+        <v>524</v>
+      </c>
+      <c r="D105" t="s">
         <v>525</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>525</v>
+      </c>
+      <c r="F105" t="s">
+        <v>49</v>
+      </c>
+      <c r="I105" t="s">
+        <v>514</v>
+      </c>
+      <c r="K105" t="s">
+        <v>634</v>
+      </c>
+      <c r="L105" t="s">
         <v>526</v>
       </c>
-      <c r="E105" t="s">
-        <v>526</v>
-      </c>
-      <c r="F105" t="s">
-        <v>49</v>
-      </c>
-      <c r="I105" t="s">
-        <v>515</v>
-      </c>
-      <c r="K105" t="s">
-        <v>635</v>
-      </c>
-      <c r="L105" t="s">
+      <c r="M105" t="s">
         <v>527</v>
       </c>
-      <c r="M105" t="s">
+      <c r="N105" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="N105" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="P105" s="1" t="s">
         <v>78</v>
@@ -8803,7 +8803,7 @@
         <v>79</v>
       </c>
       <c r="R105" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U105" t="s">
         <v>35</v>
@@ -8826,19 +8826,19 @@
         <v>22</v>
       </c>
       <c r="C106" t="s">
+        <v>530</v>
+      </c>
+      <c r="D106" t="s">
         <v>531</v>
       </c>
-      <c r="D106" t="s">
-        <v>532</v>
-      </c>
       <c r="E106" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F106" t="s">
         <v>49</v>
       </c>
       <c r="I106" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K106" t="s">
         <v>41</v>
@@ -8864,28 +8864,28 @@
         <v>22</v>
       </c>
       <c r="C107" t="s">
+        <v>532</v>
+      </c>
+      <c r="D107" t="s">
         <v>533</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>534</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
+        <v>49</v>
+      </c>
+      <c r="I107" t="s">
         <v>535</v>
       </c>
-      <c r="F107" t="s">
-        <v>49</v>
-      </c>
-      <c r="I107" t="s">
+      <c r="J107" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="K107" t="s">
         <v>41</v>
       </c>
       <c r="T107" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="U107" t="s">
         <v>86</v>
@@ -8908,22 +8908,22 @@
         <v>22</v>
       </c>
       <c r="C108" t="s">
+        <v>538</v>
+      </c>
+      <c r="D108" t="s">
         <v>539</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>540</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
+        <v>49</v>
+      </c>
+      <c r="I108" t="s">
+        <v>535</v>
+      </c>
+      <c r="J108" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="F108" t="s">
-        <v>49</v>
-      </c>
-      <c r="I108" t="s">
-        <v>536</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="K108" t="s">
         <v>41</v>
@@ -8949,22 +8949,22 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
+        <v>542</v>
+      </c>
+      <c r="D109" t="s">
         <v>543</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>544</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
+        <v>49</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F109" t="s">
-        <v>49</v>
-      </c>
-      <c r="I109" s="1" t="s">
+      <c r="J109" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="K109" t="s">
         <v>41</v>
@@ -8990,34 +8990,34 @@
         <v>22</v>
       </c>
       <c r="C110" t="s">
+        <v>547</v>
+      </c>
+      <c r="D110" t="s">
         <v>548</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>549</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>49</v>
+      </c>
+      <c r="I110" t="s">
         <v>550</v>
       </c>
-      <c r="F110" t="s">
-        <v>49</v>
-      </c>
-      <c r="I110" t="s">
+      <c r="J110" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K110" t="s">
+        <v>635</v>
+      </c>
+      <c r="L110" t="s">
         <v>551</v>
       </c>
-      <c r="J110" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K110" t="s">
-        <v>636</v>
-      </c>
-      <c r="L110" t="s">
+      <c r="M110" t="s">
         <v>552</v>
       </c>
-      <c r="M110" t="s">
+      <c r="N110" t="s">
         <v>553</v>
-      </c>
-      <c r="N110" t="s">
-        <v>554</v>
       </c>
       <c r="P110" s="1" t="s">
         <v>78</v>
@@ -9026,7 +9026,7 @@
         <v>33</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="U110" t="s">
         <v>35</v>
@@ -9038,7 +9038,7 @@
         <v>68</v>
       </c>
       <c r="X110" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9049,34 +9049,34 @@
         <v>22</v>
       </c>
       <c r="C111" t="s">
+        <v>556</v>
+      </c>
+      <c r="D111" t="s">
         <v>557</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>558</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>49</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F111" t="s">
-        <v>49</v>
-      </c>
-      <c r="I111" s="1" t="s">
+      <c r="J111" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K111" t="s">
+        <v>636</v>
+      </c>
+      <c r="L111" t="s">
         <v>560</v>
       </c>
-      <c r="J111" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K111" t="s">
-        <v>637</v>
-      </c>
-      <c r="L111" t="s">
+      <c r="M111" t="s">
         <v>561</v>
       </c>
-      <c r="M111" t="s">
+      <c r="N111" t="s">
         <v>562</v>
-      </c>
-      <c r="N111" t="s">
-        <v>563</v>
       </c>
       <c r="P111" s="1" t="s">
         <v>78</v>
@@ -9085,10 +9085,10 @@
         <v>33</v>
       </c>
       <c r="R111" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="T111" t="s">
         <v>564</v>
-      </c>
-      <c r="T111" t="s">
-        <v>565</v>
       </c>
       <c r="U111" t="s">
         <v>35</v>
@@ -9100,7 +9100,7 @@
         <v>68</v>
       </c>
       <c r="X111" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9111,19 +9111,19 @@
         <v>22</v>
       </c>
       <c r="C112" t="s">
+        <v>566</v>
+      </c>
+      <c r="D112" t="s">
         <v>567</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>568</v>
-      </c>
-      <c r="E112" t="s">
-        <v>569</v>
       </c>
       <c r="F112" t="s">
         <v>112</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="U112" t="s">
         <v>35</v>
@@ -9135,7 +9135,7 @@
         <v>59</v>
       </c>
       <c r="X112" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="113" spans="1:24" ht="270" x14ac:dyDescent="0.25">
@@ -9146,22 +9146,22 @@
         <v>22</v>
       </c>
       <c r="C113" t="s">
+        <v>569</v>
+      </c>
+      <c r="D113" t="s">
         <v>570</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>571</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>49</v>
+      </c>
+      <c r="G113" t="s">
         <v>572</v>
       </c>
-      <c r="F113" t="s">
-        <v>49</v>
-      </c>
-      <c r="G113" t="s">
-        <v>573</v>
-      </c>
       <c r="K113" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="U113" t="s">
         <v>35</v>
@@ -9173,7 +9173,7 @@
         <v>59</v>
       </c>
       <c r="X113" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.25">
@@ -9181,7 +9181,7 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C114" t="s">
         <v>23</v>
@@ -9202,10 +9202,10 @@
         <v>28</v>
       </c>
       <c r="L114" t="s">
+        <v>574</v>
+      </c>
+      <c r="M114" t="s">
         <v>575</v>
-      </c>
-      <c r="M114" t="s">
-        <v>576</v>
       </c>
       <c r="U114" t="s">
         <v>35</v>
@@ -9225,7 +9225,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C115" t="s">
         <v>38</v>
@@ -9255,7 +9255,7 @@
         <v>43</v>
       </c>
       <c r="X115" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.25">
@@ -9263,7 +9263,7 @@
         <v>3</v>
       </c>
       <c r="B116" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C116" t="s">
         <v>44</v>
@@ -9293,7 +9293,7 @@
         <v>43</v>
       </c>
       <c r="X116" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.25">
@@ -9301,7 +9301,7 @@
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C117" t="s">
         <v>47</v>
@@ -9339,7 +9339,7 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C118" t="s">
         <v>51</v>
@@ -9360,7 +9360,7 @@
         <v>56</v>
       </c>
       <c r="K118" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L118" t="s">
         <v>57</v>
@@ -9381,7 +9381,7 @@
         <v>59</v>
       </c>
       <c r="X118" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="119" spans="1:24" ht="45" x14ac:dyDescent="0.25">
@@ -9389,7 +9389,7 @@
         <v>6</v>
       </c>
       <c r="B119" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C119" t="s">
         <v>60</v>
@@ -9436,7 +9436,7 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C120" t="s">
         <v>70</v>
@@ -9457,7 +9457,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="L120" t="s">
         <v>75</v>
@@ -9495,7 +9495,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C121" t="s">
         <v>81</v>
@@ -9536,7 +9536,7 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C122" t="s">
         <v>88</v>
@@ -9577,7 +9577,7 @@
         <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C123" t="s">
         <v>92</v>
@@ -9598,7 +9598,7 @@
         <v>96</v>
       </c>
       <c r="K123" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L123" t="s">
         <v>97</v>
@@ -9639,7 +9639,7 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C124" t="s">
         <v>103</v>
@@ -9660,7 +9660,7 @@
         <v>107</v>
       </c>
       <c r="K124" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L124" t="s">
         <v>97</v>
@@ -9701,7 +9701,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C125" t="s">
         <v>110</v>
@@ -9739,7 +9739,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C126" t="s">
         <v>114</v>
@@ -9774,7 +9774,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C127" t="s">
         <v>117</v>
@@ -9795,7 +9795,7 @@
         <v>121</v>
       </c>
       <c r="K127" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="L127" t="s">
         <v>97</v>
@@ -9836,7 +9836,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C128" t="s">
         <v>123</v>
@@ -9854,7 +9854,7 @@
         <v>125</v>
       </c>
       <c r="K128" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L128" t="s">
         <v>126</v>
@@ -9892,7 +9892,7 @@
         <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C129" t="s">
         <v>131</v>
@@ -9933,7 +9933,7 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C130" t="s">
         <v>136</v>
@@ -9954,7 +9954,7 @@
         <v>139</v>
       </c>
       <c r="K130" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L130" t="s">
         <v>140</v>
@@ -9995,7 +9995,7 @@
         <v>18</v>
       </c>
       <c r="B131" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C131" t="s">
         <v>144</v>
@@ -10013,7 +10013,7 @@
         <v>146</v>
       </c>
       <c r="K131" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="U131" t="s">
         <v>35</v>
@@ -10025,7 +10025,7 @@
         <v>59</v>
       </c>
       <c r="X131" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="132" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -10033,7 +10033,7 @@
         <v>19</v>
       </c>
       <c r="B132" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C132" t="s">
         <v>147</v>
@@ -10054,7 +10054,7 @@
         <v>139</v>
       </c>
       <c r="K132" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L132" t="s">
         <v>150</v>
@@ -10095,7 +10095,7 @@
         <v>20</v>
       </c>
       <c r="B133" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C133" t="s">
         <v>153</v>
@@ -10113,7 +10113,7 @@
         <v>146</v>
       </c>
       <c r="K133" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="U133" t="s">
         <v>35</v>
@@ -10125,7 +10125,7 @@
         <v>59</v>
       </c>
       <c r="X133" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="134" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -10133,7 +10133,7 @@
         <v>21</v>
       </c>
       <c r="B134" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C134" t="s">
         <v>155</v>
@@ -10154,7 +10154,7 @@
         <v>158</v>
       </c>
       <c r="K134" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L134" t="s">
         <v>159</v>
@@ -10195,7 +10195,7 @@
         <v>22</v>
       </c>
       <c r="B135" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C135" t="s">
         <v>162</v>
@@ -10216,7 +10216,7 @@
         <v>139</v>
       </c>
       <c r="K135" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L135" t="s">
         <v>164</v>
@@ -10237,7 +10237,7 @@
         <v>143</v>
       </c>
       <c r="T135" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="U135" t="s">
         <v>35</v>
@@ -10257,7 +10257,7 @@
         <v>23</v>
       </c>
       <c r="B136" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C136" t="s">
         <v>169</v>
@@ -10275,7 +10275,7 @@
         <v>146</v>
       </c>
       <c r="K136" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L136" t="s">
         <v>164</v>
@@ -10305,7 +10305,7 @@
         <v>59</v>
       </c>
       <c r="X136" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
         <v>24</v>
       </c>
       <c r="B137" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C137" t="s">
         <v>171</v>
@@ -10331,7 +10331,7 @@
         <v>173</v>
       </c>
       <c r="K137" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="L137" t="s">
         <v>174</v>
@@ -10361,7 +10361,7 @@
         <v>59</v>
       </c>
       <c r="X137" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.25">
@@ -10369,7 +10369,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C138" t="s">
         <v>178</v>
@@ -10384,7 +10384,7 @@
         <v>26</v>
       </c>
       <c r="K138" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="U138" t="s">
         <v>35</v>
@@ -10396,7 +10396,7 @@
         <v>59</v>
       </c>
       <c r="X138" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="139" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -10404,7 +10404,7 @@
         <v>26</v>
       </c>
       <c r="B139" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C139" t="s">
         <v>180</v>
@@ -10425,7 +10425,7 @@
         <v>184</v>
       </c>
       <c r="K139" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="L139" t="s">
         <v>185</v>
@@ -10443,7 +10443,7 @@
         <v>183</v>
       </c>
       <c r="T139" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="U139" t="s">
         <v>35</v>
@@ -10455,7 +10455,7 @@
         <v>59</v>
       </c>
       <c r="X139" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="140" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -10463,7 +10463,7 @@
         <v>27</v>
       </c>
       <c r="B140" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C140" t="s">
         <v>188</v>
@@ -10484,7 +10484,7 @@
         <v>184</v>
       </c>
       <c r="K140" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L140" t="s">
         <v>191</v>
@@ -10502,7 +10502,7 @@
         <v>183</v>
       </c>
       <c r="T140" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="U140" t="s">
         <v>35</v>
@@ -10514,7 +10514,7 @@
         <v>59</v>
       </c>
       <c r="X140" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.25">
@@ -10522,7 +10522,7 @@
         <v>28</v>
       </c>
       <c r="B141" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C141" t="s">
         <v>193</v>
@@ -10563,7 +10563,7 @@
         <v>29</v>
       </c>
       <c r="B142" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C142" t="s">
         <v>196</v>
@@ -10604,7 +10604,7 @@
         <v>30</v>
       </c>
       <c r="B143" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C143" t="s">
         <v>200</v>
@@ -10642,7 +10642,7 @@
         <v>31</v>
       </c>
       <c r="B144" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C144" t="s">
         <v>203</v>
@@ -10680,7 +10680,7 @@
         <v>32</v>
       </c>
       <c r="B145" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C145" t="s">
         <v>206</v>
@@ -10718,7 +10718,7 @@
         <v>33</v>
       </c>
       <c r="B146" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C146" t="s">
         <v>209</v>
@@ -10736,7 +10736,7 @@
         <v>211</v>
       </c>
       <c r="K146" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="L146" t="s">
         <v>210</v>
@@ -10765,7 +10765,7 @@
         <v>34</v>
       </c>
       <c r="B147" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C147" t="s">
         <v>214</v>
@@ -10783,7 +10783,7 @@
         <v>211</v>
       </c>
       <c r="K147" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L147" t="s">
         <v>215</v>
@@ -10812,7 +10812,7 @@
         <v>35</v>
       </c>
       <c r="B148" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C148" t="s">
         <v>218</v>
@@ -10830,7 +10830,7 @@
         <v>211</v>
       </c>
       <c r="K148" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L148" t="s">
         <v>219</v>
@@ -10859,7 +10859,7 @@
         <v>36</v>
       </c>
       <c r="B149" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C149" t="s">
         <v>222</v>
@@ -10880,7 +10880,7 @@
         <v>224</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L149" s="1" t="s">
         <v>225</v>
@@ -10895,7 +10895,7 @@
         <v>59</v>
       </c>
       <c r="X149" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.25">
@@ -10903,7 +10903,7 @@
         <v>37</v>
       </c>
       <c r="B150" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C150" t="s">
         <v>226</v>
@@ -10921,7 +10921,7 @@
         <v>211</v>
       </c>
       <c r="K150" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L150" t="s">
         <v>227</v>
@@ -10950,7 +10950,7 @@
         <v>38</v>
       </c>
       <c r="B151" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C151" t="s">
         <v>230</v>
@@ -10968,7 +10968,7 @@
         <v>232</v>
       </c>
       <c r="K151" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="L151" t="s">
         <v>231</v>
@@ -10997,7 +10997,7 @@
         <v>39</v>
       </c>
       <c r="B152" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C152" t="s">
         <v>235</v>
@@ -11038,7 +11038,7 @@
         <v>40</v>
       </c>
       <c r="B153" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C153" t="s">
         <v>240</v>
@@ -11079,7 +11079,7 @@
         <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C154" t="s">
         <v>245</v>
@@ -11120,7 +11120,7 @@
         <v>42</v>
       </c>
       <c r="B155" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C155" t="s">
         <v>248</v>
@@ -11141,7 +11141,7 @@
         <v>244</v>
       </c>
       <c r="K155" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L155" t="s">
         <v>252</v>
@@ -11176,7 +11176,7 @@
         <v>43</v>
       </c>
       <c r="B156" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C156" t="s">
         <v>257</v>
@@ -11214,7 +11214,7 @@
         <v>44</v>
       </c>
       <c r="B157" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C157" t="s">
         <v>260</v>
@@ -11235,7 +11235,7 @@
         <v>263</v>
       </c>
       <c r="K157" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L157" t="s">
         <v>264</v>
@@ -11267,7 +11267,7 @@
         <v>45</v>
       </c>
       <c r="B158" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C158" t="s">
         <v>267</v>
@@ -11305,7 +11305,7 @@
         <v>46</v>
       </c>
       <c r="B159" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C159" t="s">
         <v>270</v>
@@ -11326,7 +11326,7 @@
         <v>273</v>
       </c>
       <c r="K159" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="L159" t="s">
         <v>274</v>
@@ -11364,7 +11364,7 @@
         <v>47</v>
       </c>
       <c r="B160" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C160" t="s">
         <v>279</v>
@@ -11423,7 +11423,7 @@
         <v>48</v>
       </c>
       <c r="B161" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C161" t="s">
         <v>283</v>
@@ -11464,7 +11464,7 @@
         <v>49</v>
       </c>
       <c r="B162" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C162" t="s">
         <v>287</v>
@@ -11482,7 +11482,7 @@
         <v>113</v>
       </c>
       <c r="K162" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L162" t="s">
         <v>289</v>
@@ -11523,7 +11523,7 @@
         <v>50</v>
       </c>
       <c r="B163" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C163" t="s">
         <v>296</v>
@@ -11544,7 +11544,7 @@
         <v>299</v>
       </c>
       <c r="K163" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L163" t="s">
         <v>289</v>
@@ -11582,7 +11582,7 @@
         <v>51</v>
       </c>
       <c r="B164" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C164" t="s">
         <v>301</v>
@@ -11603,7 +11603,7 @@
         <v>304</v>
       </c>
       <c r="K164" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L164" t="s">
         <v>305</v>
@@ -11641,7 +11641,7 @@
         <v>52</v>
       </c>
       <c r="B165" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C165" t="s">
         <v>310</v>
@@ -11682,7 +11682,7 @@
         <v>53</v>
       </c>
       <c r="B166" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C166" t="s">
         <v>314</v>
@@ -11700,7 +11700,7 @@
         <v>313</v>
       </c>
       <c r="K166" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L166" t="s">
         <v>316</v>
@@ -11721,7 +11721,7 @@
         <v>320</v>
       </c>
       <c r="T166" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="U166" t="s">
         <v>35</v>
@@ -11741,7 +11741,7 @@
         <v>54</v>
       </c>
       <c r="B167" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C167" t="s">
         <v>323</v>
@@ -11779,7 +11779,7 @@
         <v>55</v>
       </c>
       <c r="B168" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C168" t="s">
         <v>325</v>
@@ -11797,7 +11797,7 @@
         <v>328</v>
       </c>
       <c r="K168" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L168" t="s">
         <v>329</v>
@@ -11818,7 +11818,7 @@
         <v>320</v>
       </c>
       <c r="T168" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="U168" t="s">
         <v>35</v>
@@ -11830,7 +11830,7 @@
         <v>59</v>
       </c>
       <c r="X168" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="169" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -11838,7 +11838,7 @@
         <v>56</v>
       </c>
       <c r="B169" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C169" t="s">
         <v>333</v>
@@ -11879,7 +11879,7 @@
         <v>57</v>
       </c>
       <c r="B170" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C170" t="s">
         <v>337</v>
@@ -11920,7 +11920,7 @@
         <v>58</v>
       </c>
       <c r="B171" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C171" t="s">
         <v>340</v>
@@ -11941,7 +11941,7 @@
         <v>312</v>
       </c>
       <c r="K171" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L171" s="1" t="s">
         <v>343</v>
@@ -11971,7 +11971,7 @@
         <v>59</v>
       </c>
       <c r="X171" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="172" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -11979,7 +11979,7 @@
         <v>59</v>
       </c>
       <c r="B172" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C172" t="s">
         <v>347</v>
@@ -11997,7 +11997,7 @@
         <v>350</v>
       </c>
       <c r="K172" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L172" s="1" t="s">
         <v>343</v>
@@ -12027,7 +12027,7 @@
         <v>352</v>
       </c>
       <c r="X172" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="173" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -12035,7 +12035,7 @@
         <v>60</v>
       </c>
       <c r="B173" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C173" t="s">
         <v>353</v>
@@ -12056,7 +12056,7 @@
         <v>356</v>
       </c>
       <c r="K173" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L173" t="s">
         <v>358</v>
@@ -12097,7 +12097,7 @@
         <v>61</v>
       </c>
       <c r="B174" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C174" t="s">
         <v>363</v>
@@ -12118,7 +12118,7 @@
         <v>367</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L174" t="s">
         <v>368</v>
@@ -12151,7 +12151,7 @@
         <v>352</v>
       </c>
       <c r="X174" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="175" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -12159,7 +12159,7 @@
         <v>62</v>
       </c>
       <c r="B175" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C175" t="s">
         <v>374</v>
@@ -12180,7 +12180,7 @@
         <v>367</v>
       </c>
       <c r="K175" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="L175" t="s">
         <v>377</v>
@@ -12221,7 +12221,7 @@
         <v>63</v>
       </c>
       <c r="B176" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C176" t="s">
         <v>381</v>
@@ -12242,7 +12242,7 @@
         <v>367</v>
       </c>
       <c r="K176" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="L176" t="s">
         <v>377</v>
@@ -12280,7 +12280,7 @@
         <v>64</v>
       </c>
       <c r="B177" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C177" t="s">
         <v>386</v>
@@ -12301,7 +12301,7 @@
         <v>367</v>
       </c>
       <c r="K177" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L177" t="s">
         <v>389</v>
@@ -12339,7 +12339,7 @@
         <v>65</v>
       </c>
       <c r="B178" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C178" t="s">
         <v>391</v>
@@ -12360,7 +12360,7 @@
         <v>367</v>
       </c>
       <c r="K178" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="L178" t="s">
         <v>394</v>
@@ -12398,7 +12398,7 @@
         <v>66</v>
       </c>
       <c r="B179" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C179" t="s">
         <v>396</v>
@@ -12419,7 +12419,7 @@
         <v>367</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L179" t="s">
         <v>368</v>
@@ -12457,7 +12457,7 @@
         <v>67</v>
       </c>
       <c r="B180" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C180" t="s">
         <v>400</v>
@@ -12498,7 +12498,7 @@
         <v>68</v>
       </c>
       <c r="B181" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C181" t="s">
         <v>403</v>
@@ -12519,7 +12519,7 @@
         <v>367</v>
       </c>
       <c r="K181" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="L181" t="s">
         <v>406</v>
@@ -12557,7 +12557,7 @@
         <v>69</v>
       </c>
       <c r="B182" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C182" t="s">
         <v>408</v>
@@ -12578,7 +12578,7 @@
         <v>367</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="U182" t="s">
         <v>35</v>
@@ -12590,7 +12590,7 @@
         <v>352</v>
       </c>
       <c r="X182" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="183" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -12598,7 +12598,7 @@
         <v>70</v>
       </c>
       <c r="B183" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C183" t="s">
         <v>411</v>
@@ -12619,7 +12619,7 @@
         <v>367</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L183" s="1" t="s">
         <v>415</v>
@@ -12652,7 +12652,7 @@
         <v>352</v>
       </c>
       <c r="X183" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="184" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -12660,7 +12660,7 @@
         <v>71</v>
       </c>
       <c r="B184" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C184" t="s">
         <v>420</v>
@@ -12681,16 +12681,16 @@
         <v>367</v>
       </c>
       <c r="K184" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L184" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M184" t="s">
         <v>384</v>
       </c>
       <c r="N184" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P184" s="1" t="s">
         <v>78</v>
@@ -12699,10 +12699,10 @@
         <v>33</v>
       </c>
       <c r="R184" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="T184" t="s">
         <v>427</v>
-      </c>
-      <c r="T184" t="s">
-        <v>428</v>
       </c>
       <c r="U184" t="s">
         <v>86</v>
@@ -12722,37 +12722,37 @@
         <v>72</v>
       </c>
       <c r="B185" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C185" t="s">
+        <v>428</v>
+      </c>
+      <c r="D185" t="s">
         <v>429</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
+        <v>429</v>
+      </c>
+      <c r="F185" t="s">
+        <v>49</v>
+      </c>
+      <c r="I185" t="s">
         <v>430</v>
       </c>
-      <c r="E185" t="s">
-        <v>430</v>
-      </c>
-      <c r="F185" t="s">
-        <v>49</v>
-      </c>
-      <c r="I185" t="s">
+      <c r="J185" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="J185" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="K185" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L185" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M185" t="s">
         <v>384</v>
       </c>
       <c r="N185" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P185" s="1" t="s">
         <v>78</v>
@@ -12761,10 +12761,10 @@
         <v>33</v>
       </c>
       <c r="R185" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="T185" t="s">
         <v>427</v>
-      </c>
-      <c r="T185" t="s">
-        <v>428</v>
       </c>
       <c r="U185" t="s">
         <v>86</v>
@@ -12784,37 +12784,37 @@
         <v>73</v>
       </c>
       <c r="B186" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C186" t="s">
+        <v>432</v>
+      </c>
+      <c r="D186" t="s">
         <v>433</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
+        <v>433</v>
+      </c>
+      <c r="F186" t="s">
+        <v>49</v>
+      </c>
+      <c r="I186" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="E186" t="s">
-        <v>434</v>
-      </c>
-      <c r="F186" t="s">
-        <v>49</v>
-      </c>
-      <c r="I186" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="J186" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K186" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L186" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M186" t="s">
         <v>384</v>
       </c>
       <c r="N186" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P186" s="1" t="s">
         <v>78</v>
@@ -12823,7 +12823,7 @@
         <v>33</v>
       </c>
       <c r="R186" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U186" t="s">
         <v>35</v>
@@ -12843,22 +12843,22 @@
         <v>74</v>
       </c>
       <c r="B187" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C187" t="s">
+        <v>437</v>
+      </c>
+      <c r="D187" t="s">
         <v>438</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
+        <v>438</v>
+      </c>
+      <c r="F187" t="s">
+        <v>49</v>
+      </c>
+      <c r="I187" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E187" t="s">
-        <v>439</v>
-      </c>
-      <c r="F187" t="s">
-        <v>49</v>
-      </c>
-      <c r="I187" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="J187" s="1" t="s">
         <v>367</v>
@@ -12884,22 +12884,22 @@
         <v>75</v>
       </c>
       <c r="B188" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C188" t="s">
+        <v>440</v>
+      </c>
+      <c r="D188" t="s">
         <v>441</v>
       </c>
-      <c r="D188" t="s">
-        <v>442</v>
-      </c>
       <c r="E188" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F188" t="s">
         <v>49</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J188" s="1" t="s">
         <v>367</v>
@@ -12925,22 +12925,22 @@
         <v>76</v>
       </c>
       <c r="B189" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C189" t="s">
+        <v>442</v>
+      </c>
+      <c r="D189" t="s">
         <v>443</v>
       </c>
-      <c r="D189" t="s">
-        <v>444</v>
-      </c>
       <c r="E189" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F189" t="s">
         <v>49</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J189" s="1" t="s">
         <v>367</v>
@@ -12966,22 +12966,22 @@
         <v>77</v>
       </c>
       <c r="B190" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C190" t="s">
+        <v>444</v>
+      </c>
+      <c r="D190" t="s">
         <v>445</v>
       </c>
-      <c r="D190" t="s">
-        <v>446</v>
-      </c>
       <c r="E190" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F190" t="s">
         <v>49</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>367</v>
@@ -13007,22 +13007,22 @@
         <v>78</v>
       </c>
       <c r="B191" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C191" t="s">
+        <v>446</v>
+      </c>
+      <c r="D191" t="s">
         <v>447</v>
       </c>
-      <c r="D191" t="s">
-        <v>448</v>
-      </c>
       <c r="E191" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F191" t="s">
         <v>49</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J191" s="1" t="s">
         <v>367</v>
@@ -13048,22 +13048,22 @@
         <v>79</v>
       </c>
       <c r="B192" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C192" t="s">
+        <v>448</v>
+      </c>
+      <c r="D192" t="s">
         <v>449</v>
       </c>
-      <c r="D192" t="s">
-        <v>450</v>
-      </c>
       <c r="E192" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F192" t="s">
         <v>49</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J192" s="1" t="s">
         <v>367</v>
@@ -13089,22 +13089,22 @@
         <v>80</v>
       </c>
       <c r="B193" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C193" t="s">
+        <v>450</v>
+      </c>
+      <c r="D193" t="s">
         <v>451</v>
       </c>
-      <c r="D193" t="s">
-        <v>452</v>
-      </c>
       <c r="E193" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F193" t="s">
         <v>49</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J193" s="1" t="s">
         <v>367</v>
@@ -13130,22 +13130,22 @@
         <v>81</v>
       </c>
       <c r="B194" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C194" t="s">
+        <v>452</v>
+      </c>
+      <c r="D194" t="s">
         <v>453</v>
       </c>
-      <c r="D194" t="s">
-        <v>454</v>
-      </c>
       <c r="E194" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F194" t="s">
         <v>49</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J194" s="1" t="s">
         <v>367</v>
@@ -13171,22 +13171,22 @@
         <v>82</v>
       </c>
       <c r="B195" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C195" t="s">
+        <v>454</v>
+      </c>
+      <c r="D195" t="s">
         <v>455</v>
       </c>
-      <c r="D195" t="s">
-        <v>456</v>
-      </c>
       <c r="E195" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F195" t="s">
         <v>49</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>367</v>
@@ -13212,22 +13212,22 @@
         <v>83</v>
       </c>
       <c r="B196" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C196" t="s">
+        <v>456</v>
+      </c>
+      <c r="D196" t="s">
         <v>457</v>
       </c>
-      <c r="D196" t="s">
-        <v>458</v>
-      </c>
       <c r="E196" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F196" t="s">
         <v>49</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J196" s="1" t="s">
         <v>367</v>
@@ -13253,22 +13253,22 @@
         <v>84</v>
       </c>
       <c r="B197" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C197" t="s">
+        <v>458</v>
+      </c>
+      <c r="D197" t="s">
         <v>459</v>
       </c>
-      <c r="D197" t="s">
-        <v>460</v>
-      </c>
       <c r="E197" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F197" t="s">
         <v>49</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J197" s="1" t="s">
         <v>367</v>
@@ -13294,22 +13294,22 @@
         <v>85</v>
       </c>
       <c r="B198" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C198" t="s">
+        <v>460</v>
+      </c>
+      <c r="D198" t="s">
         <v>461</v>
       </c>
-      <c r="D198" t="s">
-        <v>462</v>
-      </c>
       <c r="E198" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F198" t="s">
         <v>49</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J198" s="1" t="s">
         <v>367</v>
@@ -13335,22 +13335,22 @@
         <v>86</v>
       </c>
       <c r="B199" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C199" t="s">
+        <v>462</v>
+      </c>
+      <c r="D199" t="s">
         <v>463</v>
       </c>
-      <c r="D199" t="s">
-        <v>464</v>
-      </c>
       <c r="E199" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F199" t="s">
         <v>49</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J199" s="1" t="s">
         <v>367</v>
@@ -13376,22 +13376,22 @@
         <v>87</v>
       </c>
       <c r="B200" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C200" t="s">
+        <v>464</v>
+      </c>
+      <c r="D200" t="s">
         <v>465</v>
       </c>
-      <c r="D200" t="s">
-        <v>466</v>
-      </c>
       <c r="E200" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F200" t="s">
         <v>49</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J200" s="1" t="s">
         <v>367</v>
@@ -13417,22 +13417,22 @@
         <v>88</v>
       </c>
       <c r="B201" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C201" t="s">
+        <v>466</v>
+      </c>
+      <c r="D201" t="s">
         <v>467</v>
       </c>
-      <c r="D201" t="s">
-        <v>468</v>
-      </c>
       <c r="E201" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F201" t="s">
         <v>49</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J201" s="1" t="s">
         <v>367</v>
@@ -13458,22 +13458,22 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C202" t="s">
+        <v>468</v>
+      </c>
+      <c r="D202" t="s">
         <v>469</v>
       </c>
-      <c r="D202" t="s">
-        <v>470</v>
-      </c>
       <c r="E202" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F202" t="s">
         <v>49</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J202" s="1" t="s">
         <v>367</v>
@@ -13499,22 +13499,22 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C203" t="s">
+        <v>470</v>
+      </c>
+      <c r="D203" t="s">
         <v>471</v>
       </c>
-      <c r="D203" t="s">
-        <v>472</v>
-      </c>
       <c r="E203" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F203" t="s">
         <v>49</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J203" s="1" t="s">
         <v>367</v>
@@ -13540,22 +13540,22 @@
         <v>91</v>
       </c>
       <c r="B204" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C204" t="s">
+        <v>472</v>
+      </c>
+      <c r="D204" t="s">
         <v>473</v>
       </c>
-      <c r="D204" t="s">
-        <v>474</v>
-      </c>
       <c r="E204" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F204" t="s">
         <v>49</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J204" s="1" t="s">
         <v>367</v>
@@ -13581,22 +13581,22 @@
         <v>92</v>
       </c>
       <c r="B205" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C205" t="s">
+        <v>474</v>
+      </c>
+      <c r="D205" t="s">
         <v>475</v>
       </c>
-      <c r="D205" t="s">
-        <v>476</v>
-      </c>
       <c r="E205" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F205" t="s">
         <v>49</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J205" s="1" t="s">
         <v>367</v>
@@ -13622,37 +13622,37 @@
         <v>93</v>
       </c>
       <c r="B206" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C206" t="s">
+        <v>476</v>
+      </c>
+      <c r="D206" t="s">
         <v>477</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
+        <v>477</v>
+      </c>
+      <c r="F206" t="s">
+        <v>49</v>
+      </c>
+      <c r="I206" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="E206" t="s">
-        <v>478</v>
-      </c>
-      <c r="F206" t="s">
-        <v>49</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K206" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L206" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M206" t="s">
         <v>384</v>
       </c>
       <c r="N206" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P206" s="1" t="s">
         <v>78</v>
@@ -13661,7 +13661,7 @@
         <v>33</v>
       </c>
       <c r="R206" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U206" t="s">
         <v>35</v>
@@ -13681,37 +13681,37 @@
         <v>94</v>
       </c>
       <c r="B207" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C207" t="s">
+        <v>481</v>
+      </c>
+      <c r="D207" t="s">
         <v>482</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>483</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
+        <v>49</v>
+      </c>
+      <c r="I207" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="F207" t="s">
-        <v>49</v>
-      </c>
-      <c r="I207" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K207" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L207" t="s">
+        <v>485</v>
+      </c>
+      <c r="M207" t="s">
         <v>486</v>
       </c>
-      <c r="M207" t="s">
+      <c r="N207" t="s">
         <v>487</v>
-      </c>
-      <c r="N207" t="s">
-        <v>488</v>
       </c>
       <c r="P207" s="1" t="s">
         <v>78</v>
@@ -13720,7 +13720,7 @@
         <v>33</v>
       </c>
       <c r="R207" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U207" t="s">
         <v>35</v>
@@ -13740,37 +13740,37 @@
         <v>95</v>
       </c>
       <c r="B208" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C208" t="s">
+        <v>488</v>
+      </c>
+      <c r="D208" t="s">
         <v>489</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
         <v>490</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
+        <v>49</v>
+      </c>
+      <c r="I208" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F208" t="s">
-        <v>49</v>
-      </c>
-      <c r="I208" s="1" t="s">
+      <c r="J208" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="J208" s="1" t="s">
+      <c r="K208" t="s">
+        <v>684</v>
+      </c>
+      <c r="L208" t="s">
         <v>493</v>
       </c>
-      <c r="K208" t="s">
-        <v>685</v>
-      </c>
-      <c r="L208" t="s">
+      <c r="M208" t="s">
         <v>494</v>
       </c>
-      <c r="M208" t="s">
+      <c r="N208" t="s">
         <v>495</v>
-      </c>
-      <c r="N208" t="s">
-        <v>496</v>
       </c>
       <c r="P208" s="1" t="s">
         <v>78</v>
@@ -13779,7 +13779,7 @@
         <v>33</v>
       </c>
       <c r="R208" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U208" t="s">
         <v>35</v>
@@ -13799,37 +13799,37 @@
         <v>96</v>
       </c>
       <c r="B209" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C209" t="s">
+        <v>496</v>
+      </c>
+      <c r="D209" t="s">
         <v>497</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
+        <v>497</v>
+      </c>
+      <c r="F209" t="s">
+        <v>49</v>
+      </c>
+      <c r="I209" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="E209" t="s">
-        <v>498</v>
-      </c>
-      <c r="F209" t="s">
-        <v>49</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L209" t="s">
+        <v>499</v>
+      </c>
+      <c r="M209" t="s">
         <v>500</v>
       </c>
-      <c r="M209" t="s">
+      <c r="N209" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N209" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P209" s="1" t="s">
         <v>78</v>
@@ -13838,7 +13838,7 @@
         <v>33</v>
       </c>
       <c r="R209" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U209" t="s">
         <v>35</v>
@@ -13850,7 +13850,7 @@
         <v>352</v>
       </c>
       <c r="X209" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="210" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -13858,37 +13858,37 @@
         <v>97</v>
       </c>
       <c r="B210" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C210" t="s">
+        <v>503</v>
+      </c>
+      <c r="D210" t="s">
         <v>504</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
+        <v>504</v>
+      </c>
+      <c r="F210" t="s">
+        <v>49</v>
+      </c>
+      <c r="I210" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="E210" t="s">
-        <v>505</v>
-      </c>
-      <c r="F210" t="s">
-        <v>49</v>
-      </c>
-      <c r="I210" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L210" t="s">
+        <v>499</v>
+      </c>
+      <c r="M210" t="s">
         <v>500</v>
       </c>
-      <c r="M210" t="s">
+      <c r="N210" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N210" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P210" s="1" t="s">
         <v>78</v>
@@ -13897,7 +13897,7 @@
         <v>33</v>
       </c>
       <c r="R210" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U210" t="s">
         <v>35</v>
@@ -13909,7 +13909,7 @@
         <v>352</v>
       </c>
       <c r="X210" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="211" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -13917,37 +13917,37 @@
         <v>98</v>
       </c>
       <c r="B211" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C211" t="s">
+        <v>506</v>
+      </c>
+      <c r="D211" t="s">
         <v>507</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
+        <v>507</v>
+      </c>
+      <c r="F211" t="s">
+        <v>49</v>
+      </c>
+      <c r="I211" t="s">
         <v>508</v>
-      </c>
-      <c r="E211" t="s">
-        <v>508</v>
-      </c>
-      <c r="F211" t="s">
-        <v>49</v>
-      </c>
-      <c r="I211" t="s">
-        <v>509</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L211" t="s">
+        <v>499</v>
+      </c>
+      <c r="M211" t="s">
         <v>500</v>
       </c>
-      <c r="M211" t="s">
+      <c r="N211" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N211" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P211" s="1" t="s">
         <v>78</v>
@@ -13956,7 +13956,7 @@
         <v>33</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U211" t="s">
         <v>35</v>
@@ -13968,7 +13968,7 @@
         <v>352</v>
       </c>
       <c r="X211" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.25">
@@ -13976,22 +13976,22 @@
         <v>99</v>
       </c>
       <c r="B212" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C212" t="s">
+        <v>509</v>
+      </c>
+      <c r="D212" t="s">
         <v>510</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
+        <v>510</v>
+      </c>
+      <c r="F212" t="s">
+        <v>49</v>
+      </c>
+      <c r="I212" t="s">
         <v>511</v>
-      </c>
-      <c r="E212" t="s">
-        <v>511</v>
-      </c>
-      <c r="F212" t="s">
-        <v>49</v>
-      </c>
-      <c r="I212" t="s">
-        <v>512</v>
       </c>
       <c r="K212" t="s">
         <v>41</v>
@@ -14014,22 +14014,22 @@
         <v>100</v>
       </c>
       <c r="B213" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C213" t="s">
+        <v>512</v>
+      </c>
+      <c r="D213" t="s">
         <v>513</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
+        <v>513</v>
+      </c>
+      <c r="F213" t="s">
+        <v>49</v>
+      </c>
+      <c r="I213" t="s">
         <v>514</v>
-      </c>
-      <c r="E213" t="s">
-        <v>514</v>
-      </c>
-      <c r="F213" t="s">
-        <v>49</v>
-      </c>
-      <c r="I213" t="s">
-        <v>515</v>
       </c>
       <c r="K213" t="s">
         <v>41</v>
@@ -14052,22 +14052,22 @@
         <v>101</v>
       </c>
       <c r="B214" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C214" t="s">
+        <v>515</v>
+      </c>
+      <c r="D214" t="s">
         <v>516</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
+        <v>516</v>
+      </c>
+      <c r="F214" t="s">
+        <v>49</v>
+      </c>
+      <c r="I214" t="s">
         <v>517</v>
-      </c>
-      <c r="E214" t="s">
-        <v>517</v>
-      </c>
-      <c r="F214" t="s">
-        <v>49</v>
-      </c>
-      <c r="I214" t="s">
-        <v>518</v>
       </c>
       <c r="K214" t="s">
         <v>41</v>
@@ -14090,22 +14090,22 @@
         <v>102</v>
       </c>
       <c r="B215" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C215" t="s">
+        <v>518</v>
+      </c>
+      <c r="D215" t="s">
         <v>519</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
+        <v>519</v>
+      </c>
+      <c r="F215" t="s">
+        <v>49</v>
+      </c>
+      <c r="I215" t="s">
         <v>520</v>
-      </c>
-      <c r="E215" t="s">
-        <v>520</v>
-      </c>
-      <c r="F215" t="s">
-        <v>49</v>
-      </c>
-      <c r="I215" t="s">
-        <v>521</v>
       </c>
       <c r="K215" t="s">
         <v>41</v>
@@ -14128,22 +14128,22 @@
         <v>103</v>
       </c>
       <c r="B216" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C216" t="s">
+        <v>521</v>
+      </c>
+      <c r="D216" t="s">
         <v>522</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
+        <v>522</v>
+      </c>
+      <c r="F216" t="s">
+        <v>49</v>
+      </c>
+      <c r="I216" t="s">
         <v>523</v>
-      </c>
-      <c r="E216" t="s">
-        <v>523</v>
-      </c>
-      <c r="F216" t="s">
-        <v>49</v>
-      </c>
-      <c r="I216" t="s">
-        <v>524</v>
       </c>
       <c r="K216" t="s">
         <v>41</v>
@@ -14166,34 +14166,34 @@
         <v>104</v>
       </c>
       <c r="B217" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C217" t="s">
+        <v>524</v>
+      </c>
+      <c r="D217" t="s">
         <v>525</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
+        <v>525</v>
+      </c>
+      <c r="F217" t="s">
+        <v>49</v>
+      </c>
+      <c r="I217" t="s">
+        <v>514</v>
+      </c>
+      <c r="K217" t="s">
+        <v>766</v>
+      </c>
+      <c r="L217" t="s">
         <v>526</v>
       </c>
-      <c r="E217" t="s">
-        <v>526</v>
-      </c>
-      <c r="F217" t="s">
-        <v>49</v>
-      </c>
-      <c r="I217" t="s">
-        <v>515</v>
-      </c>
-      <c r="K217" t="s">
-        <v>767</v>
-      </c>
-      <c r="L217" t="s">
+      <c r="M217" t="s">
         <v>527</v>
       </c>
-      <c r="M217" t="s">
+      <c r="N217" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="N217" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="P217" s="1" t="s">
         <v>78</v>
@@ -14202,7 +14202,7 @@
         <v>79</v>
       </c>
       <c r="R217" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U217" t="s">
         <v>35</v>
@@ -14222,22 +14222,22 @@
         <v>105</v>
       </c>
       <c r="B218" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C218" t="s">
+        <v>530</v>
+      </c>
+      <c r="D218" t="s">
         <v>531</v>
       </c>
-      <c r="D218" t="s">
-        <v>532</v>
-      </c>
       <c r="E218" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F218" t="s">
         <v>49</v>
       </c>
       <c r="I218" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K218" t="s">
         <v>41</v>
@@ -14260,25 +14260,25 @@
         <v>106</v>
       </c>
       <c r="B219" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C219" t="s">
+        <v>532</v>
+      </c>
+      <c r="D219" t="s">
         <v>533</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>534</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
+        <v>49</v>
+      </c>
+      <c r="I219" t="s">
         <v>535</v>
       </c>
-      <c r="F219" t="s">
-        <v>49</v>
-      </c>
-      <c r="I219" t="s">
+      <c r="J219" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="J219" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="K219" t="s">
         <v>41</v>
@@ -14301,25 +14301,25 @@
         <v>107</v>
       </c>
       <c r="B220" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C220" t="s">
+        <v>538</v>
+      </c>
+      <c r="D220" t="s">
         <v>539</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
         <v>540</v>
       </c>
-      <c r="E220" t="s">
+      <c r="F220" t="s">
+        <v>49</v>
+      </c>
+      <c r="I220" t="s">
+        <v>535</v>
+      </c>
+      <c r="J220" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="F220" t="s">
-        <v>49</v>
-      </c>
-      <c r="I220" t="s">
-        <v>536</v>
-      </c>
-      <c r="J220" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="K220" t="s">
         <v>41</v>
@@ -14342,25 +14342,25 @@
         <v>108</v>
       </c>
       <c r="B221" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C221" t="s">
+        <v>542</v>
+      </c>
+      <c r="D221" t="s">
         <v>543</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>544</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
+        <v>49</v>
+      </c>
+      <c r="I221" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F221" t="s">
-        <v>49</v>
-      </c>
-      <c r="I221" s="1" t="s">
+      <c r="J221" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="J221" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="K221" t="s">
         <v>41</v>
@@ -14383,37 +14383,37 @@
         <v>109</v>
       </c>
       <c r="B222" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C222" t="s">
+        <v>547</v>
+      </c>
+      <c r="D222" t="s">
         <v>548</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>549</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
+        <v>49</v>
+      </c>
+      <c r="I222" t="s">
         <v>550</v>
       </c>
-      <c r="F222" t="s">
-        <v>49</v>
-      </c>
-      <c r="I222" t="s">
+      <c r="J222" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K222" t="s">
+        <v>689</v>
+      </c>
+      <c r="L222" t="s">
         <v>551</v>
       </c>
-      <c r="J222" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K222" t="s">
-        <v>690</v>
-      </c>
-      <c r="L222" t="s">
+      <c r="M222" t="s">
         <v>552</v>
       </c>
-      <c r="M222" t="s">
+      <c r="N222" t="s">
         <v>553</v>
-      </c>
-      <c r="N222" t="s">
-        <v>554</v>
       </c>
       <c r="P222" s="1" t="s">
         <v>78</v>
@@ -14422,7 +14422,7 @@
         <v>33</v>
       </c>
       <c r="R222" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="U222" t="s">
         <v>35</v>
@@ -14434,7 +14434,7 @@
         <v>68</v>
       </c>
       <c r="X222" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="223" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -14442,37 +14442,37 @@
         <v>110</v>
       </c>
       <c r="B223" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C223" t="s">
+        <v>556</v>
+      </c>
+      <c r="D223" t="s">
         <v>557</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>558</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
+        <v>49</v>
+      </c>
+      <c r="I223" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F223" t="s">
-        <v>49</v>
-      </c>
-      <c r="I223" s="1" t="s">
+      <c r="J223" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K223" t="s">
+        <v>690</v>
+      </c>
+      <c r="L223" t="s">
         <v>560</v>
       </c>
-      <c r="J223" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K223" t="s">
-        <v>691</v>
-      </c>
-      <c r="L223" t="s">
+      <c r="M223" t="s">
         <v>561</v>
       </c>
-      <c r="M223" t="s">
+      <c r="N223" t="s">
         <v>562</v>
-      </c>
-      <c r="N223" t="s">
-        <v>563</v>
       </c>
       <c r="P223" s="1" t="s">
         <v>78</v>
@@ -14481,10 +14481,10 @@
         <v>33</v>
       </c>
       <c r="R223" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="T223" t="s">
         <v>564</v>
-      </c>
-      <c r="T223" t="s">
-        <v>565</v>
       </c>
       <c r="U223" t="s">
         <v>35</v>
@@ -14496,7 +14496,7 @@
         <v>68</v>
       </c>
       <c r="X223" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="224" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -14504,22 +14504,22 @@
         <v>111</v>
       </c>
       <c r="B224" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C224" t="s">
+        <v>566</v>
+      </c>
+      <c r="D224" t="s">
         <v>567</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>568</v>
-      </c>
-      <c r="E224" t="s">
-        <v>569</v>
       </c>
       <c r="F224" t="s">
         <v>112</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="U224" t="s">
         <v>35</v>
@@ -14531,7 +14531,7 @@
         <v>59</v>
       </c>
       <c r="X224" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="225" spans="1:24" ht="270" x14ac:dyDescent="0.25">
@@ -14539,25 +14539,25 @@
         <v>112</v>
       </c>
       <c r="B225" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C225" t="s">
+        <v>569</v>
+      </c>
+      <c r="D225" t="s">
         <v>570</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>571</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
+        <v>49</v>
+      </c>
+      <c r="G225" t="s">
         <v>572</v>
       </c>
-      <c r="F225" t="s">
-        <v>49</v>
-      </c>
-      <c r="G225" t="s">
-        <v>573</v>
-      </c>
       <c r="K225" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="U225" t="s">
         <v>35</v>
@@ -14569,7 +14569,7 @@
         <v>59</v>
       </c>
       <c r="X225" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="226" spans="1:24" x14ac:dyDescent="0.25">
@@ -14577,7 +14577,7 @@
         <v>1</v>
       </c>
       <c r="B226" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C226" t="s">
         <v>23</v>
@@ -14598,10 +14598,10 @@
         <v>28</v>
       </c>
       <c r="L226" t="s">
+        <v>574</v>
+      </c>
+      <c r="M226" t="s">
         <v>575</v>
-      </c>
-      <c r="M226" t="s">
-        <v>576</v>
       </c>
       <c r="U226" t="s">
         <v>35</v>
@@ -14621,7 +14621,7 @@
         <v>2</v>
       </c>
       <c r="B227" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C227" t="s">
         <v>38</v>
@@ -14651,7 +14651,7 @@
         <v>43</v>
       </c>
       <c r="X227" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="228" spans="1:24" x14ac:dyDescent="0.25">
@@ -14659,7 +14659,7 @@
         <v>3</v>
       </c>
       <c r="B228" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C228" t="s">
         <v>44</v>
@@ -14689,7 +14689,7 @@
         <v>43</v>
       </c>
       <c r="X228" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="229" spans="1:24" x14ac:dyDescent="0.25">
@@ -14697,7 +14697,7 @@
         <v>4</v>
       </c>
       <c r="B229" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C229" t="s">
         <v>47</v>
@@ -14735,7 +14735,7 @@
         <v>5</v>
       </c>
       <c r="B230" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C230" t="s">
         <v>51</v>
@@ -14756,7 +14756,7 @@
         <v>56</v>
       </c>
       <c r="K230" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="L230" t="s">
         <v>57</v>
@@ -14777,7 +14777,7 @@
         <v>59</v>
       </c>
       <c r="X230" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="231" spans="1:24" ht="45" x14ac:dyDescent="0.25">
@@ -14785,7 +14785,7 @@
         <v>6</v>
       </c>
       <c r="B231" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C231" t="s">
         <v>60</v>
@@ -14832,7 +14832,7 @@
         <v>7</v>
       </c>
       <c r="B232" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C232" t="s">
         <v>70</v>
@@ -14853,7 +14853,7 @@
         <v>74</v>
       </c>
       <c r="K232" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="L232" t="s">
         <v>75</v>
@@ -14891,7 +14891,7 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C233" t="s">
         <v>81</v>
@@ -14932,7 +14932,7 @@
         <v>9</v>
       </c>
       <c r="B234" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C234" t="s">
         <v>88</v>
@@ -14973,7 +14973,7 @@
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C235" t="s">
         <v>92</v>
@@ -14994,7 +14994,7 @@
         <v>96</v>
       </c>
       <c r="K235" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="L235" t="s">
         <v>97</v>
@@ -15035,7 +15035,7 @@
         <v>11</v>
       </c>
       <c r="B236" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C236" t="s">
         <v>103</v>
@@ -15056,7 +15056,7 @@
         <v>107</v>
       </c>
       <c r="K236" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="L236" t="s">
         <v>97</v>
@@ -15097,7 +15097,7 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C237" t="s">
         <v>110</v>
@@ -15135,7 +15135,7 @@
         <v>13</v>
       </c>
       <c r="B238" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C238" t="s">
         <v>114</v>
@@ -15170,7 +15170,7 @@
         <v>14</v>
       </c>
       <c r="B239" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C239" t="s">
         <v>117</v>
@@ -15191,7 +15191,7 @@
         <v>121</v>
       </c>
       <c r="K239" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="L239" t="s">
         <v>97</v>
@@ -15232,7 +15232,7 @@
         <v>15</v>
       </c>
       <c r="B240" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C240" t="s">
         <v>123</v>
@@ -15250,7 +15250,7 @@
         <v>125</v>
       </c>
       <c r="K240" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="L240" t="s">
         <v>126</v>
@@ -15288,7 +15288,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C241" t="s">
         <v>131</v>
@@ -15329,7 +15329,7 @@
         <v>17</v>
       </c>
       <c r="B242" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C242" t="s">
         <v>136</v>
@@ -15350,7 +15350,7 @@
         <v>139</v>
       </c>
       <c r="K242" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="L242" t="s">
         <v>140</v>
@@ -15391,7 +15391,7 @@
         <v>18</v>
       </c>
       <c r="B243" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C243" t="s">
         <v>144</v>
@@ -15409,7 +15409,7 @@
         <v>146</v>
       </c>
       <c r="K243" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="U243" t="s">
         <v>35</v>
@@ -15421,7 +15421,7 @@
         <v>59</v>
       </c>
       <c r="X243" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="244" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -15429,7 +15429,7 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C244" t="s">
         <v>147</v>
@@ -15450,7 +15450,7 @@
         <v>139</v>
       </c>
       <c r="K244" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="L244" t="s">
         <v>150</v>
@@ -15491,7 +15491,7 @@
         <v>20</v>
       </c>
       <c r="B245" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C245" t="s">
         <v>153</v>
@@ -15509,7 +15509,7 @@
         <v>146</v>
       </c>
       <c r="K245" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="U245" t="s">
         <v>35</v>
@@ -15521,7 +15521,7 @@
         <v>59</v>
       </c>
       <c r="X245" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="246" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -15529,7 +15529,7 @@
         <v>21</v>
       </c>
       <c r="B246" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C246" t="s">
         <v>155</v>
@@ -15550,7 +15550,7 @@
         <v>158</v>
       </c>
       <c r="K246" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L246" t="s">
         <v>159</v>
@@ -15591,7 +15591,7 @@
         <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C247" t="s">
         <v>162</v>
@@ -15612,7 +15612,7 @@
         <v>139</v>
       </c>
       <c r="K247" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L247" t="s">
         <v>164</v>
@@ -15633,7 +15633,7 @@
         <v>143</v>
       </c>
       <c r="T247" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="U247" t="s">
         <v>35</v>
@@ -15653,7 +15653,7 @@
         <v>23</v>
       </c>
       <c r="B248" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C248" t="s">
         <v>169</v>
@@ -15671,7 +15671,7 @@
         <v>146</v>
       </c>
       <c r="K248" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L248" t="s">
         <v>164</v>
@@ -15701,7 +15701,7 @@
         <v>59</v>
       </c>
       <c r="X248" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="249" spans="1:24" x14ac:dyDescent="0.25">
@@ -15709,7 +15709,7 @@
         <v>24</v>
       </c>
       <c r="B249" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C249" t="s">
         <v>171</v>
@@ -15727,7 +15727,7 @@
         <v>173</v>
       </c>
       <c r="K249" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="L249" t="s">
         <v>174</v>
@@ -15757,7 +15757,7 @@
         <v>59</v>
       </c>
       <c r="X249" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="250" spans="1:24" x14ac:dyDescent="0.25">
@@ -15765,7 +15765,7 @@
         <v>25</v>
       </c>
       <c r="B250" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C250" t="s">
         <v>178</v>
@@ -15780,7 +15780,7 @@
         <v>26</v>
       </c>
       <c r="K250" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="U250" t="s">
         <v>35</v>
@@ -15792,7 +15792,7 @@
         <v>59</v>
       </c>
       <c r="X250" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="251" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -15800,7 +15800,7 @@
         <v>26</v>
       </c>
       <c r="B251" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C251" t="s">
         <v>180</v>
@@ -15821,7 +15821,7 @@
         <v>184</v>
       </c>
       <c r="K251" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L251" t="s">
         <v>185</v>
@@ -15839,7 +15839,7 @@
         <v>183</v>
       </c>
       <c r="T251" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="U251" t="s">
         <v>35</v>
@@ -15851,7 +15851,7 @@
         <v>59</v>
       </c>
       <c r="X251" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="252" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -15859,7 +15859,7 @@
         <v>27</v>
       </c>
       <c r="B252" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C252" t="s">
         <v>188</v>
@@ -15880,7 +15880,7 @@
         <v>184</v>
       </c>
       <c r="K252" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L252" t="s">
         <v>191</v>
@@ -15898,7 +15898,7 @@
         <v>183</v>
       </c>
       <c r="T252" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="U252" t="s">
         <v>35</v>
@@ -15910,7 +15910,7 @@
         <v>59</v>
       </c>
       <c r="X252" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="253" spans="1:24" x14ac:dyDescent="0.25">
@@ -15918,7 +15918,7 @@
         <v>28</v>
       </c>
       <c r="B253" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C253" t="s">
         <v>193</v>
@@ -15959,7 +15959,7 @@
         <v>29</v>
       </c>
       <c r="B254" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C254" t="s">
         <v>196</v>
@@ -16000,7 +16000,7 @@
         <v>30</v>
       </c>
       <c r="B255" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C255" t="s">
         <v>200</v>
@@ -16038,7 +16038,7 @@
         <v>31</v>
       </c>
       <c r="B256" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C256" t="s">
         <v>203</v>
@@ -16076,7 +16076,7 @@
         <v>32</v>
       </c>
       <c r="B257" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C257" t="s">
         <v>206</v>
@@ -16114,7 +16114,7 @@
         <v>33</v>
       </c>
       <c r="B258" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C258" t="s">
         <v>209</v>
@@ -16132,7 +16132,7 @@
         <v>211</v>
       </c>
       <c r="K258" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L258" t="s">
         <v>210</v>
@@ -16161,7 +16161,7 @@
         <v>34</v>
       </c>
       <c r="B259" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C259" t="s">
         <v>214</v>
@@ -16179,7 +16179,7 @@
         <v>211</v>
       </c>
       <c r="K259" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L259" t="s">
         <v>215</v>
@@ -16208,7 +16208,7 @@
         <v>35</v>
       </c>
       <c r="B260" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C260" t="s">
         <v>218</v>
@@ -16226,7 +16226,7 @@
         <v>211</v>
       </c>
       <c r="K260" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L260" t="s">
         <v>219</v>
@@ -16255,7 +16255,7 @@
         <v>36</v>
       </c>
       <c r="B261" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C261" t="s">
         <v>222</v>
@@ -16276,7 +16276,7 @@
         <v>224</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="L261" s="1" t="s">
         <v>225</v>
@@ -16291,7 +16291,7 @@
         <v>59</v>
       </c>
       <c r="X261" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="262" spans="1:24" x14ac:dyDescent="0.25">
@@ -16299,7 +16299,7 @@
         <v>37</v>
       </c>
       <c r="B262" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C262" t="s">
         <v>226</v>
@@ -16317,7 +16317,7 @@
         <v>211</v>
       </c>
       <c r="K262" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L262" t="s">
         <v>227</v>
@@ -16346,7 +16346,7 @@
         <v>38</v>
       </c>
       <c r="B263" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C263" t="s">
         <v>230</v>
@@ -16364,7 +16364,7 @@
         <v>232</v>
       </c>
       <c r="K263" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="L263" t="s">
         <v>231</v>
@@ -16393,7 +16393,7 @@
         <v>39</v>
       </c>
       <c r="B264" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C264" t="s">
         <v>235</v>
@@ -16434,7 +16434,7 @@
         <v>40</v>
       </c>
       <c r="B265" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C265" t="s">
         <v>240</v>
@@ -16475,7 +16475,7 @@
         <v>41</v>
       </c>
       <c r="B266" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C266" t="s">
         <v>245</v>
@@ -16516,7 +16516,7 @@
         <v>42</v>
       </c>
       <c r="B267" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C267" t="s">
         <v>248</v>
@@ -16537,7 +16537,7 @@
         <v>244</v>
       </c>
       <c r="K267" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L267" t="s">
         <v>252</v>
@@ -16572,7 +16572,7 @@
         <v>43</v>
       </c>
       <c r="B268" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C268" t="s">
         <v>257</v>
@@ -16610,7 +16610,7 @@
         <v>44</v>
       </c>
       <c r="B269" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C269" t="s">
         <v>260</v>
@@ -16631,7 +16631,7 @@
         <v>263</v>
       </c>
       <c r="K269" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="L269" t="s">
         <v>264</v>
@@ -16663,7 +16663,7 @@
         <v>45</v>
       </c>
       <c r="B270" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C270" t="s">
         <v>267</v>
@@ -16701,7 +16701,7 @@
         <v>46</v>
       </c>
       <c r="B271" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C271" t="s">
         <v>270</v>
@@ -16722,7 +16722,7 @@
         <v>273</v>
       </c>
       <c r="K271" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="L271" t="s">
         <v>274</v>
@@ -16760,7 +16760,7 @@
         <v>47</v>
       </c>
       <c r="B272" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C272" t="s">
         <v>279</v>
@@ -16819,7 +16819,7 @@
         <v>48</v>
       </c>
       <c r="B273" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C273" t="s">
         <v>283</v>
@@ -16860,7 +16860,7 @@
         <v>49</v>
       </c>
       <c r="B274" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C274" t="s">
         <v>287</v>
@@ -16878,7 +16878,7 @@
         <v>113</v>
       </c>
       <c r="K274" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="L274" t="s">
         <v>289</v>
@@ -16919,7 +16919,7 @@
         <v>50</v>
       </c>
       <c r="B275" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C275" t="s">
         <v>296</v>
@@ -16940,7 +16940,7 @@
         <v>299</v>
       </c>
       <c r="K275" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="L275" t="s">
         <v>289</v>
@@ -16978,7 +16978,7 @@
         <v>51</v>
       </c>
       <c r="B276" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C276" t="s">
         <v>301</v>
@@ -16999,7 +16999,7 @@
         <v>304</v>
       </c>
       <c r="K276" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="L276" t="s">
         <v>305</v>
@@ -17037,7 +17037,7 @@
         <v>52</v>
       </c>
       <c r="B277" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C277" t="s">
         <v>310</v>
@@ -17078,7 +17078,7 @@
         <v>53</v>
       </c>
       <c r="B278" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C278" t="s">
         <v>314</v>
@@ -17096,7 +17096,7 @@
         <v>313</v>
       </c>
       <c r="K278" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="L278" t="s">
         <v>316</v>
@@ -17117,7 +17117,7 @@
         <v>320</v>
       </c>
       <c r="T278" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="U278" t="s">
         <v>35</v>
@@ -17137,7 +17137,7 @@
         <v>54</v>
       </c>
       <c r="B279" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C279" t="s">
         <v>323</v>
@@ -17175,7 +17175,7 @@
         <v>55</v>
       </c>
       <c r="B280" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C280" t="s">
         <v>325</v>
@@ -17193,7 +17193,7 @@
         <v>328</v>
       </c>
       <c r="K280" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="L280" t="s">
         <v>329</v>
@@ -17214,7 +17214,7 @@
         <v>320</v>
       </c>
       <c r="T280" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="U280" t="s">
         <v>35</v>
@@ -17226,7 +17226,7 @@
         <v>59</v>
       </c>
       <c r="X280" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="281" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -17234,7 +17234,7 @@
         <v>56</v>
       </c>
       <c r="B281" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C281" t="s">
         <v>333</v>
@@ -17275,7 +17275,7 @@
         <v>57</v>
       </c>
       <c r="B282" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C282" t="s">
         <v>337</v>
@@ -17316,7 +17316,7 @@
         <v>58</v>
       </c>
       <c r="B283" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C283" t="s">
         <v>340</v>
@@ -17337,7 +17337,7 @@
         <v>312</v>
       </c>
       <c r="K283" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="L283" s="1" t="s">
         <v>343</v>
@@ -17367,7 +17367,7 @@
         <v>59</v>
       </c>
       <c r="X283" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="284" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -17375,7 +17375,7 @@
         <v>59</v>
       </c>
       <c r="B284" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C284" t="s">
         <v>347</v>
@@ -17393,7 +17393,7 @@
         <v>350</v>
       </c>
       <c r="K284" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="L284" s="1" t="s">
         <v>343</v>
@@ -17423,7 +17423,7 @@
         <v>352</v>
       </c>
       <c r="X284" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="285" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -17431,7 +17431,7 @@
         <v>60</v>
       </c>
       <c r="B285" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C285" t="s">
         <v>353</v>
@@ -17452,7 +17452,7 @@
         <v>356</v>
       </c>
       <c r="K285" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L285" t="s">
         <v>358</v>
@@ -17493,7 +17493,7 @@
         <v>61</v>
       </c>
       <c r="B286" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C286" t="s">
         <v>363</v>
@@ -17514,7 +17514,7 @@
         <v>367</v>
       </c>
       <c r="K286" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="L286" t="s">
         <v>368</v>
@@ -17547,7 +17547,7 @@
         <v>352</v>
       </c>
       <c r="X286" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="287" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -17555,7 +17555,7 @@
         <v>62</v>
       </c>
       <c r="B287" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C287" t="s">
         <v>374</v>
@@ -17576,7 +17576,7 @@
         <v>367</v>
       </c>
       <c r="K287" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L287" t="s">
         <v>377</v>
@@ -17617,7 +17617,7 @@
         <v>63</v>
       </c>
       <c r="B288" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C288" t="s">
         <v>381</v>
@@ -17638,7 +17638,7 @@
         <v>367</v>
       </c>
       <c r="K288" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L288" t="s">
         <v>377</v>
@@ -17676,7 +17676,7 @@
         <v>64</v>
       </c>
       <c r="B289" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C289" t="s">
         <v>386</v>
@@ -17697,7 +17697,7 @@
         <v>367</v>
       </c>
       <c r="K289" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="L289" t="s">
         <v>389</v>
@@ -17735,7 +17735,7 @@
         <v>65</v>
       </c>
       <c r="B290" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C290" t="s">
         <v>391</v>
@@ -17756,7 +17756,7 @@
         <v>367</v>
       </c>
       <c r="K290" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L290" t="s">
         <v>394</v>
@@ -17794,7 +17794,7 @@
         <v>66</v>
       </c>
       <c r="B291" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C291" t="s">
         <v>396</v>
@@ -17815,7 +17815,7 @@
         <v>367</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="L291" t="s">
         <v>368</v>
@@ -17853,7 +17853,7 @@
         <v>67</v>
       </c>
       <c r="B292" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C292" t="s">
         <v>400</v>
@@ -17894,7 +17894,7 @@
         <v>68</v>
       </c>
       <c r="B293" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C293" t="s">
         <v>403</v>
@@ -17915,7 +17915,7 @@
         <v>367</v>
       </c>
       <c r="K293" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="L293" t="s">
         <v>406</v>
@@ -17953,7 +17953,7 @@
         <v>69</v>
       </c>
       <c r="B294" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C294" t="s">
         <v>408</v>
@@ -17974,7 +17974,7 @@
         <v>367</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="U294" t="s">
         <v>35</v>
@@ -17986,7 +17986,7 @@
         <v>352</v>
       </c>
       <c r="X294" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="295" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -17994,7 +17994,7 @@
         <v>70</v>
       </c>
       <c r="B295" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C295" t="s">
         <v>411</v>
@@ -18015,7 +18015,7 @@
         <v>367</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L295" s="1" t="s">
         <v>415</v>
@@ -18048,7 +18048,7 @@
         <v>352</v>
       </c>
       <c r="X295" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="296" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -18056,7 +18056,7 @@
         <v>71</v>
       </c>
       <c r="B296" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C296" t="s">
         <v>420</v>
@@ -18077,16 +18077,16 @@
         <v>367</v>
       </c>
       <c r="K296" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L296" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M296" t="s">
         <v>384</v>
       </c>
       <c r="N296" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P296" s="1" t="s">
         <v>78</v>
@@ -18095,10 +18095,10 @@
         <v>33</v>
       </c>
       <c r="R296" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="T296" t="s">
         <v>427</v>
-      </c>
-      <c r="T296" t="s">
-        <v>428</v>
       </c>
       <c r="U296" t="s">
         <v>86</v>
@@ -18118,37 +18118,37 @@
         <v>72</v>
       </c>
       <c r="B297" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C297" t="s">
+        <v>428</v>
+      </c>
+      <c r="D297" t="s">
         <v>429</v>
       </c>
-      <c r="D297" t="s">
+      <c r="E297" t="s">
+        <v>429</v>
+      </c>
+      <c r="F297" t="s">
+        <v>49</v>
+      </c>
+      <c r="I297" t="s">
         <v>430</v>
       </c>
-      <c r="E297" t="s">
-        <v>430</v>
-      </c>
-      <c r="F297" t="s">
-        <v>49</v>
-      </c>
-      <c r="I297" t="s">
+      <c r="J297" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="J297" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="K297" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L297" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M297" t="s">
         <v>384</v>
       </c>
       <c r="N297" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P297" s="1" t="s">
         <v>78</v>
@@ -18157,10 +18157,10 @@
         <v>33</v>
       </c>
       <c r="R297" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="T297" t="s">
         <v>427</v>
-      </c>
-      <c r="T297" t="s">
-        <v>428</v>
       </c>
       <c r="U297" t="s">
         <v>86</v>
@@ -18180,37 +18180,37 @@
         <v>73</v>
       </c>
       <c r="B298" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C298" t="s">
+        <v>432</v>
+      </c>
+      <c r="D298" t="s">
         <v>433</v>
       </c>
-      <c r="D298" t="s">
+      <c r="E298" t="s">
+        <v>433</v>
+      </c>
+      <c r="F298" t="s">
+        <v>49</v>
+      </c>
+      <c r="I298" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="E298" t="s">
-        <v>434</v>
-      </c>
-      <c r="F298" t="s">
-        <v>49</v>
-      </c>
-      <c r="I298" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K298" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L298" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M298" t="s">
         <v>384</v>
       </c>
       <c r="N298" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P298" s="1" t="s">
         <v>78</v>
@@ -18219,7 +18219,7 @@
         <v>33</v>
       </c>
       <c r="R298" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U298" t="s">
         <v>35</v>
@@ -18239,22 +18239,22 @@
         <v>74</v>
       </c>
       <c r="B299" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C299" t="s">
+        <v>437</v>
+      </c>
+      <c r="D299" t="s">
         <v>438</v>
       </c>
-      <c r="D299" t="s">
+      <c r="E299" t="s">
+        <v>438</v>
+      </c>
+      <c r="F299" t="s">
+        <v>49</v>
+      </c>
+      <c r="I299" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E299" t="s">
-        <v>439</v>
-      </c>
-      <c r="F299" t="s">
-        <v>49</v>
-      </c>
-      <c r="I299" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>367</v>
@@ -18280,22 +18280,22 @@
         <v>75</v>
       </c>
       <c r="B300" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C300" t="s">
+        <v>440</v>
+      </c>
+      <c r="D300" t="s">
         <v>441</v>
       </c>
-      <c r="D300" t="s">
-        <v>442</v>
-      </c>
       <c r="E300" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F300" t="s">
         <v>49</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>367</v>
@@ -18321,22 +18321,22 @@
         <v>76</v>
       </c>
       <c r="B301" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C301" t="s">
+        <v>442</v>
+      </c>
+      <c r="D301" t="s">
         <v>443</v>
       </c>
-      <c r="D301" t="s">
-        <v>444</v>
-      </c>
       <c r="E301" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F301" t="s">
         <v>49</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>367</v>
@@ -18362,22 +18362,22 @@
         <v>77</v>
       </c>
       <c r="B302" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C302" t="s">
+        <v>444</v>
+      </c>
+      <c r="D302" t="s">
         <v>445</v>
       </c>
-      <c r="D302" t="s">
-        <v>446</v>
-      </c>
       <c r="E302" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F302" t="s">
         <v>49</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J302" s="1" t="s">
         <v>367</v>
@@ -18403,22 +18403,22 @@
         <v>78</v>
       </c>
       <c r="B303" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C303" t="s">
+        <v>446</v>
+      </c>
+      <c r="D303" t="s">
         <v>447</v>
       </c>
-      <c r="D303" t="s">
-        <v>448</v>
-      </c>
       <c r="E303" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F303" t="s">
         <v>49</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>367</v>
@@ -18444,22 +18444,22 @@
         <v>79</v>
       </c>
       <c r="B304" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C304" t="s">
+        <v>448</v>
+      </c>
+      <c r="D304" t="s">
         <v>449</v>
       </c>
-      <c r="D304" t="s">
-        <v>450</v>
-      </c>
       <c r="E304" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F304" t="s">
         <v>49</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J304" s="1" t="s">
         <v>367</v>
@@ -18485,22 +18485,22 @@
         <v>80</v>
       </c>
       <c r="B305" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C305" t="s">
+        <v>450</v>
+      </c>
+      <c r="D305" t="s">
         <v>451</v>
       </c>
-      <c r="D305" t="s">
-        <v>452</v>
-      </c>
       <c r="E305" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F305" t="s">
         <v>49</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>367</v>
@@ -18526,22 +18526,22 @@
         <v>81</v>
       </c>
       <c r="B306" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C306" t="s">
+        <v>452</v>
+      </c>
+      <c r="D306" t="s">
         <v>453</v>
       </c>
-      <c r="D306" t="s">
-        <v>454</v>
-      </c>
       <c r="E306" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F306" t="s">
         <v>49</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>367</v>
@@ -18567,22 +18567,22 @@
         <v>82</v>
       </c>
       <c r="B307" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C307" t="s">
+        <v>454</v>
+      </c>
+      <c r="D307" t="s">
         <v>455</v>
       </c>
-      <c r="D307" t="s">
-        <v>456</v>
-      </c>
       <c r="E307" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F307" t="s">
         <v>49</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>367</v>
@@ -18608,22 +18608,22 @@
         <v>83</v>
       </c>
       <c r="B308" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C308" t="s">
+        <v>456</v>
+      </c>
+      <c r="D308" t="s">
         <v>457</v>
       </c>
-      <c r="D308" t="s">
-        <v>458</v>
-      </c>
       <c r="E308" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F308" t="s">
         <v>49</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>367</v>
@@ -18649,22 +18649,22 @@
         <v>84</v>
       </c>
       <c r="B309" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C309" t="s">
+        <v>458</v>
+      </c>
+      <c r="D309" t="s">
         <v>459</v>
       </c>
-      <c r="D309" t="s">
-        <v>460</v>
-      </c>
       <c r="E309" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F309" t="s">
         <v>49</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>367</v>
@@ -18690,22 +18690,22 @@
         <v>85</v>
       </c>
       <c r="B310" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C310" t="s">
+        <v>460</v>
+      </c>
+      <c r="D310" t="s">
         <v>461</v>
       </c>
-      <c r="D310" t="s">
-        <v>462</v>
-      </c>
       <c r="E310" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F310" t="s">
         <v>49</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>367</v>
@@ -18731,22 +18731,22 @@
         <v>86</v>
       </c>
       <c r="B311" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C311" t="s">
+        <v>462</v>
+      </c>
+      <c r="D311" t="s">
         <v>463</v>
       </c>
-      <c r="D311" t="s">
-        <v>464</v>
-      </c>
       <c r="E311" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F311" t="s">
         <v>49</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>367</v>
@@ -18772,22 +18772,22 @@
         <v>87</v>
       </c>
       <c r="B312" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C312" t="s">
+        <v>464</v>
+      </c>
+      <c r="D312" t="s">
         <v>465</v>
       </c>
-      <c r="D312" t="s">
-        <v>466</v>
-      </c>
       <c r="E312" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F312" t="s">
         <v>49</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>367</v>
@@ -18813,22 +18813,22 @@
         <v>88</v>
       </c>
       <c r="B313" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C313" t="s">
+        <v>466</v>
+      </c>
+      <c r="D313" t="s">
         <v>467</v>
       </c>
-      <c r="D313" t="s">
-        <v>468</v>
-      </c>
       <c r="E313" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F313" t="s">
         <v>49</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>367</v>
@@ -18854,22 +18854,22 @@
         <v>89</v>
       </c>
       <c r="B314" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C314" t="s">
+        <v>468</v>
+      </c>
+      <c r="D314" t="s">
         <v>469</v>
       </c>
-      <c r="D314" t="s">
-        <v>470</v>
-      </c>
       <c r="E314" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F314" t="s">
         <v>49</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>367</v>
@@ -18895,22 +18895,22 @@
         <v>90</v>
       </c>
       <c r="B315" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C315" t="s">
+        <v>470</v>
+      </c>
+      <c r="D315" t="s">
         <v>471</v>
       </c>
-      <c r="D315" t="s">
-        <v>472</v>
-      </c>
       <c r="E315" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F315" t="s">
         <v>49</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>367</v>
@@ -18936,22 +18936,22 @@
         <v>91</v>
       </c>
       <c r="B316" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C316" t="s">
+        <v>472</v>
+      </c>
+      <c r="D316" t="s">
         <v>473</v>
       </c>
-      <c r="D316" t="s">
-        <v>474</v>
-      </c>
       <c r="E316" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F316" t="s">
         <v>49</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>367</v>
@@ -18977,22 +18977,22 @@
         <v>92</v>
       </c>
       <c r="B317" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C317" t="s">
+        <v>474</v>
+      </c>
+      <c r="D317" t="s">
         <v>475</v>
       </c>
-      <c r="D317" t="s">
-        <v>476</v>
-      </c>
       <c r="E317" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F317" t="s">
         <v>49</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J317" s="1" t="s">
         <v>367</v>
@@ -19018,37 +19018,37 @@
         <v>93</v>
       </c>
       <c r="B318" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C318" t="s">
+        <v>476</v>
+      </c>
+      <c r="D318" t="s">
         <v>477</v>
       </c>
-      <c r="D318" t="s">
+      <c r="E318" t="s">
+        <v>477</v>
+      </c>
+      <c r="F318" t="s">
+        <v>49</v>
+      </c>
+      <c r="I318" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="E318" t="s">
-        <v>478</v>
-      </c>
-      <c r="F318" t="s">
-        <v>49</v>
-      </c>
-      <c r="I318" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K318" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L318" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M318" t="s">
         <v>384</v>
       </c>
       <c r="N318" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P318" s="1" t="s">
         <v>78</v>
@@ -19057,7 +19057,7 @@
         <v>33</v>
       </c>
       <c r="R318" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U318" t="s">
         <v>35</v>
@@ -19077,37 +19077,37 @@
         <v>94</v>
       </c>
       <c r="B319" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C319" t="s">
+        <v>481</v>
+      </c>
+      <c r="D319" t="s">
         <v>482</v>
       </c>
-      <c r="D319" t="s">
+      <c r="E319" t="s">
         <v>483</v>
       </c>
-      <c r="E319" t="s">
+      <c r="F319" t="s">
+        <v>49</v>
+      </c>
+      <c r="I319" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="F319" t="s">
-        <v>49</v>
-      </c>
-      <c r="I319" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="J319" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K319" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L319" t="s">
+        <v>485</v>
+      </c>
+      <c r="M319" t="s">
         <v>486</v>
       </c>
-      <c r="M319" t="s">
+      <c r="N319" t="s">
         <v>487</v>
-      </c>
-      <c r="N319" t="s">
-        <v>488</v>
       </c>
       <c r="P319" s="1" t="s">
         <v>78</v>
@@ -19116,7 +19116,7 @@
         <v>33</v>
       </c>
       <c r="R319" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U319" t="s">
         <v>35</v>
@@ -19136,37 +19136,37 @@
         <v>95</v>
       </c>
       <c r="B320" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C320" t="s">
+        <v>488</v>
+      </c>
+      <c r="D320" t="s">
         <v>489</v>
       </c>
-      <c r="D320" t="s">
+      <c r="E320" t="s">
         <v>490</v>
       </c>
-      <c r="E320" t="s">
+      <c r="F320" t="s">
+        <v>49</v>
+      </c>
+      <c r="I320" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F320" t="s">
-        <v>49</v>
-      </c>
-      <c r="I320" s="1" t="s">
+      <c r="J320" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="J320" s="1" t="s">
+      <c r="K320" t="s">
+        <v>738</v>
+      </c>
+      <c r="L320" t="s">
         <v>493</v>
       </c>
-      <c r="K320" t="s">
-        <v>739</v>
-      </c>
-      <c r="L320" t="s">
+      <c r="M320" t="s">
         <v>494</v>
       </c>
-      <c r="M320" t="s">
+      <c r="N320" t="s">
         <v>495</v>
-      </c>
-      <c r="N320" t="s">
-        <v>496</v>
       </c>
       <c r="P320" s="1" t="s">
         <v>78</v>
@@ -19175,7 +19175,7 @@
         <v>33</v>
       </c>
       <c r="R320" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U320" t="s">
         <v>35</v>
@@ -19195,37 +19195,37 @@
         <v>96</v>
       </c>
       <c r="B321" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C321" t="s">
+        <v>496</v>
+      </c>
+      <c r="D321" t="s">
         <v>497</v>
       </c>
-      <c r="D321" t="s">
+      <c r="E321" t="s">
+        <v>497</v>
+      </c>
+      <c r="F321" t="s">
+        <v>49</v>
+      </c>
+      <c r="I321" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="E321" t="s">
-        <v>498</v>
-      </c>
-      <c r="F321" t="s">
-        <v>49</v>
-      </c>
-      <c r="I321" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="J321" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L321" t="s">
+        <v>499</v>
+      </c>
+      <c r="M321" t="s">
         <v>500</v>
       </c>
-      <c r="M321" t="s">
+      <c r="N321" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N321" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P321" s="1" t="s">
         <v>78</v>
@@ -19234,7 +19234,7 @@
         <v>33</v>
       </c>
       <c r="R321" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U321" t="s">
         <v>35</v>
@@ -19246,7 +19246,7 @@
         <v>352</v>
       </c>
       <c r="X321" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="322" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19254,37 +19254,37 @@
         <v>97</v>
       </c>
       <c r="B322" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C322" t="s">
+        <v>503</v>
+      </c>
+      <c r="D322" t="s">
         <v>504</v>
       </c>
-      <c r="D322" t="s">
+      <c r="E322" t="s">
+        <v>504</v>
+      </c>
+      <c r="F322" t="s">
+        <v>49</v>
+      </c>
+      <c r="I322" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="E322" t="s">
-        <v>505</v>
-      </c>
-      <c r="F322" t="s">
-        <v>49</v>
-      </c>
-      <c r="I322" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K322" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L322" t="s">
+        <v>499</v>
+      </c>
+      <c r="M322" t="s">
         <v>500</v>
       </c>
-      <c r="M322" t="s">
+      <c r="N322" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N322" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P322" s="1" t="s">
         <v>78</v>
@@ -19293,7 +19293,7 @@
         <v>33</v>
       </c>
       <c r="R322" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U322" t="s">
         <v>35</v>
@@ -19305,7 +19305,7 @@
         <v>352</v>
       </c>
       <c r="X322" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="323" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19313,37 +19313,37 @@
         <v>98</v>
       </c>
       <c r="B323" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C323" t="s">
+        <v>506</v>
+      </c>
+      <c r="D323" t="s">
         <v>507</v>
       </c>
-      <c r="D323" t="s">
+      <c r="E323" t="s">
+        <v>507</v>
+      </c>
+      <c r="F323" t="s">
+        <v>49</v>
+      </c>
+      <c r="I323" t="s">
         <v>508</v>
-      </c>
-      <c r="E323" t="s">
-        <v>508</v>
-      </c>
-      <c r="F323" t="s">
-        <v>49</v>
-      </c>
-      <c r="I323" t="s">
-        <v>509</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>367</v>
       </c>
       <c r="K323" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L323" t="s">
+        <v>499</v>
+      </c>
+      <c r="M323" t="s">
         <v>500</v>
       </c>
-      <c r="M323" t="s">
+      <c r="N323" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N323" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="P323" s="1" t="s">
         <v>78</v>
@@ -19352,7 +19352,7 @@
         <v>33</v>
       </c>
       <c r="R323" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="U323" t="s">
         <v>35</v>
@@ -19364,7 +19364,7 @@
         <v>352</v>
       </c>
       <c r="X323" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="324" spans="1:24" x14ac:dyDescent="0.25">
@@ -19372,22 +19372,22 @@
         <v>99</v>
       </c>
       <c r="B324" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C324" t="s">
+        <v>509</v>
+      </c>
+      <c r="D324" t="s">
         <v>510</v>
       </c>
-      <c r="D324" t="s">
+      <c r="E324" t="s">
+        <v>510</v>
+      </c>
+      <c r="F324" t="s">
+        <v>49</v>
+      </c>
+      <c r="I324" t="s">
         <v>511</v>
-      </c>
-      <c r="E324" t="s">
-        <v>511</v>
-      </c>
-      <c r="F324" t="s">
-        <v>49</v>
-      </c>
-      <c r="I324" t="s">
-        <v>512</v>
       </c>
       <c r="K324" t="s">
         <v>41</v>
@@ -19410,22 +19410,22 @@
         <v>100</v>
       </c>
       <c r="B325" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C325" t="s">
+        <v>512</v>
+      </c>
+      <c r="D325" t="s">
         <v>513</v>
       </c>
-      <c r="D325" t="s">
+      <c r="E325" t="s">
+        <v>513</v>
+      </c>
+      <c r="F325" t="s">
+        <v>49</v>
+      </c>
+      <c r="I325" t="s">
         <v>514</v>
-      </c>
-      <c r="E325" t="s">
-        <v>514</v>
-      </c>
-      <c r="F325" t="s">
-        <v>49</v>
-      </c>
-      <c r="I325" t="s">
-        <v>515</v>
       </c>
       <c r="K325" t="s">
         <v>41</v>
@@ -19448,22 +19448,22 @@
         <v>101</v>
       </c>
       <c r="B326" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C326" t="s">
+        <v>515</v>
+      </c>
+      <c r="D326" t="s">
         <v>516</v>
       </c>
-      <c r="D326" t="s">
+      <c r="E326" t="s">
+        <v>516</v>
+      </c>
+      <c r="F326" t="s">
+        <v>49</v>
+      </c>
+      <c r="I326" t="s">
         <v>517</v>
-      </c>
-      <c r="E326" t="s">
-        <v>517</v>
-      </c>
-      <c r="F326" t="s">
-        <v>49</v>
-      </c>
-      <c r="I326" t="s">
-        <v>518</v>
       </c>
       <c r="K326" t="s">
         <v>41</v>
@@ -19486,22 +19486,22 @@
         <v>102</v>
       </c>
       <c r="B327" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C327" t="s">
+        <v>518</v>
+      </c>
+      <c r="D327" t="s">
         <v>519</v>
       </c>
-      <c r="D327" t="s">
+      <c r="E327" t="s">
+        <v>519</v>
+      </c>
+      <c r="F327" t="s">
+        <v>49</v>
+      </c>
+      <c r="I327" t="s">
         <v>520</v>
-      </c>
-      <c r="E327" t="s">
-        <v>520</v>
-      </c>
-      <c r="F327" t="s">
-        <v>49</v>
-      </c>
-      <c r="I327" t="s">
-        <v>521</v>
       </c>
       <c r="K327" t="s">
         <v>41</v>
@@ -19524,22 +19524,22 @@
         <v>103</v>
       </c>
       <c r="B328" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C328" t="s">
+        <v>521</v>
+      </c>
+      <c r="D328" t="s">
         <v>522</v>
       </c>
-      <c r="D328" t="s">
+      <c r="E328" t="s">
+        <v>522</v>
+      </c>
+      <c r="F328" t="s">
+        <v>49</v>
+      </c>
+      <c r="I328" t="s">
         <v>523</v>
-      </c>
-      <c r="E328" t="s">
-        <v>523</v>
-      </c>
-      <c r="F328" t="s">
-        <v>49</v>
-      </c>
-      <c r="I328" t="s">
-        <v>524</v>
       </c>
       <c r="K328" t="s">
         <v>41</v>
@@ -19562,34 +19562,34 @@
         <v>104</v>
       </c>
       <c r="B329" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C329" t="s">
+        <v>524</v>
+      </c>
+      <c r="D329" t="s">
         <v>525</v>
       </c>
-      <c r="D329" t="s">
+      <c r="E329" t="s">
+        <v>525</v>
+      </c>
+      <c r="F329" t="s">
+        <v>49</v>
+      </c>
+      <c r="I329" t="s">
+        <v>514</v>
+      </c>
+      <c r="K329" t="s">
+        <v>767</v>
+      </c>
+      <c r="L329" t="s">
         <v>526</v>
       </c>
-      <c r="E329" t="s">
-        <v>526</v>
-      </c>
-      <c r="F329" t="s">
-        <v>49</v>
-      </c>
-      <c r="I329" t="s">
-        <v>515</v>
-      </c>
-      <c r="K329" t="s">
-        <v>768</v>
-      </c>
-      <c r="L329" t="s">
+      <c r="M329" t="s">
         <v>527</v>
       </c>
-      <c r="M329" t="s">
+      <c r="N329" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="N329" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="P329" s="1" t="s">
         <v>78</v>
@@ -19598,7 +19598,7 @@
         <v>79</v>
       </c>
       <c r="R329" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U329" t="s">
         <v>35</v>
@@ -19618,22 +19618,22 @@
         <v>105</v>
       </c>
       <c r="B330" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C330" t="s">
+        <v>530</v>
+      </c>
+      <c r="D330" t="s">
         <v>531</v>
       </c>
-      <c r="D330" t="s">
-        <v>532</v>
-      </c>
       <c r="E330" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F330" t="s">
         <v>49</v>
       </c>
       <c r="I330" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K330" t="s">
         <v>41</v>
@@ -19656,25 +19656,25 @@
         <v>106</v>
       </c>
       <c r="B331" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C331" t="s">
+        <v>532</v>
+      </c>
+      <c r="D331" t="s">
         <v>533</v>
       </c>
-      <c r="D331" t="s">
+      <c r="E331" t="s">
         <v>534</v>
       </c>
-      <c r="E331" t="s">
+      <c r="F331" t="s">
+        <v>49</v>
+      </c>
+      <c r="I331" t="s">
         <v>535</v>
       </c>
-      <c r="F331" t="s">
-        <v>49</v>
-      </c>
-      <c r="I331" t="s">
+      <c r="J331" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="J331" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="K331" t="s">
         <v>41</v>
@@ -19697,25 +19697,25 @@
         <v>107</v>
       </c>
       <c r="B332" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C332" t="s">
+        <v>538</v>
+      </c>
+      <c r="D332" t="s">
         <v>539</v>
       </c>
-      <c r="D332" t="s">
+      <c r="E332" t="s">
         <v>540</v>
       </c>
-      <c r="E332" t="s">
+      <c r="F332" t="s">
+        <v>49</v>
+      </c>
+      <c r="I332" t="s">
+        <v>535</v>
+      </c>
+      <c r="J332" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="F332" t="s">
-        <v>49</v>
-      </c>
-      <c r="I332" t="s">
-        <v>536</v>
-      </c>
-      <c r="J332" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="K332" t="s">
         <v>41</v>
@@ -19738,25 +19738,25 @@
         <v>108</v>
       </c>
       <c r="B333" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C333" t="s">
+        <v>542</v>
+      </c>
+      <c r="D333" t="s">
         <v>543</v>
       </c>
-      <c r="D333" t="s">
+      <c r="E333" t="s">
         <v>544</v>
       </c>
-      <c r="E333" t="s">
+      <c r="F333" t="s">
+        <v>49</v>
+      </c>
+      <c r="I333" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F333" t="s">
-        <v>49</v>
-      </c>
-      <c r="I333" s="1" t="s">
+      <c r="J333" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="J333" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="K333" t="s">
         <v>41</v>
@@ -19779,37 +19779,37 @@
         <v>109</v>
       </c>
       <c r="B334" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C334" t="s">
+        <v>547</v>
+      </c>
+      <c r="D334" t="s">
         <v>548</v>
       </c>
-      <c r="D334" t="s">
+      <c r="E334" t="s">
         <v>549</v>
       </c>
-      <c r="E334" t="s">
+      <c r="F334" t="s">
+        <v>49</v>
+      </c>
+      <c r="I334" t="s">
         <v>550</v>
       </c>
-      <c r="F334" t="s">
-        <v>49</v>
-      </c>
-      <c r="I334" t="s">
+      <c r="J334" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K334" t="s">
+        <v>743</v>
+      </c>
+      <c r="L334" t="s">
         <v>551</v>
       </c>
-      <c r="J334" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K334" t="s">
-        <v>744</v>
-      </c>
-      <c r="L334" t="s">
+      <c r="M334" t="s">
         <v>552</v>
       </c>
-      <c r="M334" t="s">
+      <c r="N334" t="s">
         <v>553</v>
-      </c>
-      <c r="N334" t="s">
-        <v>554</v>
       </c>
       <c r="P334" s="1" t="s">
         <v>78</v>
@@ -19818,7 +19818,7 @@
         <v>33</v>
       </c>
       <c r="R334" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="U334" t="s">
         <v>35</v>
@@ -19830,7 +19830,7 @@
         <v>68</v>
       </c>
       <c r="X334" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="335" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19838,37 +19838,37 @@
         <v>110</v>
       </c>
       <c r="B335" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C335" t="s">
+        <v>556</v>
+      </c>
+      <c r="D335" t="s">
         <v>557</v>
       </c>
-      <c r="D335" t="s">
+      <c r="E335" t="s">
         <v>558</v>
       </c>
-      <c r="E335" t="s">
+      <c r="F335" t="s">
+        <v>49</v>
+      </c>
+      <c r="I335" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F335" t="s">
-        <v>49</v>
-      </c>
-      <c r="I335" s="1" t="s">
+      <c r="J335" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K335" t="s">
+        <v>744</v>
+      </c>
+      <c r="L335" t="s">
         <v>560</v>
       </c>
-      <c r="J335" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K335" t="s">
-        <v>745</v>
-      </c>
-      <c r="L335" t="s">
+      <c r="M335" t="s">
         <v>561</v>
       </c>
-      <c r="M335" t="s">
+      <c r="N335" t="s">
         <v>562</v>
-      </c>
-      <c r="N335" t="s">
-        <v>563</v>
       </c>
       <c r="P335" s="1" t="s">
         <v>78</v>
@@ -19877,10 +19877,10 @@
         <v>33</v>
       </c>
       <c r="R335" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="T335" t="s">
         <v>564</v>
-      </c>
-      <c r="T335" t="s">
-        <v>565</v>
       </c>
       <c r="U335" t="s">
         <v>35</v>
@@ -19892,7 +19892,7 @@
         <v>68</v>
       </c>
       <c r="X335" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="336" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -19900,22 +19900,22 @@
         <v>111</v>
       </c>
       <c r="B336" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C336" t="s">
+        <v>566</v>
+      </c>
+      <c r="D336" t="s">
         <v>567</v>
       </c>
-      <c r="D336" t="s">
+      <c r="E336" t="s">
         <v>568</v>
-      </c>
-      <c r="E336" t="s">
-        <v>569</v>
       </c>
       <c r="F336" t="s">
         <v>112</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="U336" t="s">
         <v>35</v>
@@ -19927,7 +19927,7 @@
         <v>59</v>
       </c>
       <c r="X336" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="337" spans="1:24" ht="270" x14ac:dyDescent="0.25">
@@ -19935,25 +19935,25 @@
         <v>112</v>
       </c>
       <c r="B337" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C337" t="s">
+        <v>569</v>
+      </c>
+      <c r="D337" t="s">
         <v>570</v>
       </c>
-      <c r="D337" t="s">
+      <c r="E337" t="s">
         <v>571</v>
       </c>
-      <c r="E337" t="s">
+      <c r="F337" t="s">
+        <v>49</v>
+      </c>
+      <c r="G337" t="s">
         <v>572</v>
       </c>
-      <c r="F337" t="s">
-        <v>49</v>
-      </c>
-      <c r="G337" t="s">
-        <v>573</v>
-      </c>
       <c r="K337" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="U337" t="s">
         <v>35</v>
@@ -19965,7 +19965,7 @@
         <v>59</v>
       </c>
       <c r="X337" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
   </sheetData>

--- a/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-FRA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7885343-4EF6-4B01-A3BC-F0B6A6687140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF84B2A-DEBB-40DB-93D2-D92994D6D59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95E6C139-84C6-42BA-8CBB-FF1D79072BFF}"/>
   </bookViews>
@@ -2398,23 +2398,6 @@
 na.rm = TRUE))</t>
   </si>
   <si>
-    <t>rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w2)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w2)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift_w2)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w2)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w2)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending_w2)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w2)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w2)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w2)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath_w2))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) %&gt;%
-mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
-  </si>
-  <si>
     <t>ifelse(rowSums(mutate(.,
 temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
 temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
@@ -2445,23 +2428,6 @@
 na.rm = TRUE))</t>
   </si>
   <si>
-    <t>rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift_w3)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w3)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w3)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending_w3)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w3)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w3)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w3)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath_w3))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) %&gt;%
-mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
-  </si>
-  <si>
     <t>ifelse(rowSums(mutate(.,
 temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w4)), 
 temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w4)),
@@ -2492,7 +2458,1024 @@
 na.rm = TRUE))</t>
   </si>
   <si>
-    <t>rowSums(mutate(.,
+    <t>bmi_w3</t>
+  </si>
+  <si>
+    <t>round(rowMeans(select(., systolicBP_right_w3, systolicBP_left_w3), na.rm=TRUE), 2)</t>
+  </si>
+  <si>
+    <t>mci_w3</t>
+  </si>
+  <si>
+    <t>mci_w4</t>
+  </si>
+  <si>
+    <t>bmi_w4</t>
+  </si>
+  <si>
+    <t>ifelse(!is.na(waist_mean_w4), 2, NA)</t>
+  </si>
+  <si>
+    <t>round(rowMeans(select(., systolicBP_right_w4, systolicBP_left_w4), na.rm=TRUE), 2)</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w2;
+dis_moderate_w2;
+dis_lift_w2;
+dis_climbseveral_w2;
+dis_climbone_w2;
+dis_bending_w2;
+dis_walk2km_w2;
+dis_walk1km_w2;
+dis_walk100m_w2;
+dis_bath_w2</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w3;
+dis_moderate_w3;
+dis_lift_w3;
+dis_climbseveral_w3;
+dis_climbone_w3;
+dis_bending_w3;
+dis_walk2km_w3;
+dis_walk1km_w3;
+dis_walk100m_w3;
+dis_bath_w3</t>
+  </si>
+  <si>
+    <t>dis_vigorous_w4;
+dis_moderate_w4;
+dis_lift_w4;
+dis_climbseveral_w4;
+dis_climbone_w4;
+dis_bending_w4;
+dis_walk2km_w4;
+dis_walk1km_w4;
+dis_walk100m_w4;
+dis_bath_w4</t>
+  </si>
+  <si>
+    <t>diabetes_w2</t>
+  </si>
+  <si>
+    <t>Participant identifier</t>
+  </si>
+  <si>
+    <t>Unique participant identifier</t>
+  </si>
+  <si>
+    <t>Must be unique within the study.</t>
+  </si>
+  <si>
+    <t>Acronym of the study</t>
+  </si>
+  <si>
+    <t>Take the study identifier from the study acronym, e.g., LISS or CLSA.</t>
+  </si>
+  <si>
+    <t>Identifier of the study population</t>
+  </si>
+  <si>
+    <t>If there is only one population, use the same value as adm_study_id. If there is more than one population, use adm_study_id (the study acronym) followed by "_" and a word or number that describes the population. For example, LISS has two populations with different baseline years, which are identified as LISS_2012 and LISS_2019. CLSA has two populations with different data collection protocols, which are identified as CLSA_Tracking and CLSA_Comprehensive.</t>
+  </si>
+  <si>
+    <t>Identifier of the data collection wave</t>
+  </si>
+  <si>
+    <t>Baseline should be "1", Follow-up 1 " 2", etc.</t>
+  </si>
+  <si>
+    <t>Questionnaire completion date</t>
+  </si>
+  <si>
+    <t>If only month and year are available, set day as 15.</t>
+  </si>
+  <si>
+    <t>Record when day was set to 15 because only month and year were available.</t>
+  </si>
+  <si>
+    <t>1 = Female ; 
+2 = Male</t>
+  </si>
+  <si>
+    <t>Age of the participant</t>
+  </si>
+  <si>
+    <t>If only month and year are available to calculate age, set day as 15.</t>
+  </si>
+  <si>
+    <t>Record when day was set to 15 because only month and year were used to calculate age.</t>
+  </si>
+  <si>
+    <t>Highest level of education completed by the participant</t>
+  </si>
+  <si>
+    <t>Refer to the ISCED 2011 levels associated with each category.</t>
+  </si>
+  <si>
+    <t>Record any coding assumptions, for example when years of education were used to determine the ISCED level.</t>
+  </si>
+  <si>
+    <t>0 = Lower secondary or less (ISCED 2011 levels 0-2); 
+1 = Upper secondary (ISCED 2011 levels 3); 
+2 = Post-secondary non-tertiary education or short-cycle tertiary education (ISCED 2011 levels 4, 5); 
+3 = Bachelor's, master's, doctorate, or equivalent (ISCED 2011 levels 6, 7, 8)</t>
+  </si>
+  <si>
+    <t>0 = No ; 
+1 = Yes</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant is currently in paid employement or unemployed</t>
+  </si>
+  <si>
+    <t>Code homemaker/housewife/househusband as unemployed. Code rentier as employed. Code students, apprentices, retired, and voluntary workers as NA.
+Validate the meaning of "Family worker" with the study to determine the appropriate coding.</t>
+  </si>
+  <si>
+    <t>0 = Unemployed ; 
+1 = Employed</t>
+  </si>
+  <si>
+    <t>Use the study's definition of full-time and part-time work.</t>
+  </si>
+  <si>
+    <t>Record the study's definition and threshold for full-time and part-time work, where available.</t>
+  </si>
+  <si>
+    <t>1 = Part-time ; 
+2 = Full-time</t>
+  </si>
+  <si>
+    <t>Current average number of hours worked per week</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant is currently retired</t>
+  </si>
+  <si>
+    <t>If there is no separate variable for retired/not, code anyone currently in paid employment as not retired and anyone not in paid employment or unknown (e.g., homemaker, students, voluntary workers) as NA. Code combined retired/pensioner as retired.</t>
+  </si>
+  <si>
+    <t>0 = Not retired ; 
+1 = Retired</t>
+  </si>
+  <si>
+    <t>Best descriptor of the participant's current marital status</t>
+  </si>
+  <si>
+    <t>1 = Never married ; 
+2 = Married/In a partnership/Living together ; 
+3 = Divorced/Separated ; 
+4 = Widowed</t>
+  </si>
+  <si>
+    <t>Living in urban or rural location</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant is currently living in an urban or rural area</t>
+  </si>
+  <si>
+    <t>Code 1 = urban, 2 = rural following the study's own urban/rural classification.</t>
+  </si>
+  <si>
+    <t>Record the study's definition of urban vs rural.</t>
+  </si>
+  <si>
+    <t>1 = Rural ; 
+2 = Urban</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Use physical measurements over self-reported values.</t>
+  </si>
+  <si>
+    <t>Record whether multiple input measurements were used, the number of measurements, and whether the harmonized value is an average.</t>
+  </si>
+  <si>
+    <t>Method used to measure height</t>
+  </si>
+  <si>
+    <t>1 = Self-reported ; 
+2 = Measured by professional</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Method used to measure weight</t>
+  </si>
+  <si>
+    <t>Body mass index (BMI)</t>
+  </si>
+  <si>
+    <t>Participant's body mass index (BMI)</t>
+  </si>
+  <si>
+    <t>Participant's waist circumference</t>
+  </si>
+  <si>
+    <t>Method used to measure waist circumference</t>
+  </si>
+  <si>
+    <t>Participant's body fat percentage</t>
+  </si>
+  <si>
+    <t>Method or equipment used to measure body fat percentage</t>
+  </si>
+  <si>
+    <t>Systolic blood pressure (average of all available measures)</t>
+  </si>
+  <si>
+    <t>Use the average of all available measurements from the same collection event.</t>
+  </si>
+  <si>
+    <t>Record the number of measurements and relevant method details, including device, cuff size, position, and rest period.</t>
+  </si>
+  <si>
+    <t>Diastolic blood pressure (average of all available measures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resting heart rate (average of all available measures) </t>
+  </si>
+  <si>
+    <t>Record the number of measurements and relevant method details, including device, position, and rest period.</t>
+  </si>
+  <si>
+    <t>Cardiorespiratory fitness</t>
+  </si>
+  <si>
+    <t>Cardiorespiratory fitness as VO2max in ml/min/kg, from a maximal or submaximal exercise test (e.g., treadmill or cycle ergometer).</t>
+  </si>
+  <si>
+    <t>Record the specific exercise test and protocol.</t>
+  </si>
+  <si>
+    <t>Blood sampling fasting duration</t>
+  </si>
+  <si>
+    <t>Description of the fasting duration used for blood sampling</t>
+  </si>
+  <si>
+    <t>0 = Non-fasted ; 
+1 = Short-fast (&lt;=4h) ; 
+2 = Long fast (&gt;4h)</t>
+  </si>
+  <si>
+    <t>Red blood cell (RBC) count</t>
+  </si>
+  <si>
+    <t>Glycated hemoglobin (HbA1c)</t>
+  </si>
+  <si>
+    <t>High-density lipoprotein (HDL) cholesterol</t>
+  </si>
+  <si>
+    <t>Low-density lipoprotein (LDL) cholesterol</t>
+  </si>
+  <si>
+    <t>Calculated low-density lipoprotein (LDL) cholesterol</t>
+  </si>
+  <si>
+    <t>If there is no study-specific LDL cholesterol variable, calculate with the Friedewald equation (mmol/L): LDL = total cholesterol - HDL - (triglycerides / 2.2). Use a divisor of 5 for mg/dL. Leave missing when triglycerides exceed 4.5 mmol/L (400 mg/dL).</t>
+  </si>
+  <si>
+    <t>C-reactive protein (CRP)</t>
+  </si>
+  <si>
+    <t>Fruit intake: quantity per day</t>
+  </si>
+  <si>
+    <t>If conversion from servings or cups to grams is needed, obtain the conversion factor from the study.</t>
+  </si>
+  <si>
+    <t>Record the conversion factor used and the study-specific definition of fruit, including whether dried fruit is included and whether nuts are collected separately.</t>
+  </si>
+  <si>
+    <t>Fruit intake: frequency per week</t>
+  </si>
+  <si>
+    <t>Record the study-specific definition of fruit, including whether dried fruit is included and whether nuts are collected separately.</t>
+  </si>
+  <si>
+    <t>1 = Rarely ; 
+2 = Several times a week ; 
+3 = Every day</t>
+  </si>
+  <si>
+    <t>Vegetable intake: quantity per day</t>
+  </si>
+  <si>
+    <t>If conversion from servings or cups to grams is needed, obtain the conversion factor from the study. Legumes should not be considered vegetables.</t>
+  </si>
+  <si>
+    <t>Record the conversion factor used and the study-specific definition of vegetables.</t>
+  </si>
+  <si>
+    <t>Vegetable intake: frequency per week</t>
+  </si>
+  <si>
+    <t>Legumes should not be considered as vegetables.</t>
+  </si>
+  <si>
+    <t>Record the study-specific definition of vegetables.</t>
+  </si>
+  <si>
+    <t>Current alcohol consumption quantity</t>
+  </si>
+  <si>
+    <t>Code non-drinkers as 0.</t>
+  </si>
+  <si>
+    <t>Record study-specific data-collection methods and question wording, including the types of alcohol included.</t>
+  </si>
+  <si>
+    <t>Current alcohol consumption frequency</t>
+  </si>
+  <si>
+    <t>0 = Never/Almost never ; 
+1 = Monthly ; 
+2 = Weekly ; 
+3 = Daily/Almost daily</t>
+  </si>
+  <si>
+    <t>Code occasional smokers as Currently smoke.</t>
+  </si>
+  <si>
+    <t>Record study-specific data-collection methods and question wording.</t>
+  </si>
+  <si>
+    <t>0 = Never smoked ; 
+1 = Previously smoked ; 
+2 = Currently smoke</t>
+  </si>
+  <si>
+    <t>1 = Occasionally ; 
+2 = Daily/Almost daily</t>
+  </si>
+  <si>
+    <t>Number of cigarettes smoked per week</t>
+  </si>
+  <si>
+    <t>Code non-smokers as 0.</t>
+  </si>
+  <si>
+    <t>If the input variable is continuous, use the following category cut-offs:
+ &gt;= 0 &amp;  &lt; 6.25 ~ 1L;
+ &gt;= 6.25 &amp; &lt; 6.75 ~ 2L;
+ &gt;= 6.75 &amp; &lt; 7.25 ~ 3L;
+ &gt;= 7.25 &amp; &lt; 7.75 ~ 4L;
+ &gt;= 7.75 &amp; &lt; 8.25 ~ 5L;
+ &gt;= 8.25 &amp; &lt; 8.75 ~ 6L;
+ &gt;= 8.75 &amp; &lt; 9.25 ~ 7L;
+ &gt;= 9.25 &amp; &lt; 9.75 ~ 8L;
+ &gt;= 9.75 &amp; &lt;= 12 ~ 9L.</t>
+  </si>
+  <si>
+    <t>1 = 0 to 6 hours ; 
+2 = 6.5 hours ; 
+3 = 7 hours ; 
+4 = 7.5 hours ; 
+5 = 8 hours ; 
+6 = 8.5 hours ; 
+7 = 9 hours ; 
+8 = 9.5 hours ; 
+9 = 10 hours or more</t>
+  </si>
+  <si>
+    <t>Difficulties sleeping</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant has difficulties sleeping</t>
+  </si>
+  <si>
+    <t>Record how input variables are coded, if relevant.</t>
+  </si>
+  <si>
+    <t>0 = Never/Rarely ; 
+1 = Some difficulties</t>
+  </si>
+  <si>
+    <t>1 = Less than 1 hour per day ; 
+2 = 1 to 3 hours per day ; 
+3 = More than 3 hours per day</t>
+  </si>
+  <si>
+    <t>Daily TV viewing during weekdays</t>
+  </si>
+  <si>
+    <t>Daily TV viewing during weekends</t>
+  </si>
+  <si>
+    <t>Time spent using a computer</t>
+  </si>
+  <si>
+    <t>Time spent using a computer per day on weekdays, excluding computer use at work</t>
+  </si>
+  <si>
+    <t>1 = 0 to less than 1 hour per day ; 
+2 = 1 to less than 2 hours per day ; 
+3 = 2 to less than 3 hours per day ; 
+4 = 3 to less than 4 hours per day ; 
+5 = 4 to less than 5 hours per day ; 
+6 = 5 to less than 6 hours per day ; 
+7 = 6 to less than 7 hours per day ; 
+8 = 7 to less than 8 hours per day ; 
+9 = 8 to less than 9 hours per day ; 
+10 = 9 to less than 10 hours per day ; 
+11 = 10 hours or more per day</t>
+  </si>
+  <si>
+    <t>Time spent playing video games</t>
+  </si>
+  <si>
+    <t>Time spent reading</t>
+  </si>
+  <si>
+    <t>Total time spent sitting per day - continuous</t>
+  </si>
+  <si>
+    <t>Total time spent sitting per day - categorical</t>
+  </si>
+  <si>
+    <t>0 = Not at all ; 
+1 = Less than 1 hour per day ; 
+2 = 1 to less than 3 hours per day ; 
+3 = 3 to less than 5 hours per day ; 
+4 = 5 to less than 7 hours per day ; 
+5 = 7 hours or more per day</t>
+  </si>
+  <si>
+    <t>Frequency of walking for leisure</t>
+  </si>
+  <si>
+    <t>Frequency per week of walking for leisure (recreation or exercise, not transport), in bouts of at least 10 minutes</t>
+  </si>
+  <si>
+    <t>Record differences in information source, wording, and/or collection method between the study-specific variable and the DataSchema variable.</t>
+  </si>
+  <si>
+    <t>1 = Less than once a week ; 
+2 = 1 to 5 times a week ; 
+3 = 6 times or more times a week</t>
+  </si>
+  <si>
+    <t>1 = Mostly sedentary with no physical demands ; 
+2 = Mostly standing or walking ; 
+3 = Standing and walking with lifting or carrying ; 
+4 = Strenuous physical work</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant currently participates in sport activity</t>
+  </si>
+  <si>
+    <t>Include any sport or structured physical activity of moderate or higher intensity, organized or recreational. If the study asks about sports in a select-all-that-apply list, 0 can only be coded if there is an option for "Other" sports. Otherwise only 1 and NA can be coded.</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant currently engages in active commuting for transport (walking, biking or other active modes).</t>
+  </si>
+  <si>
+    <t>Only considered as active commuting when engaged in for at least 15 minutes.</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant currently engages in physical activity during leisure time (including sport)</t>
+  </si>
+  <si>
+    <t>Include any physical activity where the intensity was moderate or higher.</t>
+  </si>
+  <si>
+    <t>36-Item Short Form Health Survey (SF-36) physical function subscale score</t>
+  </si>
+  <si>
+    <t>Total score from the physical function subscale of the Short Form-36 (SF-36)</t>
+  </si>
+  <si>
+    <t>Score on the SF-36 physical function subscale (0-100, higher = better function). Set to NA if fewer than 5 of the 10 items are completed.</t>
+  </si>
+  <si>
+    <t>Number of Short-Form-36 (SF-36) physical function subscale non-missing items</t>
+  </si>
+  <si>
+    <t>Number of non-missing items in the Short Form-36 (SF-36) physical function subscale</t>
+  </si>
+  <si>
+    <t>Record any assumptions or transformations applied when input categories do not directly match the DataSchema categories.</t>
+  </si>
+  <si>
+    <t>1 = Poor/Very Poor ; 
+2 = Moderate/Fair ; 
+3 = Good ; 
+4 = Very good/Excellent</t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever</t>
+  </si>
+  <si>
+    <t>Ever had any cardiovascular disease (ischemic heart disease, stroke, hypertension, heart failure, atrial fibrillation, thrombosis, cerebrovascular disease, or angina pectoris)</t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.
+If the study did not collect a variable for "any cardiovascular disease" and only collected individual cardiovascular diseases (ischemic heart disease, stroke, hypertension, heart failure, atrial fibrillation, thrombosis, cerebrovascular disease, angina pectoris), Yes values can be assigned if any individual cardiovascular diseases are Yes. If the study also collected a variable for "Other cardiovascular disease", Yes/No values can be assigned. If the study did not collect "Other cardiovascular disease", the harmonized values can only be Yes or NA.</t>
+  </si>
+  <si>
+    <t>If the study did not collect a variable about "ever had any cardiovascular disease", record the decisions used to derive the DataSchema variable from individual cardiovascular diseases, including whether an Other cardiovascular disease option was available.</t>
+  </si>
+  <si>
+    <t>0 = No ; 
+1 = Yes ; 
+2 = Presumed no</t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Ischemic heart disease (coronary heart disease)</t>
+  </si>
+  <si>
+    <t>Ever had ischemic heart disease (coronary heart disease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptable wording is "Ischemic heart", "Coronary heart disease", "MI", "Myocardial infarction", or "Heart attack". </t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any of the following cardiovascular diseases? Yes/No) or there is a response option for "None of the above" for a list including this disease, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Myocardial infarction (MI)</t>
+  </si>
+  <si>
+    <t>Ever had myocardial infarction (MI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptable wording is "MI", "Myocardial infarction", or "Heart attack". </t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Angina pectoris</t>
+  </si>
+  <si>
+    <t>Ever had angina pectoris</t>
+  </si>
+  <si>
+    <t>Acceptable wording is "Angina" or "Angina pectoris".</t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Stroke</t>
+  </si>
+  <si>
+    <t>Ever had stroke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptable wording is "Stroke", "cerebrovascular accident", "CVA", "apoplexy", "seizure", "cerebral infarction", or "cerebral hemorrhage".  </t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Heart failure</t>
+  </si>
+  <si>
+    <t>Ever had heart failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptable wording is "heart failure" or "congestive heart failure". </t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Atrial fibrillation</t>
+  </si>
+  <si>
+    <t>Ever had atrial fibrillation</t>
+  </si>
+  <si>
+    <t>Acceptable wording is "atrial fibrillation".</t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Hypertension or high blood pressure diagnosis</t>
+  </si>
+  <si>
+    <t>Ever had hypertension or high blood pressure diagnosis</t>
+  </si>
+  <si>
+    <t>Acceptable wording is "high blood pressure" or "hypertension".</t>
+  </si>
+  <si>
+    <t>Code Yes if there is a diagnosis of hypertension or high blood pressure. Base it on diagnosis only, not medication use. Self-reported diagnosis is acceptable.
+If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any of the following cardiovascular diseases? Yes/No) or there is a response option for "None of the above" for a list including this disease, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>Record cases where it is unclear whether the reported condition was diagnosed.</t>
+  </si>
+  <si>
+    <t>Cardiovascular disease ever - Hypertension or high blood pressure diagnosis or take medication</t>
+  </si>
+  <si>
+    <t>Ever had hypertension or high blood pressure diagnosis or take medication</t>
+  </si>
+  <si>
+    <t>Harmonize based on either diagnosed condition or medication use for hypertension or high blood pressure. 
+If Yes to either diagnosed condition or taking medication, code as Yes.
+If No to both diagnosed condition and taking medication, code as No.
+If No to only one of diagnosed condition or taking medication, codes as Presumed no.
+If the study-specific variables were collected as part of select-all-that-apply sections without a response option for No, code as "Presumed no" if neither diagnosed condition nor taking medication were selected but at least one other item in the sections was selected.</t>
+  </si>
+  <si>
+    <t>Musculoskeletal disease ever</t>
+  </si>
+  <si>
+    <t>Ever had musculoskeletal disease</t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any of the following diseases? Yes/No) or there is a response option for "None of the above" for a list including this disease, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>Diabetes ever</t>
+  </si>
+  <si>
+    <t>Ever had diabetes</t>
+  </si>
+  <si>
+    <t>Includes gestational diabetes and other types of diabetes, but excludes impaired fasting glucose and impaired glucose tolerance.</t>
+  </si>
+  <si>
+    <t>Record study-specific wording used to collect diabetes information, such as type-specific collection or exclusion of gestational diabetes.</t>
+  </si>
+  <si>
+    <t>Record study-specific wording used to collect diabetes type information, such as whether only Type 2 diabetes was collected.</t>
+  </si>
+  <si>
+    <t>1 = Type 1 ; 
+2 = Type 2 ; 
+3 = Other</t>
+  </si>
+  <si>
+    <t>Ever had cancer</t>
+  </si>
+  <si>
+    <t>Code Yes if the participant has ever had any cancer; code No if explicitly none.
+If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>If the study did not collect a variable about "ever had any cancer", record the decisions used to derive the DataSchema variable from individual cancers, including whether an "Other cancer" option was available.</t>
+  </si>
+  <si>
+    <t>Ever had bladder cancer</t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any cancer? Yes/No) or there is a response option for "None of the above" for a list including this cancer, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>Ever had breast cancer</t>
+  </si>
+  <si>
+    <t>Ever had cervical cancer</t>
+  </si>
+  <si>
+    <t>Cancer ever - Colorectal</t>
+  </si>
+  <si>
+    <t>Ever had colorectal cancer</t>
+  </si>
+  <si>
+    <t>Ever had kidney cancer</t>
+  </si>
+  <si>
+    <t>Cancer ever - Throat (Larynx or Pharynx)</t>
+  </si>
+  <si>
+    <t>Ever had throat cancer (pharyngeal or laryngeal cancer)</t>
+  </si>
+  <si>
+    <t>Ever had leukaemia</t>
+  </si>
+  <si>
+    <t>Ever had lung cancer</t>
+  </si>
+  <si>
+    <t>Ever had lymphoma</t>
+  </si>
+  <si>
+    <t>Ever had prostate cancer</t>
+  </si>
+  <si>
+    <t>Ever had skin cancer</t>
+  </si>
+  <si>
+    <t>Ever had stomach cancer</t>
+  </si>
+  <si>
+    <t>Ever had testicular cancer</t>
+  </si>
+  <si>
+    <t>Ever had uterine cancer</t>
+  </si>
+  <si>
+    <t>Ever had brain cancer</t>
+  </si>
+  <si>
+    <t>Ever had liver cancer</t>
+  </si>
+  <si>
+    <t>Ever had ovarian cancer</t>
+  </si>
+  <si>
+    <t>Ever had pancreatic cancer</t>
+  </si>
+  <si>
+    <t>Ever had thyroid cancer</t>
+  </si>
+  <si>
+    <t>Hypercholesterolemia ever</t>
+  </si>
+  <si>
+    <t>Ever had hypercholesterolemia</t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had have any of the following conditions? Yes/No) or there is a response option for "None of the above" for a list including this condition, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant currently has depression</t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Do you have any of the following conditions? Yes/No) or there is a response option for "None of the above" for a list including this condition, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>Alzheimer's/dementia</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant has Alzheimer's or other dementia</t>
+  </si>
+  <si>
+    <t>Current use of lipid-lowering medication</t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Do you currently take any medication? Yes/No) or there is a response option for "None of the above" for a list including this medication, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
+If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Do you currently take any medication? If yes, specify...) or there is a response option for "None of the above" for a list including this medication, the harmonized values can be Yes/No. 
+If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
+  </si>
+  <si>
+    <t>Center for Epidemiologic Studies Depression Scale (CES-D) 20-item score</t>
+  </si>
+  <si>
+    <t>Where possible, validate the calculation of the score. Allowed range is 0-60.</t>
+  </si>
+  <si>
+    <t>Center for Epidemiologic Studies Depression Scale (CES-D) 10-item score</t>
+  </si>
+  <si>
+    <t>Where possible, validate the calculation of the score. Allowed range is 0-30.</t>
+  </si>
+  <si>
+    <t>Malaise Inventory 9-item score</t>
+  </si>
+  <si>
+    <t>Where possible, validate the calculation of the score. Allowed range is 0-9.</t>
+  </si>
+  <si>
+    <t>Kessler Psychological Distress Scale (K-10) score</t>
+  </si>
+  <si>
+    <t>Where possible, validate the calculation of the score. Allowed range is 10-50.</t>
+  </si>
+  <si>
+    <t>Patient Health Questionnaire-9 (PHQ-9) score</t>
+  </si>
+  <si>
+    <t>Where possible, validate the calculation of the score. Allowed range is 0-27.</t>
+  </si>
+  <si>
+    <t>Mini-Mental State Examination (MMSE) score</t>
+  </si>
+  <si>
+    <t>Montreal Cognitive Assessment (MoCA) score</t>
+  </si>
+  <si>
+    <t>adm_participant_id</t>
+  </si>
+  <si>
+    <t>sdc_education_highest</t>
+  </si>
+  <si>
+    <t>sdc_education_secondary</t>
+  </si>
+  <si>
+    <t>phy_height</t>
+  </si>
+  <si>
+    <t>phy_height_method</t>
+  </si>
+  <si>
+    <t>phy_weight</t>
+  </si>
+  <si>
+    <t>phy_weight_method</t>
+  </si>
+  <si>
+    <t>phy_bmi</t>
+  </si>
+  <si>
+    <t>phy_waist_circ</t>
+  </si>
+  <si>
+    <t>phy_waist_circ_method</t>
+  </si>
+  <si>
+    <t>phy_bodyfat_perc</t>
+  </si>
+  <si>
+    <t>phy_bodyfat_perc_method</t>
+  </si>
+  <si>
+    <t>phy_systolic_bp</t>
+  </si>
+  <si>
+    <t>phy_diastolic_bp</t>
+  </si>
+  <si>
+    <t>phy_resting_heart_rate</t>
+  </si>
+  <si>
+    <t>phy_cardiorespiratory_fitness</t>
+  </si>
+  <si>
+    <t>lab_rbc</t>
+  </si>
+  <si>
+    <t>lab_hba1c</t>
+  </si>
+  <si>
+    <t>lab_chol_total</t>
+  </si>
+  <si>
+    <t>lab_tg</t>
+  </si>
+  <si>
+    <t>lab_crp</t>
+  </si>
+  <si>
+    <t>lsb_nut_energy_total</t>
+  </si>
+  <si>
+    <t>lsb_sed_beh_tv_week</t>
+  </si>
+  <si>
+    <t>lsb_sed_beh_tv_weekday</t>
+  </si>
+  <si>
+    <t>lsb_sed_beh_tv_weekend</t>
+  </si>
+  <si>
+    <t>lsb_sed_beh_computer_use</t>
+  </si>
+  <si>
+    <t>lsb_sed_beh_total_sitting</t>
+  </si>
+  <si>
+    <t>lsb_sed_beh_total_sitting_cat</t>
+  </si>
+  <si>
+    <t>lsb_pa_walking</t>
+  </si>
+  <si>
+    <t>lsb_pa_occupational</t>
+  </si>
+  <si>
+    <t>lsb_pa_sport_participation</t>
+  </si>
+  <si>
+    <t>lsb_pa_active_commuting</t>
+  </si>
+  <si>
+    <t>lsb_pa_leisure_time</t>
+  </si>
+  <si>
+    <t>phe_sf36_phys_function</t>
+  </si>
+  <si>
+    <t>phe_sf36_n_items</t>
+  </si>
+  <si>
+    <t>dis_cvd_hf_ever</t>
+  </si>
+  <si>
+    <t>dis_cvd_af_ever</t>
+  </si>
+  <si>
+    <t>dis_diabetes_ever</t>
+  </si>
+  <si>
+    <t>dis_hypercholesterolemia_ever</t>
+  </si>
+  <si>
+    <t>med_lipid_lowering_curr</t>
+  </si>
+  <si>
+    <t>med_blood_pressure_curr</t>
+  </si>
+  <si>
+    <t>med_diabetes_curr</t>
+  </si>
+  <si>
+    <t>cog_dep_cesd20</t>
+  </si>
+  <si>
+    <t>cog_dep_cesd10</t>
+  </si>
+  <si>
+    <t>cog_dep_malaise</t>
+  </si>
+  <si>
+    <t>cog_dep_kessler</t>
+  </si>
+  <si>
+    <t>cog_dep_phq9</t>
+  </si>
+  <si>
+    <t>cog_mci_mmse</t>
+  </si>
+  <si>
+    <t>cog_mci_moca</t>
+  </si>
+  <si>
+    <t>wording</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>ifelse(rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w2)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w2)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w2)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w2)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w2)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w2)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w2)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w2)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w2)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w2))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE) ==0,NA,
+rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w2)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w2)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w2)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w2)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w2)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w2)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w2)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w2)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w2)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w2))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE))</t>
+  </si>
+  <si>
+    <t>ifelse( rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w3)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w3)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w3)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w3)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w3)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w3)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w3)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w3))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE) == 0,NA,
+rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w3)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w3)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w3)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w3)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w3)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w3)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w3)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w3)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w3)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w3))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE))</t>
+  </si>
+  <si>
+    <t>ifelse(rowSums(mutate(.,
 temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w4)), 
 temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w4)),
 temp_dis_lift1 = as.numeric(!is.na(dis_lift_w4)),
@@ -2505,965 +3488,21 @@
 temp_dis_bath1 = as.numeric(!is.na(dis_bath_w4))) %&gt;%
 select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
 temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) %&gt;%
-mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
-  </si>
-  <si>
-    <t>bmi_w3</t>
-  </si>
-  <si>
-    <t>round(rowMeans(select(., systolicBP_right_w3, systolicBP_left_w3), na.rm=TRUE), 2)</t>
-  </si>
-  <si>
-    <t>mci_w3</t>
-  </si>
-  <si>
-    <t>mci_w4</t>
-  </si>
-  <si>
-    <t>bmi_w4</t>
-  </si>
-  <si>
-    <t>ifelse(!is.na(waist_mean_w4), 2, NA)</t>
-  </si>
-  <si>
-    <t>round(rowMeans(select(., systolicBP_right_w4, systolicBP_left_w4), na.rm=TRUE), 2)</t>
-  </si>
-  <si>
-    <t>dis_vigorous_w2;
-dis_moderate_w2;
-dis_lift_w2;
-dis_climbseveral_w2;
-dis_climbone_w2;
-dis_bending_w2;
-dis_walk2km_w2;
-dis_walk1km_w2;
-dis_walk100m_w2;
-dis_bath_w2</t>
-  </si>
-  <si>
-    <t>dis_vigorous_w3;
-dis_moderate_w3;
-dis_lift_w3;
-dis_climbseveral_w3;
-dis_climbone_w3;
-dis_bending_w3;
-dis_walk2km_w3;
-dis_walk1km_w3;
-dis_walk100m_w3;
-dis_bath_w3</t>
-  </si>
-  <si>
-    <t>dis_vigorous_w4;
-dis_moderate_w4;
-dis_lift_w4;
-dis_climbseveral_w4;
-dis_climbone_w4;
-dis_bending_w4;
-dis_walk2km_w4;
-dis_walk1km_w4;
-dis_walk100m_w4;
-dis_bath_w4</t>
-  </si>
-  <si>
-    <t>diabetes_w2</t>
-  </si>
-  <si>
-    <t>Participant identifier</t>
-  </si>
-  <si>
-    <t>Unique participant identifier</t>
-  </si>
-  <si>
-    <t>Must be unique within the study.</t>
-  </si>
-  <si>
-    <t>Acronym of the study</t>
-  </si>
-  <si>
-    <t>Take the study identifier from the study acronym, e.g., LISS or CLSA.</t>
-  </si>
-  <si>
-    <t>Identifier of the study population</t>
-  </si>
-  <si>
-    <t>If there is only one population, use the same value as adm_study_id. If there is more than one population, use adm_study_id (the study acronym) followed by "_" and a word or number that describes the population. For example, LISS has two populations with different baseline years, which are identified as LISS_2012 and LISS_2019. CLSA has two populations with different data collection protocols, which are identified as CLSA_Tracking and CLSA_Comprehensive.</t>
-  </si>
-  <si>
-    <t>Identifier of the data collection wave</t>
-  </si>
-  <si>
-    <t>Baseline should be "1", Follow-up 1 " 2", etc.</t>
-  </si>
-  <si>
-    <t>Questionnaire completion date</t>
-  </si>
-  <si>
-    <t>If only month and year are available, set day as 15.</t>
-  </si>
-  <si>
-    <t>Record when day was set to 15 because only month and year were available.</t>
-  </si>
-  <si>
-    <t>1 = Female ; 
-2 = Male</t>
-  </si>
-  <si>
-    <t>Age of the participant</t>
-  </si>
-  <si>
-    <t>If only month and year are available to calculate age, set day as 15.</t>
-  </si>
-  <si>
-    <t>Record when day was set to 15 because only month and year were used to calculate age.</t>
-  </si>
-  <si>
-    <t>Highest level of education completed by the participant</t>
-  </si>
-  <si>
-    <t>Refer to the ISCED 2011 levels associated with each category.</t>
-  </si>
-  <si>
-    <t>Record any coding assumptions, for example when years of education were used to determine the ISCED level.</t>
-  </si>
-  <si>
-    <t>0 = Lower secondary or less (ISCED 2011 levels 0-2); 
-1 = Upper secondary (ISCED 2011 levels 3); 
-2 = Post-secondary non-tertiary education or short-cycle tertiary education (ISCED 2011 levels 4, 5); 
-3 = Bachelor's, master's, doctorate, or equivalent (ISCED 2011 levels 6, 7, 8)</t>
-  </si>
-  <si>
-    <t>0 = No ; 
-1 = Yes</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant is currently in paid employement or unemployed</t>
-  </si>
-  <si>
-    <t>Code homemaker/housewife/househusband as unemployed. Code rentier as employed. Code students, apprentices, retired, and voluntary workers as NA.
-Validate the meaning of "Family worker" with the study to determine the appropriate coding.</t>
-  </si>
-  <si>
-    <t>0 = Unemployed ; 
-1 = Employed</t>
-  </si>
-  <si>
-    <t>Use the study's definition of full-time and part-time work.</t>
-  </si>
-  <si>
-    <t>Record the study's definition and threshold for full-time and part-time work, where available.</t>
-  </si>
-  <si>
-    <t>1 = Part-time ; 
-2 = Full-time</t>
-  </si>
-  <si>
-    <t>Current average number of hours worked per week</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant is currently retired</t>
-  </si>
-  <si>
-    <t>If there is no separate variable for retired/not, code anyone currently in paid employment as not retired and anyone not in paid employment or unknown (e.g., homemaker, students, voluntary workers) as NA. Code combined retired/pensioner as retired.</t>
-  </si>
-  <si>
-    <t>0 = Not retired ; 
-1 = Retired</t>
-  </si>
-  <si>
-    <t>Best descriptor of the participant's current marital status</t>
-  </si>
-  <si>
-    <t>1 = Never married ; 
-2 = Married/In a partnership/Living together ; 
-3 = Divorced/Separated ; 
-4 = Widowed</t>
-  </si>
-  <si>
-    <t>Living in urban or rural location</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant is currently living in an urban or rural area</t>
-  </si>
-  <si>
-    <t>Code 1 = urban, 2 = rural following the study's own urban/rural classification.</t>
-  </si>
-  <si>
-    <t>Record the study's definition of urban vs rural.</t>
-  </si>
-  <si>
-    <t>1 = Rural ; 
-2 = Urban</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Use physical measurements over self-reported values.</t>
-  </si>
-  <si>
-    <t>Record whether multiple input measurements were used, the number of measurements, and whether the harmonized value is an average.</t>
-  </si>
-  <si>
-    <t>Method used to measure height</t>
-  </si>
-  <si>
-    <t>1 = Self-reported ; 
-2 = Measured by professional</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Method used to measure weight</t>
-  </si>
-  <si>
-    <t>Body mass index (BMI)</t>
-  </si>
-  <si>
-    <t>Participant's body mass index (BMI)</t>
-  </si>
-  <si>
-    <t>Participant's waist circumference</t>
-  </si>
-  <si>
-    <t>Method used to measure waist circumference</t>
-  </si>
-  <si>
-    <t>Participant's body fat percentage</t>
-  </si>
-  <si>
-    <t>Method or equipment used to measure body fat percentage</t>
-  </si>
-  <si>
-    <t>Systolic blood pressure (average of all available measures)</t>
-  </si>
-  <si>
-    <t>Use the average of all available measurements from the same collection event.</t>
-  </si>
-  <si>
-    <t>Record the number of measurements and relevant method details, including device, cuff size, position, and rest period.</t>
-  </si>
-  <si>
-    <t>Diastolic blood pressure (average of all available measures)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resting heart rate (average of all available measures) </t>
-  </si>
-  <si>
-    <t>Record the number of measurements and relevant method details, including device, position, and rest period.</t>
-  </si>
-  <si>
-    <t>Cardiorespiratory fitness</t>
-  </si>
-  <si>
-    <t>Cardiorespiratory fitness as VO2max in ml/min/kg, from a maximal or submaximal exercise test (e.g., treadmill or cycle ergometer).</t>
-  </si>
-  <si>
-    <t>Record the specific exercise test and protocol.</t>
-  </si>
-  <si>
-    <t>Blood sampling fasting duration</t>
-  </si>
-  <si>
-    <t>Description of the fasting duration used for blood sampling</t>
-  </si>
-  <si>
-    <t>0 = Non-fasted ; 
-1 = Short-fast (&lt;=4h) ; 
-2 = Long fast (&gt;4h)</t>
-  </si>
-  <si>
-    <t>Red blood cell (RBC) count</t>
-  </si>
-  <si>
-    <t>Glycated hemoglobin (HbA1c)</t>
-  </si>
-  <si>
-    <t>High-density lipoprotein (HDL) cholesterol</t>
-  </si>
-  <si>
-    <t>Low-density lipoprotein (LDL) cholesterol</t>
-  </si>
-  <si>
-    <t>Calculated low-density lipoprotein (LDL) cholesterol</t>
-  </si>
-  <si>
-    <t>If there is no study-specific LDL cholesterol variable, calculate with the Friedewald equation (mmol/L): LDL = total cholesterol - HDL - (triglycerides / 2.2). Use a divisor of 5 for mg/dL. Leave missing when triglycerides exceed 4.5 mmol/L (400 mg/dL).</t>
-  </si>
-  <si>
-    <t>C-reactive protein (CRP)</t>
-  </si>
-  <si>
-    <t>Fruit intake: quantity per day</t>
-  </si>
-  <si>
-    <t>If conversion from servings or cups to grams is needed, obtain the conversion factor from the study.</t>
-  </si>
-  <si>
-    <t>Record the conversion factor used and the study-specific definition of fruit, including whether dried fruit is included and whether nuts are collected separately.</t>
-  </si>
-  <si>
-    <t>Fruit intake: frequency per week</t>
-  </si>
-  <si>
-    <t>Record the study-specific definition of fruit, including whether dried fruit is included and whether nuts are collected separately.</t>
-  </si>
-  <si>
-    <t>1 = Rarely ; 
-2 = Several times a week ; 
-3 = Every day</t>
-  </si>
-  <si>
-    <t>Vegetable intake: quantity per day</t>
-  </si>
-  <si>
-    <t>If conversion from servings or cups to grams is needed, obtain the conversion factor from the study. Legumes should not be considered vegetables.</t>
-  </si>
-  <si>
-    <t>Record the conversion factor used and the study-specific definition of vegetables.</t>
-  </si>
-  <si>
-    <t>Vegetable intake: frequency per week</t>
-  </si>
-  <si>
-    <t>Legumes should not be considered as vegetables.</t>
-  </si>
-  <si>
-    <t>Record the study-specific definition of vegetables.</t>
-  </si>
-  <si>
-    <t>Current alcohol consumption quantity</t>
-  </si>
-  <si>
-    <t>Code non-drinkers as 0.</t>
-  </si>
-  <si>
-    <t>Record study-specific data-collection methods and question wording, including the types of alcohol included.</t>
-  </si>
-  <si>
-    <t>Current alcohol consumption frequency</t>
-  </si>
-  <si>
-    <t>0 = Never/Almost never ; 
-1 = Monthly ; 
-2 = Weekly ; 
-3 = Daily/Almost daily</t>
-  </si>
-  <si>
-    <t>Code occasional smokers as Currently smoke.</t>
-  </si>
-  <si>
-    <t>Record study-specific data-collection methods and question wording.</t>
-  </si>
-  <si>
-    <t>0 = Never smoked ; 
-1 = Previously smoked ; 
-2 = Currently smoke</t>
-  </si>
-  <si>
-    <t>1 = Occasionally ; 
-2 = Daily/Almost daily</t>
-  </si>
-  <si>
-    <t>Number of cigarettes smoked per week</t>
-  </si>
-  <si>
-    <t>Code non-smokers as 0.</t>
-  </si>
-  <si>
-    <t>If the input variable is continuous, use the following category cut-offs:
- &gt;= 0 &amp;  &lt; 6.25 ~ 1L;
- &gt;= 6.25 &amp; &lt; 6.75 ~ 2L;
- &gt;= 6.75 &amp; &lt; 7.25 ~ 3L;
- &gt;= 7.25 &amp; &lt; 7.75 ~ 4L;
- &gt;= 7.75 &amp; &lt; 8.25 ~ 5L;
- &gt;= 8.25 &amp; &lt; 8.75 ~ 6L;
- &gt;= 8.75 &amp; &lt; 9.25 ~ 7L;
- &gt;= 9.25 &amp; &lt; 9.75 ~ 8L;
- &gt;= 9.75 &amp; &lt;= 12 ~ 9L.</t>
-  </si>
-  <si>
-    <t>1 = 0 to 6 hours ; 
-2 = 6.5 hours ; 
-3 = 7 hours ; 
-4 = 7.5 hours ; 
-5 = 8 hours ; 
-6 = 8.5 hours ; 
-7 = 9 hours ; 
-8 = 9.5 hours ; 
-9 = 10 hours or more</t>
-  </si>
-  <si>
-    <t>Difficulties sleeping</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant has difficulties sleeping</t>
-  </si>
-  <si>
-    <t>Record how input variables are coded, if relevant.</t>
-  </si>
-  <si>
-    <t>0 = Never/Rarely ; 
-1 = Some difficulties</t>
-  </si>
-  <si>
-    <t>1 = Less than 1 hour per day ; 
-2 = 1 to 3 hours per day ; 
-3 = More than 3 hours per day</t>
-  </si>
-  <si>
-    <t>Daily TV viewing during weekdays</t>
-  </si>
-  <si>
-    <t>Daily TV viewing during weekends</t>
-  </si>
-  <si>
-    <t>Time spent using a computer</t>
-  </si>
-  <si>
-    <t>Time spent using a computer per day on weekdays, excluding computer use at work</t>
-  </si>
-  <si>
-    <t>1 = 0 to less than 1 hour per day ; 
-2 = 1 to less than 2 hours per day ; 
-3 = 2 to less than 3 hours per day ; 
-4 = 3 to less than 4 hours per day ; 
-5 = 4 to less than 5 hours per day ; 
-6 = 5 to less than 6 hours per day ; 
-7 = 6 to less than 7 hours per day ; 
-8 = 7 to less than 8 hours per day ; 
-9 = 8 to less than 9 hours per day ; 
-10 = 9 to less than 10 hours per day ; 
-11 = 10 hours or more per day</t>
-  </si>
-  <si>
-    <t>Time spent playing video games</t>
-  </si>
-  <si>
-    <t>Time spent reading</t>
-  </si>
-  <si>
-    <t>Total time spent sitting per day - continuous</t>
-  </si>
-  <si>
-    <t>Total time spent sitting per day - categorical</t>
-  </si>
-  <si>
-    <t>0 = Not at all ; 
-1 = Less than 1 hour per day ; 
-2 = 1 to less than 3 hours per day ; 
-3 = 3 to less than 5 hours per day ; 
-4 = 5 to less than 7 hours per day ; 
-5 = 7 hours or more per day</t>
-  </si>
-  <si>
-    <t>Frequency of walking for leisure</t>
-  </si>
-  <si>
-    <t>Frequency per week of walking for leisure (recreation or exercise, not transport), in bouts of at least 10 minutes</t>
-  </si>
-  <si>
-    <t>Record differences in information source, wording, and/or collection method between the study-specific variable and the DataSchema variable.</t>
-  </si>
-  <si>
-    <t>1 = Less than once a week ; 
-2 = 1 to 5 times a week ; 
-3 = 6 times or more times a week</t>
-  </si>
-  <si>
-    <t>1 = Mostly sedentary with no physical demands ; 
-2 = Mostly standing or walking ; 
-3 = Standing and walking with lifting or carrying ; 
-4 = Strenuous physical work</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant currently participates in sport activity</t>
-  </si>
-  <si>
-    <t>Include any sport or structured physical activity of moderate or higher intensity, organized or recreational. If the study asks about sports in a select-all-that-apply list, 0 can only be coded if there is an option for "Other" sports. Otherwise only 1 and NA can be coded.</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant currently engages in active commuting for transport (walking, biking or other active modes).</t>
-  </si>
-  <si>
-    <t>Only considered as active commuting when engaged in for at least 15 minutes.</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant currently engages in physical activity during leisure time (including sport)</t>
-  </si>
-  <si>
-    <t>Include any physical activity where the intensity was moderate or higher.</t>
-  </si>
-  <si>
-    <t>36-Item Short Form Health Survey (SF-36) physical function subscale score</t>
-  </si>
-  <si>
-    <t>Total score from the physical function subscale of the Short Form-36 (SF-36)</t>
-  </si>
-  <si>
-    <t>Score on the SF-36 physical function subscale (0-100, higher = better function). Set to NA if fewer than 5 of the 10 items are completed.</t>
-  </si>
-  <si>
-    <t>Number of Short-Form-36 (SF-36) physical function subscale non-missing items</t>
-  </si>
-  <si>
-    <t>Number of non-missing items in the Short Form-36 (SF-36) physical function subscale</t>
-  </si>
-  <si>
-    <t>Record any assumptions or transformations applied when input categories do not directly match the DataSchema categories.</t>
-  </si>
-  <si>
-    <t>1 = Poor/Very Poor ; 
-2 = Moderate/Fair ; 
-3 = Good ; 
-4 = Very good/Excellent</t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever</t>
-  </si>
-  <si>
-    <t>Ever had any cardiovascular disease (ischemic heart disease, stroke, hypertension, heart failure, atrial fibrillation, thrombosis, cerebrovascular disease, or angina pectoris)</t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.
-If the study did not collect a variable for "any cardiovascular disease" and only collected individual cardiovascular diseases (ischemic heart disease, stroke, hypertension, heart failure, atrial fibrillation, thrombosis, cerebrovascular disease, angina pectoris), Yes values can be assigned if any individual cardiovascular diseases are Yes. If the study also collected a variable for "Other cardiovascular disease", Yes/No values can be assigned. If the study did not collect "Other cardiovascular disease", the harmonized values can only be Yes or NA.</t>
-  </si>
-  <si>
-    <t>If the study did not collect a variable about "ever had any cardiovascular disease", record the decisions used to derive the DataSchema variable from individual cardiovascular diseases, including whether an Other cardiovascular disease option was available.</t>
-  </si>
-  <si>
-    <t>0 = No ; 
-1 = Yes ; 
-2 = Presumed no</t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Ischemic heart disease (coronary heart disease)</t>
-  </si>
-  <si>
-    <t>Ever had ischemic heart disease (coronary heart disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceptable wording is "Ischemic heart", "Coronary heart disease", "MI", "Myocardial infarction", or "Heart attack". </t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any of the following cardiovascular diseases? Yes/No) or there is a response option for "None of the above" for a list including this disease, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Myocardial infarction (MI)</t>
-  </si>
-  <si>
-    <t>Ever had myocardial infarction (MI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceptable wording is "MI", "Myocardial infarction", or "Heart attack". </t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Angina pectoris</t>
-  </si>
-  <si>
-    <t>Ever had angina pectoris</t>
-  </si>
-  <si>
-    <t>Acceptable wording is "Angina" or "Angina pectoris".</t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Stroke</t>
-  </si>
-  <si>
-    <t>Ever had stroke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceptable wording is "Stroke", "cerebrovascular accident", "CVA", "apoplexy", "seizure", "cerebral infarction", or "cerebral hemorrhage".  </t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Heart failure</t>
-  </si>
-  <si>
-    <t>Ever had heart failure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceptable wording is "heart failure" or "congestive heart failure". </t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Atrial fibrillation</t>
-  </si>
-  <si>
-    <t>Ever had atrial fibrillation</t>
-  </si>
-  <si>
-    <t>Acceptable wording is "atrial fibrillation".</t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Hypertension or high blood pressure diagnosis</t>
-  </si>
-  <si>
-    <t>Ever had hypertension or high blood pressure diagnosis</t>
-  </si>
-  <si>
-    <t>Acceptable wording is "high blood pressure" or "hypertension".</t>
-  </si>
-  <si>
-    <t>Code Yes if there is a diagnosis of hypertension or high blood pressure. Base it on diagnosis only, not medication use. Self-reported diagnosis is acceptable.
-If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any of the following cardiovascular diseases? Yes/No) or there is a response option for "None of the above" for a list including this disease, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>Record cases where it is unclear whether the reported condition was diagnosed.</t>
-  </si>
-  <si>
-    <t>Cardiovascular disease ever - Hypertension or high blood pressure diagnosis or take medication</t>
-  </si>
-  <si>
-    <t>Ever had hypertension or high blood pressure diagnosis or take medication</t>
-  </si>
-  <si>
-    <t>Harmonize based on either diagnosed condition or medication use for hypertension or high blood pressure. 
-If Yes to either diagnosed condition or taking medication, code as Yes.
-If No to both diagnosed condition and taking medication, code as No.
-If No to only one of diagnosed condition or taking medication, codes as Presumed no.
-If the study-specific variables were collected as part of select-all-that-apply sections without a response option for No, code as "Presumed no" if neither diagnosed condition nor taking medication were selected but at least one other item in the sections was selected.</t>
-  </si>
-  <si>
-    <t>Musculoskeletal disease ever</t>
-  </si>
-  <si>
-    <t>Ever had musculoskeletal disease</t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any of the following diseases? Yes/No) or there is a response option for "None of the above" for a list including this disease, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>Diabetes ever</t>
-  </si>
-  <si>
-    <t>Ever had diabetes</t>
-  </si>
-  <si>
-    <t>Includes gestational diabetes and other types of diabetes, but excludes impaired fasting glucose and impaired glucose tolerance.</t>
-  </si>
-  <si>
-    <t>Record study-specific wording used to collect diabetes information, such as type-specific collection or exclusion of gestational diabetes.</t>
-  </si>
-  <si>
-    <t>Record study-specific wording used to collect diabetes type information, such as whether only Type 2 diabetes was collected.</t>
-  </si>
-  <si>
-    <t>1 = Type 1 ; 
-2 = Type 2 ; 
-3 = Other</t>
-  </si>
-  <si>
-    <t>Ever had cancer</t>
-  </si>
-  <si>
-    <t>Code Yes if the participant has ever had any cancer; code No if explicitly none.
-If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>If the study did not collect a variable about "ever had any cancer", record the decisions used to derive the DataSchema variable from individual cancers, including whether an "Other cancer" option was available.</t>
-  </si>
-  <si>
-    <t>Ever had bladder cancer</t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had any cancer? Yes/No) or there is a response option for "None of the above" for a list including this cancer, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>Ever had breast cancer</t>
-  </si>
-  <si>
-    <t>Ever had cervical cancer</t>
-  </si>
-  <si>
-    <t>Cancer ever - Colorectal</t>
-  </si>
-  <si>
-    <t>Ever had colorectal cancer</t>
-  </si>
-  <si>
-    <t>Ever had kidney cancer</t>
-  </si>
-  <si>
-    <t>Cancer ever - Throat (Larynx or Pharynx)</t>
-  </si>
-  <si>
-    <t>Ever had throat cancer (pharyngeal or laryngeal cancer)</t>
-  </si>
-  <si>
-    <t>Ever had leukaemia</t>
-  </si>
-  <si>
-    <t>Ever had lung cancer</t>
-  </si>
-  <si>
-    <t>Ever had lymphoma</t>
-  </si>
-  <si>
-    <t>Ever had prostate cancer</t>
-  </si>
-  <si>
-    <t>Ever had skin cancer</t>
-  </si>
-  <si>
-    <t>Ever had stomach cancer</t>
-  </si>
-  <si>
-    <t>Ever had testicular cancer</t>
-  </si>
-  <si>
-    <t>Ever had uterine cancer</t>
-  </si>
-  <si>
-    <t>Ever had brain cancer</t>
-  </si>
-  <si>
-    <t>Ever had liver cancer</t>
-  </si>
-  <si>
-    <t>Ever had ovarian cancer</t>
-  </si>
-  <si>
-    <t>Ever had pancreatic cancer</t>
-  </si>
-  <si>
-    <t>Ever had thyroid cancer</t>
-  </si>
-  <si>
-    <t>Hypercholesterolemia ever</t>
-  </si>
-  <si>
-    <t>Ever had hypercholesterolemia</t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Have you ever had have any of the following conditions? Yes/No) or there is a response option for "None of the above" for a list including this condition, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant currently has depression</t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Do you have any of the following conditions? Yes/No) or there is a response option for "None of the above" for a list including this condition, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>Alzheimer's/dementia</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant has Alzheimer's or other dementia</t>
-  </si>
-  <si>
-    <t>Current use of lipid-lowering medication</t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Do you currently take any medication? Yes/No) or there is a response option for "None of the above" for a list including this medication, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>If the study-specific variable has Yes/No responses, the harmonized values can be Yes/No. 
-If the study-specific variable is conditional on a parent variable with Yes/No responses (e.g., Do you currently take any medication? If yes, specify...) or there is a response option for "None of the above" for a list including this medication, the harmonized values can be Yes/No. 
-If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
-  </si>
-  <si>
-    <t>Center for Epidemiologic Studies Depression Scale (CES-D) 20-item score</t>
-  </si>
-  <si>
-    <t>Where possible, validate the calculation of the score. Allowed range is 0-60.</t>
-  </si>
-  <si>
-    <t>Center for Epidemiologic Studies Depression Scale (CES-D) 10-item score</t>
-  </si>
-  <si>
-    <t>Where possible, validate the calculation of the score. Allowed range is 0-30.</t>
-  </si>
-  <si>
-    <t>Malaise Inventory 9-item score</t>
-  </si>
-  <si>
-    <t>Where possible, validate the calculation of the score. Allowed range is 0-9.</t>
-  </si>
-  <si>
-    <t>Kessler Psychological Distress Scale (K-10) score</t>
-  </si>
-  <si>
-    <t>Where possible, validate the calculation of the score. Allowed range is 10-50.</t>
-  </si>
-  <si>
-    <t>Patient Health Questionnaire-9 (PHQ-9) score</t>
-  </si>
-  <si>
-    <t>Where possible, validate the calculation of the score. Allowed range is 0-27.</t>
-  </si>
-  <si>
-    <t>Mini-Mental State Examination (MMSE) score</t>
-  </si>
-  <si>
-    <t>Montreal Cognitive Assessment (MoCA) score</t>
-  </si>
-  <si>
-    <t>adm_participant_id</t>
-  </si>
-  <si>
-    <t>sdc_education_highest</t>
-  </si>
-  <si>
-    <t>sdc_education_secondary</t>
-  </si>
-  <si>
-    <t>phy_height</t>
-  </si>
-  <si>
-    <t>phy_height_method</t>
-  </si>
-  <si>
-    <t>phy_weight</t>
-  </si>
-  <si>
-    <t>phy_weight_method</t>
-  </si>
-  <si>
-    <t>phy_bmi</t>
-  </si>
-  <si>
-    <t>phy_waist_circ</t>
-  </si>
-  <si>
-    <t>phy_waist_circ_method</t>
-  </si>
-  <si>
-    <t>phy_bodyfat_perc</t>
-  </si>
-  <si>
-    <t>phy_bodyfat_perc_method</t>
-  </si>
-  <si>
-    <t>phy_systolic_bp</t>
-  </si>
-  <si>
-    <t>phy_diastolic_bp</t>
-  </si>
-  <si>
-    <t>phy_resting_heart_rate</t>
-  </si>
-  <si>
-    <t>phy_cardiorespiratory_fitness</t>
-  </si>
-  <si>
-    <t>lab_rbc</t>
-  </si>
-  <si>
-    <t>lab_hba1c</t>
-  </si>
-  <si>
-    <t>lab_chol_total</t>
-  </si>
-  <si>
-    <t>lab_tg</t>
-  </si>
-  <si>
-    <t>lab_crp</t>
-  </si>
-  <si>
-    <t>lsb_nut_energy_total</t>
-  </si>
-  <si>
-    <t>lsb_sed_beh_tv_week</t>
-  </si>
-  <si>
-    <t>lsb_sed_beh_tv_weekday</t>
-  </si>
-  <si>
-    <t>lsb_sed_beh_tv_weekend</t>
-  </si>
-  <si>
-    <t>lsb_sed_beh_computer_use</t>
-  </si>
-  <si>
-    <t>lsb_sed_beh_total_sitting</t>
-  </si>
-  <si>
-    <t>lsb_sed_beh_total_sitting_cat</t>
-  </si>
-  <si>
-    <t>lsb_pa_walking</t>
-  </si>
-  <si>
-    <t>lsb_pa_occupational</t>
-  </si>
-  <si>
-    <t>lsb_pa_sport_participation</t>
-  </si>
-  <si>
-    <t>lsb_pa_active_commuting</t>
-  </si>
-  <si>
-    <t>lsb_pa_leisure_time</t>
-  </si>
-  <si>
-    <t>phe_sf36_phys_function</t>
-  </si>
-  <si>
-    <t>phe_sf36_n_items</t>
-  </si>
-  <si>
-    <t>dis_cvd_hf_ever</t>
-  </si>
-  <si>
-    <t>dis_cvd_af_ever</t>
-  </si>
-  <si>
-    <t>dis_diabetes_ever</t>
-  </si>
-  <si>
-    <t>dis_hypercholesterolemia_ever</t>
-  </si>
-  <si>
-    <t>med_lipid_lowering_curr</t>
-  </si>
-  <si>
-    <t>med_blood_pressure_curr</t>
-  </si>
-  <si>
-    <t>med_diabetes_curr</t>
-  </si>
-  <si>
-    <t>cog_dep_cesd20</t>
-  </si>
-  <si>
-    <t>cog_dep_cesd10</t>
-  </si>
-  <si>
-    <t>cog_dep_malaise</t>
-  </si>
-  <si>
-    <t>cog_dep_kessler</t>
-  </si>
-  <si>
-    <t>cog_dep_phq9</t>
-  </si>
-  <si>
-    <t>cog_mci_mmse</t>
-  </si>
-  <si>
-    <t>cog_mci_moca</t>
-  </si>
-  <si>
-    <t>wording</t>
-  </si>
-  <si>
-    <t>comments</t>
+na.rm = TRUE) == 0, NA,
+ rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous_w4)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate_w4)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift_w4)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral_w4)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone_w4)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending_w4)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_w4)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_w4)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_w4)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath_w4))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE))</t>
   </si>
 </sst>
 </file>
@@ -3874,13 +3913,13 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
@@ -3936,19 +3975,19 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="M2" t="s">
         <v>24</v>
@@ -3998,13 +4037,13 @@
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="M3" t="s">
         <v>36</v>
@@ -4036,13 +4075,13 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="M4" t="s">
         <v>36</v>
@@ -4074,13 +4113,13 @@
         <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M5" t="s">
         <v>36</v>
@@ -4109,7 +4148,7 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E6" t="s">
         <v>45</v>
@@ -4121,10 +4160,10 @@
         <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="K6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M6" t="s">
         <v>372</v>
@@ -4171,7 +4210,7 @@
         <v>43</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M7" t="s">
         <v>54</v>
@@ -4212,7 +4251,7 @@
         <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
@@ -4221,10 +4260,10 @@
         <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K8" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="M8" t="s">
         <v>374</v>
@@ -4268,25 +4307,25 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D9" t="s">
         <v>69</v>
       </c>
       <c r="E9" t="s">
+        <v>576</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" t="s">
+        <v>577</v>
+      </c>
+      <c r="K9" t="s">
+        <v>578</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" t="s">
-        <v>580</v>
-      </c>
-      <c r="K9" t="s">
-        <v>581</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>582</v>
       </c>
       <c r="M9" t="s">
         <v>36</v>
@@ -4312,7 +4351,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D10" t="s">
         <v>72</v>
@@ -4324,13 +4363,13 @@
         <v>43</v>
       </c>
       <c r="J10" t="s">
+        <v>577</v>
+      </c>
+      <c r="K10" t="s">
+        <v>578</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="K10" t="s">
-        <v>581</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="M10" t="s">
         <v>36</v>
@@ -4362,16 +4401,16 @@
         <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F11" t="s">
         <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L11" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="M11" t="s">
         <v>375</v>
@@ -4430,13 +4469,13 @@
         <v>43</v>
       </c>
       <c r="J12" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="K12" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M12" t="s">
         <v>375</v>
@@ -4486,10 +4525,10 @@
         <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E13" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F13" t="s">
         <v>88</v>
@@ -4562,16 +4601,16 @@
         <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F15" t="s">
         <v>43</v>
       </c>
       <c r="J15" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="M15" t="s">
         <v>375</v>
@@ -4624,13 +4663,13 @@
         <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F16" t="s">
         <v>43</v>
       </c>
       <c r="L16" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="M16" t="s">
         <v>376</v>
@@ -4677,22 +4716,22 @@
         <v>103</v>
       </c>
       <c r="D17" t="s">
+        <v>593</v>
+      </c>
+      <c r="E17" t="s">
+        <v>594</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" t="s">
+        <v>595</v>
+      </c>
+      <c r="K17" t="s">
         <v>596</v>
       </c>
-      <c r="E17" t="s">
+      <c r="L17" t="s">
         <v>597</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" t="s">
-        <v>598</v>
-      </c>
-      <c r="K17" t="s">
-        <v>599</v>
-      </c>
-      <c r="L17" t="s">
-        <v>600</v>
       </c>
       <c r="M17" t="s">
         <v>36</v>
@@ -4718,10 +4757,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D18" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E18" t="s">
         <v>104</v>
@@ -4733,10 +4772,10 @@
         <v>105</v>
       </c>
       <c r="J18" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K18" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M18" t="s">
         <v>377</v>
@@ -4783,19 +4822,19 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D19" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E19" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F19" t="s">
         <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M19" t="s">
         <v>377</v>
@@ -4821,10 +4860,10 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D20" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E20" t="s">
         <v>110</v>
@@ -4836,10 +4875,10 @@
         <v>111</v>
       </c>
       <c r="J20" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K20" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M20" t="s">
         <v>380</v>
@@ -4886,19 +4925,19 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D21" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E21" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F21" t="s">
         <v>43</v>
       </c>
       <c r="L21" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M21" t="s">
         <v>380</v>
@@ -4924,13 +4963,13 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D22" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E22" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="F22" t="s">
         <v>88</v>
@@ -4939,10 +4978,10 @@
         <v>115</v>
       </c>
       <c r="J22" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K22" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" t="s">
@@ -4990,13 +5029,13 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D23" t="s">
         <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F23" t="s">
         <v>88</v>
@@ -5005,10 +5044,10 @@
         <v>105</v>
       </c>
       <c r="J23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K23" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M23" t="s">
         <v>382</v>
@@ -5058,19 +5097,19 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D24" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E24" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F24" t="s">
         <v>43</v>
       </c>
       <c r="L24" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M24" t="s">
         <v>382</v>
@@ -5117,13 +5156,13 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D25" t="s">
         <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F25" t="s">
         <v>88</v>
@@ -5176,13 +5215,13 @@
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D26" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E26" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F26" t="s">
         <v>23</v>
@@ -5211,13 +5250,13 @@
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D27" t="s">
         <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F27" t="s">
         <v>88</v>
@@ -5226,10 +5265,10 @@
         <v>132</v>
       </c>
       <c r="J27" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K27" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M27" t="s">
         <v>388</v>
@@ -5273,13 +5312,13 @@
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F28" t="s">
         <v>88</v>
@@ -5288,10 +5327,10 @@
         <v>132</v>
       </c>
       <c r="J28" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K28" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M28" t="s">
         <v>391</v>
@@ -5335,13 +5374,13 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D29" t="s">
         <v>139</v>
       </c>
       <c r="E29" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="F29" t="s">
         <v>88</v>
@@ -5350,10 +5389,10 @@
         <v>140</v>
       </c>
       <c r="J29" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K29" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="M29" t="s">
         <v>36</v>
@@ -5379,13 +5418,13 @@
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D30" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E30" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F30" t="s">
         <v>88</v>
@@ -5394,10 +5433,10 @@
         <v>141</v>
       </c>
       <c r="J30" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="K30" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M30" t="s">
         <v>36</v>
@@ -5426,16 +5465,16 @@
         <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E31" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F31" t="s">
         <v>43</v>
       </c>
       <c r="L31" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="M31" t="s">
         <v>36</v>
@@ -5461,13 +5500,13 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D32" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E32" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F32" t="s">
         <v>88</v>
@@ -5500,13 +5539,13 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D33" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E33" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F33" t="s">
         <v>88</v>
@@ -5538,7 +5577,7 @@
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D34" t="s">
         <v>145</v>
@@ -5589,10 +5628,10 @@
         <v>149</v>
       </c>
       <c r="D35" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E35" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F35" t="s">
         <v>88</v>
@@ -5636,10 +5675,10 @@
         <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E36" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F36" t="s">
         <v>88</v>
@@ -5683,10 +5722,10 @@
         <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E37" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F37" t="s">
         <v>88</v>
@@ -5695,7 +5734,7 @@
         <v>146</v>
       </c>
       <c r="J37" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
@@ -5725,7 +5764,7 @@
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D38" t="s">
         <v>159</v>
@@ -5773,13 +5812,13 @@
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D39" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E39" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F39" t="s">
         <v>88</v>
@@ -5824,10 +5863,10 @@
         <v>166</v>
       </c>
       <c r="D40" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E40" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F40" t="s">
         <v>88</v>
@@ -5836,10 +5875,10 @@
         <v>167</v>
       </c>
       <c r="J40" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K40" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="M40" t="s">
         <v>36</v>
@@ -5868,19 +5907,19 @@
         <v>168</v>
       </c>
       <c r="D41" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E41" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F41" t="s">
         <v>43</v>
       </c>
       <c r="K41" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="L41" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M41" t="s">
         <v>36</v>
@@ -5909,10 +5948,10 @@
         <v>169</v>
       </c>
       <c r="D42" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E42" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F42" t="s">
         <v>88</v>
@@ -5921,10 +5960,10 @@
         <v>167</v>
       </c>
       <c r="J42" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K42" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" t="s">
@@ -5954,22 +5993,22 @@
         <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E43" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F43" t="s">
         <v>43</v>
       </c>
       <c r="J43" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="K43" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M43" t="s">
         <v>399</v>
@@ -6010,7 +6049,7 @@
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D44" t="s">
         <v>176</v>
@@ -6052,10 +6091,10 @@
         <v>178</v>
       </c>
       <c r="D45" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E45" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F45" t="s">
         <v>88</v>
@@ -6064,10 +6103,10 @@
         <v>179</v>
       </c>
       <c r="J45" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K45" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" t="s">
@@ -6109,16 +6148,16 @@
         <v>183</v>
       </c>
       <c r="D46" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E46" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F46" t="s">
         <v>43</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="M46" t="s">
         <v>36</v>
@@ -6156,13 +6195,13 @@
         <v>43</v>
       </c>
       <c r="J47" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="K47" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M47" t="s">
         <v>401</v>
@@ -6218,10 +6257,10 @@
         <v>43</v>
       </c>
       <c r="K48" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="M48" t="s">
         <v>36</v>
@@ -6250,10 +6289,10 @@
         <v>193</v>
       </c>
       <c r="D49" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E49" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F49" t="s">
         <v>88</v>
@@ -6262,10 +6301,10 @@
         <v>194</v>
       </c>
       <c r="J49" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K49" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" t="s">
@@ -6363,10 +6402,10 @@
         <v>43</v>
       </c>
       <c r="J51" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="M51" t="s">
         <v>402</v>
@@ -6413,19 +6452,19 @@
         <v>207</v>
       </c>
       <c r="D52" t="s">
+        <v>655</v>
+      </c>
+      <c r="E52" t="s">
+        <v>656</v>
+      </c>
+      <c r="F52" t="s">
+        <v>43</v>
+      </c>
+      <c r="K52" t="s">
+        <v>657</v>
+      </c>
+      <c r="L52" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="E52" t="s">
-        <v>659</v>
-      </c>
-      <c r="F52" t="s">
-        <v>43</v>
-      </c>
-      <c r="K52" t="s">
-        <v>660</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>661</v>
       </c>
       <c r="M52" t="s">
         <v>403</v>
@@ -6469,7 +6508,7 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D53" t="s">
         <v>213</v>
@@ -6484,7 +6523,7 @@
         <v>214</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M53" t="s">
         <v>36</v>
@@ -6510,19 +6549,19 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D54" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E54" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F54" t="s">
         <v>43</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M54" t="s">
         <v>404</v>
@@ -6569,19 +6608,19 @@
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D55" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E55" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F55" t="s">
         <v>43</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M55" t="s">
         <v>36</v>
@@ -6607,19 +6646,19 @@
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D56" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E56" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="F56" t="s">
         <v>43</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="M56" t="s">
         <v>405</v>
@@ -6669,7 +6708,7 @@
         <v>226</v>
       </c>
       <c r="D57" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E57" t="s">
         <v>227</v>
@@ -6681,7 +6720,7 @@
         <v>214</v>
       </c>
       <c r="L57" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M57" t="s">
         <v>36</v>
@@ -6710,7 +6749,7 @@
         <v>228</v>
       </c>
       <c r="D58" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E58" t="s">
         <v>229</v>
@@ -6722,7 +6761,7 @@
         <v>214</v>
       </c>
       <c r="L58" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M58" t="s">
         <v>36</v>
@@ -6748,13 +6787,13 @@
         <v>22</v>
       </c>
       <c r="C59" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D59" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E59" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F59" t="s">
         <v>88</v>
@@ -6811,19 +6850,19 @@
         <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D60" t="s">
         <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F60" t="s">
         <v>43</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="M60" t="s">
         <v>407</v>
@@ -6870,22 +6909,22 @@
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D61" t="s">
+        <v>670</v>
+      </c>
+      <c r="E61" t="s">
+        <v>671</v>
+      </c>
+      <c r="F61" t="s">
+        <v>43</v>
+      </c>
+      <c r="K61" t="s">
+        <v>672</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="E61" t="s">
-        <v>674</v>
-      </c>
-      <c r="F61" t="s">
-        <v>43</v>
-      </c>
-      <c r="K61" t="s">
-        <v>675</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>676</v>
       </c>
       <c r="M61" t="s">
         <v>36</v>
@@ -6914,7 +6953,7 @@
         <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D62" t="s">
         <v>344</v>
@@ -6926,10 +6965,10 @@
         <v>43</v>
       </c>
       <c r="K62" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="M62" t="s">
         <v>36</v>
@@ -6955,25 +6994,25 @@
         <v>22</v>
       </c>
       <c r="C63" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D63" t="s">
         <v>346</v>
       </c>
       <c r="E63" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F63" t="s">
         <v>43</v>
       </c>
       <c r="J63" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="K63" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M63" t="s">
         <v>36</v>
@@ -6999,22 +7038,22 @@
         <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D64" t="s">
         <v>347</v>
       </c>
       <c r="E64" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F64" t="s">
         <v>43</v>
       </c>
       <c r="J64" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M64" t="s">
         <v>423</v>
@@ -7058,25 +7097,25 @@
         <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D65" t="s">
         <v>353</v>
       </c>
       <c r="E65" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F65" t="s">
         <v>43</v>
       </c>
       <c r="J65" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="K65" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M65" t="s">
         <v>424</v>
@@ -7123,23 +7162,23 @@
         <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D66" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E66" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F66" t="s">
         <v>88</v>
       </c>
       <c r="J66" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="W66" t="s">
         <v>31</v>
@@ -7154,7 +7193,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="270" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7162,13 +7201,13 @@
         <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D67" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E67" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F67" t="s">
         <v>43</v>
@@ -7178,7 +7217,7 @@
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="W67" t="s">
         <v>31</v>
@@ -7190,7 +7229,7 @@
         <v>50</v>
       </c>
       <c r="Z67" s="1" t="s">
-        <v>547</v>
+        <v>827</v>
       </c>
     </row>
     <row r="68" spans="1:26" ht="390" x14ac:dyDescent="0.25">
@@ -7213,10 +7252,10 @@
         <v>43</v>
       </c>
       <c r="K68" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="M68" t="s">
         <v>238</v>
@@ -7266,22 +7305,22 @@
         <v>244</v>
       </c>
       <c r="D69" t="s">
+        <v>688</v>
+      </c>
+      <c r="E69" t="s">
+        <v>689</v>
+      </c>
+      <c r="F69" t="s">
+        <v>43</v>
+      </c>
+      <c r="J69" t="s">
+        <v>690</v>
+      </c>
+      <c r="K69" t="s">
         <v>691</v>
       </c>
-      <c r="E69" t="s">
+      <c r="L69" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="F69" t="s">
-        <v>43</v>
-      </c>
-      <c r="J69" t="s">
-        <v>693</v>
-      </c>
-      <c r="K69" t="s">
-        <v>694</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>410</v>
@@ -7331,22 +7370,22 @@
         <v>251</v>
       </c>
       <c r="D70" t="s">
+        <v>693</v>
+      </c>
+      <c r="E70" t="s">
+        <v>694</v>
+      </c>
+      <c r="F70" t="s">
+        <v>43</v>
+      </c>
+      <c r="I70" t="s">
+        <v>695</v>
+      </c>
+      <c r="J70" t="s">
         <v>696</v>
       </c>
-      <c r="E70" t="s">
-        <v>697</v>
-      </c>
-      <c r="F70" t="s">
-        <v>43</v>
-      </c>
-      <c r="I70" t="s">
-        <v>698</v>
-      </c>
-      <c r="J70" t="s">
-        <v>699</v>
-      </c>
       <c r="L70" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M70" t="s">
         <v>412</v>
@@ -7396,22 +7435,22 @@
         <v>256</v>
       </c>
       <c r="D71" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E71" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F71" t="s">
         <v>43</v>
       </c>
       <c r="I71" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="J71" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M71" t="s">
         <v>412</v>
@@ -7458,22 +7497,22 @@
         <v>259</v>
       </c>
       <c r="D72" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E72" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F72" t="s">
         <v>43</v>
       </c>
       <c r="I72" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="J72" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M72" t="s">
         <v>413</v>
@@ -7520,22 +7559,22 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E73" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F73" t="s">
         <v>43</v>
       </c>
       <c r="I73" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="J73" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M73" t="s">
         <v>414</v>
@@ -7579,25 +7618,25 @@
         <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D74" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E74" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F74" t="s">
         <v>43</v>
       </c>
       <c r="I74" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="J74" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>410</v>
@@ -7641,25 +7680,25 @@
         <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D75" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E75" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F75" t="s">
         <v>43</v>
       </c>
       <c r="I75" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="J75" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M75" t="s">
         <v>36</v>
@@ -7688,25 +7727,25 @@
         <v>266</v>
       </c>
       <c r="D76" t="s">
+        <v>712</v>
+      </c>
+      <c r="E76" t="s">
+        <v>713</v>
+      </c>
+      <c r="F76" t="s">
+        <v>43</v>
+      </c>
+      <c r="I76" t="s">
+        <v>714</v>
+      </c>
+      <c r="J76" t="s">
         <v>715</v>
       </c>
-      <c r="E76" t="s">
+      <c r="K76" t="s">
         <v>716</v>
       </c>
-      <c r="F76" t="s">
-        <v>43</v>
-      </c>
-      <c r="I76" t="s">
-        <v>717</v>
-      </c>
-      <c r="J76" t="s">
-        <v>718</v>
-      </c>
-      <c r="K76" t="s">
-        <v>719</v>
-      </c>
       <c r="L76" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M76" t="s">
         <v>415</v>
@@ -7753,22 +7792,22 @@
         <v>269</v>
       </c>
       <c r="D77" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E77" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F77" t="s">
         <v>43</v>
       </c>
       <c r="I77" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="J77" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>416</v>
@@ -7797,19 +7836,19 @@
         <v>270</v>
       </c>
       <c r="D78" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E78" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F78" t="s">
         <v>43</v>
       </c>
       <c r="J78" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>417</v>
@@ -7856,31 +7895,31 @@
         <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D79" t="s">
+        <v>723</v>
+      </c>
+      <c r="E79" t="s">
+        <v>724</v>
+      </c>
+      <c r="F79" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" t="s">
+        <v>725</v>
+      </c>
+      <c r="J79" t="s">
+        <v>722</v>
+      </c>
+      <c r="K79" t="s">
         <v>726</v>
       </c>
-      <c r="E79" t="s">
-        <v>727</v>
-      </c>
-      <c r="F79" t="s">
-        <v>43</v>
-      </c>
-      <c r="I79" t="s">
-        <v>728</v>
-      </c>
-      <c r="J79" t="s">
-        <v>725</v>
-      </c>
-      <c r="K79" t="s">
-        <v>729</v>
-      </c>
       <c r="L79" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M79" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="N79" t="s">
         <v>276</v>
@@ -7936,13 +7975,13 @@
         <v>43</v>
       </c>
       <c r="K80" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="M80" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="N80" t="s">
         <v>276</v>
@@ -7992,19 +8031,19 @@
         <v>283</v>
       </c>
       <c r="E81" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F81" t="s">
         <v>43</v>
       </c>
       <c r="J81" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="K81" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M81" t="s">
         <v>544</v>
@@ -8054,16 +8093,16 @@
         <v>287</v>
       </c>
       <c r="E82" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F82" t="s">
         <v>43</v>
       </c>
       <c r="J82" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M82" t="s">
         <v>36</v>
@@ -8095,16 +8134,16 @@
         <v>289</v>
       </c>
       <c r="E83" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F83" t="s">
         <v>43</v>
       </c>
       <c r="J83" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M83" t="s">
         <v>36</v>
@@ -8136,16 +8175,16 @@
         <v>291</v>
       </c>
       <c r="E84" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="F84" t="s">
         <v>43</v>
       </c>
       <c r="J84" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M84" t="s">
         <v>36</v>
@@ -8174,19 +8213,19 @@
         <v>292</v>
       </c>
       <c r="D85" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E85" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F85" t="s">
         <v>43</v>
       </c>
       <c r="J85" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M85" t="s">
         <v>36</v>
@@ -8218,16 +8257,16 @@
         <v>294</v>
       </c>
       <c r="E86" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F86" t="s">
         <v>43</v>
       </c>
       <c r="J86" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M86" t="s">
         <v>36</v>
@@ -8256,19 +8295,19 @@
         <v>295</v>
       </c>
       <c r="D87" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E87" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="F87" t="s">
         <v>43</v>
       </c>
       <c r="J87" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M87" t="s">
         <v>36</v>
@@ -8300,16 +8339,16 @@
         <v>297</v>
       </c>
       <c r="E88" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F88" t="s">
         <v>43</v>
       </c>
       <c r="J88" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M88" t="s">
         <v>36</v>
@@ -8341,16 +8380,16 @@
         <v>299</v>
       </c>
       <c r="E89" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="F89" t="s">
         <v>43</v>
       </c>
       <c r="J89" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M89" t="s">
         <v>36</v>
@@ -8382,16 +8421,16 @@
         <v>301</v>
       </c>
       <c r="E90" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="F90" t="s">
         <v>43</v>
       </c>
       <c r="J90" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M90" t="s">
         <v>36</v>
@@ -8423,16 +8462,16 @@
         <v>303</v>
       </c>
       <c r="E91" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F91" t="s">
         <v>43</v>
       </c>
       <c r="J91" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M91" t="s">
         <v>36</v>
@@ -8464,16 +8503,16 @@
         <v>305</v>
       </c>
       <c r="E92" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F92" t="s">
         <v>43</v>
       </c>
       <c r="J92" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M92" t="s">
         <v>36</v>
@@ -8505,16 +8544,16 @@
         <v>307</v>
       </c>
       <c r="E93" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F93" t="s">
         <v>43</v>
       </c>
       <c r="J93" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M93" t="s">
         <v>36</v>
@@ -8546,16 +8585,16 @@
         <v>309</v>
       </c>
       <c r="E94" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="F94" t="s">
         <v>43</v>
       </c>
       <c r="J94" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M94" t="s">
         <v>36</v>
@@ -8587,16 +8626,16 @@
         <v>311</v>
       </c>
       <c r="E95" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F95" t="s">
         <v>43</v>
       </c>
       <c r="J95" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M95" t="s">
         <v>36</v>
@@ -8628,16 +8667,16 @@
         <v>313</v>
       </c>
       <c r="E96" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F96" t="s">
         <v>43</v>
       </c>
       <c r="J96" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M96" t="s">
         <v>36</v>
@@ -8669,16 +8708,16 @@
         <v>315</v>
       </c>
       <c r="E97" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F97" t="s">
         <v>43</v>
       </c>
       <c r="J97" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M97" t="s">
         <v>36</v>
@@ -8710,16 +8749,16 @@
         <v>317</v>
       </c>
       <c r="E98" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="F98" t="s">
         <v>43</v>
       </c>
       <c r="J98" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L98" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M98" t="s">
         <v>36</v>
@@ -8751,16 +8790,16 @@
         <v>319</v>
       </c>
       <c r="E99" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F99" t="s">
         <v>43</v>
       </c>
       <c r="J99" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L99" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M99" t="s">
         <v>36</v>
@@ -8792,16 +8831,16 @@
         <v>321</v>
       </c>
       <c r="E100" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F100" t="s">
         <v>43</v>
       </c>
       <c r="J100" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L100" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M100" t="s">
         <v>36</v>
@@ -8827,22 +8866,22 @@
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D101" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E101" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="F101" t="s">
         <v>43</v>
       </c>
       <c r="J101" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="L101" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M101" t="s">
         <v>545</v>
@@ -8892,16 +8931,16 @@
         <v>325</v>
       </c>
       <c r="E102" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="F102" t="s">
         <v>43</v>
       </c>
       <c r="J102" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L102" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M102" t="s">
         <v>419</v>
@@ -8948,19 +8987,19 @@
         <v>329</v>
       </c>
       <c r="D103" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E103" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="F103" t="s">
         <v>43</v>
       </c>
       <c r="J103" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L103" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M103" t="s">
         <v>420</v>
@@ -9004,22 +9043,22 @@
         <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D104" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E104" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="F104" t="s">
         <v>43</v>
       </c>
       <c r="J104" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="L104" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>421</v>
@@ -9063,7 +9102,7 @@
         <v>22</v>
       </c>
       <c r="C105" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D105" t="s">
         <v>337</v>
@@ -9075,10 +9114,10 @@
         <v>43</v>
       </c>
       <c r="J105" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L105" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>421</v>
@@ -9122,7 +9161,7 @@
         <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D106" t="s">
         <v>338</v>
@@ -9134,10 +9173,10 @@
         <v>43</v>
       </c>
       <c r="J106" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L106" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>421</v>
@@ -9181,19 +9220,19 @@
         <v>22</v>
       </c>
       <c r="C107" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D107" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E107" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="F107" t="s">
         <v>43</v>
       </c>
       <c r="J107" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="M107" t="s">
         <v>36</v>
@@ -9219,19 +9258,19 @@
         <v>22</v>
       </c>
       <c r="C108" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D108" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E108" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="F108" t="s">
         <v>43</v>
       </c>
       <c r="J108" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="M108" t="s">
         <v>36</v>
@@ -9257,19 +9296,19 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D109" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E109" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="F109" t="s">
         <v>43</v>
       </c>
       <c r="J109" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="M109" t="s">
         <v>36</v>
@@ -9295,19 +9334,19 @@
         <v>22</v>
       </c>
       <c r="C110" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D110" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E110" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F110" t="s">
         <v>43</v>
       </c>
       <c r="J110" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" t="s">
@@ -9334,19 +9373,19 @@
         <v>22</v>
       </c>
       <c r="C111" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D111" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E111" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="F111" t="s">
         <v>43</v>
       </c>
       <c r="J111" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="M111" t="s">
         <v>36</v>
@@ -9372,19 +9411,19 @@
         <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D112" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E112" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="F112" t="s">
         <v>43</v>
       </c>
       <c r="J112" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L112" s="1"/>
       <c r="M112" t="s">
@@ -9429,19 +9468,19 @@
         <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D113" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E113" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="F113" t="s">
         <v>43</v>
       </c>
       <c r="J113" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L113" s="1"/>
       <c r="M113" t="s">
@@ -9468,19 +9507,19 @@
         <v>361</v>
       </c>
       <c r="C114" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D114" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E114" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F114" t="s">
         <v>23</v>
       </c>
       <c r="J114" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="M114" t="s">
         <v>24</v>
@@ -9518,13 +9557,13 @@
         <v>35</v>
       </c>
       <c r="E115" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F115" t="s">
         <v>23</v>
       </c>
       <c r="J115" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="M115" t="s">
         <v>36</v>
@@ -9556,13 +9595,13 @@
         <v>40</v>
       </c>
       <c r="E116" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F116" t="s">
         <v>23</v>
       </c>
       <c r="J116" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="M116" t="s">
         <v>36</v>
@@ -9594,13 +9633,13 @@
         <v>42</v>
       </c>
       <c r="E117" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F117" t="s">
         <v>43</v>
       </c>
       <c r="J117" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M117" t="s">
         <v>36</v>
@@ -9629,7 +9668,7 @@
         <v>44</v>
       </c>
       <c r="D118" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E118" t="s">
         <v>45</v>
@@ -9641,10 +9680,10 @@
         <v>47</v>
       </c>
       <c r="J118" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="K118" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M118" t="s">
         <v>425</v>
@@ -9691,7 +9730,7 @@
         <v>43</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M119" t="s">
         <v>54</v>
@@ -9732,7 +9771,7 @@
         <v>61</v>
       </c>
       <c r="E120" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F120" t="s">
         <v>43</v>
@@ -9741,10 +9780,10 @@
         <v>62</v>
       </c>
       <c r="J120" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K120" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="M120" t="s">
         <v>427</v>
@@ -9788,25 +9827,25 @@
         <v>361</v>
       </c>
       <c r="C121" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D121" t="s">
         <v>69</v>
       </c>
       <c r="E121" t="s">
+        <v>576</v>
+      </c>
+      <c r="F121" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" t="s">
+        <v>577</v>
+      </c>
+      <c r="K121" t="s">
+        <v>578</v>
+      </c>
+      <c r="L121" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="F121" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" t="s">
-        <v>580</v>
-      </c>
-      <c r="K121" t="s">
-        <v>581</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>582</v>
       </c>
       <c r="M121" t="s">
         <v>36</v>
@@ -9832,7 +9871,7 @@
         <v>361</v>
       </c>
       <c r="C122" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D122" t="s">
         <v>72</v>
@@ -9844,13 +9883,13 @@
         <v>43</v>
       </c>
       <c r="J122" t="s">
+        <v>577</v>
+      </c>
+      <c r="K122" t="s">
+        <v>578</v>
+      </c>
+      <c r="L122" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="K122" t="s">
-        <v>581</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="M122" t="s">
         <v>36</v>
@@ -9882,16 +9921,16 @@
         <v>75</v>
       </c>
       <c r="E123" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F123" t="s">
         <v>43</v>
       </c>
       <c r="J123" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L123" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="M123" t="s">
         <v>428</v>
@@ -9950,13 +9989,13 @@
         <v>43</v>
       </c>
       <c r="J124" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="K124" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M124" t="s">
         <v>428</v>
@@ -10006,10 +10045,10 @@
         <v>87</v>
       </c>
       <c r="D125" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E125" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F125" t="s">
         <v>88</v>
@@ -10082,16 +10121,16 @@
         <v>94</v>
       </c>
       <c r="E127" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F127" t="s">
         <v>43</v>
       </c>
       <c r="J127" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="M127" t="s">
         <v>428</v>
@@ -10144,13 +10183,13 @@
         <v>97</v>
       </c>
       <c r="E128" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F128" t="s">
         <v>43</v>
       </c>
       <c r="L128" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="M128" t="s">
         <v>429</v>
@@ -10197,22 +10236,22 @@
         <v>103</v>
       </c>
       <c r="D129" t="s">
+        <v>593</v>
+      </c>
+      <c r="E129" t="s">
+        <v>594</v>
+      </c>
+      <c r="F129" t="s">
+        <v>43</v>
+      </c>
+      <c r="J129" t="s">
+        <v>595</v>
+      </c>
+      <c r="K129" t="s">
         <v>596</v>
       </c>
-      <c r="E129" t="s">
+      <c r="L129" t="s">
         <v>597</v>
-      </c>
-      <c r="F129" t="s">
-        <v>43</v>
-      </c>
-      <c r="J129" t="s">
-        <v>598</v>
-      </c>
-      <c r="K129" t="s">
-        <v>599</v>
-      </c>
-      <c r="L129" t="s">
-        <v>600</v>
       </c>
       <c r="M129" t="s">
         <v>36</v>
@@ -10238,10 +10277,10 @@
         <v>361</v>
       </c>
       <c r="C130" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D130" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E130" t="s">
         <v>104</v>
@@ -10253,10 +10292,10 @@
         <v>105</v>
       </c>
       <c r="J130" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K130" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M130" t="s">
         <v>430</v>
@@ -10303,19 +10342,19 @@
         <v>361</v>
       </c>
       <c r="C131" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D131" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E131" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F131" t="s">
         <v>43</v>
       </c>
       <c r="L131" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M131" t="s">
         <v>430</v>
@@ -10341,10 +10380,10 @@
         <v>361</v>
       </c>
       <c r="C132" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D132" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E132" t="s">
         <v>110</v>
@@ -10356,10 +10395,10 @@
         <v>111</v>
       </c>
       <c r="J132" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K132" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M132" t="s">
         <v>432</v>
@@ -10406,19 +10445,19 @@
         <v>361</v>
       </c>
       <c r="C133" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D133" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E133" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F133" t="s">
         <v>43</v>
       </c>
       <c r="L133" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M133" t="s">
         <v>432</v>
@@ -10444,13 +10483,13 @@
         <v>361</v>
       </c>
       <c r="C134" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D134" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E134" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="F134" t="s">
         <v>88</v>
@@ -10459,14 +10498,14 @@
         <v>115</v>
       </c>
       <c r="J134" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K134" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="L134" s="1"/>
       <c r="M134" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="N134" t="s">
         <v>116</v>
@@ -10510,13 +10549,13 @@
         <v>361</v>
       </c>
       <c r="C135" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D135" t="s">
         <v>119</v>
       </c>
       <c r="E135" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F135" t="s">
         <v>88</v>
@@ -10525,10 +10564,10 @@
         <v>105</v>
       </c>
       <c r="J135" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K135" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M135" t="s">
         <v>533</v>
@@ -10575,19 +10614,19 @@
         <v>361</v>
       </c>
       <c r="C136" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D136" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E136" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F136" t="s">
         <v>43</v>
       </c>
       <c r="L136" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M136" t="s">
         <v>533</v>
@@ -10631,13 +10670,13 @@
         <v>361</v>
       </c>
       <c r="C137" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D137" t="s">
         <v>125</v>
       </c>
       <c r="E137" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F137" t="s">
         <v>88</v>
@@ -10687,13 +10726,13 @@
         <v>361</v>
       </c>
       <c r="C138" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D138" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E138" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F138" t="s">
         <v>23</v>
@@ -10722,13 +10761,13 @@
         <v>361</v>
       </c>
       <c r="C139" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D139" t="s">
         <v>131</v>
       </c>
       <c r="E139" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F139" t="s">
         <v>88</v>
@@ -10737,10 +10776,10 @@
         <v>132</v>
       </c>
       <c r="J139" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K139" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M139" t="s">
         <v>437</v>
@@ -10773,7 +10812,7 @@
         <v>50</v>
       </c>
       <c r="Z139" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="140" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
@@ -10784,13 +10823,13 @@
         <v>361</v>
       </c>
       <c r="C140" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D140" t="s">
         <v>136</v>
       </c>
       <c r="E140" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F140" t="s">
         <v>88</v>
@@ -10799,10 +10838,10 @@
         <v>132</v>
       </c>
       <c r="J140" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K140" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M140" t="s">
         <v>438</v>
@@ -10846,13 +10885,13 @@
         <v>361</v>
       </c>
       <c r="C141" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D141" t="s">
         <v>139</v>
       </c>
       <c r="E141" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="F141" t="s">
         <v>88</v>
@@ -10861,10 +10900,10 @@
         <v>140</v>
       </c>
       <c r="J141" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K141" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="M141" t="s">
         <v>36</v>
@@ -10890,13 +10929,13 @@
         <v>361</v>
       </c>
       <c r="C142" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D142" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E142" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F142" t="s">
         <v>88</v>
@@ -10905,10 +10944,10 @@
         <v>141</v>
       </c>
       <c r="J142" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="K142" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M142" t="s">
         <v>36</v>
@@ -10937,16 +10976,16 @@
         <v>142</v>
       </c>
       <c r="D143" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E143" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F143" t="s">
         <v>43</v>
       </c>
       <c r="L143" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="M143" t="s">
         <v>36</v>
@@ -10972,13 +11011,13 @@
         <v>361</v>
       </c>
       <c r="C144" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D144" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E144" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F144" t="s">
         <v>88</v>
@@ -11011,13 +11050,13 @@
         <v>361</v>
       </c>
       <c r="C145" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D145" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E145" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F145" t="s">
         <v>88</v>
@@ -11049,7 +11088,7 @@
         <v>361</v>
       </c>
       <c r="C146" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D146" t="s">
         <v>145</v>
@@ -11100,10 +11139,10 @@
         <v>149</v>
       </c>
       <c r="D147" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E147" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F147" t="s">
         <v>88</v>
@@ -11147,10 +11186,10 @@
         <v>153</v>
       </c>
       <c r="D148" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E148" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F148" t="s">
         <v>88</v>
@@ -11194,10 +11233,10 @@
         <v>157</v>
       </c>
       <c r="D149" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E149" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F149" t="s">
         <v>88</v>
@@ -11206,7 +11245,7 @@
         <v>146</v>
       </c>
       <c r="J149" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="L149" s="1"/>
       <c r="M149" s="1" t="s">
@@ -11236,7 +11275,7 @@
         <v>361</v>
       </c>
       <c r="C150" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D150" t="s">
         <v>159</v>
@@ -11284,13 +11323,13 @@
         <v>361</v>
       </c>
       <c r="C151" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D151" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E151" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F151" t="s">
         <v>88</v>
@@ -11335,10 +11374,10 @@
         <v>166</v>
       </c>
       <c r="D152" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E152" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F152" t="s">
         <v>88</v>
@@ -11347,10 +11386,10 @@
         <v>167</v>
       </c>
       <c r="J152" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K152" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="M152" t="s">
         <v>36</v>
@@ -11379,19 +11418,19 @@
         <v>168</v>
       </c>
       <c r="D153" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E153" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F153" t="s">
         <v>43</v>
       </c>
       <c r="K153" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="L153" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M153" t="s">
         <v>36</v>
@@ -11420,10 +11459,10 @@
         <v>169</v>
       </c>
       <c r="D154" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E154" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F154" t="s">
         <v>88</v>
@@ -11432,10 +11471,10 @@
         <v>167</v>
       </c>
       <c r="J154" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K154" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="L154" s="1"/>
       <c r="M154" t="s">
@@ -11465,22 +11504,22 @@
         <v>170</v>
       </c>
       <c r="D155" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E155" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F155" t="s">
         <v>43</v>
       </c>
       <c r="J155" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="K155" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M155" t="s">
         <v>447</v>
@@ -11521,7 +11560,7 @@
         <v>361</v>
       </c>
       <c r="C156" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D156" t="s">
         <v>176</v>
@@ -11563,10 +11602,10 @@
         <v>178</v>
       </c>
       <c r="D157" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E157" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F157" t="s">
         <v>88</v>
@@ -11575,10 +11614,10 @@
         <v>179</v>
       </c>
       <c r="J157" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K157" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="L157" s="1"/>
       <c r="M157" t="s">
@@ -11620,16 +11659,16 @@
         <v>183</v>
       </c>
       <c r="D158" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E158" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F158" t="s">
         <v>43</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="M158" t="s">
         <v>36</v>
@@ -11667,13 +11706,13 @@
         <v>43</v>
       </c>
       <c r="J159" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="K159" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M159" t="s">
         <v>536</v>
@@ -11729,10 +11768,10 @@
         <v>43</v>
       </c>
       <c r="K160" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="M160" t="s">
         <v>36</v>
@@ -11779,10 +11818,10 @@
         <v>193</v>
       </c>
       <c r="D161" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E161" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F161" t="s">
         <v>88</v>
@@ -11791,10 +11830,10 @@
         <v>194</v>
       </c>
       <c r="J161" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K161" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L161" s="1"/>
       <c r="M161" t="s">
@@ -11892,10 +11931,10 @@
         <v>43</v>
       </c>
       <c r="J163" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="M163" t="s">
         <v>449</v>
@@ -11942,19 +11981,19 @@
         <v>207</v>
       </c>
       <c r="D164" t="s">
+        <v>655</v>
+      </c>
+      <c r="E164" t="s">
+        <v>656</v>
+      </c>
+      <c r="F164" t="s">
+        <v>43</v>
+      </c>
+      <c r="K164" t="s">
+        <v>657</v>
+      </c>
+      <c r="L164" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="E164" t="s">
-        <v>659</v>
-      </c>
-      <c r="F164" t="s">
-        <v>43</v>
-      </c>
-      <c r="K164" t="s">
-        <v>660</v>
-      </c>
-      <c r="L164" s="1" t="s">
-        <v>661</v>
       </c>
       <c r="M164" t="s">
         <v>450</v>
@@ -11998,7 +12037,7 @@
         <v>361</v>
       </c>
       <c r="C165" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D165" t="s">
         <v>213</v>
@@ -12013,7 +12052,7 @@
         <v>214</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M165" t="s">
         <v>36</v>
@@ -12039,19 +12078,19 @@
         <v>361</v>
       </c>
       <c r="C166" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D166" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E166" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F166" t="s">
         <v>43</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M166" t="s">
         <v>451</v>
@@ -12098,19 +12137,19 @@
         <v>361</v>
       </c>
       <c r="C167" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D167" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E167" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F167" t="s">
         <v>43</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M167" t="s">
         <v>36</v>
@@ -12136,19 +12175,19 @@
         <v>361</v>
       </c>
       <c r="C168" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D168" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E168" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="F168" t="s">
         <v>43</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="M168" t="s">
         <v>452</v>
@@ -12198,7 +12237,7 @@
         <v>226</v>
       </c>
       <c r="D169" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E169" t="s">
         <v>227</v>
@@ -12210,7 +12249,7 @@
         <v>214</v>
       </c>
       <c r="L169" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M169" t="s">
         <v>36</v>
@@ -12239,7 +12278,7 @@
         <v>228</v>
       </c>
       <c r="D170" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E170" t="s">
         <v>229</v>
@@ -12251,7 +12290,7 @@
         <v>214</v>
       </c>
       <c r="L170" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M170" t="s">
         <v>36</v>
@@ -12277,13 +12316,13 @@
         <v>361</v>
       </c>
       <c r="C171" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D171" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E171" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F171" t="s">
         <v>88</v>
@@ -12337,19 +12376,19 @@
         <v>361</v>
       </c>
       <c r="C172" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D172" t="s">
         <v>234</v>
       </c>
       <c r="E172" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F172" t="s">
         <v>43</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="M172" t="s">
         <v>456</v>
@@ -12393,22 +12432,22 @@
         <v>361</v>
       </c>
       <c r="C173" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D173" t="s">
+        <v>670</v>
+      </c>
+      <c r="E173" t="s">
+        <v>671</v>
+      </c>
+      <c r="F173" t="s">
+        <v>43</v>
+      </c>
+      <c r="K173" t="s">
+        <v>672</v>
+      </c>
+      <c r="L173" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="E173" t="s">
-        <v>674</v>
-      </c>
-      <c r="F173" t="s">
-        <v>43</v>
-      </c>
-      <c r="K173" t="s">
-        <v>675</v>
-      </c>
-      <c r="L173" s="1" t="s">
-        <v>676</v>
       </c>
       <c r="M173" t="s">
         <v>36</v>
@@ -12434,7 +12473,7 @@
         <v>361</v>
       </c>
       <c r="C174" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D174" t="s">
         <v>344</v>
@@ -12446,10 +12485,10 @@
         <v>43</v>
       </c>
       <c r="K174" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="M174" t="s">
         <v>36</v>
@@ -12475,25 +12514,25 @@
         <v>361</v>
       </c>
       <c r="C175" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D175" t="s">
         <v>346</v>
       </c>
       <c r="E175" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F175" t="s">
         <v>43</v>
       </c>
       <c r="J175" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="K175" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M175" t="s">
         <v>36</v>
@@ -12519,22 +12558,22 @@
         <v>361</v>
       </c>
       <c r="C176" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D176" t="s">
         <v>347</v>
       </c>
       <c r="E176" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F176" t="s">
         <v>43</v>
       </c>
       <c r="J176" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M176" t="s">
         <v>477</v>
@@ -12578,25 +12617,25 @@
         <v>361</v>
       </c>
       <c r="C177" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D177" t="s">
         <v>353</v>
       </c>
       <c r="E177" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F177" t="s">
         <v>43</v>
       </c>
       <c r="J177" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="K177" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M177" t="s">
         <v>478</v>
@@ -12643,23 +12682,23 @@
         <v>361</v>
       </c>
       <c r="C178" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D178" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E178" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F178" t="s">
         <v>88</v>
       </c>
       <c r="J178" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="L178" s="1"/>
       <c r="M178" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="W178" t="s">
         <v>31</v>
@@ -12671,10 +12710,10 @@
         <v>50</v>
       </c>
       <c r="Z178" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="179" spans="1:26" ht="270" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="179" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>66</v>
       </c>
@@ -12682,13 +12721,13 @@
         <v>361</v>
       </c>
       <c r="C179" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D179" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E179" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F179" t="s">
         <v>43</v>
@@ -12698,7 +12737,7 @@
       </c>
       <c r="L179" s="1"/>
       <c r="M179" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="W179" t="s">
         <v>31</v>
@@ -12710,7 +12749,7 @@
         <v>50</v>
       </c>
       <c r="Z179" s="1" t="s">
-        <v>549</v>
+        <v>828</v>
       </c>
     </row>
     <row r="180" spans="1:26" ht="390" x14ac:dyDescent="0.25">
@@ -12733,10 +12772,10 @@
         <v>43</v>
       </c>
       <c r="K180" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="M180" t="s">
         <v>458</v>
@@ -12786,22 +12825,22 @@
         <v>244</v>
       </c>
       <c r="D181" t="s">
+        <v>688</v>
+      </c>
+      <c r="E181" t="s">
+        <v>689</v>
+      </c>
+      <c r="F181" t="s">
+        <v>43</v>
+      </c>
+      <c r="J181" t="s">
+        <v>690</v>
+      </c>
+      <c r="K181" t="s">
         <v>691</v>
       </c>
-      <c r="E181" t="s">
+      <c r="L181" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="F181" t="s">
-        <v>43</v>
-      </c>
-      <c r="J181" t="s">
-        <v>693</v>
-      </c>
-      <c r="K181" t="s">
-        <v>694</v>
-      </c>
-      <c r="L181" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="M181" s="1" t="s">
         <v>459</v>
@@ -12851,22 +12890,22 @@
         <v>251</v>
       </c>
       <c r="D182" t="s">
+        <v>693</v>
+      </c>
+      <c r="E182" t="s">
+        <v>694</v>
+      </c>
+      <c r="F182" t="s">
+        <v>43</v>
+      </c>
+      <c r="I182" t="s">
+        <v>695</v>
+      </c>
+      <c r="J182" t="s">
         <v>696</v>
       </c>
-      <c r="E182" t="s">
-        <v>697</v>
-      </c>
-      <c r="F182" t="s">
-        <v>43</v>
-      </c>
-      <c r="I182" t="s">
-        <v>698</v>
-      </c>
-      <c r="J182" t="s">
-        <v>699</v>
-      </c>
       <c r="L182" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M182" t="s">
         <v>461</v>
@@ -12916,22 +12955,22 @@
         <v>256</v>
       </c>
       <c r="D183" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E183" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F183" t="s">
         <v>43</v>
       </c>
       <c r="I183" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="J183" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M183" t="s">
         <v>461</v>
@@ -12978,22 +13017,22 @@
         <v>259</v>
       </c>
       <c r="D184" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E184" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F184" t="s">
         <v>43</v>
       </c>
       <c r="I184" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="J184" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M184" t="s">
         <v>462</v>
@@ -13040,22 +13079,22 @@
         <v>262</v>
       </c>
       <c r="D185" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E185" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F185" t="s">
         <v>43</v>
       </c>
       <c r="I185" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="J185" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M185" t="s">
         <v>463</v>
@@ -13099,25 +13138,25 @@
         <v>361</v>
       </c>
       <c r="C186" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D186" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E186" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F186" t="s">
         <v>43</v>
       </c>
       <c r="I186" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="J186" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M186" s="1" t="s">
         <v>459</v>
@@ -13161,25 +13200,25 @@
         <v>361</v>
       </c>
       <c r="C187" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D187" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E187" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F187" t="s">
         <v>43</v>
       </c>
       <c r="I187" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="J187" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M187" t="s">
         <v>36</v>
@@ -13208,25 +13247,25 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
+        <v>712</v>
+      </c>
+      <c r="E188" t="s">
+        <v>713</v>
+      </c>
+      <c r="F188" t="s">
+        <v>43</v>
+      </c>
+      <c r="I188" t="s">
+        <v>714</v>
+      </c>
+      <c r="J188" t="s">
         <v>715</v>
       </c>
-      <c r="E188" t="s">
+      <c r="K188" t="s">
         <v>716</v>
       </c>
-      <c r="F188" t="s">
-        <v>43</v>
-      </c>
-      <c r="I188" t="s">
-        <v>717</v>
-      </c>
-      <c r="J188" t="s">
-        <v>718</v>
-      </c>
-      <c r="K188" t="s">
-        <v>719</v>
-      </c>
       <c r="L188" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M188" t="s">
         <v>464</v>
@@ -13273,22 +13312,22 @@
         <v>269</v>
       </c>
       <c r="D189" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E189" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F189" t="s">
         <v>43</v>
       </c>
       <c r="I189" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="J189" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>465</v>
@@ -13317,19 +13356,19 @@
         <v>270</v>
       </c>
       <c r="D190" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E190" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F190" t="s">
         <v>43</v>
       </c>
       <c r="J190" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M190" s="1" t="s">
         <v>466</v>
@@ -13376,28 +13415,28 @@
         <v>361</v>
       </c>
       <c r="C191" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D191" t="s">
+        <v>723</v>
+      </c>
+      <c r="E191" t="s">
+        <v>724</v>
+      </c>
+      <c r="F191" t="s">
+        <v>43</v>
+      </c>
+      <c r="I191" t="s">
+        <v>725</v>
+      </c>
+      <c r="J191" t="s">
+        <v>722</v>
+      </c>
+      <c r="K191" t="s">
         <v>726</v>
       </c>
-      <c r="E191" t="s">
-        <v>727</v>
-      </c>
-      <c r="F191" t="s">
-        <v>43</v>
-      </c>
-      <c r="I191" t="s">
-        <v>728</v>
-      </c>
-      <c r="J191" t="s">
-        <v>725</v>
-      </c>
-      <c r="K191" t="s">
-        <v>729</v>
-      </c>
       <c r="L191" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M191" t="s">
         <v>468</v>
@@ -13456,10 +13495,10 @@
         <v>43</v>
       </c>
       <c r="K192" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="M192" t="s">
         <v>468</v>
@@ -13512,19 +13551,19 @@
         <v>283</v>
       </c>
       <c r="E193" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F193" t="s">
         <v>43</v>
       </c>
       <c r="J193" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="K193" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M193" t="s">
         <v>469</v>
@@ -13574,16 +13613,16 @@
         <v>287</v>
       </c>
       <c r="E194" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F194" t="s">
         <v>43</v>
       </c>
       <c r="J194" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M194" t="s">
         <v>36</v>
@@ -13615,16 +13654,16 @@
         <v>289</v>
       </c>
       <c r="E195" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F195" t="s">
         <v>43</v>
       </c>
       <c r="J195" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M195" t="s">
         <v>36</v>
@@ -13656,16 +13695,16 @@
         <v>291</v>
       </c>
       <c r="E196" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="F196" t="s">
         <v>43</v>
       </c>
       <c r="J196" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M196" t="s">
         <v>36</v>
@@ -13694,19 +13733,19 @@
         <v>292</v>
       </c>
       <c r="D197" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E197" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F197" t="s">
         <v>43</v>
       </c>
       <c r="J197" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M197" t="s">
         <v>36</v>
@@ -13738,16 +13777,16 @@
         <v>294</v>
       </c>
       <c r="E198" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F198" t="s">
         <v>43</v>
       </c>
       <c r="J198" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M198" t="s">
         <v>36</v>
@@ -13776,19 +13815,19 @@
         <v>295</v>
       </c>
       <c r="D199" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E199" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="F199" t="s">
         <v>43</v>
       </c>
       <c r="J199" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M199" t="s">
         <v>36</v>
@@ -13820,16 +13859,16 @@
         <v>297</v>
       </c>
       <c r="E200" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F200" t="s">
         <v>43</v>
       </c>
       <c r="J200" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M200" t="s">
         <v>36</v>
@@ -13861,16 +13900,16 @@
         <v>299</v>
       </c>
       <c r="E201" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="F201" t="s">
         <v>43</v>
       </c>
       <c r="J201" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M201" t="s">
         <v>36</v>
@@ -13902,16 +13941,16 @@
         <v>301</v>
       </c>
       <c r="E202" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="F202" t="s">
         <v>43</v>
       </c>
       <c r="J202" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M202" t="s">
         <v>36</v>
@@ -13943,16 +13982,16 @@
         <v>303</v>
       </c>
       <c r="E203" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F203" t="s">
         <v>43</v>
       </c>
       <c r="J203" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M203" t="s">
         <v>36</v>
@@ -13984,16 +14023,16 @@
         <v>305</v>
       </c>
       <c r="E204" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F204" t="s">
         <v>43</v>
       </c>
       <c r="J204" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M204" t="s">
         <v>36</v>
@@ -14025,16 +14064,16 @@
         <v>307</v>
       </c>
       <c r="E205" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F205" t="s">
         <v>43</v>
       </c>
       <c r="J205" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M205" t="s">
         <v>36</v>
@@ -14066,16 +14105,16 @@
         <v>309</v>
       </c>
       <c r="E206" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="F206" t="s">
         <v>43</v>
       </c>
       <c r="J206" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M206" t="s">
         <v>36</v>
@@ -14107,16 +14146,16 @@
         <v>311</v>
       </c>
       <c r="E207" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F207" t="s">
         <v>43</v>
       </c>
       <c r="J207" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M207" t="s">
         <v>36</v>
@@ -14148,16 +14187,16 @@
         <v>313</v>
       </c>
       <c r="E208" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F208" t="s">
         <v>43</v>
       </c>
       <c r="J208" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M208" t="s">
         <v>36</v>
@@ -14189,16 +14228,16 @@
         <v>315</v>
       </c>
       <c r="E209" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F209" t="s">
         <v>43</v>
       </c>
       <c r="J209" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M209" t="s">
         <v>36</v>
@@ -14230,16 +14269,16 @@
         <v>317</v>
       </c>
       <c r="E210" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="F210" t="s">
         <v>43</v>
       </c>
       <c r="J210" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L210" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M210" t="s">
         <v>36</v>
@@ -14271,16 +14310,16 @@
         <v>319</v>
       </c>
       <c r="E211" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F211" t="s">
         <v>43</v>
       </c>
       <c r="J211" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L211" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M211" t="s">
         <v>36</v>
@@ -14312,16 +14351,16 @@
         <v>321</v>
       </c>
       <c r="E212" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F212" t="s">
         <v>43</v>
       </c>
       <c r="J212" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L212" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M212" t="s">
         <v>36</v>
@@ -14347,22 +14386,22 @@
         <v>361</v>
       </c>
       <c r="C213" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D213" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E213" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="F213" t="s">
         <v>43</v>
       </c>
       <c r="J213" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="L213" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M213" t="s">
         <v>470</v>
@@ -14412,16 +14451,16 @@
         <v>325</v>
       </c>
       <c r="E214" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="F214" t="s">
         <v>43</v>
       </c>
       <c r="J214" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L214" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M214" t="s">
         <v>471</v>
@@ -14468,19 +14507,19 @@
         <v>329</v>
       </c>
       <c r="D215" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E215" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="F215" t="s">
         <v>43</v>
       </c>
       <c r="J215" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L215" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M215" t="s">
         <v>472</v>
@@ -14524,22 +14563,22 @@
         <v>361</v>
       </c>
       <c r="C216" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D216" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E216" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="F216" t="s">
         <v>43</v>
       </c>
       <c r="J216" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="L216" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M216" s="1" t="s">
         <v>473</v>
@@ -14583,7 +14622,7 @@
         <v>361</v>
       </c>
       <c r="C217" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D217" t="s">
         <v>337</v>
@@ -14595,10 +14634,10 @@
         <v>43</v>
       </c>
       <c r="J217" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L217" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M217" s="1" t="s">
         <v>473</v>
@@ -14642,7 +14681,7 @@
         <v>361</v>
       </c>
       <c r="C218" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D218" t="s">
         <v>338</v>
@@ -14654,10 +14693,10 @@
         <v>43</v>
       </c>
       <c r="J218" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L218" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>473</v>
@@ -14701,19 +14740,19 @@
         <v>361</v>
       </c>
       <c r="C219" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D219" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E219" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="F219" t="s">
         <v>43</v>
       </c>
       <c r="J219" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="M219" t="s">
         <v>36</v>
@@ -14739,19 +14778,19 @@
         <v>361</v>
       </c>
       <c r="C220" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D220" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E220" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="F220" t="s">
         <v>43</v>
       </c>
       <c r="J220" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="M220" t="s">
         <v>36</v>
@@ -14777,19 +14816,19 @@
         <v>361</v>
       </c>
       <c r="C221" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D221" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E221" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="F221" t="s">
         <v>43</v>
       </c>
       <c r="J221" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="M221" t="s">
         <v>36</v>
@@ -14815,19 +14854,19 @@
         <v>361</v>
       </c>
       <c r="C222" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D222" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E222" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F222" t="s">
         <v>43</v>
       </c>
       <c r="J222" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L222" s="1"/>
       <c r="M222" t="s">
@@ -14854,19 +14893,19 @@
         <v>361</v>
       </c>
       <c r="C223" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D223" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E223" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="F223" t="s">
         <v>43</v>
       </c>
       <c r="J223" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="M223" t="s">
         <v>36</v>
@@ -14892,23 +14931,23 @@
         <v>361</v>
       </c>
       <c r="C224" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D224" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E224" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="F224" t="s">
         <v>43</v>
       </c>
       <c r="J224" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L224" s="1"/>
       <c r="M224" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="N224" t="s">
         <v>339</v>
@@ -14949,19 +14988,19 @@
         <v>361</v>
       </c>
       <c r="C225" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D225" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E225" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="F225" t="s">
         <v>43</v>
       </c>
       <c r="J225" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L225" s="1"/>
       <c r="M225" t="s">
@@ -14988,19 +15027,19 @@
         <v>368</v>
       </c>
       <c r="C226" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D226" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E226" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F226" t="s">
         <v>23</v>
       </c>
       <c r="J226" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="M226" t="s">
         <v>24</v>
@@ -15038,13 +15077,13 @@
         <v>35</v>
       </c>
       <c r="E227" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F227" t="s">
         <v>23</v>
       </c>
       <c r="J227" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="M227" t="s">
         <v>36</v>
@@ -15076,13 +15115,13 @@
         <v>40</v>
       </c>
       <c r="E228" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F228" t="s">
         <v>23</v>
       </c>
       <c r="J228" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="M228" t="s">
         <v>36</v>
@@ -15114,13 +15153,13 @@
         <v>42</v>
       </c>
       <c r="E229" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F229" t="s">
         <v>43</v>
       </c>
       <c r="J229" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M229" t="s">
         <v>36</v>
@@ -15149,7 +15188,7 @@
         <v>44</v>
       </c>
       <c r="D230" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E230" t="s">
         <v>45</v>
@@ -15161,10 +15200,10 @@
         <v>47</v>
       </c>
       <c r="J230" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="K230" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M230" t="s">
         <v>479</v>
@@ -15211,7 +15250,7 @@
         <v>43</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M231" t="s">
         <v>54</v>
@@ -15252,7 +15291,7 @@
         <v>61</v>
       </c>
       <c r="E232" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F232" t="s">
         <v>43</v>
@@ -15261,10 +15300,10 @@
         <v>62</v>
       </c>
       <c r="J232" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K232" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="M232" t="s">
         <v>481</v>
@@ -15308,25 +15347,25 @@
         <v>368</v>
       </c>
       <c r="C233" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D233" t="s">
         <v>69</v>
       </c>
       <c r="E233" t="s">
+        <v>576</v>
+      </c>
+      <c r="F233" t="s">
+        <v>43</v>
+      </c>
+      <c r="J233" t="s">
+        <v>577</v>
+      </c>
+      <c r="K233" t="s">
+        <v>578</v>
+      </c>
+      <c r="L233" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="F233" t="s">
-        <v>43</v>
-      </c>
-      <c r="J233" t="s">
-        <v>580</v>
-      </c>
-      <c r="K233" t="s">
-        <v>581</v>
-      </c>
-      <c r="L233" s="1" t="s">
-        <v>582</v>
       </c>
       <c r="M233" t="s">
         <v>36</v>
@@ -15352,7 +15391,7 @@
         <v>368</v>
       </c>
       <c r="C234" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D234" t="s">
         <v>72</v>
@@ -15364,13 +15403,13 @@
         <v>43</v>
       </c>
       <c r="J234" t="s">
+        <v>577</v>
+      </c>
+      <c r="K234" t="s">
+        <v>578</v>
+      </c>
+      <c r="L234" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="K234" t="s">
-        <v>581</v>
-      </c>
-      <c r="L234" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="M234" t="s">
         <v>36</v>
@@ -15402,16 +15441,16 @@
         <v>75</v>
       </c>
       <c r="E235" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F235" t="s">
         <v>43</v>
       </c>
       <c r="J235" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L235" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="M235" t="s">
         <v>482</v>
@@ -15470,13 +15509,13 @@
         <v>43</v>
       </c>
       <c r="J236" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="K236" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M236" t="s">
         <v>482</v>
@@ -15526,10 +15565,10 @@
         <v>87</v>
       </c>
       <c r="D237" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E237" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F237" t="s">
         <v>88</v>
@@ -15602,16 +15641,16 @@
         <v>94</v>
       </c>
       <c r="E239" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F239" t="s">
         <v>43</v>
       </c>
       <c r="J239" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="M239" t="s">
         <v>482</v>
@@ -15664,13 +15703,13 @@
         <v>97</v>
       </c>
       <c r="E240" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F240" t="s">
         <v>43</v>
       </c>
       <c r="L240" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="M240" t="s">
         <v>483</v>
@@ -15717,22 +15756,22 @@
         <v>103</v>
       </c>
       <c r="D241" t="s">
+        <v>593</v>
+      </c>
+      <c r="E241" t="s">
+        <v>594</v>
+      </c>
+      <c r="F241" t="s">
+        <v>43</v>
+      </c>
+      <c r="J241" t="s">
+        <v>595</v>
+      </c>
+      <c r="K241" t="s">
         <v>596</v>
       </c>
-      <c r="E241" t="s">
+      <c r="L241" t="s">
         <v>597</v>
-      </c>
-      <c r="F241" t="s">
-        <v>43</v>
-      </c>
-      <c r="J241" t="s">
-        <v>598</v>
-      </c>
-      <c r="K241" t="s">
-        <v>599</v>
-      </c>
-      <c r="L241" t="s">
-        <v>600</v>
       </c>
       <c r="M241" t="s">
         <v>36</v>
@@ -15758,10 +15797,10 @@
         <v>368</v>
       </c>
       <c r="C242" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D242" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E242" t="s">
         <v>104</v>
@@ -15773,10 +15812,10 @@
         <v>105</v>
       </c>
       <c r="J242" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K242" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M242" t="s">
         <v>484</v>
@@ -15823,19 +15862,19 @@
         <v>368</v>
       </c>
       <c r="C243" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D243" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E243" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F243" t="s">
         <v>43</v>
       </c>
       <c r="L243" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M243" t="s">
         <v>484</v>
@@ -15861,10 +15900,10 @@
         <v>368</v>
       </c>
       <c r="C244" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D244" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E244" t="s">
         <v>110</v>
@@ -15876,10 +15915,10 @@
         <v>111</v>
       </c>
       <c r="J244" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K244" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M244" t="s">
         <v>486</v>
@@ -15926,19 +15965,19 @@
         <v>368</v>
       </c>
       <c r="C245" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D245" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E245" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F245" t="s">
         <v>43</v>
       </c>
       <c r="L245" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M245" t="s">
         <v>486</v>
@@ -15964,13 +16003,13 @@
         <v>368</v>
       </c>
       <c r="C246" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D246" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E246" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="F246" t="s">
         <v>88</v>
@@ -15979,14 +16018,14 @@
         <v>115</v>
       </c>
       <c r="J246" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K246" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="L246" s="1"/>
       <c r="M246" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N246" t="s">
         <v>116</v>
@@ -16030,13 +16069,13 @@
         <v>368</v>
       </c>
       <c r="C247" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D247" t="s">
         <v>119</v>
       </c>
       <c r="E247" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F247" t="s">
         <v>88</v>
@@ -16045,10 +16084,10 @@
         <v>105</v>
       </c>
       <c r="J247" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K247" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M247" t="s">
         <v>535</v>
@@ -16095,19 +16134,19 @@
         <v>368</v>
       </c>
       <c r="C248" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D248" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E248" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F248" t="s">
         <v>43</v>
       </c>
       <c r="L248" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M248" t="s">
         <v>535</v>
@@ -16140,7 +16179,7 @@
         <v>50</v>
       </c>
       <c r="Z248" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="249" spans="1:26" x14ac:dyDescent="0.25">
@@ -16151,13 +16190,13 @@
         <v>368</v>
       </c>
       <c r="C249" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D249" t="s">
         <v>125</v>
       </c>
       <c r="E249" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F249" t="s">
         <v>88</v>
@@ -16207,13 +16246,13 @@
         <v>368</v>
       </c>
       <c r="C250" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D250" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E250" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F250" t="s">
         <v>23</v>
@@ -16242,13 +16281,13 @@
         <v>368</v>
       </c>
       <c r="C251" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D251" t="s">
         <v>131</v>
       </c>
       <c r="E251" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F251" t="s">
         <v>88</v>
@@ -16257,10 +16296,10 @@
         <v>132</v>
       </c>
       <c r="J251" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K251" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M251" t="s">
         <v>491</v>
@@ -16293,7 +16332,7 @@
         <v>50</v>
       </c>
       <c r="Z251" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="252" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
@@ -16304,13 +16343,13 @@
         <v>368</v>
       </c>
       <c r="C252" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D252" t="s">
         <v>136</v>
       </c>
       <c r="E252" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F252" t="s">
         <v>88</v>
@@ -16319,10 +16358,10 @@
         <v>132</v>
       </c>
       <c r="J252" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K252" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M252" t="s">
         <v>492</v>
@@ -16366,13 +16405,13 @@
         <v>368</v>
       </c>
       <c r="C253" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D253" t="s">
         <v>139</v>
       </c>
       <c r="E253" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="F253" t="s">
         <v>88</v>
@@ -16381,10 +16420,10 @@
         <v>140</v>
       </c>
       <c r="J253" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K253" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="M253" t="s">
         <v>36</v>
@@ -16410,13 +16449,13 @@
         <v>368</v>
       </c>
       <c r="C254" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D254" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E254" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F254" t="s">
         <v>88</v>
@@ -16425,10 +16464,10 @@
         <v>141</v>
       </c>
       <c r="J254" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="K254" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M254" t="s">
         <v>36</v>
@@ -16457,16 +16496,16 @@
         <v>142</v>
       </c>
       <c r="D255" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E255" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F255" t="s">
         <v>43</v>
       </c>
       <c r="L255" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="M255" t="s">
         <v>36</v>
@@ -16492,13 +16531,13 @@
         <v>368</v>
       </c>
       <c r="C256" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D256" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E256" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F256" t="s">
         <v>88</v>
@@ -16531,13 +16570,13 @@
         <v>368</v>
       </c>
       <c r="C257" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D257" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E257" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F257" t="s">
         <v>88</v>
@@ -16569,7 +16608,7 @@
         <v>368</v>
       </c>
       <c r="C258" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D258" t="s">
         <v>145</v>
@@ -16620,10 +16659,10 @@
         <v>149</v>
       </c>
       <c r="D259" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E259" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F259" t="s">
         <v>88</v>
@@ -16667,10 +16706,10 @@
         <v>153</v>
       </c>
       <c r="D260" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E260" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F260" t="s">
         <v>88</v>
@@ -16714,10 +16753,10 @@
         <v>157</v>
       </c>
       <c r="D261" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E261" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F261" t="s">
         <v>88</v>
@@ -16726,7 +16765,7 @@
         <v>146</v>
       </c>
       <c r="J261" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="L261" s="1"/>
       <c r="M261" s="1" t="s">
@@ -16756,7 +16795,7 @@
         <v>368</v>
       </c>
       <c r="C262" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D262" t="s">
         <v>159</v>
@@ -16804,13 +16843,13 @@
         <v>368</v>
       </c>
       <c r="C263" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D263" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E263" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F263" t="s">
         <v>88</v>
@@ -16855,10 +16894,10 @@
         <v>166</v>
       </c>
       <c r="D264" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E264" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F264" t="s">
         <v>88</v>
@@ -16867,10 +16906,10 @@
         <v>167</v>
       </c>
       <c r="J264" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K264" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="M264" t="s">
         <v>36</v>
@@ -16899,19 +16938,19 @@
         <v>168</v>
       </c>
       <c r="D265" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E265" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F265" t="s">
         <v>43</v>
       </c>
       <c r="K265" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="L265" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M265" t="s">
         <v>36</v>
@@ -16940,10 +16979,10 @@
         <v>169</v>
       </c>
       <c r="D266" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E266" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F266" t="s">
         <v>88</v>
@@ -16952,10 +16991,10 @@
         <v>167</v>
       </c>
       <c r="J266" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K266" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="L266" s="1"/>
       <c r="M266" t="s">
@@ -16985,22 +17024,22 @@
         <v>170</v>
       </c>
       <c r="D267" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E267" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F267" t="s">
         <v>43</v>
       </c>
       <c r="J267" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="K267" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M267" t="s">
         <v>501</v>
@@ -17041,7 +17080,7 @@
         <v>368</v>
       </c>
       <c r="C268" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D268" t="s">
         <v>176</v>
@@ -17083,10 +17122,10 @@
         <v>178</v>
       </c>
       <c r="D269" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E269" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F269" t="s">
         <v>88</v>
@@ -17095,10 +17134,10 @@
         <v>179</v>
       </c>
       <c r="J269" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K269" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="L269" s="1"/>
       <c r="M269" t="s">
@@ -17140,16 +17179,16 @@
         <v>183</v>
       </c>
       <c r="D270" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E270" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F270" t="s">
         <v>43</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="M270" t="s">
         <v>36</v>
@@ -17187,13 +17226,13 @@
         <v>43</v>
       </c>
       <c r="J271" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="K271" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M271" t="s">
         <v>537</v>
@@ -17249,10 +17288,10 @@
         <v>43</v>
       </c>
       <c r="K272" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="M272" t="s">
         <v>36</v>
@@ -17299,10 +17338,10 @@
         <v>193</v>
       </c>
       <c r="D273" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E273" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F273" t="s">
         <v>88</v>
@@ -17311,10 +17350,10 @@
         <v>194</v>
       </c>
       <c r="J273" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K273" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L273" s="1"/>
       <c r="M273" t="s">
@@ -17412,10 +17451,10 @@
         <v>43</v>
       </c>
       <c r="J275" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="M275" t="s">
         <v>503</v>
@@ -17462,19 +17501,19 @@
         <v>207</v>
       </c>
       <c r="D276" t="s">
+        <v>655</v>
+      </c>
+      <c r="E276" t="s">
+        <v>656</v>
+      </c>
+      <c r="F276" t="s">
+        <v>43</v>
+      </c>
+      <c r="K276" t="s">
+        <v>657</v>
+      </c>
+      <c r="L276" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="E276" t="s">
-        <v>659</v>
-      </c>
-      <c r="F276" t="s">
-        <v>43</v>
-      </c>
-      <c r="K276" t="s">
-        <v>660</v>
-      </c>
-      <c r="L276" s="1" t="s">
-        <v>661</v>
       </c>
       <c r="M276" t="s">
         <v>504</v>
@@ -17518,7 +17557,7 @@
         <v>368</v>
       </c>
       <c r="C277" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D277" t="s">
         <v>213</v>
@@ -17533,7 +17572,7 @@
         <v>214</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M277" t="s">
         <v>36</v>
@@ -17559,19 +17598,19 @@
         <v>368</v>
       </c>
       <c r="C278" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D278" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E278" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F278" t="s">
         <v>43</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M278" t="s">
         <v>505</v>
@@ -17618,19 +17657,19 @@
         <v>368</v>
       </c>
       <c r="C279" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D279" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E279" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F279" t="s">
         <v>43</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M279" t="s">
         <v>36</v>
@@ -17656,19 +17695,19 @@
         <v>368</v>
       </c>
       <c r="C280" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D280" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E280" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="F280" t="s">
         <v>43</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="M280" t="s">
         <v>506</v>
@@ -17718,7 +17757,7 @@
         <v>226</v>
       </c>
       <c r="D281" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E281" t="s">
         <v>227</v>
@@ -17730,7 +17769,7 @@
         <v>214</v>
       </c>
       <c r="L281" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M281" t="s">
         <v>36</v>
@@ -17759,7 +17798,7 @@
         <v>228</v>
       </c>
       <c r="D282" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E282" t="s">
         <v>229</v>
@@ -17771,7 +17810,7 @@
         <v>214</v>
       </c>
       <c r="L282" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M282" t="s">
         <v>36</v>
@@ -17797,13 +17836,13 @@
         <v>368</v>
       </c>
       <c r="C283" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D283" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E283" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F283" t="s">
         <v>88</v>
@@ -17857,19 +17896,19 @@
         <v>368</v>
       </c>
       <c r="C284" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D284" t="s">
         <v>234</v>
       </c>
       <c r="E284" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F284" t="s">
         <v>43</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="M284" t="s">
         <v>510</v>
@@ -17913,22 +17952,22 @@
         <v>368</v>
       </c>
       <c r="C285" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D285" t="s">
+        <v>670</v>
+      </c>
+      <c r="E285" t="s">
+        <v>671</v>
+      </c>
+      <c r="F285" t="s">
+        <v>43</v>
+      </c>
+      <c r="K285" t="s">
+        <v>672</v>
+      </c>
+      <c r="L285" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="E285" t="s">
-        <v>674</v>
-      </c>
-      <c r="F285" t="s">
-        <v>43</v>
-      </c>
-      <c r="K285" t="s">
-        <v>675</v>
-      </c>
-      <c r="L285" s="1" t="s">
-        <v>676</v>
       </c>
       <c r="M285" t="s">
         <v>36</v>
@@ -17954,7 +17993,7 @@
         <v>368</v>
       </c>
       <c r="C286" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D286" t="s">
         <v>344</v>
@@ -17966,10 +18005,10 @@
         <v>43</v>
       </c>
       <c r="K286" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="M286" t="s">
         <v>36</v>
@@ -17995,25 +18034,25 @@
         <v>368</v>
       </c>
       <c r="C287" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D287" t="s">
         <v>346</v>
       </c>
       <c r="E287" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F287" t="s">
         <v>43</v>
       </c>
       <c r="J287" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="K287" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M287" t="s">
         <v>36</v>
@@ -18039,22 +18078,22 @@
         <v>368</v>
       </c>
       <c r="C288" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D288" t="s">
         <v>347</v>
       </c>
       <c r="E288" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F288" t="s">
         <v>43</v>
       </c>
       <c r="J288" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M288" t="s">
         <v>531</v>
@@ -18098,25 +18137,25 @@
         <v>368</v>
       </c>
       <c r="C289" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D289" t="s">
         <v>353</v>
       </c>
       <c r="E289" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F289" t="s">
         <v>43</v>
       </c>
       <c r="J289" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="K289" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M289" t="s">
         <v>532</v>
@@ -18163,23 +18202,23 @@
         <v>368</v>
       </c>
       <c r="C290" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D290" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E290" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F290" t="s">
         <v>88</v>
       </c>
       <c r="J290" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="L290" s="1"/>
       <c r="M290" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="W290" t="s">
         <v>31</v>
@@ -18191,10 +18230,10 @@
         <v>50</v>
       </c>
       <c r="Z290" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="291" spans="1:26" ht="270" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="291" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>66</v>
       </c>
@@ -18202,13 +18241,13 @@
         <v>368</v>
       </c>
       <c r="C291" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D291" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E291" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F291" t="s">
         <v>43</v>
@@ -18218,7 +18257,7 @@
       </c>
       <c r="L291" s="1"/>
       <c r="M291" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="W291" t="s">
         <v>31</v>
@@ -18230,7 +18269,7 @@
         <v>50</v>
       </c>
       <c r="Z291" s="1" t="s">
-        <v>551</v>
+        <v>829</v>
       </c>
     </row>
     <row r="292" spans="1:26" ht="390" x14ac:dyDescent="0.25">
@@ -18253,10 +18292,10 @@
         <v>43</v>
       </c>
       <c r="K292" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="M292" t="s">
         <v>512</v>
@@ -18306,22 +18345,22 @@
         <v>244</v>
       </c>
       <c r="D293" t="s">
+        <v>688</v>
+      </c>
+      <c r="E293" t="s">
+        <v>689</v>
+      </c>
+      <c r="F293" t="s">
+        <v>43</v>
+      </c>
+      <c r="J293" t="s">
+        <v>690</v>
+      </c>
+      <c r="K293" t="s">
         <v>691</v>
       </c>
-      <c r="E293" t="s">
+      <c r="L293" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="F293" t="s">
-        <v>43</v>
-      </c>
-      <c r="J293" t="s">
-        <v>693</v>
-      </c>
-      <c r="K293" t="s">
-        <v>694</v>
-      </c>
-      <c r="L293" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="M293" s="1" t="s">
         <v>513</v>
@@ -18371,22 +18410,22 @@
         <v>251</v>
       </c>
       <c r="D294" t="s">
+        <v>693</v>
+      </c>
+      <c r="E294" t="s">
+        <v>694</v>
+      </c>
+      <c r="F294" t="s">
+        <v>43</v>
+      </c>
+      <c r="I294" t="s">
+        <v>695</v>
+      </c>
+      <c r="J294" t="s">
         <v>696</v>
       </c>
-      <c r="E294" t="s">
-        <v>697</v>
-      </c>
-      <c r="F294" t="s">
-        <v>43</v>
-      </c>
-      <c r="I294" t="s">
-        <v>698</v>
-      </c>
-      <c r="J294" t="s">
-        <v>699</v>
-      </c>
       <c r="L294" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M294" t="s">
         <v>515</v>
@@ -18436,22 +18475,22 @@
         <v>256</v>
       </c>
       <c r="D295" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E295" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F295" t="s">
         <v>43</v>
       </c>
       <c r="I295" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="J295" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M295" t="s">
         <v>515</v>
@@ -18498,22 +18537,22 @@
         <v>259</v>
       </c>
       <c r="D296" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E296" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F296" t="s">
         <v>43</v>
       </c>
       <c r="I296" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="J296" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M296" t="s">
         <v>516</v>
@@ -18560,22 +18599,22 @@
         <v>262</v>
       </c>
       <c r="D297" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E297" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F297" t="s">
         <v>43</v>
       </c>
       <c r="I297" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="J297" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M297" t="s">
         <v>517</v>
@@ -18619,25 +18658,25 @@
         <v>368</v>
       </c>
       <c r="C298" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D298" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E298" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F298" t="s">
         <v>43</v>
       </c>
       <c r="I298" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="J298" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M298" s="1" t="s">
         <v>513</v>
@@ -18681,25 +18720,25 @@
         <v>368</v>
       </c>
       <c r="C299" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D299" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E299" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F299" t="s">
         <v>43</v>
       </c>
       <c r="I299" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="J299" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M299" t="s">
         <v>36</v>
@@ -18728,25 +18767,25 @@
         <v>266</v>
       </c>
       <c r="D300" t="s">
+        <v>712</v>
+      </c>
+      <c r="E300" t="s">
+        <v>713</v>
+      </c>
+      <c r="F300" t="s">
+        <v>43</v>
+      </c>
+      <c r="I300" t="s">
+        <v>714</v>
+      </c>
+      <c r="J300" t="s">
         <v>715</v>
       </c>
-      <c r="E300" t="s">
+      <c r="K300" t="s">
         <v>716</v>
       </c>
-      <c r="F300" t="s">
-        <v>43</v>
-      </c>
-      <c r="I300" t="s">
-        <v>717</v>
-      </c>
-      <c r="J300" t="s">
-        <v>718</v>
-      </c>
-      <c r="K300" t="s">
-        <v>719</v>
-      </c>
       <c r="L300" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M300" t="s">
         <v>518</v>
@@ -18793,22 +18832,22 @@
         <v>269</v>
       </c>
       <c r="D301" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E301" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F301" t="s">
         <v>43</v>
       </c>
       <c r="I301" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="J301" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M301" s="1" t="s">
         <v>519</v>
@@ -18837,19 +18876,19 @@
         <v>270</v>
       </c>
       <c r="D302" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E302" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F302" t="s">
         <v>43</v>
       </c>
       <c r="J302" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M302" s="1" t="s">
         <v>520</v>
@@ -18896,28 +18935,28 @@
         <v>368</v>
       </c>
       <c r="C303" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D303" t="s">
+        <v>723</v>
+      </c>
+      <c r="E303" t="s">
+        <v>724</v>
+      </c>
+      <c r="F303" t="s">
+        <v>43</v>
+      </c>
+      <c r="I303" t="s">
+        <v>725</v>
+      </c>
+      <c r="J303" t="s">
+        <v>722</v>
+      </c>
+      <c r="K303" t="s">
         <v>726</v>
       </c>
-      <c r="E303" t="s">
-        <v>727</v>
-      </c>
-      <c r="F303" t="s">
-        <v>43</v>
-      </c>
-      <c r="I303" t="s">
-        <v>728</v>
-      </c>
-      <c r="J303" t="s">
-        <v>725</v>
-      </c>
-      <c r="K303" t="s">
-        <v>729</v>
-      </c>
       <c r="L303" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M303" t="s">
         <v>522</v>
@@ -18976,10 +19015,10 @@
         <v>43</v>
       </c>
       <c r="K304" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="M304" t="s">
         <v>522</v>
@@ -19032,19 +19071,19 @@
         <v>283</v>
       </c>
       <c r="E305" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F305" t="s">
         <v>43</v>
       </c>
       <c r="J305" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="K305" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M305" t="s">
         <v>523</v>
@@ -19094,16 +19133,16 @@
         <v>287</v>
       </c>
       <c r="E306" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F306" t="s">
         <v>43</v>
       </c>
       <c r="J306" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M306" t="s">
         <v>36</v>
@@ -19135,16 +19174,16 @@
         <v>289</v>
       </c>
       <c r="E307" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F307" t="s">
         <v>43</v>
       </c>
       <c r="J307" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M307" t="s">
         <v>36</v>
@@ -19176,16 +19215,16 @@
         <v>291</v>
       </c>
       <c r="E308" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="F308" t="s">
         <v>43</v>
       </c>
       <c r="J308" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M308" t="s">
         <v>36</v>
@@ -19214,19 +19253,19 @@
         <v>292</v>
       </c>
       <c r="D309" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E309" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="F309" t="s">
         <v>43</v>
       </c>
       <c r="J309" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M309" t="s">
         <v>36</v>
@@ -19258,16 +19297,16 @@
         <v>294</v>
       </c>
       <c r="E310" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F310" t="s">
         <v>43</v>
       </c>
       <c r="J310" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M310" t="s">
         <v>36</v>
@@ -19296,19 +19335,19 @@
         <v>295</v>
       </c>
       <c r="D311" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E311" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="F311" t="s">
         <v>43</v>
       </c>
       <c r="J311" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M311" t="s">
         <v>36</v>
@@ -19340,16 +19379,16 @@
         <v>297</v>
       </c>
       <c r="E312" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F312" t="s">
         <v>43</v>
       </c>
       <c r="J312" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M312" t="s">
         <v>36</v>
@@ -19381,16 +19420,16 @@
         <v>299</v>
       </c>
       <c r="E313" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="F313" t="s">
         <v>43</v>
       </c>
       <c r="J313" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M313" t="s">
         <v>36</v>
@@ -19422,16 +19461,16 @@
         <v>301</v>
       </c>
       <c r="E314" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="F314" t="s">
         <v>43</v>
       </c>
       <c r="J314" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M314" t="s">
         <v>36</v>
@@ -19463,16 +19502,16 @@
         <v>303</v>
       </c>
       <c r="E315" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F315" t="s">
         <v>43</v>
       </c>
       <c r="J315" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M315" t="s">
         <v>36</v>
@@ -19504,16 +19543,16 @@
         <v>305</v>
       </c>
       <c r="E316" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F316" t="s">
         <v>43</v>
       </c>
       <c r="J316" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M316" t="s">
         <v>36</v>
@@ -19545,16 +19584,16 @@
         <v>307</v>
       </c>
       <c r="E317" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F317" t="s">
         <v>43</v>
       </c>
       <c r="J317" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M317" t="s">
         <v>36</v>
@@ -19586,16 +19625,16 @@
         <v>309</v>
       </c>
       <c r="E318" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="F318" t="s">
         <v>43</v>
       </c>
       <c r="J318" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M318" t="s">
         <v>36</v>
@@ -19627,16 +19666,16 @@
         <v>311</v>
       </c>
       <c r="E319" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F319" t="s">
         <v>43</v>
       </c>
       <c r="J319" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M319" t="s">
         <v>36</v>
@@ -19668,16 +19707,16 @@
         <v>313</v>
       </c>
       <c r="E320" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F320" t="s">
         <v>43</v>
       </c>
       <c r="J320" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M320" t="s">
         <v>36</v>
@@ -19709,16 +19748,16 @@
         <v>315</v>
       </c>
       <c r="E321" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F321" t="s">
         <v>43</v>
       </c>
       <c r="J321" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M321" t="s">
         <v>36</v>
@@ -19750,16 +19789,16 @@
         <v>317</v>
       </c>
       <c r="E322" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="F322" t="s">
         <v>43</v>
       </c>
       <c r="J322" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L322" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M322" t="s">
         <v>36</v>
@@ -19791,16 +19830,16 @@
         <v>319</v>
       </c>
       <c r="E323" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F323" t="s">
         <v>43</v>
       </c>
       <c r="J323" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L323" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M323" t="s">
         <v>36</v>
@@ -19832,16 +19871,16 @@
         <v>321</v>
       </c>
       <c r="E324" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F324" t="s">
         <v>43</v>
       </c>
       <c r="J324" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L324" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M324" t="s">
         <v>36</v>
@@ -19867,22 +19906,22 @@
         <v>368</v>
       </c>
       <c r="C325" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D325" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E325" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="F325" t="s">
         <v>43</v>
       </c>
       <c r="J325" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="L325" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M325" t="s">
         <v>524</v>
@@ -19932,16 +19971,16 @@
         <v>325</v>
       </c>
       <c r="E326" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="F326" t="s">
         <v>43</v>
       </c>
       <c r="J326" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L326" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M326" t="s">
         <v>525</v>
@@ -19988,19 +20027,19 @@
         <v>329</v>
       </c>
       <c r="D327" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E327" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="F327" t="s">
         <v>43</v>
       </c>
       <c r="J327" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L327" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M327" t="s">
         <v>526</v>
@@ -20044,22 +20083,22 @@
         <v>368</v>
       </c>
       <c r="C328" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D328" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E328" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="F328" t="s">
         <v>43</v>
       </c>
       <c r="J328" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="L328" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M328" s="1" t="s">
         <v>527</v>
@@ -20103,7 +20142,7 @@
         <v>368</v>
       </c>
       <c r="C329" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D329" t="s">
         <v>337</v>
@@ -20115,10 +20154,10 @@
         <v>43</v>
       </c>
       <c r="J329" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L329" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M329" s="1" t="s">
         <v>527</v>
@@ -20162,7 +20201,7 @@
         <v>368</v>
       </c>
       <c r="C330" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D330" t="s">
         <v>338</v>
@@ -20174,10 +20213,10 @@
         <v>43</v>
       </c>
       <c r="J330" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L330" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M330" s="1" t="s">
         <v>527</v>
@@ -20221,19 +20260,19 @@
         <v>368</v>
       </c>
       <c r="C331" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D331" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E331" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="F331" t="s">
         <v>43</v>
       </c>
       <c r="J331" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="M331" t="s">
         <v>36</v>
@@ -20259,19 +20298,19 @@
         <v>368</v>
       </c>
       <c r="C332" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D332" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E332" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="F332" t="s">
         <v>43</v>
       </c>
       <c r="J332" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="M332" t="s">
         <v>36</v>
@@ -20297,19 +20336,19 @@
         <v>368</v>
       </c>
       <c r="C333" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D333" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E333" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="F333" t="s">
         <v>43</v>
       </c>
       <c r="J333" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="M333" t="s">
         <v>36</v>
@@ -20335,19 +20374,19 @@
         <v>368</v>
       </c>
       <c r="C334" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D334" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E334" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F334" t="s">
         <v>43</v>
       </c>
       <c r="J334" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L334" s="1"/>
       <c r="M334" t="s">
@@ -20374,19 +20413,19 @@
         <v>368</v>
       </c>
       <c r="C335" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D335" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E335" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="F335" t="s">
         <v>43</v>
       </c>
       <c r="J335" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="M335" t="s">
         <v>36</v>
@@ -20412,23 +20451,23 @@
         <v>368</v>
       </c>
       <c r="C336" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D336" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E336" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="F336" t="s">
         <v>43</v>
       </c>
       <c r="J336" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L336" s="1"/>
       <c r="M336" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="N336" t="s">
         <v>339</v>
@@ -20469,19 +20508,19 @@
         <v>368</v>
       </c>
       <c r="C337" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D337" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E337" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="F337" t="s">
         <v>43</v>
       </c>
       <c r="J337" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L337" s="1"/>
       <c r="M337" t="s">
